--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>8.202838012414803</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>8.178237199860005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>7.334687434564635</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>7.293330465807379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>6.549972307376173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>6.549972307376173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>5.409141129804662</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>5.403184189365562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>3.828255046016815</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>3.826013285086283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>3.81630650924889</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>3.57838349108357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>3.574710982272844</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>3.574151273251136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>3.557137003829069</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>3.551863608610062</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>3.54544614921517</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>3.544360146713721</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>3.542009500593646</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>3.509814549977741</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>3.507472069513184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>3.468276405330906</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>3.468022734235343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>3.42431207195103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>3.422734364086577</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>3.385528792910431</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>3.38342701674883</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>3.382141805636252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>3.378084757999056</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>3.366022521711698</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>3.359213809171568</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>3.358867410711652</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>3.350520881558605</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>3.350520881558605</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>3.349449539702243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>3.345037686427021</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>3.335850237962878</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>3.320845940684669</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>3.31891731446281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>3.310297187201527</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>3.307582527142028</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>3.300000000000058</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>3.300000000000036</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>3.300000000000014</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>3.299999999999992</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>3.29999999999997</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>3.299999999999947</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>3.299999999999947</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>3.299999999999947</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>3.299999999999925</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>3.299999999999925</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>3.299999999999925</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -4755,7 +4755,7 @@
         <v>546</v>
       </c>
       <c r="B548">
-        <v>-1</v>
+        <v>11.00547641878097</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -4763,7 +4763,7 @@
         <v>547</v>
       </c>
       <c r="B549">
-        <v>-1</v>
+        <v>16.42270719313683</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -4771,7 +4771,7 @@
         <v>548</v>
       </c>
       <c r="B550">
-        <v>-1</v>
+        <v>9.748882581518281</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -11547,7 +11547,7 @@
         <v>1395</v>
       </c>
       <c r="B1397">
-        <v>-1</v>
+        <v>3.314154436364558</v>
       </c>
     </row>
     <row r="1398" spans="1:2">
@@ -11555,7 +11555,7 @@
         <v>1396</v>
       </c>
       <c r="B1398">
-        <v>-1</v>
+        <v>3.614120549393207</v>
       </c>
     </row>
     <row r="1399" spans="1:2">
@@ -11563,7 +11563,7 @@
         <v>1397</v>
       </c>
       <c r="B1399">
-        <v>-1</v>
+        <v>3.469788641804383</v>
       </c>
     </row>
     <row r="1400" spans="1:2">
@@ -19923,7 +19923,7 @@
         <v>2442</v>
       </c>
       <c r="B2444">
-        <v>-1</v>
+        <v>4.482105239838175</v>
       </c>
     </row>
     <row r="2445" spans="1:2">
@@ -19931,7 +19931,7 @@
         <v>2443</v>
       </c>
       <c r="B2445">
-        <v>-1</v>
+        <v>4.71101094419809</v>
       </c>
     </row>
     <row r="2446" spans="1:2">
@@ -19939,7 +19939,7 @@
         <v>2444</v>
       </c>
       <c r="B2446">
-        <v>-1</v>
+        <v>3.761513044845577</v>
       </c>
     </row>
     <row r="2447" spans="1:2">
@@ -20763,7 +20763,7 @@
         <v>2547</v>
       </c>
       <c r="B2549">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2550" spans="1:2">
@@ -20771,7 +20771,7 @@
         <v>2548</v>
       </c>
       <c r="B2550">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2551" spans="1:2">
@@ -20779,7 +20779,7 @@
         <v>2549</v>
       </c>
       <c r="B2551">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2552" spans="1:2">
@@ -20883,7 +20883,7 @@
         <v>2562</v>
       </c>
       <c r="B2564">
-        <v>-1</v>
+        <v>13.51593400623589</v>
       </c>
     </row>
     <row r="2565" spans="1:2">
@@ -20891,7 +20891,7 @@
         <v>2563</v>
       </c>
       <c r="B2565">
-        <v>-1</v>
+        <v>19.77309802076347</v>
       </c>
     </row>
     <row r="2566" spans="1:2">
@@ -20899,7 +20899,7 @@
         <v>2564</v>
       </c>
       <c r="B2566">
-        <v>-1</v>
+        <v>11.46476604935449</v>
       </c>
     </row>
     <row r="2567" spans="1:2">
@@ -23187,7 +23187,7 @@
         <v>2850</v>
       </c>
       <c r="B2852">
-        <v>-1</v>
+        <v>13.55766052333834</v>
       </c>
     </row>
     <row r="2853" spans="1:2">
@@ -23195,7 +23195,7 @@
         <v>2851</v>
       </c>
       <c r="B2853">
-        <v>-1</v>
+        <v>20.95676196635776</v>
       </c>
     </row>
     <row r="2854" spans="1:2">
@@ -23203,7 +23203,7 @@
         <v>2852</v>
       </c>
       <c r="B2854">
-        <v>-1</v>
+        <v>11.69619897956937</v>
       </c>
     </row>
     <row r="2855" spans="1:2">
@@ -25371,7 +25371,7 @@
         <v>3123</v>
       </c>
       <c r="B3125">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3126" spans="1:2">
@@ -25379,7 +25379,7 @@
         <v>3124</v>
       </c>
       <c r="B3126">
-        <v>-1</v>
+        <v>101.0859662951187</v>
       </c>
     </row>
     <row r="3127" spans="1:2">
@@ -25387,7 +25387,7 @@
         <v>3125</v>
       </c>
       <c r="B3127">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3128" spans="1:2">
@@ -28827,7 +28827,7 @@
         <v>3555</v>
       </c>
       <c r="B3557">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3558" spans="1:2">
@@ -28835,7 +28835,7 @@
         <v>3556</v>
       </c>
       <c r="B3558">
-        <v>-1</v>
+        <v>3.351684412542233</v>
       </c>
     </row>
     <row r="3559" spans="1:2">
@@ -28843,7 +28843,7 @@
         <v>3557</v>
       </c>
       <c r="B3559">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3560" spans="1:2">
@@ -29115,7 +29115,7 @@
         <v>3591</v>
       </c>
       <c r="B3593">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3594" spans="1:2">
@@ -29123,7 +29123,7 @@
         <v>3592</v>
       </c>
       <c r="B3594">
-        <v>-1</v>
+        <v>3.337240587425461</v>
       </c>
     </row>
     <row r="3595" spans="1:2">
@@ -29131,7 +29131,7 @@
         <v>3593</v>
       </c>
       <c r="B3595">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="3596" spans="1:2">
@@ -29979,7 +29979,7 @@
         <v>3699</v>
       </c>
       <c r="B3701">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3702" spans="1:2">
@@ -29987,7 +29987,7 @@
         <v>3700</v>
       </c>
       <c r="B3702">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3703" spans="1:2">
@@ -29995,7 +29995,7 @@
         <v>3701</v>
       </c>
       <c r="B3703">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3704" spans="1:2">
@@ -30123,7 +30123,7 @@
         <v>3717</v>
       </c>
       <c r="B3719">
-        <v>-1</v>
+        <v>4.070439157498273</v>
       </c>
     </row>
     <row r="3720" spans="1:2">
@@ -30131,7 +30131,7 @@
         <v>3718</v>
       </c>
       <c r="B3720">
-        <v>-1</v>
+        <v>6.392348079690735</v>
       </c>
     </row>
     <row r="3721" spans="1:2">
@@ -30139,7 +30139,7 @@
         <v>3719</v>
       </c>
       <c r="B3721">
-        <v>-1</v>
+        <v>3.375154017732129</v>
       </c>
     </row>
     <row r="3722" spans="1:2">
@@ -31491,7 +31491,7 @@
         <v>3888</v>
       </c>
       <c r="B3890">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3891" spans="1:2">
@@ -31499,7 +31499,7 @@
         <v>3889</v>
       </c>
       <c r="B3891">
-        <v>-1</v>
+        <v>3.581842168261984</v>
       </c>
     </row>
     <row r="3892" spans="1:2">
@@ -31507,7 +31507,7 @@
         <v>3890</v>
       </c>
       <c r="B3892">
-        <v>-1</v>
+        <v>3.424039618286256</v>
       </c>
     </row>
     <row r="3893" spans="1:2">
@@ -32067,7 +32067,7 @@
         <v>3960</v>
       </c>
       <c r="B3962">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="3963" spans="1:2">
@@ -32075,7 +32075,7 @@
         <v>3961</v>
       </c>
       <c r="B3963">
-        <v>-1</v>
+        <v>3.509885644757516</v>
       </c>
     </row>
     <row r="3964" spans="1:2">
@@ -32083,7 +32083,7 @@
         <v>3962</v>
       </c>
       <c r="B3964">
-        <v>-1</v>
+        <v>3.376520684353035</v>
       </c>
     </row>
     <row r="3965" spans="1:2">
@@ -32547,7 +32547,7 @@
         <v>4020</v>
       </c>
       <c r="B4022">
-        <v>-1</v>
+        <v>13.81858972877037</v>
       </c>
     </row>
     <row r="4023" spans="1:2">
@@ -32555,7 +32555,7 @@
         <v>4021</v>
       </c>
       <c r="B4023">
-        <v>-1</v>
+        <v>24.71728668525623</v>
       </c>
     </row>
     <row r="4024" spans="1:2">
@@ -32563,7 +32563,7 @@
         <v>4022</v>
       </c>
       <c r="B4024">
-        <v>-1</v>
+        <v>12.50769593894612</v>
       </c>
     </row>
     <row r="4025" spans="1:2">
@@ -34443,7 +34443,7 @@
         <v>4257</v>
       </c>
       <c r="B4259">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4260" spans="1:2">
@@ -34451,7 +34451,7 @@
         <v>4258</v>
       </c>
       <c r="B4260">
-        <v>-1</v>
+        <v>105.6169723701042</v>
       </c>
     </row>
     <row r="4261" spans="1:2">
@@ -34459,7 +34459,7 @@
         <v>4259</v>
       </c>
       <c r="B4261">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4262" spans="1:2">
@@ -34587,7 +34587,7 @@
         <v>4275</v>
       </c>
       <c r="B4277">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4278" spans="1:2">
@@ -34595,7 +34595,7 @@
         <v>4276</v>
       </c>
       <c r="B4278">
-        <v>-1</v>
+        <v>105.6362230187248</v>
       </c>
     </row>
     <row r="4279" spans="1:2">
@@ -34603,7 +34603,7 @@
         <v>4277</v>
       </c>
       <c r="B4279">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4280" spans="1:2">
@@ -39195,7 +39195,7 @@
         <v>4851</v>
       </c>
       <c r="B4853">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4854" spans="1:2">
@@ -39203,7 +39203,7 @@
         <v>4852</v>
       </c>
       <c r="B4854">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4855" spans="1:2">
@@ -39211,7 +39211,7 @@
         <v>4853</v>
       </c>
       <c r="B4855">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4856" spans="1:2">
@@ -40011,7 +40011,7 @@
         <v>4953</v>
       </c>
       <c r="B4955">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4956" spans="1:2">
@@ -40019,7 +40019,7 @@
         <v>4954</v>
       </c>
       <c r="B4956">
-        <v>-1</v>
+        <v>3.937548403398616</v>
       </c>
     </row>
     <row r="4957" spans="1:2">
@@ -40027,7 +40027,7 @@
         <v>4955</v>
       </c>
       <c r="B4957">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4958" spans="1:2">
@@ -40347,7 +40347,7 @@
         <v>4995</v>
       </c>
       <c r="B4997">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4998" spans="1:2">
@@ -40355,7 +40355,7 @@
         <v>4996</v>
       </c>
       <c r="B4998">
-        <v>-1</v>
+        <v>3.412562805503505</v>
       </c>
     </row>
     <row r="4999" spans="1:2">
@@ -40363,7 +40363,7 @@
         <v>4997</v>
       </c>
       <c r="B4999">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5000" spans="1:2">
@@ -43755,7 +43755,7 @@
         <v>5421</v>
       </c>
       <c r="B5423">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5424" spans="1:2">
@@ -43763,7 +43763,7 @@
         <v>5422</v>
       </c>
       <c r="B5424">
-        <v>-1</v>
+        <v>8.546921830202002</v>
       </c>
     </row>
     <row r="5425" spans="1:2">
@@ -43771,7 +43771,7 @@
         <v>5423</v>
       </c>
       <c r="B5425">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5426" spans="1:2">
@@ -43779,7 +43779,7 @@
         <v>5424</v>
       </c>
       <c r="B5426">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5427" spans="1:2">
@@ -43787,7 +43787,7 @@
         <v>5425</v>
       </c>
       <c r="B5427">
-        <v>-1</v>
+        <v>34.49724064587354</v>
       </c>
     </row>
     <row r="5428" spans="1:2">
@@ -43795,7 +43795,7 @@
         <v>5426</v>
       </c>
       <c r="B5428">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5429" spans="1:2">
@@ -44475,7 +44475,7 @@
         <v>5511</v>
       </c>
       <c r="B5513">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5514" spans="1:2">
@@ -44483,7 +44483,7 @@
         <v>5512</v>
       </c>
       <c r="B5514">
-        <v>-1</v>
+        <v>4.581698453734317</v>
       </c>
     </row>
     <row r="5515" spans="1:2">
@@ -44491,7 +44491,7 @@
         <v>5513</v>
       </c>
       <c r="B5515">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5516" spans="1:2">
@@ -47259,7 +47259,7 @@
         <v>5859</v>
       </c>
       <c r="B5861">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5862" spans="1:2">
@@ -47267,7 +47267,7 @@
         <v>5860</v>
       </c>
       <c r="B5862">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5863" spans="1:2">
@@ -47275,7 +47275,7 @@
         <v>5861</v>
       </c>
       <c r="B5863">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5864" spans="1:2">
@@ -47283,7 +47283,7 @@
         <v>5862</v>
       </c>
       <c r="B5864">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5865" spans="1:2">
@@ -47291,7 +47291,7 @@
         <v>5863</v>
       </c>
       <c r="B5865">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5866" spans="1:2">
@@ -47299,7 +47299,7 @@
         <v>5864</v>
       </c>
       <c r="B5866">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5867" spans="1:2">
@@ -48003,7 +48003,7 @@
         <v>5952</v>
       </c>
       <c r="B5954">
-        <v>-1</v>
+        <v>3.66954480424686</v>
       </c>
     </row>
     <row r="5955" spans="1:2">
@@ -48011,7 +48011,7 @@
         <v>5953</v>
       </c>
       <c r="B5955">
-        <v>-1</v>
+        <v>6.925453291996031</v>
       </c>
     </row>
     <row r="5956" spans="1:2">
@@ -48019,7 +48019,7 @@
         <v>5954</v>
       </c>
       <c r="B5956">
-        <v>-1</v>
+        <v>3.66954480424686</v>
       </c>
     </row>
     <row r="5957" spans="1:2">
@@ -48339,7 +48339,7 @@
         <v>5994</v>
       </c>
       <c r="B5996">
-        <v>-1</v>
+        <v>3.463168099514879</v>
       </c>
     </row>
     <row r="5997" spans="1:2">
@@ -48347,7 +48347,7 @@
         <v>5995</v>
       </c>
       <c r="B5997">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5998" spans="1:2">
@@ -48355,7 +48355,7 @@
         <v>5996</v>
       </c>
       <c r="B5998">
-        <v>-1</v>
+        <v>3.314154436364558</v>
       </c>
     </row>
     <row r="5999" spans="1:2">
@@ -48411,7 +48411,7 @@
         <v>6003</v>
       </c>
       <c r="B6005">
-        <v>-1</v>
+        <v>3.314154436364558</v>
       </c>
     </row>
     <row r="6006" spans="1:2">
@@ -48419,7 +48419,7 @@
         <v>6004</v>
       </c>
       <c r="B6006">
-        <v>-1</v>
+        <v>3.314646619276496</v>
       </c>
     </row>
     <row r="6007" spans="1:2">
@@ -48427,7 +48427,7 @@
         <v>6005</v>
       </c>
       <c r="B6007">
-        <v>-1</v>
+        <v>3.314154436364558</v>
       </c>
     </row>
     <row r="6008" spans="1:2">
@@ -48915,7 +48915,7 @@
         <v>6066</v>
       </c>
       <c r="B6068">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6069" spans="1:2">
@@ -48923,7 +48923,7 @@
         <v>6067</v>
       </c>
       <c r="B6069">
-        <v>-1</v>
+        <v>3.593462867766495</v>
       </c>
     </row>
     <row r="6070" spans="1:2">
@@ -48931,7 +48931,7 @@
         <v>6068</v>
       </c>
       <c r="B6070">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6071" spans="1:2">
@@ -49563,7 +49563,7 @@
         <v>6147</v>
       </c>
       <c r="B6149">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6150" spans="1:2">
@@ -49571,7 +49571,7 @@
         <v>6148</v>
       </c>
       <c r="B6150">
-        <v>-1</v>
+        <v>3.458505877990081</v>
       </c>
     </row>
     <row r="6151" spans="1:2">
@@ -49579,7 +49579,7 @@
         <v>6149</v>
       </c>
       <c r="B6151">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6152" spans="1:2">
@@ -56019,7 +56019,7 @@
         <v>6954</v>
       </c>
       <c r="B6956">
-        <v>-1</v>
+        <v>9.097988548745839</v>
       </c>
     </row>
     <row r="6957" spans="1:2">
@@ -56027,7 +56027,7 @@
         <v>6955</v>
       </c>
       <c r="B6957">
-        <v>-1</v>
+        <v>10.87404536418171</v>
       </c>
     </row>
     <row r="6958" spans="1:2">
@@ -56035,7 +56035,7 @@
         <v>6956</v>
       </c>
       <c r="B6958">
-        <v>-1</v>
+        <v>9.151457215023907</v>
       </c>
     </row>
     <row r="6959" spans="1:2">
@@ -56499,7 +56499,7 @@
         <v>7014</v>
       </c>
       <c r="B7016">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7017" spans="1:2">
@@ -56507,7 +56507,7 @@
         <v>7015</v>
       </c>
       <c r="B7017">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7018" spans="1:2">
@@ -56515,7 +56515,7 @@
         <v>7016</v>
       </c>
       <c r="B7018">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7019" spans="1:2">
@@ -57627,7 +57627,7 @@
         <v>7155</v>
       </c>
       <c r="B7157">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7158" spans="1:2">
@@ -57635,7 +57635,7 @@
         <v>7156</v>
       </c>
       <c r="B7158">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7159" spans="1:2">
@@ -57643,7 +57643,7 @@
         <v>7157</v>
       </c>
       <c r="B7159">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7160" spans="1:2">
@@ -59283,7 +59283,7 @@
         <v>7362</v>
       </c>
       <c r="B7364">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="7365" spans="1:2">
@@ -59291,7 +59291,7 @@
         <v>7363</v>
       </c>
       <c r="B7365">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="7366" spans="1:2">
@@ -59299,7 +59299,7 @@
         <v>7364</v>
       </c>
       <c r="B7366">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7367" spans="1:2">
@@ -70131,7 +70131,7 @@
         <v>8718</v>
       </c>
       <c r="B8720">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8721" spans="1:2">
@@ -70139,7 +70139,7 @@
         <v>8719</v>
       </c>
       <c r="B8721">
-        <v>-1</v>
+        <v>8.424750326130781</v>
       </c>
     </row>
     <row r="8722" spans="1:2">
@@ -70147,7 +70147,7 @@
         <v>8720</v>
       </c>
       <c r="B8722">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8723" spans="1:2">
@@ -71019,7 +71019,7 @@
         <v>8829</v>
       </c>
       <c r="B8831">
-        <v>-1</v>
+        <v>3.433147864791808</v>
       </c>
     </row>
     <row r="8832" spans="1:2">
@@ -71027,7 +71027,7 @@
         <v>8830</v>
       </c>
       <c r="B8832">
-        <v>-1</v>
+        <v>108.8671674348155</v>
       </c>
     </row>
     <row r="8833" spans="1:2">
@@ -71035,7 +71035,7 @@
         <v>8831</v>
       </c>
       <c r="B8833">
-        <v>-1</v>
+        <v>3.433147864791808</v>
       </c>
     </row>
     <row r="8834" spans="1:2">
@@ -71163,7 +71163,7 @@
         <v>8847</v>
       </c>
       <c r="B8849">
-        <v>-1</v>
+        <v>3.434661602376454</v>
       </c>
     </row>
     <row r="8850" spans="1:2">
@@ -71171,7 +71171,7 @@
         <v>8848</v>
       </c>
       <c r="B8850">
-        <v>-1</v>
+        <v>108.8823572545256</v>
       </c>
     </row>
     <row r="8851" spans="1:2">
@@ -71179,7 +71179,7 @@
         <v>8849</v>
       </c>
       <c r="B8851">
-        <v>-1</v>
+        <v>3.434661602376454</v>
       </c>
     </row>
     <row r="8852" spans="1:2">
@@ -71307,7 +71307,7 @@
         <v>8865</v>
       </c>
       <c r="B8867">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8868" spans="1:2">
@@ -71315,7 +71315,7 @@
         <v>8866</v>
       </c>
       <c r="B8868">
-        <v>-1</v>
+        <v>116.9933386190708</v>
       </c>
     </row>
     <row r="8869" spans="1:2">
@@ -71323,7 +71323,7 @@
         <v>8867</v>
       </c>
       <c r="B8869">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8870" spans="1:2">
@@ -71451,7 +71451,7 @@
         <v>8883</v>
       </c>
       <c r="B8885">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8886" spans="1:2">
@@ -71459,7 +71459,7 @@
         <v>8884</v>
       </c>
       <c r="B8886">
-        <v>-1</v>
+        <v>117.0217045190241</v>
       </c>
     </row>
     <row r="8887" spans="1:2">
@@ -71467,7 +71467,7 @@
         <v>8885</v>
       </c>
       <c r="B8887">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8888" spans="1:2">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -1443,7 +1443,7 @@
         <v>132</v>
       </c>
       <c r="B134">
-        <v>-1</v>
+        <v>8.86212771391326</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -1451,7 +1451,7 @@
         <v>133</v>
       </c>
       <c r="B135">
-        <v>-1</v>
+        <v>9.777586651088953</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1459,7 +1459,7 @@
         <v>134</v>
       </c>
       <c r="B136">
-        <v>-1</v>
+        <v>7.82616223722552</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2523,7 +2523,7 @@
         <v>267</v>
       </c>
       <c r="B269">
-        <v>-1</v>
+        <v>10.79415387497151</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -2531,7 +2531,7 @@
         <v>268</v>
       </c>
       <c r="B270">
-        <v>-1</v>
+        <v>20.72053787421033</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -2539,7 +2539,7 @@
         <v>269</v>
       </c>
       <c r="B271">
-        <v>-1</v>
+        <v>9.645844289694915</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -2547,7 +2547,7 @@
         <v>270</v>
       </c>
       <c r="B272">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -2555,7 +2555,7 @@
         <v>271</v>
       </c>
       <c r="B273">
-        <v>-1</v>
+        <v>4.270770784629752</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -2563,7 +2563,7 @@
         <v>272</v>
       </c>
       <c r="B274">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -2643,7 +2643,7 @@
         <v>282</v>
       </c>
       <c r="B284">
-        <v>-1</v>
+        <v>4.198671494649487</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -2651,7 +2651,7 @@
         <v>283</v>
       </c>
       <c r="B285">
-        <v>-1</v>
+        <v>7.288108950933736</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -2659,7 +2659,7 @@
         <v>284</v>
       </c>
       <c r="B286">
-        <v>-1</v>
+        <v>3.7442740263541</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3219,7 +3219,7 @@
         <v>354</v>
       </c>
       <c r="B356">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -3227,7 +3227,7 @@
         <v>355</v>
       </c>
       <c r="B357">
-        <v>-1</v>
+        <v>3.930143820132914</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -3235,7 +3235,7 @@
         <v>356</v>
       </c>
       <c r="B358">
-        <v>-1</v>
+        <v>3.336222411265832</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -3243,7 +3243,7 @@
         <v>357</v>
       </c>
       <c r="B359">
-        <v>-1</v>
+        <v>7.94212529552728</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -3251,7 +3251,7 @@
         <v>358</v>
       </c>
       <c r="B360">
-        <v>-1</v>
+        <v>9.135672982009059</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -3259,7 +3259,7 @@
         <v>359</v>
       </c>
       <c r="B361">
-        <v>-1</v>
+        <v>7.160717695127294</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -3771,7 +3771,7 @@
         <v>423</v>
       </c>
       <c r="B425">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -3779,7 +3779,7 @@
         <v>424</v>
       </c>
       <c r="B426">
-        <v>-1</v>
+        <v>3.761335773362573</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -3787,7 +3787,7 @@
         <v>425</v>
       </c>
       <c r="B427">
-        <v>-1</v>
+        <v>3.492018208276537</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -3795,7 +3795,7 @@
         <v>426</v>
       </c>
       <c r="B428">
-        <v>-1</v>
+        <v>3.555883656856829</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -3803,7 +3803,7 @@
         <v>427</v>
       </c>
       <c r="B429">
-        <v>-1</v>
+        <v>4.229492414958392</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -3811,7 +3811,7 @@
         <v>428</v>
       </c>
       <c r="B430">
-        <v>-1</v>
+        <v>3.301364510995208</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -3819,7 +3819,7 @@
         <v>429</v>
       </c>
       <c r="B431">
-        <v>-1</v>
+        <v>9.133817596963933</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -3827,7 +3827,7 @@
         <v>430</v>
       </c>
       <c r="B432">
-        <v>-1</v>
+        <v>10.22332367707279</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -3835,7 +3835,7 @@
         <v>431</v>
       </c>
       <c r="B433">
-        <v>-1</v>
+        <v>8.071244113993359</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -4083,7 +4083,7 @@
         <v>462</v>
       </c>
       <c r="B464">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -4091,7 +4091,7 @@
         <v>463</v>
       </c>
       <c r="B465">
-        <v>-1</v>
+        <v>3.350550223141813</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -4099,7 +4099,7 @@
         <v>464</v>
       </c>
       <c r="B466">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -4275,7 +4275,7 @@
         <v>486</v>
       </c>
       <c r="B488">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -4283,7 +4283,7 @@
         <v>487</v>
       </c>
       <c r="B489">
-        <v>-1</v>
+        <v>4.250725840747349</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -4291,7 +4291,7 @@
         <v>488</v>
       </c>
       <c r="B490">
-        <v>-1</v>
+        <v>3.363045768029882</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -4371,7 +4371,7 @@
         <v>498</v>
       </c>
       <c r="B500">
-        <v>-1</v>
+        <v>3.778365912883286</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -4379,7 +4379,7 @@
         <v>499</v>
       </c>
       <c r="B501">
-        <v>-1</v>
+        <v>6.517880014462774</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -4387,7 +4387,7 @@
         <v>500</v>
       </c>
       <c r="B502">
-        <v>-1</v>
+        <v>3.473335840763969</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -4851,7 +4851,7 @@
         <v>558</v>
       </c>
       <c r="B560">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -4859,7 +4859,7 @@
         <v>559</v>
       </c>
       <c r="B561">
-        <v>-1</v>
+        <v>4.585789574355504</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -4867,7 +4867,7 @@
         <v>560</v>
       </c>
       <c r="B562">
-        <v>-1</v>
+        <v>3.326315049077166</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -5811,7 +5811,7 @@
         <v>678</v>
       </c>
       <c r="B680">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -5819,7 +5819,7 @@
         <v>679</v>
       </c>
       <c r="B681">
-        <v>-1</v>
+        <v>4.645989098596736</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -5827,7 +5827,7 @@
         <v>680</v>
       </c>
       <c r="B682">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -5835,7 +5835,7 @@
         <v>681</v>
       </c>
       <c r="B683">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -5843,7 +5843,7 @@
         <v>682</v>
       </c>
       <c r="B684">
-        <v>-1</v>
+        <v>11.46793490404536</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -5851,7 +5851,7 @@
         <v>683</v>
       </c>
       <c r="B685">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -6075,7 +6075,7 @@
         <v>711</v>
       </c>
       <c r="B713">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -6083,7 +6083,7 @@
         <v>712</v>
       </c>
       <c r="B714">
-        <v>-1</v>
+        <v>4.305590183067065</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -6091,7 +6091,7 @@
         <v>713</v>
       </c>
       <c r="B715">
-        <v>-1</v>
+        <v>3.313312588990369</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -6387,7 +6387,7 @@
         <v>750</v>
       </c>
       <c r="B752">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -6395,7 +6395,7 @@
         <v>751</v>
       </c>
       <c r="B753">
-        <v>-1</v>
+        <v>107.2922031388455</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -6403,7 +6403,7 @@
         <v>752</v>
       </c>
       <c r="B754">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -6651,7 +6651,7 @@
         <v>783</v>
       </c>
       <c r="B785">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -6659,7 +6659,7 @@
         <v>784</v>
       </c>
       <c r="B786">
-        <v>-1</v>
+        <v>92.4774949720189</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -6667,7 +6667,7 @@
         <v>785</v>
       </c>
       <c r="B787">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="788" spans="1:2">
@@ -6675,7 +6675,7 @@
         <v>786</v>
       </c>
       <c r="B788">
-        <v>-1</v>
+        <v>3.804706132461344</v>
       </c>
     </row>
     <row r="789" spans="1:2">
@@ -6683,7 +6683,7 @@
         <v>787</v>
       </c>
       <c r="B789">
-        <v>-1</v>
+        <v>126.4342622605372</v>
       </c>
     </row>
     <row r="790" spans="1:2">
@@ -6691,7 +6691,7 @@
         <v>788</v>
       </c>
       <c r="B790">
-        <v>-1</v>
+        <v>3.473843231508211</v>
       </c>
     </row>
     <row r="791" spans="1:2">
@@ -6891,7 +6891,7 @@
         <v>813</v>
       </c>
       <c r="B815">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="816" spans="1:2">
@@ -6899,7 +6899,7 @@
         <v>814</v>
       </c>
       <c r="B816">
-        <v>-1</v>
+        <v>7.166321731425529</v>
       </c>
     </row>
     <row r="817" spans="1:2">
@@ -6907,7 +6907,7 @@
         <v>815</v>
       </c>
       <c r="B817">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="818" spans="1:2">
@@ -6987,7 +6987,7 @@
         <v>825</v>
       </c>
       <c r="B827">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="828" spans="1:2">
@@ -6995,7 +6995,7 @@
         <v>826</v>
       </c>
       <c r="B828">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -7003,7 +7003,7 @@
         <v>827</v>
       </c>
       <c r="B829">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="830" spans="1:2">
@@ -7107,7 +7107,7 @@
         <v>840</v>
       </c>
       <c r="B842">
-        <v>-1</v>
+        <v>4.252779359590542</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -7115,7 +7115,7 @@
         <v>841</v>
       </c>
       <c r="B843">
-        <v>-1</v>
+        <v>151.7510254665272</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -7123,7 +7123,7 @@
         <v>842</v>
       </c>
       <c r="B844">
-        <v>-1</v>
+        <v>3.7966585031043</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -7227,7 +7227,7 @@
         <v>855</v>
       </c>
       <c r="B857">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="858" spans="1:2">
@@ -7235,7 +7235,7 @@
         <v>856</v>
       </c>
       <c r="B858">
-        <v>-1</v>
+        <v>106.7735007074881</v>
       </c>
     </row>
     <row r="859" spans="1:2">
@@ -7243,7 +7243,7 @@
         <v>857</v>
       </c>
       <c r="B859">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="860" spans="1:2">
@@ -7683,7 +7683,7 @@
         <v>912</v>
       </c>
       <c r="B914">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="915" spans="1:2">
@@ -7691,7 +7691,7 @@
         <v>913</v>
       </c>
       <c r="B915">
-        <v>-1</v>
+        <v>5.452892442228197</v>
       </c>
     </row>
     <row r="916" spans="1:2">
@@ -7699,7 +7699,7 @@
         <v>914</v>
       </c>
       <c r="B916">
-        <v>-1</v>
+        <v>3.386895574781934</v>
       </c>
     </row>
     <row r="917" spans="1:2">
@@ -7731,7 +7731,7 @@
         <v>918</v>
       </c>
       <c r="B920">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="921" spans="1:2">
@@ -7739,7 +7739,7 @@
         <v>919</v>
       </c>
       <c r="B921">
-        <v>-1</v>
+        <v>4.372116160781703</v>
       </c>
     </row>
     <row r="922" spans="1:2">
@@ -7747,7 +7747,7 @@
         <v>920</v>
       </c>
       <c r="B922">
-        <v>-1</v>
+        <v>3.528223562096411</v>
       </c>
     </row>
     <row r="923" spans="1:2">
@@ -7803,7 +7803,7 @@
         <v>927</v>
       </c>
       <c r="B929">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="930" spans="1:2">
@@ -7811,7 +7811,7 @@
         <v>928</v>
       </c>
       <c r="B930">
-        <v>-1</v>
+        <v>4.656005567195898</v>
       </c>
     </row>
     <row r="931" spans="1:2">
@@ -7819,7 +7819,7 @@
         <v>929</v>
       </c>
       <c r="B931">
-        <v>-1</v>
+        <v>3.528223562096411</v>
       </c>
     </row>
     <row r="932" spans="1:2">
@@ -7995,7 +7995,7 @@
         <v>951</v>
       </c>
       <c r="B953">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="954" spans="1:2">
@@ -8003,7 +8003,7 @@
         <v>952</v>
       </c>
       <c r="B954">
-        <v>-1</v>
+        <v>10.73695781378116</v>
       </c>
     </row>
     <row r="955" spans="1:2">
@@ -8011,7 +8011,7 @@
         <v>953</v>
       </c>
       <c r="B955">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="956" spans="1:2">
@@ -8115,7 +8115,7 @@
         <v>966</v>
       </c>
       <c r="B968">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="969" spans="1:2">
@@ -8123,7 +8123,7 @@
         <v>967</v>
       </c>
       <c r="B969">
-        <v>-1</v>
+        <v>5.553113055767989</v>
       </c>
     </row>
     <row r="970" spans="1:2">
@@ -8131,7 +8131,7 @@
         <v>968</v>
       </c>
       <c r="B970">
-        <v>-1</v>
+        <v>3.324613978511004</v>
       </c>
     </row>
     <row r="971" spans="1:2">
@@ -8379,7 +8379,7 @@
         <v>999</v>
       </c>
       <c r="B1001">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
@@ -8387,7 +8387,7 @@
         <v>1000</v>
       </c>
       <c r="B1002">
-        <v>-1</v>
+        <v>5.20600694990927</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
@@ -8395,7 +8395,7 @@
         <v>1001</v>
       </c>
       <c r="B1003">
-        <v>-1</v>
+        <v>3.500065699725385</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
@@ -8595,7 +8595,7 @@
         <v>1026</v>
       </c>
       <c r="B1028">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
@@ -8603,7 +8603,7 @@
         <v>1027</v>
       </c>
       <c r="B1029">
-        <v>-1</v>
+        <v>4.384518845267305</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
@@ -8611,7 +8611,7 @@
         <v>1028</v>
       </c>
       <c r="B1030">
-        <v>-1</v>
+        <v>3.387269539219662</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
@@ -8643,7 +8643,7 @@
         <v>1032</v>
       </c>
       <c r="B1034">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
@@ -8651,7 +8651,7 @@
         <v>1033</v>
       </c>
       <c r="B1035">
-        <v>-1</v>
+        <v>28.16702454768144</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
@@ -8659,7 +8659,7 @@
         <v>1034</v>
       </c>
       <c r="B1036">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
@@ -8811,7 +8811,7 @@
         <v>1053</v>
       </c>
       <c r="B1055">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
@@ -8819,7 +8819,7 @@
         <v>1054</v>
       </c>
       <c r="B1056">
-        <v>-1</v>
+        <v>93.34769441851688</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
@@ -8827,7 +8827,7 @@
         <v>1055</v>
       </c>
       <c r="B1057">
-        <v>-1</v>
+        <v>3.369920423183204</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
@@ -8955,7 +8955,7 @@
         <v>1071</v>
       </c>
       <c r="B1073">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
@@ -8963,7 +8963,7 @@
         <v>1072</v>
       </c>
       <c r="B1074">
-        <v>-1</v>
+        <v>93.3649659813796</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
@@ -8971,7 +8971,7 @@
         <v>1073</v>
       </c>
       <c r="B1075">
-        <v>-1</v>
+        <v>3.369463273245299</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
@@ -9483,7 +9483,7 @@
         <v>1137</v>
       </c>
       <c r="B1139">
-        <v>-1</v>
+        <v>4.339491720663135</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
@@ -9491,7 +9491,7 @@
         <v>1138</v>
       </c>
       <c r="B1140">
-        <v>-1</v>
+        <v>16.4877008948492</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
@@ -9499,7 +9499,7 @@
         <v>1139</v>
       </c>
       <c r="B1141">
-        <v>-1</v>
+        <v>3.851180476177241</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
@@ -10419,7 +10419,7 @@
         <v>1254</v>
       </c>
       <c r="B1256">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1257" spans="1:2">
@@ -10427,7 +10427,7 @@
         <v>1255</v>
       </c>
       <c r="B1257">
-        <v>-1</v>
+        <v>3.376818666558545</v>
       </c>
     </row>
     <row r="1258" spans="1:2">
@@ -10435,7 +10435,7 @@
         <v>1256</v>
       </c>
       <c r="B1258">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1259" spans="1:2">
@@ -10611,7 +10611,7 @@
         <v>1278</v>
       </c>
       <c r="B1280">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1281" spans="1:2">
@@ -10619,7 +10619,7 @@
         <v>1279</v>
       </c>
       <c r="B1281">
-        <v>-1</v>
+        <v>3.623343380460731</v>
       </c>
     </row>
     <row r="1282" spans="1:2">
@@ -10627,7 +10627,7 @@
         <v>1280</v>
       </c>
       <c r="B1282">
-        <v>-1</v>
+        <v>3.408770262171412</v>
       </c>
     </row>
     <row r="1283" spans="1:2">
@@ -10659,7 +10659,7 @@
         <v>1284</v>
       </c>
       <c r="B1286">
-        <v>-1</v>
+        <v>8.297603870355708</v>
       </c>
     </row>
     <row r="1287" spans="1:2">
@@ -10667,7 +10667,7 @@
         <v>1285</v>
       </c>
       <c r="B1287">
-        <v>-1</v>
+        <v>9.419023232510625</v>
       </c>
     </row>
     <row r="1288" spans="1:2">
@@ -10675,7 +10675,7 @@
         <v>1286</v>
       </c>
       <c r="B1288">
-        <v>-1</v>
+        <v>7.237654458056076</v>
       </c>
     </row>
     <row r="1289" spans="1:2">
@@ -11019,7 +11019,7 @@
         <v>1329</v>
       </c>
       <c r="B1331">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1332" spans="1:2">
@@ -11027,7 +11027,7 @@
         <v>1330</v>
       </c>
       <c r="B1332">
-        <v>-1</v>
+        <v>5.660103533165017</v>
       </c>
     </row>
     <row r="1333" spans="1:2">
@@ -11035,7 +11035,7 @@
         <v>1331</v>
       </c>
       <c r="B1333">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1334" spans="1:2">
@@ -11163,7 +11163,7 @@
         <v>1347</v>
       </c>
       <c r="B1349">
-        <v>-1</v>
+        <v>9.266619382900387</v>
       </c>
     </row>
     <row r="1350" spans="1:2">
@@ -11171,7 +11171,7 @@
         <v>1348</v>
       </c>
       <c r="B1350">
-        <v>-1</v>
+        <v>17.10147417544097</v>
       </c>
     </row>
     <row r="1351" spans="1:2">
@@ -11179,7 +11179,7 @@
         <v>1349</v>
       </c>
       <c r="B1351">
-        <v>-1</v>
+        <v>8.365563056264813</v>
       </c>
     </row>
     <row r="1352" spans="1:2">
@@ -11187,7 +11187,7 @@
         <v>1350</v>
       </c>
       <c r="B1352">
-        <v>-1</v>
+        <v>3.496832619967361</v>
       </c>
     </row>
     <row r="1353" spans="1:2">
@@ -11195,7 +11195,7 @@
         <v>1351</v>
       </c>
       <c r="B1353">
-        <v>-1</v>
+        <v>3.948766948941262</v>
       </c>
     </row>
     <row r="1354" spans="1:2">
@@ -11203,7 +11203,7 @@
         <v>1352</v>
       </c>
       <c r="B1354">
-        <v>-1</v>
+        <v>3.514679351257821</v>
       </c>
     </row>
     <row r="1355" spans="1:2">
@@ -11235,7 +11235,7 @@
         <v>1356</v>
       </c>
       <c r="B1358">
-        <v>-1</v>
+        <v>9.379956687282665</v>
       </c>
     </row>
     <row r="1359" spans="1:2">
@@ -11243,7 +11243,7 @@
         <v>1357</v>
       </c>
       <c r="B1359">
-        <v>-1</v>
+        <v>13.58844008610722</v>
       </c>
     </row>
     <row r="1360" spans="1:2">
@@ -11251,7 +11251,7 @@
         <v>1358</v>
       </c>
       <c r="B1360">
-        <v>-1</v>
+        <v>8.370065681542748</v>
       </c>
     </row>
     <row r="1361" spans="1:2">
@@ -11643,7 +11643,7 @@
         <v>1407</v>
       </c>
       <c r="B1409">
-        <v>-1</v>
+        <v>4.19646712822016</v>
       </c>
     </row>
     <row r="1410" spans="1:2">
@@ -11651,7 +11651,7 @@
         <v>1408</v>
       </c>
       <c r="B1410">
-        <v>-1</v>
+        <v>6.20617021710459</v>
       </c>
     </row>
     <row r="1411" spans="1:2">
@@ -11659,7 +11659,7 @@
         <v>1409</v>
       </c>
       <c r="B1411">
-        <v>-1</v>
+        <v>3.686577460843043</v>
       </c>
     </row>
     <row r="1412" spans="1:2">
@@ -12123,7 +12123,7 @@
         <v>1467</v>
       </c>
       <c r="B1469">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1470" spans="1:2">
@@ -12131,7 +12131,7 @@
         <v>1468</v>
       </c>
       <c r="B1470">
-        <v>-1</v>
+        <v>3.867167148442507</v>
       </c>
     </row>
     <row r="1471" spans="1:2">
@@ -12139,7 +12139,7 @@
         <v>1469</v>
       </c>
       <c r="B1471">
-        <v>-1</v>
+        <v>3.619219325498135</v>
       </c>
     </row>
     <row r="1472" spans="1:2">
@@ -12315,7 +12315,7 @@
         <v>1491</v>
       </c>
       <c r="B1493">
-        <v>-1</v>
+        <v>6.930377656953435</v>
       </c>
     </row>
     <row r="1494" spans="1:2">
@@ -12323,7 +12323,7 @@
         <v>1492</v>
       </c>
       <c r="B1494">
-        <v>-1</v>
+        <v>8.296729053279551</v>
       </c>
     </row>
     <row r="1495" spans="1:2">
@@ -12331,7 +12331,7 @@
         <v>1493</v>
       </c>
       <c r="B1495">
-        <v>-1</v>
+        <v>6.14929915898853</v>
       </c>
     </row>
     <row r="1496" spans="1:2">
@@ -12387,7 +12387,7 @@
         <v>1500</v>
       </c>
       <c r="B1502">
-        <v>-1</v>
+        <v>7.196177325585329</v>
       </c>
     </row>
     <row r="1503" spans="1:2">
@@ -12395,7 +12395,7 @@
         <v>1501</v>
       </c>
       <c r="B1503">
-        <v>-1</v>
+        <v>9.067382258807179</v>
       </c>
     </row>
     <row r="1504" spans="1:2">
@@ -12403,7 +12403,7 @@
         <v>1502</v>
       </c>
       <c r="B1504">
-        <v>-1</v>
+        <v>6.567358528240685</v>
       </c>
     </row>
     <row r="1505" spans="1:2">
@@ -12603,7 +12603,7 @@
         <v>1527</v>
       </c>
       <c r="B1529">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1530" spans="1:2">
@@ -12611,7 +12611,7 @@
         <v>1528</v>
       </c>
       <c r="B1530">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1531" spans="1:2">
@@ -12619,7 +12619,7 @@
         <v>1529</v>
       </c>
       <c r="B1531">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1532" spans="1:2">
@@ -12747,7 +12747,7 @@
         <v>1545</v>
       </c>
       <c r="B1547">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1548" spans="1:2">
@@ -12755,7 +12755,7 @@
         <v>1546</v>
       </c>
       <c r="B1548">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1549" spans="1:2">
@@ -12763,7 +12763,7 @@
         <v>1547</v>
       </c>
       <c r="B1549">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1550" spans="1:2">
@@ -13275,7 +13275,7 @@
         <v>1611</v>
       </c>
       <c r="B1613">
-        <v>-1</v>
+        <v>3.468972402105419</v>
       </c>
     </row>
     <row r="1614" spans="1:2">
@@ -13283,7 +13283,7 @@
         <v>1612</v>
       </c>
       <c r="B1614">
-        <v>-1</v>
+        <v>3.732532894347074</v>
       </c>
     </row>
     <row r="1615" spans="1:2">
@@ -13291,7 +13291,7 @@
         <v>1613</v>
       </c>
       <c r="B1615">
-        <v>-1</v>
+        <v>3.592052332525131</v>
       </c>
     </row>
     <row r="1616" spans="1:2">
@@ -13323,7 +13323,7 @@
         <v>1617</v>
       </c>
       <c r="B1619">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1620" spans="1:2">
@@ -13331,7 +13331,7 @@
         <v>1618</v>
       </c>
       <c r="B1620">
-        <v>-1</v>
+        <v>6.66030762284644</v>
       </c>
     </row>
     <row r="1621" spans="1:2">
@@ -13339,7 +13339,7 @@
         <v>1619</v>
       </c>
       <c r="B1621">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1622" spans="1:2">
@@ -13755,7 +13755,7 @@
         <v>1671</v>
       </c>
       <c r="B1673">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1674" spans="1:2">
@@ -13763,7 +13763,7 @@
         <v>1672</v>
       </c>
       <c r="B1674">
-        <v>-1</v>
+        <v>9.091515796985405</v>
       </c>
     </row>
     <row r="1675" spans="1:2">
@@ -13771,7 +13771,7 @@
         <v>1673</v>
       </c>
       <c r="B1675">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1676" spans="1:2">
@@ -13947,7 +13947,7 @@
         <v>1695</v>
       </c>
       <c r="B1697">
-        <v>-1</v>
+        <v>4.28015227918046</v>
       </c>
     </row>
     <row r="1698" spans="1:2">
@@ -13955,7 +13955,7 @@
         <v>1696</v>
       </c>
       <c r="B1698">
-        <v>-1</v>
+        <v>6.965695882492973</v>
       </c>
     </row>
     <row r="1699" spans="1:2">
@@ -13963,7 +13963,7 @@
         <v>1697</v>
       </c>
       <c r="B1699">
-        <v>-1</v>
+        <v>4.061644933817165</v>
       </c>
     </row>
     <row r="1700" spans="1:2">
@@ -14451,7 +14451,7 @@
         <v>1758</v>
       </c>
       <c r="B1760">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1761" spans="1:2">
@@ -14459,7 +14459,7 @@
         <v>1759</v>
       </c>
       <c r="B1761">
-        <v>-1</v>
+        <v>4.770353519866665</v>
       </c>
     </row>
     <row r="1762" spans="1:2">
@@ -14467,7 +14467,7 @@
         <v>1760</v>
       </c>
       <c r="B1762">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1763" spans="1:2">
@@ -15243,7 +15243,7 @@
         <v>1857</v>
       </c>
       <c r="B1859">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1860" spans="1:2">
@@ -15251,7 +15251,7 @@
         <v>1858</v>
       </c>
       <c r="B1860">
-        <v>-1</v>
+        <v>4.4781974566113</v>
       </c>
     </row>
     <row r="1861" spans="1:2">
@@ -15259,7 +15259,7 @@
         <v>1859</v>
       </c>
       <c r="B1861">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1862" spans="1:2">
@@ -16083,7 +16083,7 @@
         <v>1962</v>
       </c>
       <c r="B1964">
-        <v>-1</v>
+        <v>3.446329950355054</v>
       </c>
     </row>
     <row r="1965" spans="1:2">
@@ -16091,7 +16091,7 @@
         <v>1963</v>
       </c>
       <c r="B1965">
-        <v>-1</v>
+        <v>4.235841807143748</v>
       </c>
     </row>
     <row r="1966" spans="1:2">
@@ -16099,7 +16099,7 @@
         <v>1964</v>
       </c>
       <c r="B1966">
-        <v>-1</v>
+        <v>3.47682822266171</v>
       </c>
     </row>
     <row r="1967" spans="1:2">
@@ -16251,7 +16251,7 @@
         <v>1983</v>
       </c>
       <c r="B1985">
-        <v>-1</v>
+        <v>4.252584816960791</v>
       </c>
     </row>
     <row r="1986" spans="1:2">
@@ -16259,7 +16259,7 @@
         <v>1984</v>
       </c>
       <c r="B1986">
-        <v>-1</v>
+        <v>15.32865131068554</v>
       </c>
     </row>
     <row r="1987" spans="1:2">
@@ -16267,7 +16267,7 @@
         <v>1985</v>
       </c>
       <c r="B1987">
-        <v>-1</v>
+        <v>3.746660600981311</v>
       </c>
     </row>
     <row r="1988" spans="1:2">
@@ -16323,7 +16323,7 @@
         <v>1992</v>
       </c>
       <c r="B1994">
-        <v>-1</v>
+        <v>4.245371273510823</v>
       </c>
     </row>
     <row r="1995" spans="1:2">
@@ -16331,7 +16331,7 @@
         <v>1993</v>
       </c>
       <c r="B1995">
-        <v>-1</v>
+        <v>158.0708857768974</v>
       </c>
     </row>
     <row r="1996" spans="1:2">
@@ -16339,7 +16339,7 @@
         <v>1994</v>
       </c>
       <c r="B1996">
-        <v>-1</v>
+        <v>3.746660600981311</v>
       </c>
     </row>
     <row r="1997" spans="1:2">
@@ -16779,7 +16779,7 @@
         <v>2049</v>
       </c>
       <c r="B2051">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2052" spans="1:2">
@@ -16787,7 +16787,7 @@
         <v>2050</v>
       </c>
       <c r="B2052">
-        <v>-1</v>
+        <v>18.8172094473689</v>
       </c>
     </row>
     <row r="2053" spans="1:2">
@@ -16795,7 +16795,7 @@
         <v>2051</v>
       </c>
       <c r="B2053">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2054" spans="1:2">
@@ -17091,7 +17091,7 @@
         <v>2088</v>
       </c>
       <c r="B2090">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2091" spans="1:2">
@@ -17099,7 +17099,7 @@
         <v>2089</v>
       </c>
       <c r="B2091">
-        <v>-1</v>
+        <v>4.213658139957932</v>
       </c>
     </row>
     <row r="2092" spans="1:2">
@@ -17107,7 +17107,7 @@
         <v>2090</v>
       </c>
       <c r="B2092">
-        <v>-1</v>
+        <v>3.634020463509535</v>
       </c>
     </row>
     <row r="2093" spans="1:2">
@@ -17163,7 +17163,7 @@
         <v>2097</v>
       </c>
       <c r="B2099">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2100" spans="1:2">
@@ -17171,7 +17171,7 @@
         <v>2098</v>
       </c>
       <c r="B2100">
-        <v>-1</v>
+        <v>4.207527179936821</v>
       </c>
     </row>
     <row r="2101" spans="1:2">
@@ -17179,7 +17179,7 @@
         <v>2099</v>
       </c>
       <c r="B2101">
-        <v>-1</v>
+        <v>3.634020463509535</v>
       </c>
     </row>
     <row r="2102" spans="1:2">
@@ -17379,7 +17379,7 @@
         <v>2124</v>
       </c>
       <c r="B2126">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2127" spans="1:2">
@@ -17387,7 +17387,7 @@
         <v>2125</v>
       </c>
       <c r="B2127">
-        <v>-1</v>
+        <v>4.204400746653891</v>
       </c>
     </row>
     <row r="2128" spans="1:2">
@@ -17395,7 +17395,7 @@
         <v>2126</v>
       </c>
       <c r="B2128">
-        <v>-1</v>
+        <v>3.622318917094991</v>
       </c>
     </row>
     <row r="2129" spans="1:2">
@@ -17739,7 +17739,7 @@
         <v>2169</v>
       </c>
       <c r="B2171">
-        <v>-1</v>
+        <v>3.481696658002065</v>
       </c>
     </row>
     <row r="2172" spans="1:2">
@@ -17747,7 +17747,7 @@
         <v>2170</v>
       </c>
       <c r="B2172">
-        <v>-1</v>
+        <v>81.51708947770936</v>
       </c>
     </row>
     <row r="2173" spans="1:2">
@@ -17755,7 +17755,7 @@
         <v>2171</v>
       </c>
       <c r="B2173">
-        <v>-1</v>
+        <v>3.611382875049696</v>
       </c>
     </row>
     <row r="2174" spans="1:2">
@@ -18027,7 +18027,7 @@
         <v>2205</v>
       </c>
       <c r="B2207">
-        <v>-1</v>
+        <v>3.478021811090959</v>
       </c>
     </row>
     <row r="2208" spans="1:2">
@@ -18035,7 +18035,7 @@
         <v>2206</v>
       </c>
       <c r="B2208">
-        <v>-1</v>
+        <v>96.40245216398849</v>
       </c>
     </row>
     <row r="2209" spans="1:2">
@@ -18043,7 +18043,7 @@
         <v>2207</v>
       </c>
       <c r="B2209">
-        <v>-1</v>
+        <v>3.590092286514235</v>
       </c>
     </row>
     <row r="2210" spans="1:2">
@@ -18339,7 +18339,7 @@
         <v>2244</v>
       </c>
       <c r="B2246">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2247" spans="1:2">
@@ -18347,7 +18347,7 @@
         <v>2245</v>
       </c>
       <c r="B2247">
-        <v>-1</v>
+        <v>136.0821728847278</v>
       </c>
     </row>
     <row r="2248" spans="1:2">
@@ -18355,7 +18355,7 @@
         <v>2246</v>
       </c>
       <c r="B2248">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2249" spans="1:2">
@@ -20355,7 +20355,7 @@
         <v>2496</v>
       </c>
       <c r="B2498">
-        <v>-1</v>
+        <v>4.617870629751364</v>
       </c>
     </row>
     <row r="2499" spans="1:2">
@@ -20363,7 +20363,7 @@
         <v>2497</v>
       </c>
       <c r="B2499">
-        <v>-1</v>
+        <v>7.532703847856537</v>
       </c>
     </row>
     <row r="2500" spans="1:2">
@@ -20371,7 +20371,7 @@
         <v>2498</v>
       </c>
       <c r="B2500">
-        <v>-1</v>
+        <v>3.984284269574834</v>
       </c>
     </row>
     <row r="2501" spans="1:2">
@@ -20955,7 +20955,7 @@
         <v>2571</v>
       </c>
       <c r="B2573">
-        <v>-1</v>
+        <v>13.33229285730101</v>
       </c>
     </row>
     <row r="2574" spans="1:2">
@@ -20963,7 +20963,7 @@
         <v>2572</v>
       </c>
       <c r="B2574">
-        <v>-1</v>
+        <v>26.25828583298568</v>
       </c>
     </row>
     <row r="2575" spans="1:2">
@@ -20971,7 +20971,7 @@
         <v>2573</v>
       </c>
       <c r="B2575">
-        <v>-1</v>
+        <v>11.46476604935449</v>
       </c>
     </row>
     <row r="2576" spans="1:2">
@@ -21771,7 +21771,7 @@
         <v>2673</v>
       </c>
       <c r="B2675">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2676" spans="1:2">
@@ -21779,7 +21779,7 @@
         <v>2674</v>
       </c>
       <c r="B2676">
-        <v>-1</v>
+        <v>3.576700632173258</v>
       </c>
     </row>
     <row r="2677" spans="1:2">
@@ -21787,7 +21787,7 @@
         <v>2675</v>
       </c>
       <c r="B2677">
-        <v>-1</v>
+        <v>3.31671819521977</v>
       </c>
     </row>
     <row r="2678" spans="1:2">
@@ -21795,7 +21795,7 @@
         <v>2676</v>
       </c>
       <c r="B2678">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2679" spans="1:2">
@@ -21803,7 +21803,7 @@
         <v>2677</v>
       </c>
       <c r="B2679">
-        <v>-1</v>
+        <v>3.389767103741281</v>
       </c>
     </row>
     <row r="2680" spans="1:2">
@@ -21811,7 +21811,7 @@
         <v>2678</v>
       </c>
       <c r="B2680">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2681" spans="1:2">
@@ -22107,7 +22107,7 @@
         <v>2715</v>
       </c>
       <c r="B2717">
-        <v>-1</v>
+        <v>11.14678541447194</v>
       </c>
     </row>
     <row r="2718" spans="1:2">
@@ -22115,7 +22115,7 @@
         <v>2716</v>
       </c>
       <c r="B2718">
-        <v>-1</v>
+        <v>11.48223562290258</v>
       </c>
     </row>
     <row r="2719" spans="1:2">
@@ -22123,7 +22123,7 @@
         <v>2717</v>
       </c>
       <c r="B2719">
-        <v>-1</v>
+        <v>9.433151465445588</v>
       </c>
     </row>
     <row r="2720" spans="1:2">
@@ -22467,7 +22467,7 @@
         <v>2760</v>
       </c>
       <c r="B2762">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2763" spans="1:2">
@@ -22475,7 +22475,7 @@
         <v>2761</v>
       </c>
       <c r="B2763">
-        <v>-1</v>
+        <v>5.193089874552658</v>
       </c>
     </row>
     <row r="2764" spans="1:2">
@@ -22483,7 +22483,7 @@
         <v>2762</v>
       </c>
       <c r="B2764">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2765" spans="1:2">
@@ -22491,7 +22491,7 @@
         <v>2763</v>
       </c>
       <c r="B2765">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2766" spans="1:2">
@@ -22499,7 +22499,7 @@
         <v>2764</v>
       </c>
       <c r="B2766">
-        <v>-1</v>
+        <v>3.314942633128437</v>
       </c>
     </row>
     <row r="2767" spans="1:2">
@@ -22507,7 +22507,7 @@
         <v>2765</v>
       </c>
       <c r="B2767">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2768" spans="1:2">
@@ -22659,7 +22659,7 @@
         <v>2784</v>
       </c>
       <c r="B2786">
-        <v>-1</v>
+        <v>4.761159602102394</v>
       </c>
     </row>
     <row r="2787" spans="1:2">
@@ -22667,7 +22667,7 @@
         <v>2785</v>
       </c>
       <c r="B2787">
-        <v>-1</v>
+        <v>7.776973778283036</v>
       </c>
     </row>
     <row r="2788" spans="1:2">
@@ -22675,7 +22675,7 @@
         <v>2786</v>
       </c>
       <c r="B2788">
-        <v>-1</v>
+        <v>4.082433703773947</v>
       </c>
     </row>
     <row r="2789" spans="1:2">
@@ -22779,7 +22779,7 @@
         <v>2799</v>
       </c>
       <c r="B2801">
-        <v>-1</v>
+        <v>3.497440989349665</v>
       </c>
     </row>
     <row r="2802" spans="1:2">
@@ -22787,7 +22787,7 @@
         <v>2800</v>
       </c>
       <c r="B2802">
-        <v>-1</v>
+        <v>5.411945168821219</v>
       </c>
     </row>
     <row r="2803" spans="1:2">
@@ -22795,7 +22795,7 @@
         <v>2801</v>
       </c>
       <c r="B2803">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2804" spans="1:2">
@@ -22947,7 +22947,7 @@
         <v>2820</v>
       </c>
       <c r="B2822">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2823" spans="1:2">
@@ -22955,7 +22955,7 @@
         <v>2821</v>
       </c>
       <c r="B2823">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2824" spans="1:2">
@@ -22963,7 +22963,7 @@
         <v>2822</v>
       </c>
       <c r="B2824">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2825" spans="1:2">
@@ -22971,7 +22971,7 @@
         <v>2823</v>
       </c>
       <c r="B2825">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2826" spans="1:2">
@@ -22979,7 +22979,7 @@
         <v>2824</v>
       </c>
       <c r="B2826">
-        <v>-1</v>
+        <v>11.94398206835754</v>
       </c>
     </row>
     <row r="2827" spans="1:2">
@@ -22987,7 +22987,7 @@
         <v>2825</v>
       </c>
       <c r="B2827">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2828" spans="1:2">
@@ -23163,7 +23163,7 @@
         <v>2847</v>
       </c>
       <c r="B2849">
-        <v>-1</v>
+        <v>6.157726272934083</v>
       </c>
     </row>
     <row r="2850" spans="1:2">
@@ -23171,7 +23171,7 @@
         <v>2848</v>
       </c>
       <c r="B2850">
-        <v>-1</v>
+        <v>8.153354184556449</v>
       </c>
     </row>
     <row r="2851" spans="1:2">
@@ -23179,7 +23179,7 @@
         <v>2849</v>
       </c>
       <c r="B2851">
-        <v>-1</v>
+        <v>4.804376241508812</v>
       </c>
     </row>
     <row r="2852" spans="1:2">
@@ -24771,7 +24771,7 @@
         <v>3048</v>
       </c>
       <c r="B3050">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3051" spans="1:2">
@@ -24779,7 +24779,7 @@
         <v>3049</v>
       </c>
       <c r="B3051">
-        <v>-1</v>
+        <v>30.01871294200653</v>
       </c>
     </row>
     <row r="3052" spans="1:2">
@@ -24787,7 +24787,7 @@
         <v>3050</v>
       </c>
       <c r="B3052">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3053" spans="1:2">
@@ -24915,7 +24915,7 @@
         <v>3066</v>
       </c>
       <c r="B3068">
-        <v>-1</v>
+        <v>11.63915570597864</v>
       </c>
     </row>
     <row r="3069" spans="1:2">
@@ -24923,7 +24923,7 @@
         <v>3067</v>
       </c>
       <c r="B3069">
-        <v>-1</v>
+        <v>45.3231242265289</v>
       </c>
     </row>
     <row r="3070" spans="1:2">
@@ -24931,7 +24931,7 @@
         <v>3068</v>
       </c>
       <c r="B3070">
-        <v>-1</v>
+        <v>10.10426975852886</v>
       </c>
     </row>
     <row r="3071" spans="1:2">
@@ -25227,7 +25227,7 @@
         <v>3105</v>
       </c>
       <c r="B3107">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3108" spans="1:2">
@@ -25235,7 +25235,7 @@
         <v>3106</v>
       </c>
       <c r="B3108">
-        <v>-1</v>
+        <v>101.060221047936</v>
       </c>
     </row>
     <row r="3109" spans="1:2">
@@ -25243,7 +25243,7 @@
         <v>3107</v>
       </c>
       <c r="B3109">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="3110" spans="1:2">
@@ -25299,7 +25299,7 @@
         <v>3114</v>
       </c>
       <c r="B3116">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3117" spans="1:2">
@@ -25307,7 +25307,7 @@
         <v>3115</v>
       </c>
       <c r="B3117">
-        <v>-1</v>
+        <v>5.049075662131486</v>
       </c>
     </row>
     <row r="3118" spans="1:2">
@@ -25315,7 +25315,7 @@
         <v>3116</v>
       </c>
       <c r="B3118">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3119" spans="1:2">
@@ -25587,7 +25587,7 @@
         <v>3150</v>
       </c>
       <c r="B3152">
-        <v>-1</v>
+        <v>4.138240336868604</v>
       </c>
     </row>
     <row r="3153" spans="1:2">
@@ -25595,7 +25595,7 @@
         <v>3151</v>
       </c>
       <c r="B3153">
-        <v>-1</v>
+        <v>10.7104671953736</v>
       </c>
     </row>
     <row r="3154" spans="1:2">
@@ -25603,7 +25603,7 @@
         <v>3152</v>
       </c>
       <c r="B3154">
-        <v>-1</v>
+        <v>3.437480431476225</v>
       </c>
     </row>
     <row r="3155" spans="1:2">
@@ -25899,7 +25899,7 @@
         <v>3189</v>
       </c>
       <c r="B3191">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3192" spans="1:2">
@@ -25907,7 +25907,7 @@
         <v>3190</v>
       </c>
       <c r="B3192">
-        <v>-1</v>
+        <v>3.772312524503318</v>
       </c>
     </row>
     <row r="3193" spans="1:2">
@@ -25915,7 +25915,7 @@
         <v>3191</v>
       </c>
       <c r="B3193">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3194" spans="1:2">
@@ -25971,7 +25971,7 @@
         <v>3198</v>
       </c>
       <c r="B3200">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3201" spans="1:2">
@@ -25979,7 +25979,7 @@
         <v>3199</v>
       </c>
       <c r="B3201">
-        <v>-1</v>
+        <v>5.840248259370551</v>
       </c>
     </row>
     <row r="3202" spans="1:2">
@@ -25987,7 +25987,7 @@
         <v>3200</v>
       </c>
       <c r="B3202">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3203" spans="1:2">
@@ -26067,7 +26067,7 @@
         <v>3210</v>
       </c>
       <c r="B3212">
-        <v>-1</v>
+        <v>9.345673324620263</v>
       </c>
     </row>
     <row r="3213" spans="1:2">
@@ -26075,7 +26075,7 @@
         <v>3211</v>
       </c>
       <c r="B3213">
-        <v>-1</v>
+        <v>13.28974813770845</v>
       </c>
     </row>
     <row r="3214" spans="1:2">
@@ -26083,7 +26083,7 @@
         <v>3212</v>
       </c>
       <c r="B3214">
-        <v>-1</v>
+        <v>8.166903981061768</v>
       </c>
     </row>
     <row r="3215" spans="1:2">
@@ -26091,7 +26091,7 @@
         <v>3213</v>
       </c>
       <c r="B3215">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3216" spans="1:2">
@@ -26099,7 +26099,7 @@
         <v>3214</v>
       </c>
       <c r="B3216">
-        <v>-1</v>
+        <v>4.28549049548571</v>
       </c>
     </row>
     <row r="3217" spans="1:2">
@@ -26107,7 +26107,7 @@
         <v>3215</v>
       </c>
       <c r="B3217">
-        <v>-1</v>
+        <v>3.359645251200427</v>
       </c>
     </row>
     <row r="3218" spans="1:2">
@@ -26475,7 +26475,7 @@
         <v>3261</v>
       </c>
       <c r="B3263">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="3264" spans="1:2">
@@ -26483,7 +26483,7 @@
         <v>3262</v>
       </c>
       <c r="B3264">
-        <v>-1</v>
+        <v>3.723779102491065</v>
       </c>
     </row>
     <row r="3265" spans="1:2">
@@ -26491,7 +26491,7 @@
         <v>3263</v>
       </c>
       <c r="B3265">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3266" spans="1:2">
@@ -26547,7 +26547,7 @@
         <v>3270</v>
       </c>
       <c r="B3272">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3273" spans="1:2">
@@ -26555,7 +26555,7 @@
         <v>3271</v>
       </c>
       <c r="B3273">
-        <v>-1</v>
+        <v>6.571324048416994</v>
       </c>
     </row>
     <row r="3274" spans="1:2">
@@ -26563,7 +26563,7 @@
         <v>3272</v>
       </c>
       <c r="B3274">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3275" spans="1:2">
@@ -26883,7 +26883,7 @@
         <v>3312</v>
       </c>
       <c r="B3314">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3315" spans="1:2">
@@ -26891,7 +26891,7 @@
         <v>3313</v>
       </c>
       <c r="B3315">
-        <v>-1</v>
+        <v>4.804824986907796</v>
       </c>
     </row>
     <row r="3316" spans="1:2">
@@ -26899,7 +26899,7 @@
         <v>3314</v>
       </c>
       <c r="B3316">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3317" spans="1:2">
@@ -26955,7 +26955,7 @@
         <v>3321</v>
       </c>
       <c r="B3323">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3324" spans="1:2">
@@ -26963,7 +26963,7 @@
         <v>3322</v>
       </c>
       <c r="B3324">
-        <v>-1</v>
+        <v>84.89876983065356</v>
       </c>
     </row>
     <row r="3325" spans="1:2">
@@ -26971,7 +26971,7 @@
         <v>3323</v>
       </c>
       <c r="B3325">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3326" spans="1:2">
@@ -27027,7 +27027,7 @@
         <v>3330</v>
       </c>
       <c r="B3332">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3333" spans="1:2">
@@ -27035,7 +27035,7 @@
         <v>3331</v>
       </c>
       <c r="B3333">
-        <v>-1</v>
+        <v>4.836726735967545</v>
       </c>
     </row>
     <row r="3334" spans="1:2">
@@ -27043,7 +27043,7 @@
         <v>3332</v>
       </c>
       <c r="B3334">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3335" spans="1:2">
@@ -27483,7 +27483,7 @@
         <v>3387</v>
       </c>
       <c r="B3389">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3390" spans="1:2">
@@ -27491,7 +27491,7 @@
         <v>3388</v>
       </c>
       <c r="B3390">
-        <v>-1</v>
+        <v>11.53109262539601</v>
       </c>
     </row>
     <row r="3391" spans="1:2">
@@ -27499,7 +27499,7 @@
         <v>3389</v>
       </c>
       <c r="B3391">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3392" spans="1:2">
@@ -27699,7 +27699,7 @@
         <v>3414</v>
       </c>
       <c r="B3416">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3417" spans="1:2">
@@ -27707,7 +27707,7 @@
         <v>3415</v>
       </c>
       <c r="B3417">
-        <v>-1</v>
+        <v>147.3372024194005</v>
       </c>
     </row>
     <row r="3418" spans="1:2">
@@ -27715,7 +27715,7 @@
         <v>3416</v>
       </c>
       <c r="B3418">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3419" spans="1:2">
@@ -28515,7 +28515,7 @@
         <v>3516</v>
       </c>
       <c r="B3518">
-        <v>-1</v>
+        <v>8.826973551980565</v>
       </c>
     </row>
     <row r="3519" spans="1:2">
@@ -28523,7 +28523,7 @@
         <v>3517</v>
       </c>
       <c r="B3519">
-        <v>-1</v>
+        <v>9.637721884691874</v>
       </c>
     </row>
     <row r="3520" spans="1:2">
@@ -28531,7 +28531,7 @@
         <v>3518</v>
       </c>
       <c r="B3520">
-        <v>-1</v>
+        <v>7.576919860520637</v>
       </c>
     </row>
     <row r="3521" spans="1:2">
@@ -28587,7 +28587,7 @@
         <v>3525</v>
       </c>
       <c r="B3527">
-        <v>-1</v>
+        <v>8.884730039808309</v>
       </c>
     </row>
     <row r="3528" spans="1:2">
@@ -28595,7 +28595,7 @@
         <v>3526</v>
       </c>
       <c r="B3528">
-        <v>-1</v>
+        <v>9.579753194652952</v>
       </c>
     </row>
     <row r="3529" spans="1:2">
@@ -28603,7 +28603,7 @@
         <v>3527</v>
       </c>
       <c r="B3529">
-        <v>-1</v>
+        <v>7.576919860520637</v>
       </c>
     </row>
     <row r="3530" spans="1:2">
@@ -28803,7 +28803,7 @@
         <v>3552</v>
       </c>
       <c r="B3554">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3555" spans="1:2">
@@ -28811,7 +28811,7 @@
         <v>3553</v>
       </c>
       <c r="B3555">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3556" spans="1:2">
@@ -28819,7 +28819,7 @@
         <v>3554</v>
       </c>
       <c r="B3556">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3557" spans="1:2">
@@ -28875,7 +28875,7 @@
         <v>3561</v>
       </c>
       <c r="B3563">
-        <v>-1</v>
+        <v>3.300000000000081</v>
       </c>
     </row>
     <row r="3564" spans="1:2">
@@ -28883,7 +28883,7 @@
         <v>3562</v>
       </c>
       <c r="B3564">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3565" spans="1:2">
@@ -28891,7 +28891,7 @@
         <v>3563</v>
       </c>
       <c r="B3565">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3566" spans="1:2">
@@ -28995,7 +28995,7 @@
         <v>3576</v>
       </c>
       <c r="B3578">
-        <v>-1</v>
+        <v>3.918093480514229</v>
       </c>
     </row>
     <row r="3579" spans="1:2">
@@ -29003,7 +29003,7 @@
         <v>3577</v>
       </c>
       <c r="B3579">
-        <v>-1</v>
+        <v>3.970202464209427</v>
       </c>
     </row>
     <row r="3580" spans="1:2">
@@ -29011,7 +29011,7 @@
         <v>3578</v>
       </c>
       <c r="B3580">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3581" spans="1:2">
@@ -29307,7 +29307,7 @@
         <v>3615</v>
       </c>
       <c r="B3617">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3618" spans="1:2">
@@ -29315,7 +29315,7 @@
         <v>3616</v>
       </c>
       <c r="B3618">
-        <v>-1</v>
+        <v>7.997156317383413</v>
       </c>
     </row>
     <row r="3619" spans="1:2">
@@ -29323,7 +29323,7 @@
         <v>3617</v>
       </c>
       <c r="B3619">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3620" spans="1:2">
@@ -29451,7 +29451,7 @@
         <v>3633</v>
       </c>
       <c r="B3635">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3636" spans="1:2">
@@ -29459,7 +29459,7 @@
         <v>3634</v>
       </c>
       <c r="B3636">
-        <v>-1</v>
+        <v>8.009607881919168</v>
       </c>
     </row>
     <row r="3637" spans="1:2">
@@ -29467,7 +29467,7 @@
         <v>3635</v>
       </c>
       <c r="B3637">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3638" spans="1:2">
@@ -29571,7 +29571,7 @@
         <v>3648</v>
       </c>
       <c r="B3650">
-        <v>-1</v>
+        <v>4.529118787984865</v>
       </c>
     </row>
     <row r="3651" spans="1:2">
@@ -29579,7 +29579,7 @@
         <v>3649</v>
       </c>
       <c r="B3651">
-        <v>-1</v>
+        <v>7.431373874412128</v>
       </c>
     </row>
     <row r="3652" spans="1:2">
@@ -29587,7 +29587,7 @@
         <v>3650</v>
       </c>
       <c r="B3652">
-        <v>-1</v>
+        <v>3.900698138183956</v>
       </c>
     </row>
     <row r="3653" spans="1:2">
@@ -29619,7 +29619,7 @@
         <v>3654</v>
       </c>
       <c r="B3656">
-        <v>-1</v>
+        <v>3.371794929340133</v>
       </c>
     </row>
     <row r="3657" spans="1:2">
@@ -29627,7 +29627,7 @@
         <v>3655</v>
       </c>
       <c r="B3657">
-        <v>-1</v>
+        <v>4.291000434003623</v>
       </c>
     </row>
     <row r="3658" spans="1:2">
@@ -29635,7 +29635,7 @@
         <v>3656</v>
       </c>
       <c r="B3658">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3659" spans="1:2">
@@ -30195,7 +30195,7 @@
         <v>3726</v>
       </c>
       <c r="B3728">
-        <v>-1</v>
+        <v>4.057739681302208</v>
       </c>
     </row>
     <row r="3729" spans="1:2">
@@ -30203,7 +30203,7 @@
         <v>3727</v>
       </c>
       <c r="B3729">
-        <v>-1</v>
+        <v>5.342043534173913</v>
       </c>
     </row>
     <row r="3730" spans="1:2">
@@ -30211,7 +30211,7 @@
         <v>3728</v>
       </c>
       <c r="B3730">
-        <v>-1</v>
+        <v>3.376833827492398</v>
       </c>
     </row>
     <row r="3731" spans="1:2">
@@ -30267,7 +30267,7 @@
         <v>3735</v>
       </c>
       <c r="B3737">
-        <v>-1</v>
+        <v>4.072436967473426</v>
       </c>
     </row>
     <row r="3738" spans="1:2">
@@ -30275,7 +30275,7 @@
         <v>3736</v>
       </c>
       <c r="B3738">
-        <v>-1</v>
+        <v>6.39570816799333</v>
       </c>
     </row>
     <row r="3739" spans="1:2">
@@ -30283,7 +30283,7 @@
         <v>3737</v>
       </c>
       <c r="B3739">
-        <v>-1</v>
+        <v>3.376833827492398</v>
       </c>
     </row>
     <row r="3740" spans="1:2">
@@ -30459,7 +30459,7 @@
         <v>3759</v>
       </c>
       <c r="B3761">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="3762" spans="1:2">
@@ -30467,7 +30467,7 @@
         <v>3760</v>
       </c>
       <c r="B3762">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3763" spans="1:2">
@@ -30475,7 +30475,7 @@
         <v>3761</v>
       </c>
       <c r="B3763">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3764" spans="1:2">
@@ -30603,7 +30603,7 @@
         <v>3777</v>
       </c>
       <c r="B3779">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3780" spans="1:2">
@@ -30611,7 +30611,7 @@
         <v>3778</v>
       </c>
       <c r="B3780">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3781" spans="1:2">
@@ -30619,7 +30619,7 @@
         <v>3779</v>
       </c>
       <c r="B3781">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3782" spans="1:2">
@@ -31275,7 +31275,7 @@
         <v>3861</v>
       </c>
       <c r="B3863">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3864" spans="1:2">
@@ -31283,7 +31283,7 @@
         <v>3862</v>
       </c>
       <c r="B3864">
-        <v>-1</v>
+        <v>3.614973742555239</v>
       </c>
     </row>
     <row r="3865" spans="1:2">
@@ -31291,7 +31291,7 @@
         <v>3863</v>
       </c>
       <c r="B3865">
-        <v>-1</v>
+        <v>3.376732431887564</v>
       </c>
     </row>
     <row r="3866" spans="1:2">
@@ -31563,7 +31563,7 @@
         <v>3897</v>
       </c>
       <c r="B3899">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3900" spans="1:2">
@@ -31571,7 +31571,7 @@
         <v>3898</v>
       </c>
       <c r="B3900">
-        <v>-1</v>
+        <v>3.403380058621686</v>
       </c>
     </row>
     <row r="3901" spans="1:2">
@@ -31579,7 +31579,7 @@
         <v>3899</v>
       </c>
       <c r="B3901">
-        <v>-1</v>
+        <v>3.424039618286256</v>
       </c>
     </row>
     <row r="3902" spans="1:2">
@@ -31851,7 +31851,7 @@
         <v>3933</v>
       </c>
       <c r="B3935">
-        <v>-1</v>
+        <v>3.75949895690384</v>
       </c>
     </row>
     <row r="3936" spans="1:2">
@@ -31859,7 +31859,7 @@
         <v>3934</v>
       </c>
       <c r="B3936">
-        <v>-1</v>
+        <v>5.99377887591589</v>
       </c>
     </row>
     <row r="3937" spans="1:2">
@@ -31867,7 +31867,7 @@
         <v>3935</v>
       </c>
       <c r="B3937">
-        <v>-1</v>
+        <v>3.420181840905423</v>
       </c>
     </row>
     <row r="3938" spans="1:2">
@@ -32835,7 +32835,7 @@
         <v>4056</v>
       </c>
       <c r="B4058">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4059" spans="1:2">
@@ -32843,7 +32843,7 @@
         <v>4057</v>
       </c>
       <c r="B4059">
-        <v>-1</v>
+        <v>6.306526651914779</v>
       </c>
     </row>
     <row r="4060" spans="1:2">
@@ -32851,7 +32851,7 @@
         <v>4058</v>
       </c>
       <c r="B4060">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4061" spans="1:2">
@@ -32883,7 +32883,7 @@
         <v>4062</v>
       </c>
       <c r="B4064">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4065" spans="1:2">
@@ -32891,7 +32891,7 @@
         <v>4063</v>
       </c>
       <c r="B4065">
-        <v>-1</v>
+        <v>5.067610085585505</v>
       </c>
     </row>
     <row r="4066" spans="1:2">
@@ -32899,7 +32899,7 @@
         <v>4064</v>
       </c>
       <c r="B4066">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4067" spans="1:2">
@@ -33267,7 +33267,7 @@
         <v>4110</v>
       </c>
       <c r="B4112">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4113" spans="1:2">
@@ -33275,7 +33275,7 @@
         <v>4111</v>
       </c>
       <c r="B4113">
-        <v>-1</v>
+        <v>6.00748096617385</v>
       </c>
     </row>
     <row r="4114" spans="1:2">
@@ -33283,7 +33283,7 @@
         <v>4112</v>
       </c>
       <c r="B4114">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4115" spans="1:2">
@@ -33339,7 +33339,7 @@
         <v>4119</v>
       </c>
       <c r="B4121">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4122" spans="1:2">
@@ -33347,7 +33347,7 @@
         <v>4120</v>
       </c>
       <c r="B4122">
-        <v>-1</v>
+        <v>12.24718425842601</v>
       </c>
     </row>
     <row r="4123" spans="1:2">
@@ -33355,7 +33355,7 @@
         <v>4121</v>
       </c>
       <c r="B4123">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4124" spans="1:2">
@@ -33363,7 +33363,7 @@
         <v>4122</v>
       </c>
       <c r="B4124">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4125" spans="1:2">
@@ -33371,7 +33371,7 @@
         <v>4123</v>
       </c>
       <c r="B4125">
-        <v>-1</v>
+        <v>3.591219382913513</v>
       </c>
     </row>
     <row r="4126" spans="1:2">
@@ -33379,7 +33379,7 @@
         <v>4124</v>
       </c>
       <c r="B4126">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4127" spans="1:2">
@@ -33387,7 +33387,7 @@
         <v>4125</v>
       </c>
       <c r="B4127">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4128" spans="1:2">
@@ -33395,7 +33395,7 @@
         <v>4126</v>
       </c>
       <c r="B4128">
-        <v>-1</v>
+        <v>3.368153851874167</v>
       </c>
     </row>
     <row r="4129" spans="1:2">
@@ -33403,7 +33403,7 @@
         <v>4127</v>
       </c>
       <c r="B4129">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4130" spans="1:2">
@@ -33435,7 +33435,7 @@
         <v>4131</v>
       </c>
       <c r="B4133">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4134" spans="1:2">
@@ -33443,7 +33443,7 @@
         <v>4132</v>
       </c>
       <c r="B4134">
-        <v>-1</v>
+        <v>4.091137157813218</v>
       </c>
     </row>
     <row r="4135" spans="1:2">
@@ -33451,7 +33451,7 @@
         <v>4133</v>
       </c>
       <c r="B4135">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4136" spans="1:2">
@@ -33939,7 +33939,7 @@
         <v>4194</v>
       </c>
       <c r="B4196">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4197" spans="1:2">
@@ -33947,7 +33947,7 @@
         <v>4195</v>
       </c>
       <c r="B4197">
-        <v>-1</v>
+        <v>4.255011535548503</v>
       </c>
     </row>
     <row r="4198" spans="1:2">
@@ -33955,7 +33955,7 @@
         <v>4196</v>
       </c>
       <c r="B4198">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4199" spans="1:2">
@@ -33987,7 +33987,7 @@
         <v>4200</v>
       </c>
       <c r="B4202">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4203" spans="1:2">
@@ -33995,7 +33995,7 @@
         <v>4201</v>
       </c>
       <c r="B4203">
-        <v>-1</v>
+        <v>33.42877837658835</v>
       </c>
     </row>
     <row r="4204" spans="1:2">
@@ -34003,7 +34003,7 @@
         <v>4202</v>
       </c>
       <c r="B4204">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4205" spans="1:2">
@@ -34131,7 +34131,7 @@
         <v>4218</v>
       </c>
       <c r="B4220">
-        <v>-1</v>
+        <v>11.43860643356086</v>
       </c>
     </row>
     <row r="4221" spans="1:2">
@@ -34139,7 +34139,7 @@
         <v>4219</v>
       </c>
       <c r="B4221">
-        <v>-1</v>
+        <v>48.77039923663527</v>
       </c>
     </row>
     <row r="4222" spans="1:2">
@@ -34147,7 +34147,7 @@
         <v>4220</v>
       </c>
       <c r="B4222">
-        <v>-1</v>
+        <v>9.93730016662826</v>
       </c>
     </row>
     <row r="4223" spans="1:2">
@@ -34227,7 +34227,7 @@
         <v>4230</v>
       </c>
       <c r="B4232">
-        <v>-1</v>
+        <v>3.414899937501492</v>
       </c>
     </row>
     <row r="4233" spans="1:2">
@@ -34235,7 +34235,7 @@
         <v>4231</v>
       </c>
       <c r="B4233">
-        <v>-1</v>
+        <v>7.999023527520211</v>
       </c>
     </row>
     <row r="4234" spans="1:2">
@@ -34243,7 +34243,7 @@
         <v>4232</v>
       </c>
       <c r="B4234">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4235" spans="1:2">
@@ -34371,7 +34371,7 @@
         <v>4248</v>
       </c>
       <c r="B4250">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4251" spans="1:2">
@@ -34379,7 +34379,7 @@
         <v>4249</v>
       </c>
       <c r="B4251">
-        <v>-1</v>
+        <v>5.381539657133927</v>
       </c>
     </row>
     <row r="4252" spans="1:2">
@@ -34387,7 +34387,7 @@
         <v>4250</v>
       </c>
       <c r="B4252">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4253" spans="1:2">
@@ -34395,7 +34395,7 @@
         <v>4251</v>
       </c>
       <c r="B4253">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4254" spans="1:2">
@@ -34403,7 +34403,7 @@
         <v>4252</v>
       </c>
       <c r="B4254">
-        <v>-1</v>
+        <v>10.54869163598667</v>
       </c>
     </row>
     <row r="4255" spans="1:2">
@@ -34411,7 +34411,7 @@
         <v>4253</v>
       </c>
       <c r="B4255">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4256" spans="1:2">
@@ -34515,7 +34515,7 @@
         <v>4266</v>
       </c>
       <c r="B4268">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4269" spans="1:2">
@@ -34523,7 +34523,7 @@
         <v>4267</v>
       </c>
       <c r="B4269">
-        <v>-1</v>
+        <v>5.411858067200304</v>
       </c>
     </row>
     <row r="4270" spans="1:2">
@@ -34531,7 +34531,7 @@
         <v>4268</v>
       </c>
       <c r="B4270">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4271" spans="1:2">
@@ -34539,7 +34539,7 @@
         <v>4269</v>
       </c>
       <c r="B4271">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4272" spans="1:2">
@@ -34547,7 +34547,7 @@
         <v>4270</v>
       </c>
       <c r="B4272">
-        <v>-1</v>
+        <v>10.59293187246472</v>
       </c>
     </row>
     <row r="4273" spans="1:2">
@@ -34555,7 +34555,7 @@
         <v>4271</v>
       </c>
       <c r="B4273">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4274" spans="1:2">
@@ -34659,7 +34659,7 @@
         <v>4284</v>
       </c>
       <c r="B4286">
-        <v>-1</v>
+        <v>4.104968165958677</v>
       </c>
     </row>
     <row r="4287" spans="1:2">
@@ -34667,7 +34667,7 @@
         <v>4285</v>
       </c>
       <c r="B4287">
-        <v>-1</v>
+        <v>10.9538893241606</v>
       </c>
     </row>
     <row r="4288" spans="1:2">
@@ -34675,7 +34675,7 @@
         <v>4286</v>
       </c>
       <c r="B4288">
-        <v>-1</v>
+        <v>3.430503089290549</v>
       </c>
     </row>
     <row r="4289" spans="1:2">
@@ -34803,7 +34803,7 @@
         <v>4302</v>
       </c>
       <c r="B4304">
-        <v>-1</v>
+        <v>4.10761868764834</v>
       </c>
     </row>
     <row r="4305" spans="1:2">
@@ -34811,7 +34811,7 @@
         <v>4303</v>
       </c>
       <c r="B4305">
-        <v>-1</v>
+        <v>11.00167887617204</v>
       </c>
     </row>
     <row r="4306" spans="1:2">
@@ -34819,7 +34819,7 @@
         <v>4304</v>
       </c>
       <c r="B4306">
-        <v>-1</v>
+        <v>3.432184536254856</v>
       </c>
     </row>
     <row r="4307" spans="1:2">
@@ -35019,7 +35019,7 @@
         <v>4329</v>
       </c>
       <c r="B4331">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4332" spans="1:2">
@@ -35027,7 +35027,7 @@
         <v>4330</v>
       </c>
       <c r="B4332">
-        <v>-1</v>
+        <v>3.92235843266785</v>
       </c>
     </row>
     <row r="4333" spans="1:2">
@@ -35035,7 +35035,7 @@
         <v>4331</v>
       </c>
       <c r="B4333">
-        <v>-1</v>
+        <v>3.447141373253171</v>
       </c>
     </row>
     <row r="4334" spans="1:2">
@@ -35163,7 +35163,7 @@
         <v>4347</v>
       </c>
       <c r="B4349">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4350" spans="1:2">
@@ -35171,7 +35171,7 @@
         <v>4348</v>
       </c>
       <c r="B4350">
-        <v>-1</v>
+        <v>4.764941901496189</v>
       </c>
     </row>
     <row r="4351" spans="1:2">
@@ -35179,7 +35179,7 @@
         <v>4349</v>
       </c>
       <c r="B4351">
-        <v>-1</v>
+        <v>3.403445636948188</v>
       </c>
     </row>
     <row r="4352" spans="1:2">
@@ -35523,7 +35523,7 @@
         <v>4392</v>
       </c>
       <c r="B4394">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4395" spans="1:2">
@@ -35531,7 +35531,7 @@
         <v>4393</v>
       </c>
       <c r="B4395">
-        <v>-1</v>
+        <v>3.79857103348058</v>
       </c>
     </row>
     <row r="4396" spans="1:2">
@@ -35539,7 +35539,7 @@
         <v>4394</v>
       </c>
       <c r="B4396">
-        <v>-1</v>
+        <v>3.392145865394336</v>
       </c>
     </row>
     <row r="4397" spans="1:2">
@@ -35547,7 +35547,7 @@
         <v>4395</v>
       </c>
       <c r="B4397">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4398" spans="1:2">
@@ -35555,7 +35555,7 @@
         <v>4396</v>
       </c>
       <c r="B4398">
-        <v>-1</v>
+        <v>3.644577477026867</v>
       </c>
     </row>
     <row r="4399" spans="1:2">
@@ -35563,7 +35563,7 @@
         <v>4397</v>
       </c>
       <c r="B4399">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4400" spans="1:2">
@@ -35667,7 +35667,7 @@
         <v>4410</v>
       </c>
       <c r="B4412">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4413" spans="1:2">
@@ -35675,7 +35675,7 @@
         <v>4411</v>
       </c>
       <c r="B4413">
-        <v>-1</v>
+        <v>3.795212117702507</v>
       </c>
     </row>
     <row r="4414" spans="1:2">
@@ -35683,7 +35683,7 @@
         <v>4412</v>
       </c>
       <c r="B4414">
-        <v>-1</v>
+        <v>3.347031592788197</v>
       </c>
     </row>
     <row r="4415" spans="1:2">
@@ -35691,7 +35691,7 @@
         <v>4413</v>
       </c>
       <c r="B4415">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4416" spans="1:2">
@@ -35699,7 +35699,7 @@
         <v>4414</v>
       </c>
       <c r="B4416">
-        <v>-1</v>
+        <v>3.64071873105043</v>
       </c>
     </row>
     <row r="4417" spans="1:2">
@@ -35707,7 +35707,7 @@
         <v>4415</v>
       </c>
       <c r="B4417">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4418" spans="1:2">
@@ -35763,7 +35763,7 @@
         <v>4422</v>
       </c>
       <c r="B4424">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4425" spans="1:2">
@@ -35771,7 +35771,7 @@
         <v>4423</v>
       </c>
       <c r="B4425">
-        <v>-1</v>
+        <v>8.104157397873191</v>
       </c>
     </row>
     <row r="4426" spans="1:2">
@@ -35779,7 +35779,7 @@
         <v>4424</v>
       </c>
       <c r="B4426">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4427" spans="1:2">
@@ -36099,7 +36099,7 @@
         <v>4464</v>
       </c>
       <c r="B4466">
-        <v>-1</v>
+        <v>3.300000000000081</v>
       </c>
     </row>
     <row r="4467" spans="1:2">
@@ -36107,7 +36107,7 @@
         <v>4465</v>
       </c>
       <c r="B4467">
-        <v>-1</v>
+        <v>6.058750783029043</v>
       </c>
     </row>
     <row r="4468" spans="1:2">
@@ -36115,7 +36115,7 @@
         <v>4466</v>
       </c>
       <c r="B4468">
-        <v>-1</v>
+        <v>3.423618123056626</v>
       </c>
     </row>
     <row r="4469" spans="1:2">
@@ -38643,7 +38643,7 @@
         <v>4782</v>
       </c>
       <c r="B4784">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4785" spans="1:2">
@@ -38651,7 +38651,7 @@
         <v>4783</v>
       </c>
       <c r="B4785">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4786" spans="1:2">
@@ -38659,7 +38659,7 @@
         <v>4784</v>
       </c>
       <c r="B4786">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4787" spans="1:2">
@@ -39315,7 +39315,7 @@
         <v>4866</v>
       </c>
       <c r="B4868">
-        <v>-1</v>
+        <v>11.01031228660917</v>
       </c>
     </row>
     <row r="4869" spans="1:2">
@@ -39323,7 +39323,7 @@
         <v>4867</v>
       </c>
       <c r="B4869">
-        <v>-1</v>
+        <v>18.10936151238203</v>
       </c>
     </row>
     <row r="4870" spans="1:2">
@@ -39331,7 +39331,7 @@
         <v>4868</v>
       </c>
       <c r="B4870">
-        <v>-1</v>
+        <v>10.79415387497151</v>
       </c>
     </row>
     <row r="4871" spans="1:2">
@@ -39459,7 +39459,7 @@
         <v>4884</v>
       </c>
       <c r="B4886">
-        <v>-1</v>
+        <v>11.01913707022618</v>
       </c>
     </row>
     <row r="4887" spans="1:2">
@@ -39467,7 +39467,7 @@
         <v>4885</v>
       </c>
       <c r="B4887">
-        <v>-1</v>
+        <v>18.14796143393386</v>
       </c>
     </row>
     <row r="4888" spans="1:2">
@@ -39475,7 +39475,7 @@
         <v>4886</v>
       </c>
       <c r="B4888">
-        <v>-1</v>
+        <v>10.80141199556365</v>
       </c>
     </row>
     <row r="4889" spans="1:2">
@@ -39915,7 +39915,7 @@
         <v>4941</v>
       </c>
       <c r="B4943">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4944" spans="1:2">
@@ -39923,7 +39923,7 @@
         <v>4942</v>
       </c>
       <c r="B4944">
-        <v>-1</v>
+        <v>3.483543295804803</v>
       </c>
     </row>
     <row r="4945" spans="1:2">
@@ -39931,7 +39931,7 @@
         <v>4943</v>
       </c>
       <c r="B4945">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4946" spans="1:2">
@@ -40059,7 +40059,7 @@
         <v>4959</v>
       </c>
       <c r="B4961">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4962" spans="1:2">
@@ -40067,7 +40067,7 @@
         <v>4960</v>
       </c>
       <c r="B4962">
-        <v>-1</v>
+        <v>3.4492349918956</v>
       </c>
     </row>
     <row r="4963" spans="1:2">
@@ -40075,7 +40075,7 @@
         <v>4961</v>
       </c>
       <c r="B4963">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4964" spans="1:2">
@@ -40467,7 +40467,7 @@
         <v>5010</v>
       </c>
       <c r="B5012">
-        <v>-1</v>
+        <v>8.595733932638449</v>
       </c>
     </row>
     <row r="5013" spans="1:2">
@@ -40475,7 +40475,7 @@
         <v>5011</v>
       </c>
       <c r="B5013">
-        <v>-1</v>
+        <v>10.77553925319082</v>
       </c>
     </row>
     <row r="5014" spans="1:2">
@@ -40483,7 +40483,7 @@
         <v>5012</v>
       </c>
       <c r="B5014">
-        <v>-1</v>
+        <v>8.716551734864176</v>
       </c>
     </row>
     <row r="5015" spans="1:2">
@@ -40491,7 +40491,7 @@
         <v>5013</v>
       </c>
       <c r="B5015">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5016" spans="1:2">
@@ -40499,7 +40499,7 @@
         <v>5014</v>
       </c>
       <c r="B5016">
-        <v>-1</v>
+        <v>3.437070203318493</v>
       </c>
     </row>
     <row r="5017" spans="1:2">
@@ -40507,7 +40507,7 @@
         <v>5015</v>
       </c>
       <c r="B5017">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5018" spans="1:2">
@@ -40515,7 +40515,7 @@
         <v>5016</v>
       </c>
       <c r="B5018">
-        <v>-1</v>
+        <v>3.392031457296563</v>
       </c>
     </row>
     <row r="5019" spans="1:2">
@@ -40523,7 +40523,7 @@
         <v>5017</v>
       </c>
       <c r="B5019">
-        <v>-1</v>
+        <v>4.124255294973944</v>
       </c>
     </row>
     <row r="5020" spans="1:2">
@@ -40531,7 +40531,7 @@
         <v>5018</v>
       </c>
       <c r="B5020">
-        <v>-1</v>
+        <v>3.392031457296563</v>
       </c>
     </row>
     <row r="5021" spans="1:2">
@@ -40923,7 +40923,7 @@
         <v>5067</v>
       </c>
       <c r="B5069">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5070" spans="1:2">
@@ -40931,7 +40931,7 @@
         <v>5068</v>
       </c>
       <c r="B5070">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5071" spans="1:2">
@@ -40939,7 +40939,7 @@
         <v>5069</v>
       </c>
       <c r="B5071">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5072" spans="1:2">
@@ -41211,7 +41211,7 @@
         <v>5103</v>
       </c>
       <c r="B5105">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5106" spans="1:2">
@@ -41219,7 +41219,7 @@
         <v>5104</v>
       </c>
       <c r="B5106">
-        <v>-1</v>
+        <v>4.792376541172805</v>
       </c>
     </row>
     <row r="5107" spans="1:2">
@@ -41227,7 +41227,7 @@
         <v>5105</v>
       </c>
       <c r="B5107">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5108" spans="1:2">
@@ -41403,7 +41403,7 @@
         <v>5127</v>
       </c>
       <c r="B5129">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5130" spans="1:2">
@@ -41411,7 +41411,7 @@
         <v>5128</v>
       </c>
       <c r="B5130">
-        <v>-1</v>
+        <v>10.10616957829403</v>
       </c>
     </row>
     <row r="5131" spans="1:2">
@@ -41419,7 +41419,7 @@
         <v>5129</v>
       </c>
       <c r="B5131">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5132" spans="1:2">
@@ -41619,7 +41619,7 @@
         <v>5154</v>
       </c>
       <c r="B5156">
-        <v>-1</v>
+        <v>11.00547641878097</v>
       </c>
     </row>
     <row r="5157" spans="1:2">
@@ -41627,7 +41627,7 @@
         <v>5155</v>
       </c>
       <c r="B5157">
-        <v>-1</v>
+        <v>18.88378324132218</v>
       </c>
     </row>
     <row r="5158" spans="1:2">
@@ -41635,7 +41635,7 @@
         <v>5156</v>
       </c>
       <c r="B5158">
-        <v>-1</v>
+        <v>10.83133609787009</v>
       </c>
     </row>
     <row r="5159" spans="1:2">
@@ -42363,7 +42363,7 @@
         <v>5247</v>
       </c>
       <c r="B5249">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5250" spans="1:2">
@@ -42371,7 +42371,7 @@
         <v>5248</v>
       </c>
       <c r="B5250">
-        <v>-1</v>
+        <v>3.970625055246768</v>
       </c>
     </row>
     <row r="5251" spans="1:2">
@@ -42379,7 +42379,7 @@
         <v>5249</v>
       </c>
       <c r="B5251">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5252" spans="1:2">
@@ -42795,7 +42795,7 @@
         <v>5301</v>
       </c>
       <c r="B5303">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5304" spans="1:2">
@@ -42803,7 +42803,7 @@
         <v>5302</v>
       </c>
       <c r="B5304">
-        <v>-1</v>
+        <v>3.988514296906887</v>
       </c>
     </row>
     <row r="5305" spans="1:2">
@@ -42811,7 +42811,7 @@
         <v>5303</v>
       </c>
       <c r="B5305">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5306" spans="1:2">
@@ -43131,7 +43131,7 @@
         <v>5343</v>
       </c>
       <c r="B5345">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5346" spans="1:2">
@@ -43139,7 +43139,7 @@
         <v>5344</v>
       </c>
       <c r="B5346">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5347" spans="1:2">
@@ -43147,7 +43147,7 @@
         <v>5345</v>
       </c>
       <c r="B5347">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5348" spans="1:2">
@@ -43251,7 +43251,7 @@
         <v>5358</v>
       </c>
       <c r="B5360">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5361" spans="1:2">
@@ -43259,7 +43259,7 @@
         <v>5359</v>
       </c>
       <c r="B5361">
-        <v>-1</v>
+        <v>112.3813279661145</v>
       </c>
     </row>
     <row r="5362" spans="1:2">
@@ -43267,7 +43267,7 @@
         <v>5360</v>
       </c>
       <c r="B5362">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5363" spans="1:2">
@@ -43467,7 +43467,7 @@
         <v>5385</v>
       </c>
       <c r="B5387">
-        <v>-1</v>
+        <v>3.883273771148532</v>
       </c>
     </row>
     <row r="5388" spans="1:2">
@@ -43475,7 +43475,7 @@
         <v>5386</v>
       </c>
       <c r="B5388">
-        <v>-1</v>
+        <v>13.28700114663947</v>
       </c>
     </row>
     <row r="5389" spans="1:2">
@@ -43483,7 +43483,7 @@
         <v>5387</v>
       </c>
       <c r="B5389">
-        <v>-1</v>
+        <v>3.804706132461344</v>
       </c>
     </row>
     <row r="5390" spans="1:2">
@@ -43659,7 +43659,7 @@
         <v>5409</v>
       </c>
       <c r="B5411">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5412" spans="1:2">
@@ -43667,7 +43667,7 @@
         <v>5410</v>
       </c>
       <c r="B5412">
-        <v>-1</v>
+        <v>96.79940770359576</v>
       </c>
     </row>
     <row r="5413" spans="1:2">
@@ -43675,7 +43675,7 @@
         <v>5411</v>
       </c>
       <c r="B5413">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5414" spans="1:2">
@@ -44379,7 +44379,7 @@
         <v>5499</v>
       </c>
       <c r="B5501">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5502" spans="1:2">
@@ -44387,7 +44387,7 @@
         <v>5500</v>
       </c>
       <c r="B5502">
-        <v>-1</v>
+        <v>4.085452167396719</v>
       </c>
     </row>
     <row r="5503" spans="1:2">
@@ -44395,7 +44395,7 @@
         <v>5501</v>
       </c>
       <c r="B5503">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5504" spans="1:2">
@@ -44523,7 +44523,7 @@
         <v>5517</v>
       </c>
       <c r="B5519">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5520" spans="1:2">
@@ -44531,7 +44531,7 @@
         <v>5518</v>
       </c>
       <c r="B5520">
-        <v>-1</v>
+        <v>3.988932433986803</v>
       </c>
     </row>
     <row r="5521" spans="1:2">
@@ -44539,7 +44539,7 @@
         <v>5519</v>
       </c>
       <c r="B5521">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5522" spans="1:2">
@@ -44571,7 +44571,7 @@
         <v>5523</v>
       </c>
       <c r="B5525">
-        <v>-1</v>
+        <v>7.592750520398406</v>
       </c>
     </row>
     <row r="5526" spans="1:2">
@@ -44579,7 +44579,7 @@
         <v>5524</v>
       </c>
       <c r="B5526">
-        <v>-1</v>
+        <v>19.63634508189686</v>
       </c>
     </row>
     <row r="5527" spans="1:2">
@@ -44587,7 +44587,7 @@
         <v>5525</v>
       </c>
       <c r="B5527">
-        <v>-1</v>
+        <v>7.592750520398406</v>
       </c>
     </row>
     <row r="5528" spans="1:2">
@@ -44595,7 +44595,7 @@
         <v>5526</v>
       </c>
       <c r="B5528">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5529" spans="1:2">
@@ -44603,7 +44603,7 @@
         <v>5527</v>
       </c>
       <c r="B5529">
-        <v>-1</v>
+        <v>3.875497194445576</v>
       </c>
     </row>
     <row r="5530" spans="1:2">
@@ -44611,7 +44611,7 @@
         <v>5528</v>
       </c>
       <c r="B5530">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5531" spans="1:2">
@@ -44667,7 +44667,7 @@
         <v>5535</v>
       </c>
       <c r="B5537">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5538" spans="1:2">
@@ -44675,7 +44675,7 @@
         <v>5536</v>
       </c>
       <c r="B5538">
-        <v>-1</v>
+        <v>4.723645531081178</v>
       </c>
     </row>
     <row r="5539" spans="1:2">
@@ -44683,7 +44683,7 @@
         <v>5537</v>
       </c>
       <c r="B5539">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5540" spans="1:2">
@@ -44811,7 +44811,7 @@
         <v>5553</v>
       </c>
       <c r="B5555">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5556" spans="1:2">
@@ -44819,7 +44819,7 @@
         <v>5554</v>
       </c>
       <c r="B5556">
-        <v>-1</v>
+        <v>3.785428186829276</v>
       </c>
     </row>
     <row r="5557" spans="1:2">
@@ -44827,7 +44827,7 @@
         <v>5555</v>
       </c>
       <c r="B5557">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5558" spans="1:2">
@@ -44859,7 +44859,7 @@
         <v>5559</v>
       </c>
       <c r="B5561">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5562" spans="1:2">
@@ -44867,7 +44867,7 @@
         <v>5560</v>
       </c>
       <c r="B5562">
-        <v>-1</v>
+        <v>11.64598057051092</v>
       </c>
     </row>
     <row r="5563" spans="1:2">
@@ -44875,7 +44875,7 @@
         <v>5561</v>
       </c>
       <c r="B5563">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5564" spans="1:2">
@@ -44931,7 +44931,7 @@
         <v>5568</v>
       </c>
       <c r="B5570">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5571" spans="1:2">
@@ -44939,7 +44939,7 @@
         <v>5569</v>
       </c>
       <c r="B5571">
-        <v>-1</v>
+        <v>6.495276067296507</v>
       </c>
     </row>
     <row r="5572" spans="1:2">
@@ -44947,7 +44947,7 @@
         <v>5570</v>
       </c>
       <c r="B5572">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5573" spans="1:2">
@@ -44955,7 +44955,7 @@
         <v>5571</v>
       </c>
       <c r="B5573">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5574" spans="1:2">
@@ -44963,7 +44963,7 @@
         <v>5572</v>
       </c>
       <c r="B5574">
-        <v>-1</v>
+        <v>4.326642054485386</v>
       </c>
     </row>
     <row r="5575" spans="1:2">
@@ -44971,7 +44971,7 @@
         <v>5573</v>
       </c>
       <c r="B5575">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5576" spans="1:2">
@@ -45027,7 +45027,7 @@
         <v>5580</v>
       </c>
       <c r="B5582">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5583" spans="1:2">
@@ -45035,7 +45035,7 @@
         <v>5581</v>
       </c>
       <c r="B5583">
-        <v>-1</v>
+        <v>4.024714468140489</v>
       </c>
     </row>
     <row r="5584" spans="1:2">
@@ -45043,7 +45043,7 @@
         <v>5582</v>
       </c>
       <c r="B5584">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5585" spans="1:2">
@@ -45675,7 +45675,7 @@
         <v>5661</v>
       </c>
       <c r="B5663">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5664" spans="1:2">
@@ -45683,7 +45683,7 @@
         <v>5662</v>
       </c>
       <c r="B5664">
-        <v>-1</v>
+        <v>97.04930268102035</v>
       </c>
     </row>
     <row r="5665" spans="1:2">
@@ -45691,7 +45691,7 @@
         <v>5663</v>
       </c>
       <c r="B5665">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5666" spans="1:2">
@@ -46011,7 +46011,7 @@
         <v>5703</v>
       </c>
       <c r="B5705">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5706" spans="1:2">
@@ -46019,7 +46019,7 @@
         <v>5704</v>
       </c>
       <c r="B5706">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5707" spans="1:2">
@@ -46027,7 +46027,7 @@
         <v>5705</v>
       </c>
       <c r="B5707">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5708" spans="1:2">
@@ -47379,7 +47379,7 @@
         <v>5874</v>
       </c>
       <c r="B5876">
-        <v>-1</v>
+        <v>7.80532651836291</v>
       </c>
     </row>
     <row r="5877" spans="1:2">
@@ -47387,7 +47387,7 @@
         <v>5875</v>
       </c>
       <c r="B5877">
-        <v>-1</v>
+        <v>9.919152681981803</v>
       </c>
     </row>
     <row r="5878" spans="1:2">
@@ -47395,7 +47395,7 @@
         <v>5876</v>
       </c>
       <c r="B5878">
-        <v>-1</v>
+        <v>7.891898670967179</v>
       </c>
     </row>
     <row r="5879" spans="1:2">
@@ -47403,7 +47403,7 @@
         <v>5877</v>
       </c>
       <c r="B5879">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5880" spans="1:2">
@@ -47411,7 +47411,7 @@
         <v>5878</v>
       </c>
       <c r="B5880">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5881" spans="1:2">
@@ -47419,7 +47419,7 @@
         <v>5879</v>
       </c>
       <c r="B5881">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5882" spans="1:2">
@@ -47715,7 +47715,7 @@
         <v>5916</v>
       </c>
       <c r="B5918">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5919" spans="1:2">
@@ -47723,7 +47723,7 @@
         <v>5917</v>
       </c>
       <c r="B5919">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5920" spans="1:2">
@@ -47731,7 +47731,7 @@
         <v>5918</v>
       </c>
       <c r="B5920">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5921" spans="1:2">
@@ -47811,7 +47811,7 @@
         <v>5928</v>
       </c>
       <c r="B5930">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5931" spans="1:2">
@@ -47819,7 +47819,7 @@
         <v>5929</v>
       </c>
       <c r="B5931">
-        <v>-1</v>
+        <v>4.576998487800143</v>
       </c>
     </row>
     <row r="5932" spans="1:2">
@@ -47827,7 +47827,7 @@
         <v>5930</v>
       </c>
       <c r="B5932">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5933" spans="1:2">
@@ -48219,7 +48219,7 @@
         <v>5979</v>
       </c>
       <c r="B5981">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5982" spans="1:2">
@@ -48227,7 +48227,7 @@
         <v>5980</v>
       </c>
       <c r="B5982">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5983" spans="1:2">
@@ -48235,7 +48235,7 @@
         <v>5981</v>
       </c>
       <c r="B5983">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5984" spans="1:2">
@@ -48243,7 +48243,7 @@
         <v>5982</v>
       </c>
       <c r="B5984">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5985" spans="1:2">
@@ -48251,7 +48251,7 @@
         <v>5983</v>
       </c>
       <c r="B5985">
-        <v>-1</v>
+        <v>6.561794027999712</v>
       </c>
     </row>
     <row r="5986" spans="1:2">
@@ -48259,7 +48259,7 @@
         <v>5984</v>
       </c>
       <c r="B5986">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5987" spans="1:2">
@@ -48267,7 +48267,7 @@
         <v>5985</v>
       </c>
       <c r="B5987">
-        <v>-1</v>
+        <v>3.323806533686269</v>
       </c>
     </row>
     <row r="5988" spans="1:2">
@@ -48275,7 +48275,7 @@
         <v>5986</v>
       </c>
       <c r="B5988">
-        <v>-1</v>
+        <v>3.324292263028372</v>
       </c>
     </row>
     <row r="5989" spans="1:2">
@@ -48283,7 +48283,7 @@
         <v>5987</v>
       </c>
       <c r="B5989">
-        <v>-1</v>
+        <v>3.323806533686269</v>
       </c>
     </row>
     <row r="5990" spans="1:2">
@@ -48363,7 +48363,7 @@
         <v>5997</v>
       </c>
       <c r="B5999">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6000" spans="1:2">
@@ -48371,7 +48371,7 @@
         <v>5998</v>
       </c>
       <c r="B6000">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6001" spans="1:2">
@@ -48379,7 +48379,7 @@
         <v>5999</v>
       </c>
       <c r="B6001">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6002" spans="1:2">
@@ -48387,7 +48387,7 @@
         <v>6000</v>
       </c>
       <c r="B6002">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6003" spans="1:2">
@@ -48395,7 +48395,7 @@
         <v>6001</v>
       </c>
       <c r="B6003">
-        <v>-1</v>
+        <v>6.598961985655427</v>
       </c>
     </row>
     <row r="6004" spans="1:2">
@@ -48403,7 +48403,7 @@
         <v>6002</v>
       </c>
       <c r="B6004">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6005" spans="1:2">
@@ -48483,7 +48483,7 @@
         <v>6012</v>
       </c>
       <c r="B6014">
-        <v>-1</v>
+        <v>3.461678681683078</v>
       </c>
     </row>
     <row r="6015" spans="1:2">
@@ -48491,7 +48491,7 @@
         <v>6013</v>
       </c>
       <c r="B6015">
-        <v>-1</v>
+        <v>4.716812557195804</v>
       </c>
     </row>
     <row r="6016" spans="1:2">
@@ -48499,7 +48499,7 @@
         <v>6014</v>
       </c>
       <c r="B6016">
-        <v>-1</v>
+        <v>3.316900313546611</v>
       </c>
     </row>
     <row r="6017" spans="1:2">
@@ -48507,7 +48507,7 @@
         <v>6015</v>
       </c>
       <c r="B6017">
-        <v>-1</v>
+        <v>4.19646712822016</v>
       </c>
     </row>
     <row r="6018" spans="1:2">
@@ -48515,7 +48515,7 @@
         <v>6016</v>
       </c>
       <c r="B6018">
-        <v>-1</v>
+        <v>7.168068768416946</v>
       </c>
     </row>
     <row r="6019" spans="1:2">
@@ -48523,7 +48523,7 @@
         <v>6017</v>
       </c>
       <c r="B6019">
-        <v>-1</v>
+        <v>4.182939871275937</v>
       </c>
     </row>
     <row r="6020" spans="1:2">
@@ -48891,7 +48891,7 @@
         <v>6063</v>
       </c>
       <c r="B6065">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6066" spans="1:2">
@@ -48899,7 +48899,7 @@
         <v>6064</v>
       </c>
       <c r="B6066">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6067" spans="1:2">
@@ -48907,7 +48907,7 @@
         <v>6065</v>
       </c>
       <c r="B6067">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6068" spans="1:2">
@@ -49035,7 +49035,7 @@
         <v>6081</v>
       </c>
       <c r="B6083">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6084" spans="1:2">
@@ -49043,7 +49043,7 @@
         <v>6082</v>
       </c>
       <c r="B6084">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6085" spans="1:2">
@@ -49051,7 +49051,7 @@
         <v>6083</v>
       </c>
       <c r="B6085">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6086" spans="1:2">
@@ -49395,7 +49395,7 @@
         <v>6126</v>
       </c>
       <c r="B6128">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6129" spans="1:2">
@@ -49403,7 +49403,7 @@
         <v>6127</v>
       </c>
       <c r="B6129">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6130" spans="1:2">
@@ -49411,7 +49411,7 @@
         <v>6128</v>
       </c>
       <c r="B6130">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6131" spans="1:2">
@@ -49419,7 +49419,7 @@
         <v>6129</v>
       </c>
       <c r="B6131">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6132" spans="1:2">
@@ -49427,7 +49427,7 @@
         <v>6130</v>
       </c>
       <c r="B6132">
-        <v>-1</v>
+        <v>3.499764616283274</v>
       </c>
     </row>
     <row r="6133" spans="1:2">
@@ -49435,7 +49435,7 @@
         <v>6131</v>
       </c>
       <c r="B6133">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6134" spans="1:2">
@@ -49443,7 +49443,7 @@
         <v>6132</v>
       </c>
       <c r="B6134">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6135" spans="1:2">
@@ -49451,7 +49451,7 @@
         <v>6133</v>
       </c>
       <c r="B6135">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6136" spans="1:2">
@@ -49459,7 +49459,7 @@
         <v>6134</v>
       </c>
       <c r="B6136">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6137" spans="1:2">
@@ -49635,7 +49635,7 @@
         <v>6156</v>
       </c>
       <c r="B6158">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6159" spans="1:2">
@@ -49643,7 +49643,7 @@
         <v>6157</v>
       </c>
       <c r="B6159">
-        <v>-1</v>
+        <v>3.55139837679217</v>
       </c>
     </row>
     <row r="6160" spans="1:2">
@@ -49651,7 +49651,7 @@
         <v>6158</v>
       </c>
       <c r="B6160">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6161" spans="1:2">
@@ -49659,7 +49659,7 @@
         <v>6159</v>
       </c>
       <c r="B6161">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="6162" spans="1:2">
@@ -49667,7 +49667,7 @@
         <v>6160</v>
       </c>
       <c r="B6162">
-        <v>-1</v>
+        <v>3.991578423060227</v>
       </c>
     </row>
     <row r="6163" spans="1:2">
@@ -49675,7 +49675,7 @@
         <v>6161</v>
       </c>
       <c r="B6163">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6164" spans="1:2">
@@ -49683,7 +49683,7 @@
         <v>6162</v>
       </c>
       <c r="B6164">
-        <v>-1</v>
+        <v>8.047881289345904</v>
       </c>
     </row>
     <row r="6165" spans="1:2">
@@ -49691,7 +49691,7 @@
         <v>6163</v>
       </c>
       <c r="B6165">
-        <v>-1</v>
+        <v>10.85646624992092</v>
       </c>
     </row>
     <row r="6166" spans="1:2">
@@ -49699,7 +49699,7 @@
         <v>6164</v>
       </c>
       <c r="B6166">
-        <v>-1</v>
+        <v>8.290328911545863</v>
       </c>
     </row>
     <row r="6167" spans="1:2">
@@ -49707,7 +49707,7 @@
         <v>6165</v>
       </c>
       <c r="B6167">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6168" spans="1:2">
@@ -49715,7 +49715,7 @@
         <v>6166</v>
       </c>
       <c r="B6168">
-        <v>-1</v>
+        <v>3.48853313041102</v>
       </c>
     </row>
     <row r="6169" spans="1:2">
@@ -49723,7 +49723,7 @@
         <v>6167</v>
       </c>
       <c r="B6169">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6170" spans="1:2">
@@ -49731,7 +49731,7 @@
         <v>6168</v>
       </c>
       <c r="B6170">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6171" spans="1:2">
@@ -49739,7 +49739,7 @@
         <v>6169</v>
       </c>
       <c r="B6171">
-        <v>-1</v>
+        <v>3.858791972667297</v>
       </c>
     </row>
     <row r="6172" spans="1:2">
@@ -49747,7 +49747,7 @@
         <v>6170</v>
       </c>
       <c r="B6172">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6173" spans="1:2">
@@ -49779,7 +49779,7 @@
         <v>6174</v>
       </c>
       <c r="B6176">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6177" spans="1:2">
@@ -49787,7 +49787,7 @@
         <v>6175</v>
       </c>
       <c r="B6177">
-        <v>-1</v>
+        <v>3.527412585509548</v>
       </c>
     </row>
     <row r="6178" spans="1:2">
@@ -49795,7 +49795,7 @@
         <v>6176</v>
       </c>
       <c r="B6178">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6179" spans="1:2">
@@ -50499,7 +50499,7 @@
         <v>6264</v>
       </c>
       <c r="B6266">
-        <v>-1</v>
+        <v>3.392710508144559</v>
       </c>
     </row>
     <row r="6267" spans="1:2">
@@ -50507,7 +50507,7 @@
         <v>6265</v>
       </c>
       <c r="B6267">
-        <v>-1</v>
+        <v>3.375876044064086</v>
       </c>
     </row>
     <row r="6268" spans="1:2">
@@ -50515,7 +50515,7 @@
         <v>6266</v>
       </c>
       <c r="B6268">
-        <v>-1</v>
+        <v>3.442644482465473</v>
       </c>
     </row>
     <row r="6269" spans="1:2">
@@ -50547,7 +50547,7 @@
         <v>6270</v>
       </c>
       <c r="B6272">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6273" spans="1:2">
@@ -50555,7 +50555,7 @@
         <v>6271</v>
       </c>
       <c r="B6273">
-        <v>-1</v>
+        <v>9.044203876043621</v>
       </c>
     </row>
     <row r="6274" spans="1:2">
@@ -50563,7 +50563,7 @@
         <v>6272</v>
       </c>
       <c r="B6274">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6275" spans="1:2">
@@ -50571,7 +50571,7 @@
         <v>6273</v>
       </c>
       <c r="B6275">
-        <v>-1</v>
+        <v>3.442644482465473</v>
       </c>
     </row>
     <row r="6276" spans="1:2">
@@ -50579,7 +50579,7 @@
         <v>6274</v>
       </c>
       <c r="B6276">
-        <v>-1</v>
+        <v>3.416241578923551</v>
       </c>
     </row>
     <row r="6277" spans="1:2">
@@ -50587,7 +50587,7 @@
         <v>6275</v>
       </c>
       <c r="B6277">
-        <v>-1</v>
+        <v>3.442644482465473</v>
       </c>
     </row>
     <row r="6278" spans="1:2">
@@ -51867,7 +51867,7 @@
         <v>6435</v>
       </c>
       <c r="B6437">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6438" spans="1:2">
@@ -51875,7 +51875,7 @@
         <v>6436</v>
       </c>
       <c r="B6438">
-        <v>-1</v>
+        <v>3.785246680124188</v>
       </c>
     </row>
     <row r="6439" spans="1:2">
@@ -51883,7 +51883,7 @@
         <v>6437</v>
       </c>
       <c r="B6439">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6440" spans="1:2">
@@ -51939,7 +51939,7 @@
         <v>6444</v>
       </c>
       <c r="B6446">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6447" spans="1:2">
@@ -51947,7 +51947,7 @@
         <v>6445</v>
       </c>
       <c r="B6447">
-        <v>-1</v>
+        <v>3.471915804574688</v>
       </c>
     </row>
     <row r="6448" spans="1:2">
@@ -51955,7 +51955,7 @@
         <v>6446</v>
       </c>
       <c r="B6448">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6449" spans="1:2">
@@ -52011,7 +52011,7 @@
         <v>6453</v>
       </c>
       <c r="B6455">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6456" spans="1:2">
@@ -52019,7 +52019,7 @@
         <v>6454</v>
       </c>
       <c r="B6456">
-        <v>-1</v>
+        <v>3.671154510358055</v>
       </c>
     </row>
     <row r="6457" spans="1:2">
@@ -52027,7 +52027,7 @@
         <v>6455</v>
       </c>
       <c r="B6457">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6458" spans="1:2">
@@ -52059,7 +52059,7 @@
         <v>6459</v>
       </c>
       <c r="B6461">
-        <v>-1</v>
+        <v>7.931061446909793</v>
       </c>
     </row>
     <row r="6462" spans="1:2">
@@ -52067,7 +52067,7 @@
         <v>6460</v>
       </c>
       <c r="B6462">
-        <v>-1</v>
+        <v>21.9905380120823</v>
       </c>
     </row>
     <row r="6463" spans="1:2">
@@ -52075,7 +52075,7 @@
         <v>6461</v>
       </c>
       <c r="B6463">
-        <v>-1</v>
+        <v>7.931061446909793</v>
       </c>
     </row>
     <row r="6464" spans="1:2">
@@ -52419,7 +52419,7 @@
         <v>6504</v>
       </c>
       <c r="B6506">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6507" spans="1:2">
@@ -52427,7 +52427,7 @@
         <v>6505</v>
       </c>
       <c r="B6507">
-        <v>-1</v>
+        <v>31.54361766441597</v>
       </c>
     </row>
     <row r="6508" spans="1:2">
@@ -52435,7 +52435,7 @@
         <v>6506</v>
       </c>
       <c r="B6508">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6509" spans="1:2">
@@ -52659,7 +52659,7 @@
         <v>6534</v>
       </c>
       <c r="B6536">
-        <v>-1</v>
+        <v>3.480518962029167</v>
       </c>
     </row>
     <row r="6537" spans="1:2">
@@ -52667,7 +52667,7 @@
         <v>6535</v>
       </c>
       <c r="B6537">
-        <v>-1</v>
+        <v>7.124811869075542</v>
       </c>
     </row>
     <row r="6538" spans="1:2">
@@ -52675,7 +52675,7 @@
         <v>6536</v>
       </c>
       <c r="B6538">
-        <v>-1</v>
+        <v>3.348031984629474</v>
       </c>
     </row>
     <row r="6539" spans="1:2">
@@ -52803,7 +52803,7 @@
         <v>6552</v>
       </c>
       <c r="B6554">
-        <v>-1</v>
+        <v>3.454734085584854</v>
       </c>
     </row>
     <row r="6555" spans="1:2">
@@ -52811,7 +52811,7 @@
         <v>6553</v>
       </c>
       <c r="B6555">
-        <v>-1</v>
+        <v>4.678036601770319</v>
       </c>
     </row>
     <row r="6556" spans="1:2">
@@ -52819,7 +52819,7 @@
         <v>6554</v>
       </c>
       <c r="B6556">
-        <v>-1</v>
+        <v>3.324511267223462</v>
       </c>
     </row>
     <row r="6557" spans="1:2">
@@ -52827,7 +52827,7 @@
         <v>6555</v>
       </c>
       <c r="B6557">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6558" spans="1:2">
@@ -52835,7 +52835,7 @@
         <v>6556</v>
       </c>
       <c r="B6558">
-        <v>-1</v>
+        <v>9.496507040091428</v>
       </c>
     </row>
     <row r="6559" spans="1:2">
@@ -52843,7 +52843,7 @@
         <v>6557</v>
       </c>
       <c r="B6559">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6560" spans="1:2">
@@ -53091,7 +53091,7 @@
         <v>6588</v>
       </c>
       <c r="B6590">
-        <v>-1</v>
+        <v>3.444489654763894</v>
       </c>
     </row>
     <row r="6591" spans="1:2">
@@ -53099,7 +53099,7 @@
         <v>6589</v>
       </c>
       <c r="B6591">
-        <v>-1</v>
+        <v>9.553112692586318</v>
       </c>
     </row>
     <row r="6592" spans="1:2">
@@ -53107,7 +53107,7 @@
         <v>6590</v>
       </c>
       <c r="B6592">
-        <v>-1</v>
+        <v>3.317608026906482</v>
       </c>
     </row>
     <row r="6593" spans="1:2">
@@ -53595,7 +53595,7 @@
         <v>6651</v>
       </c>
       <c r="B6653">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6654" spans="1:2">
@@ -53603,7 +53603,7 @@
         <v>6652</v>
       </c>
       <c r="B6654">
-        <v>-1</v>
+        <v>4.499048585233711</v>
       </c>
     </row>
     <row r="6655" spans="1:2">
@@ -53611,7 +53611,7 @@
         <v>6653</v>
       </c>
       <c r="B6655">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6656" spans="1:2">
@@ -53691,7 +53691,7 @@
         <v>6663</v>
       </c>
       <c r="B6665">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6666" spans="1:2">
@@ -53699,7 +53699,7 @@
         <v>6664</v>
       </c>
       <c r="B6666">
-        <v>-1</v>
+        <v>4.116606091059882</v>
       </c>
     </row>
     <row r="6667" spans="1:2">
@@ -53707,7 +53707,7 @@
         <v>6665</v>
       </c>
       <c r="B6667">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6668" spans="1:2">
@@ -53835,7 +53835,7 @@
         <v>6681</v>
       </c>
       <c r="B6683">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6684" spans="1:2">
@@ -53843,7 +53843,7 @@
         <v>6682</v>
       </c>
       <c r="B6684">
-        <v>-1</v>
+        <v>4.416037802959282</v>
       </c>
     </row>
     <row r="6685" spans="1:2">
@@ -53851,7 +53851,7 @@
         <v>6683</v>
       </c>
       <c r="B6685">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6686" spans="1:2">
@@ -54051,7 +54051,7 @@
         <v>6708</v>
       </c>
       <c r="B6710">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6711" spans="1:2">
@@ -54059,7 +54059,7 @@
         <v>6709</v>
       </c>
       <c r="B6711">
-        <v>-1</v>
+        <v>5.625512182878845</v>
       </c>
     </row>
     <row r="6712" spans="1:2">
@@ -54067,7 +54067,7 @@
         <v>6710</v>
       </c>
       <c r="B6712">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6713" spans="1:2">
@@ -54171,7 +54171,7 @@
         <v>6723</v>
       </c>
       <c r="B6725">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6726" spans="1:2">
@@ -54179,7 +54179,7 @@
         <v>6724</v>
       </c>
       <c r="B6726">
-        <v>-1</v>
+        <v>4.78748637099693</v>
       </c>
     </row>
     <row r="6727" spans="1:2">
@@ -54187,7 +54187,7 @@
         <v>6725</v>
       </c>
       <c r="B6727">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6728" spans="1:2">
@@ -54243,7 +54243,7 @@
         <v>6732</v>
       </c>
       <c r="B6734">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6735" spans="1:2">
@@ -54251,7 +54251,7 @@
         <v>6733</v>
       </c>
       <c r="B6735">
-        <v>-1</v>
+        <v>3.702763091841921</v>
       </c>
     </row>
     <row r="6736" spans="1:2">
@@ -54259,7 +54259,7 @@
         <v>6734</v>
       </c>
       <c r="B6736">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6737" spans="1:2">
@@ -54555,7 +54555,7 @@
         <v>6771</v>
       </c>
       <c r="B6773">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6774" spans="1:2">
@@ -54563,7 +54563,7 @@
         <v>6772</v>
       </c>
       <c r="B6774">
-        <v>-1</v>
+        <v>10.42734693685567</v>
       </c>
     </row>
     <row r="6775" spans="1:2">
@@ -54571,7 +54571,7 @@
         <v>6773</v>
       </c>
       <c r="B6775">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6776" spans="1:2">
@@ -55923,7 +55923,7 @@
         <v>6942</v>
       </c>
       <c r="B6944">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6945" spans="1:2">
@@ -55931,7 +55931,7 @@
         <v>6943</v>
       </c>
       <c r="B6945">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6946" spans="1:2">
@@ -55939,7 +55939,7 @@
         <v>6944</v>
       </c>
       <c r="B6946">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6947" spans="1:2">
@@ -56091,7 +56091,7 @@
         <v>6963</v>
       </c>
       <c r="B6965">
-        <v>-1</v>
+        <v>9.151457215023907</v>
       </c>
     </row>
     <row r="6966" spans="1:2">
@@ -56099,7 +56099,7 @@
         <v>6964</v>
       </c>
       <c r="B6966">
-        <v>-1</v>
+        <v>10.84655951971909</v>
       </c>
     </row>
     <row r="6967" spans="1:2">
@@ -56107,7 +56107,7 @@
         <v>6965</v>
       </c>
       <c r="B6967">
-        <v>-1</v>
+        <v>9.151457215023907</v>
       </c>
     </row>
     <row r="6968" spans="1:2">
@@ -56235,7 +56235,7 @@
         <v>6981</v>
       </c>
       <c r="B6983">
-        <v>-1</v>
+        <v>9.56895084627385</v>
       </c>
     </row>
     <row r="6984" spans="1:2">
@@ -56243,7 +56243,7 @@
         <v>6982</v>
       </c>
       <c r="B6984">
-        <v>-1</v>
+        <v>11.45962781318041</v>
       </c>
     </row>
     <row r="6985" spans="1:2">
@@ -56251,7 +56251,7 @@
         <v>6983</v>
       </c>
       <c r="B6985">
-        <v>-1</v>
+        <v>9.56895084627385</v>
       </c>
     </row>
     <row r="6986" spans="1:2">
@@ -57027,7 +57027,7 @@
         <v>7080</v>
       </c>
       <c r="B7082">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7083" spans="1:2">
@@ -57035,7 +57035,7 @@
         <v>7081</v>
       </c>
       <c r="B7083">
-        <v>-1</v>
+        <v>6.823967555058541</v>
       </c>
     </row>
     <row r="7084" spans="1:2">
@@ -57043,7 +57043,7 @@
         <v>7082</v>
       </c>
       <c r="B7084">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7085" spans="1:2">
@@ -57195,7 +57195,7 @@
         <v>7101</v>
       </c>
       <c r="B7103">
-        <v>-1</v>
+        <v>3.425609462173984</v>
       </c>
     </row>
     <row r="7104" spans="1:2">
@@ -57203,7 +57203,7 @@
         <v>7102</v>
       </c>
       <c r="B7104">
-        <v>-1</v>
+        <v>6.133262541706463</v>
       </c>
     </row>
     <row r="7105" spans="1:2">
@@ -57211,7 +57211,7 @@
         <v>7103</v>
       </c>
       <c r="B7105">
-        <v>-1</v>
+        <v>3.425609462173984</v>
       </c>
     </row>
     <row r="7106" spans="1:2">
@@ -57555,7 +57555,7 @@
         <v>7146</v>
       </c>
       <c r="B7148">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7149" spans="1:2">
@@ -57563,7 +57563,7 @@
         <v>7147</v>
       </c>
       <c r="B7149">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7150" spans="1:2">
@@ -57571,7 +57571,7 @@
         <v>7148</v>
       </c>
       <c r="B7150">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7151" spans="1:2">
@@ -57579,7 +57579,7 @@
         <v>7149</v>
       </c>
       <c r="B7151">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7152" spans="1:2">
@@ -57587,7 +57587,7 @@
         <v>7150</v>
       </c>
       <c r="B7152">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7153" spans="1:2">
@@ -57595,7 +57595,7 @@
         <v>7151</v>
       </c>
       <c r="B7153">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7154" spans="1:2">
@@ -57963,7 +57963,7 @@
         <v>7197</v>
       </c>
       <c r="B7199">
-        <v>-1</v>
+        <v>13.34140750783552</v>
       </c>
     </row>
     <row r="7200" spans="1:2">
@@ -57971,7 +57971,7 @@
         <v>7198</v>
       </c>
       <c r="B7200">
-        <v>-1</v>
+        <v>32.92762955754244</v>
       </c>
     </row>
     <row r="7201" spans="1:2">
@@ -57979,7 +57979,7 @@
         <v>7199</v>
       </c>
       <c r="B7201">
-        <v>-1</v>
+        <v>13.34140750783552</v>
       </c>
     </row>
     <row r="7202" spans="1:2">
@@ -58203,7 +58203,7 @@
         <v>7227</v>
       </c>
       <c r="B7229">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="7230" spans="1:2">
@@ -58211,7 +58211,7 @@
         <v>7228</v>
       </c>
       <c r="B7230">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7231" spans="1:2">
@@ -58219,7 +58219,7 @@
         <v>7229</v>
       </c>
       <c r="B7231">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="7232" spans="1:2">
@@ -58635,7 +58635,7 @@
         <v>7281</v>
       </c>
       <c r="B7283">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7284" spans="1:2">
@@ -58643,7 +58643,7 @@
         <v>7282</v>
       </c>
       <c r="B7284">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7285" spans="1:2">
@@ -58651,7 +58651,7 @@
         <v>7283</v>
       </c>
       <c r="B7285">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7286" spans="1:2">
@@ -58683,7 +58683,7 @@
         <v>7287</v>
       </c>
       <c r="B7289">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7290" spans="1:2">
@@ -58691,7 +58691,7 @@
         <v>7288</v>
       </c>
       <c r="B7290">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7291" spans="1:2">
@@ -58699,7 +58699,7 @@
         <v>7289</v>
       </c>
       <c r="B7291">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7292" spans="1:2">
@@ -58923,7 +58923,7 @@
         <v>7317</v>
       </c>
       <c r="B7319">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7320" spans="1:2">
@@ -58931,7 +58931,7 @@
         <v>7318</v>
       </c>
       <c r="B7320">
-        <v>-1</v>
+        <v>3.952953111237079</v>
       </c>
     </row>
     <row r="7321" spans="1:2">
@@ -58939,7 +58939,7 @@
         <v>7319</v>
       </c>
       <c r="B7321">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7322" spans="1:2">
@@ -59499,7 +59499,7 @@
         <v>7389</v>
       </c>
       <c r="B7391">
-        <v>-1</v>
+        <v>3.495757646334019</v>
       </c>
     </row>
     <row r="7392" spans="1:2">
@@ -59507,7 +59507,7 @@
         <v>7390</v>
       </c>
       <c r="B7392">
-        <v>-1</v>
+        <v>6.315444830541061</v>
       </c>
     </row>
     <row r="7393" spans="1:2">
@@ -59515,7 +59515,7 @@
         <v>7391</v>
       </c>
       <c r="B7393">
-        <v>-1</v>
+        <v>3.495757646334019</v>
       </c>
     </row>
     <row r="7394" spans="1:2">
@@ -60147,7 +60147,7 @@
         <v>7470</v>
       </c>
       <c r="B7472">
-        <v>-1</v>
+        <v>4.101657075121312</v>
       </c>
     </row>
     <row r="7473" spans="1:2">
@@ -60155,7 +60155,7 @@
         <v>7471</v>
       </c>
       <c r="B7473">
-        <v>-1</v>
+        <v>6.959817905396449</v>
       </c>
     </row>
     <row r="7474" spans="1:2">
@@ -60163,7 +60163,7 @@
         <v>7472</v>
       </c>
       <c r="B7474">
-        <v>-1</v>
+        <v>4.100177921256265</v>
       </c>
     </row>
     <row r="7475" spans="1:2">
@@ -61035,7 +61035,7 @@
         <v>7581</v>
       </c>
       <c r="B7583">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7584" spans="1:2">
@@ -61043,7 +61043,7 @@
         <v>7582</v>
       </c>
       <c r="B7584">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7585" spans="1:2">
@@ -61051,7 +61051,7 @@
         <v>7583</v>
       </c>
       <c r="B7585">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7586" spans="1:2">
@@ -61611,7 +61611,7 @@
         <v>7653</v>
       </c>
       <c r="B7655">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7656" spans="1:2">
@@ -61619,7 +61619,7 @@
         <v>7654</v>
       </c>
       <c r="B7656">
-        <v>-1</v>
+        <v>9.486791416302086</v>
       </c>
     </row>
     <row r="7657" spans="1:2">
@@ -61627,7 +61627,7 @@
         <v>7655</v>
       </c>
       <c r="B7657">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7658" spans="1:2">
@@ -62691,7 +62691,7 @@
         <v>7788</v>
       </c>
       <c r="B7790">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7791" spans="1:2">
@@ -62699,7 +62699,7 @@
         <v>7789</v>
       </c>
       <c r="B7791">
-        <v>-1</v>
+        <v>4.572637669216883</v>
       </c>
     </row>
     <row r="7792" spans="1:2">
@@ -62707,7 +62707,7 @@
         <v>7790</v>
       </c>
       <c r="B7792">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7793" spans="1:2">
@@ -62955,7 +62955,7 @@
         <v>7821</v>
       </c>
       <c r="B7823">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7824" spans="1:2">
@@ -62963,7 +62963,7 @@
         <v>7822</v>
       </c>
       <c r="B7824">
-        <v>-1</v>
+        <v>4.415683444234508</v>
       </c>
     </row>
     <row r="7825" spans="1:2">
@@ -62971,7 +62971,7 @@
         <v>7823</v>
       </c>
       <c r="B7825">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7826" spans="1:2">
@@ -63315,7 +63315,7 @@
         <v>7866</v>
       </c>
       <c r="B7868">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7869" spans="1:2">
@@ -63323,7 +63323,7 @@
         <v>7867</v>
       </c>
       <c r="B7869">
-        <v>-1</v>
+        <v>3.385910112112467</v>
       </c>
     </row>
     <row r="7870" spans="1:2">
@@ -63331,7 +63331,7 @@
         <v>7868</v>
       </c>
       <c r="B7870">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="7871" spans="1:2">
@@ -63339,7 +63339,7 @@
         <v>7869</v>
       </c>
       <c r="B7871">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="7872" spans="1:2">
@@ -63347,7 +63347,7 @@
         <v>7870</v>
       </c>
       <c r="B7872">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7873" spans="1:2">
@@ -63355,7 +63355,7 @@
         <v>7871</v>
       </c>
       <c r="B7873">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7874" spans="1:2">
@@ -63459,7 +63459,7 @@
         <v>7884</v>
       </c>
       <c r="B7886">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7887" spans="1:2">
@@ -63467,7 +63467,7 @@
         <v>7885</v>
       </c>
       <c r="B7887">
-        <v>-1</v>
+        <v>4.675489236094521</v>
       </c>
     </row>
     <row r="7888" spans="1:2">
@@ -63475,7 +63475,7 @@
         <v>7886</v>
       </c>
       <c r="B7888">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7889" spans="1:2">
@@ -63771,7 +63771,7 @@
         <v>7923</v>
       </c>
       <c r="B7925">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7926" spans="1:2">
@@ -63779,7 +63779,7 @@
         <v>7924</v>
       </c>
       <c r="B7926">
-        <v>-1</v>
+        <v>10.6242087119501</v>
       </c>
     </row>
     <row r="7927" spans="1:2">
@@ -63787,7 +63787,7 @@
         <v>7925</v>
       </c>
       <c r="B7927">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7928" spans="1:2">
@@ -65019,7 +65019,7 @@
         <v>8079</v>
       </c>
       <c r="B8081">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8082" spans="1:2">
@@ -65027,7 +65027,7 @@
         <v>8080</v>
       </c>
       <c r="B8082">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8083" spans="1:2">
@@ -65035,7 +65035,7 @@
         <v>8081</v>
       </c>
       <c r="B8083">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8084" spans="1:2">
@@ -65163,7 +65163,7 @@
         <v>8097</v>
       </c>
       <c r="B8099">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8100" spans="1:2">
@@ -65171,7 +65171,7 @@
         <v>8098</v>
       </c>
       <c r="B8100">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8101" spans="1:2">
@@ -65179,7 +65179,7 @@
         <v>8099</v>
       </c>
       <c r="B8101">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8102" spans="1:2">
@@ -65547,7 +65547,7 @@
         <v>8145</v>
       </c>
       <c r="B8147">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8148" spans="1:2">
@@ -65555,7 +65555,7 @@
         <v>8146</v>
       </c>
       <c r="B8148">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8149" spans="1:2">
@@ -65563,7 +65563,7 @@
         <v>8147</v>
       </c>
       <c r="B8149">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8150" spans="1:2">
@@ -65571,7 +65571,7 @@
         <v>8148</v>
       </c>
       <c r="B8150">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8151" spans="1:2">
@@ -65579,7 +65579,7 @@
         <v>8149</v>
       </c>
       <c r="B8151">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8152" spans="1:2">
@@ -65587,7 +65587,7 @@
         <v>8150</v>
       </c>
       <c r="B8152">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8153" spans="1:2">
@@ -65643,7 +65643,7 @@
         <v>8157</v>
       </c>
       <c r="B8159">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8160" spans="1:2">
@@ -65651,7 +65651,7 @@
         <v>8158</v>
       </c>
       <c r="B8160">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8161" spans="1:2">
@@ -65659,7 +65659,7 @@
         <v>8159</v>
       </c>
       <c r="B8161">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8162" spans="1:2">
@@ -65667,7 +65667,7 @@
         <v>8160</v>
       </c>
       <c r="B8162">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8163" spans="1:2">
@@ -65675,7 +65675,7 @@
         <v>8161</v>
       </c>
       <c r="B8163">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8164" spans="1:2">
@@ -65683,7 +65683,7 @@
         <v>8162</v>
       </c>
       <c r="B8164">
-        <v>-1</v>
+        <v>3.300000000000081</v>
       </c>
     </row>
     <row r="8165" spans="1:2">
@@ -65763,7 +65763,7 @@
         <v>8172</v>
       </c>
       <c r="B8174">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8175" spans="1:2">
@@ -65771,7 +65771,7 @@
         <v>8173</v>
       </c>
       <c r="B8175">
-        <v>-1</v>
+        <v>3.526398806682163</v>
       </c>
     </row>
     <row r="8176" spans="1:2">
@@ -65779,7 +65779,7 @@
         <v>8174</v>
       </c>
       <c r="B8176">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8177" spans="1:2">
@@ -65787,7 +65787,7 @@
         <v>8175</v>
       </c>
       <c r="B8177">
-        <v>-1</v>
+        <v>3.900024834575533</v>
       </c>
     </row>
     <row r="8178" spans="1:2">
@@ -65795,7 +65795,7 @@
         <v>8176</v>
       </c>
       <c r="B8178">
-        <v>-1</v>
+        <v>5.010173644835703</v>
       </c>
     </row>
     <row r="8179" spans="1:2">
@@ -65803,7 +65803,7 @@
         <v>8177</v>
       </c>
       <c r="B8179">
-        <v>-1</v>
+        <v>3.918093480514229</v>
       </c>
     </row>
     <row r="8180" spans="1:2">
@@ -66099,7 +66099,7 @@
         <v>8214</v>
       </c>
       <c r="B8216">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8217" spans="1:2">
@@ -66107,7 +66107,7 @@
         <v>8215</v>
       </c>
       <c r="B8217">
-        <v>-1</v>
+        <v>7.417130609058198</v>
       </c>
     </row>
     <row r="8218" spans="1:2">
@@ -66115,7 +66115,7 @@
         <v>8216</v>
       </c>
       <c r="B8218">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8219" spans="1:2">
@@ -66195,7 +66195,7 @@
         <v>8226</v>
       </c>
       <c r="B8228">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8229" spans="1:2">
@@ -66203,7 +66203,7 @@
         <v>8227</v>
       </c>
       <c r="B8229">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8230" spans="1:2">
@@ -66211,7 +66211,7 @@
         <v>8228</v>
       </c>
       <c r="B8230">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8231" spans="1:2">
@@ -66243,7 +66243,7 @@
         <v>8232</v>
       </c>
       <c r="B8234">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8235" spans="1:2">
@@ -66251,7 +66251,7 @@
         <v>8233</v>
       </c>
       <c r="B8235">
-        <v>-1</v>
+        <v>7.453991862950716</v>
       </c>
     </row>
     <row r="8236" spans="1:2">
@@ -66259,7 +66259,7 @@
         <v>8234</v>
       </c>
       <c r="B8236">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8237" spans="1:2">
@@ -66267,7 +66267,7 @@
         <v>8235</v>
       </c>
       <c r="B8237">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8238" spans="1:2">
@@ -66275,7 +66275,7 @@
         <v>8236</v>
       </c>
       <c r="B8238">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8239" spans="1:2">
@@ -66283,7 +66283,7 @@
         <v>8237</v>
       </c>
       <c r="B8239">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8240" spans="1:2">
@@ -66315,7 +66315,7 @@
         <v>8241</v>
       </c>
       <c r="B8243">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8244" spans="1:2">
@@ -66323,7 +66323,7 @@
         <v>8242</v>
       </c>
       <c r="B8244">
-        <v>-1</v>
+        <v>11.24737921963617</v>
       </c>
     </row>
     <row r="8245" spans="1:2">
@@ -66331,7 +66331,7 @@
         <v>8243</v>
       </c>
       <c r="B8245">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8246" spans="1:2">
@@ -66459,7 +66459,7 @@
         <v>8259</v>
       </c>
       <c r="B8261">
-        <v>-1</v>
+        <v>11.23724563798866</v>
       </c>
     </row>
     <row r="8262" spans="1:2">
@@ -66467,7 +66467,7 @@
         <v>8260</v>
       </c>
       <c r="B8262">
-        <v>-1</v>
+        <v>25.39580701868527</v>
       </c>
     </row>
     <row r="8263" spans="1:2">
@@ -66475,7 +66475,7 @@
         <v>8261</v>
       </c>
       <c r="B8263">
-        <v>-1</v>
+        <v>11.23724563798866</v>
       </c>
     </row>
     <row r="8264" spans="1:2">
@@ -66603,7 +66603,7 @@
         <v>8277</v>
       </c>
       <c r="B8279">
-        <v>-1</v>
+        <v>11.24350138819061</v>
       </c>
     </row>
     <row r="8280" spans="1:2">
@@ -66611,7 +66611,7 @@
         <v>8278</v>
       </c>
       <c r="B8280">
-        <v>-1</v>
+        <v>25.42197154647145</v>
       </c>
     </row>
     <row r="8281" spans="1:2">
@@ -66619,7 +66619,7 @@
         <v>8279</v>
       </c>
       <c r="B8281">
-        <v>-1</v>
+        <v>11.24350138819061</v>
       </c>
     </row>
     <row r="8282" spans="1:2">
@@ -66627,7 +66627,7 @@
         <v>8280</v>
       </c>
       <c r="B8282">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8283" spans="1:2">
@@ -66635,7 +66635,7 @@
         <v>8281</v>
       </c>
       <c r="B8283">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8284" spans="1:2">
@@ -66643,7 +66643,7 @@
         <v>8282</v>
       </c>
       <c r="B8284">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8285" spans="1:2">
@@ -66651,7 +66651,7 @@
         <v>8283</v>
       </c>
       <c r="B8285">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8286" spans="1:2">
@@ -66659,7 +66659,7 @@
         <v>8284</v>
       </c>
       <c r="B8286">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8287" spans="1:2">
@@ -66667,7 +66667,7 @@
         <v>8285</v>
       </c>
       <c r="B8287">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8288" spans="1:2">
@@ -66747,7 +66747,7 @@
         <v>8295</v>
       </c>
       <c r="B8297">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8298" spans="1:2">
@@ -66755,7 +66755,7 @@
         <v>8296</v>
       </c>
       <c r="B8298">
-        <v>-1</v>
+        <v>18.02245060227803</v>
       </c>
     </row>
     <row r="8299" spans="1:2">
@@ -66763,7 +66763,7 @@
         <v>8297</v>
       </c>
       <c r="B8299">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8300" spans="1:2">
@@ -66771,7 +66771,7 @@
         <v>8298</v>
       </c>
       <c r="B8300">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8301" spans="1:2">
@@ -66779,7 +66779,7 @@
         <v>8299</v>
       </c>
       <c r="B8301">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8302" spans="1:2">
@@ -66787,7 +66787,7 @@
         <v>8300</v>
       </c>
       <c r="B8302">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8303" spans="1:2">
@@ -66819,7 +66819,7 @@
         <v>8304</v>
       </c>
       <c r="B8306">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="8307" spans="1:2">
@@ -66827,7 +66827,7 @@
         <v>8305</v>
       </c>
       <c r="B8307">
-        <v>-1</v>
+        <v>11.7627166772594</v>
       </c>
     </row>
     <row r="8308" spans="1:2">
@@ -66835,7 +66835,7 @@
         <v>8306</v>
       </c>
       <c r="B8308">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8309" spans="1:2">
@@ -66891,7 +66891,7 @@
         <v>8313</v>
       </c>
       <c r="B8315">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8316" spans="1:2">
@@ -66899,7 +66899,7 @@
         <v>8314</v>
       </c>
       <c r="B8316">
-        <v>-1</v>
+        <v>18.05353139707464</v>
       </c>
     </row>
     <row r="8317" spans="1:2">
@@ -66907,7 +66907,7 @@
         <v>8315</v>
       </c>
       <c r="B8317">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8318" spans="1:2">
@@ -67059,7 +67059,7 @@
         <v>8334</v>
       </c>
       <c r="B8336">
-        <v>-1</v>
+        <v>4.057739681302208</v>
       </c>
     </row>
     <row r="8337" spans="1:2">
@@ -67067,7 +67067,7 @@
         <v>8335</v>
       </c>
       <c r="B8337">
-        <v>-1</v>
+        <v>6.728938543831708</v>
       </c>
     </row>
     <row r="8338" spans="1:2">
@@ -67075,7 +67075,7 @@
         <v>8336</v>
       </c>
       <c r="B8338">
-        <v>-1</v>
+        <v>4.072436967473426</v>
       </c>
     </row>
     <row r="8339" spans="1:2">
@@ -67227,7 +67227,7 @@
         <v>8355</v>
       </c>
       <c r="B8357">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8358" spans="1:2">
@@ -67235,7 +67235,7 @@
         <v>8356</v>
       </c>
       <c r="B8358">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8359" spans="1:2">
@@ -67243,7 +67243,7 @@
         <v>8357</v>
       </c>
       <c r="B8359">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8360" spans="1:2">
@@ -67251,7 +67251,7 @@
         <v>8358</v>
       </c>
       <c r="B8360">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8361" spans="1:2">
@@ -67259,7 +67259,7 @@
         <v>8359</v>
       </c>
       <c r="B8361">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8362" spans="1:2">
@@ -67267,7 +67267,7 @@
         <v>8360</v>
       </c>
       <c r="B8362">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="8363" spans="1:2">
@@ -67347,7 +67347,7 @@
         <v>8370</v>
       </c>
       <c r="B8372">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8373" spans="1:2">
@@ -67355,7 +67355,7 @@
         <v>8371</v>
       </c>
       <c r="B8373">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8374" spans="1:2">
@@ -67363,7 +67363,7 @@
         <v>8372</v>
       </c>
       <c r="B8374">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8375" spans="1:2">
@@ -67467,7 +67467,7 @@
         <v>8385</v>
       </c>
       <c r="B8387">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8388" spans="1:2">
@@ -67475,7 +67475,7 @@
         <v>8386</v>
       </c>
       <c r="B8388">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8389" spans="1:2">
@@ -67483,7 +67483,7 @@
         <v>8387</v>
       </c>
       <c r="B8389">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8390" spans="1:2">
@@ -67491,7 +67491,7 @@
         <v>8388</v>
       </c>
       <c r="B8390">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8391" spans="1:2">
@@ -67499,7 +67499,7 @@
         <v>8389</v>
       </c>
       <c r="B8391">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="8392" spans="1:2">
@@ -67507,7 +67507,7 @@
         <v>8390</v>
       </c>
       <c r="B8392">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8393" spans="1:2">
@@ -67635,7 +67635,7 @@
         <v>8406</v>
       </c>
       <c r="B8408">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8409" spans="1:2">
@@ -67643,7 +67643,7 @@
         <v>8407</v>
       </c>
       <c r="B8409">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8410" spans="1:2">
@@ -67651,7 +67651,7 @@
         <v>8408</v>
       </c>
       <c r="B8410">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8411" spans="1:2">
@@ -67779,7 +67779,7 @@
         <v>8424</v>
       </c>
       <c r="B8426">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8427" spans="1:2">
@@ -67787,7 +67787,7 @@
         <v>8425</v>
       </c>
       <c r="B8427">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8428" spans="1:2">
@@ -67795,7 +67795,7 @@
         <v>8426</v>
       </c>
       <c r="B8428">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8429" spans="1:2">
@@ -67851,7 +67851,7 @@
         <v>8433</v>
       </c>
       <c r="B8435">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8436" spans="1:2">
@@ -67859,7 +67859,7 @@
         <v>8434</v>
       </c>
       <c r="B8436">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8437" spans="1:2">
@@ -67867,7 +67867,7 @@
         <v>8435</v>
       </c>
       <c r="B8437">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8438" spans="1:2">
@@ -67923,7 +67923,7 @@
         <v>8442</v>
       </c>
       <c r="B8444">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8445" spans="1:2">
@@ -67931,7 +67931,7 @@
         <v>8443</v>
       </c>
       <c r="B8445">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8446" spans="1:2">
@@ -67939,7 +67939,7 @@
         <v>8444</v>
       </c>
       <c r="B8446">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8447" spans="1:2">
@@ -68067,7 +68067,7 @@
         <v>8460</v>
       </c>
       <c r="B8462">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8463" spans="1:2">
@@ -68075,7 +68075,7 @@
         <v>8461</v>
       </c>
       <c r="B8463">
-        <v>-1</v>
+        <v>3.732248430450236</v>
       </c>
     </row>
     <row r="8464" spans="1:2">
@@ -68083,7 +68083,7 @@
         <v>8462</v>
       </c>
       <c r="B8464">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8465" spans="1:2">
@@ -68139,7 +68139,7 @@
         <v>8469</v>
       </c>
       <c r="B8471">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8472" spans="1:2">
@@ -68147,7 +68147,7 @@
         <v>8470</v>
       </c>
       <c r="B8472">
-        <v>-1</v>
+        <v>3.646863365783126</v>
       </c>
     </row>
     <row r="8473" spans="1:2">
@@ -68155,7 +68155,7 @@
         <v>8471</v>
       </c>
       <c r="B8473">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8474" spans="1:2">
@@ -68211,7 +68211,7 @@
         <v>8478</v>
       </c>
       <c r="B8480">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8481" spans="1:2">
@@ -68219,7 +68219,7 @@
         <v>8479</v>
       </c>
       <c r="B8481">
-        <v>-1</v>
+        <v>3.964984408275229</v>
       </c>
     </row>
     <row r="8482" spans="1:2">
@@ -68227,7 +68227,7 @@
         <v>8480</v>
       </c>
       <c r="B8482">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8483" spans="1:2">
@@ -68403,7 +68403,7 @@
         <v>8502</v>
       </c>
       <c r="B8504">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8505" spans="1:2">
@@ -68411,7 +68411,7 @@
         <v>8503</v>
       </c>
       <c r="B8505">
-        <v>-1</v>
+        <v>10.10688208065409</v>
       </c>
     </row>
     <row r="8506" spans="1:2">
@@ -68419,7 +68419,7 @@
         <v>8504</v>
       </c>
       <c r="B8506">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8507" spans="1:2">
@@ -68499,7 +68499,7 @@
         <v>8514</v>
       </c>
       <c r="B8516">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8517" spans="1:2">
@@ -68507,7 +68507,7 @@
         <v>8515</v>
       </c>
       <c r="B8517">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8518" spans="1:2">
@@ -68515,7 +68515,7 @@
         <v>8516</v>
       </c>
       <c r="B8518">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8519" spans="1:2">
@@ -68547,7 +68547,7 @@
         <v>8520</v>
       </c>
       <c r="B8522">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8523" spans="1:2">
@@ -68555,7 +68555,7 @@
         <v>8521</v>
       </c>
       <c r="B8523">
-        <v>-1</v>
+        <v>10.17189582078383</v>
       </c>
     </row>
     <row r="8524" spans="1:2">
@@ -68563,7 +68563,7 @@
         <v>8522</v>
       </c>
       <c r="B8524">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8525" spans="1:2">
@@ -68619,7 +68619,7 @@
         <v>8529</v>
       </c>
       <c r="B8531">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8532" spans="1:2">
@@ -68627,7 +68627,7 @@
         <v>8530</v>
       </c>
       <c r="B8532">
-        <v>-1</v>
+        <v>13.51538752081334</v>
       </c>
     </row>
     <row r="8533" spans="1:2">
@@ -68635,7 +68635,7 @@
         <v>8531</v>
       </c>
       <c r="B8533">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8534" spans="1:2">
@@ -68931,7 +68931,7 @@
         <v>8568</v>
       </c>
       <c r="B8570">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="8571" spans="1:2">
@@ -68939,7 +68939,7 @@
         <v>8569</v>
       </c>
       <c r="B8571">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8572" spans="1:2">
@@ -68947,7 +68947,7 @@
         <v>8570</v>
       </c>
       <c r="B8572">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8573" spans="1:2">
@@ -69075,7 +69075,7 @@
         <v>8586</v>
       </c>
       <c r="B8588">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8589" spans="1:2">
@@ -69083,7 +69083,7 @@
         <v>8587</v>
       </c>
       <c r="B8589">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="8590" spans="1:2">
@@ -69091,7 +69091,7 @@
         <v>8588</v>
       </c>
       <c r="B8590">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8591" spans="1:2">
@@ -69363,7 +69363,7 @@
         <v>8622</v>
       </c>
       <c r="B8624">
-        <v>-1</v>
+        <v>4.157722355869387</v>
       </c>
     </row>
     <row r="8625" spans="1:2">
@@ -69371,7 +69371,7 @@
         <v>8623</v>
       </c>
       <c r="B8625">
-        <v>-1</v>
+        <v>7.258235165366555</v>
       </c>
     </row>
     <row r="8626" spans="1:2">
@@ -69379,7 +69379,7 @@
         <v>8624</v>
       </c>
       <c r="B8626">
-        <v>-1</v>
+        <v>4.649242788282182</v>
       </c>
     </row>
     <row r="8627" spans="1:2">
@@ -69627,7 +69627,7 @@
         <v>8655</v>
       </c>
       <c r="B8657">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8658" spans="1:2">
@@ -69635,7 +69635,7 @@
         <v>8656</v>
       </c>
       <c r="B8658">
-        <v>-1</v>
+        <v>12.32712037561737</v>
       </c>
     </row>
     <row r="8659" spans="1:2">
@@ -69643,7 +69643,7 @@
         <v>8657</v>
       </c>
       <c r="B8659">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8660" spans="1:2">
@@ -70107,7 +70107,7 @@
         <v>8715</v>
       </c>
       <c r="B8717">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8718" spans="1:2">
@@ -70115,7 +70115,7 @@
         <v>8716</v>
       </c>
       <c r="B8718">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8719" spans="1:2">
@@ -70123,7 +70123,7 @@
         <v>8717</v>
       </c>
       <c r="B8719">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8720" spans="1:2">
@@ -70155,7 +70155,7 @@
         <v>8721</v>
       </c>
       <c r="B8723">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8724" spans="1:2">
@@ -70163,7 +70163,7 @@
         <v>8722</v>
       </c>
       <c r="B8724">
-        <v>-1</v>
+        <v>3.387994189354038</v>
       </c>
     </row>
     <row r="8725" spans="1:2">
@@ -70171,7 +70171,7 @@
         <v>8723</v>
       </c>
       <c r="B8725">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8726" spans="1:2">
@@ -70227,7 +70227,7 @@
         <v>8730</v>
       </c>
       <c r="B8732">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8733" spans="1:2">
@@ -70235,7 +70235,7 @@
         <v>8731</v>
       </c>
       <c r="B8733">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8734" spans="1:2">
@@ -70243,7 +70243,7 @@
         <v>8732</v>
       </c>
       <c r="B8734">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8735" spans="1:2">
@@ -70251,7 +70251,7 @@
         <v>8733</v>
       </c>
       <c r="B8735">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8736" spans="1:2">
@@ -70259,7 +70259,7 @@
         <v>8734</v>
       </c>
       <c r="B8736">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8737" spans="1:2">
@@ -70267,7 +70267,7 @@
         <v>8735</v>
       </c>
       <c r="B8737">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8738" spans="1:2">
@@ -70299,7 +70299,7 @@
         <v>8739</v>
       </c>
       <c r="B8741">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8742" spans="1:2">
@@ -70307,7 +70307,7 @@
         <v>8740</v>
       </c>
       <c r="B8742">
-        <v>-1</v>
+        <v>4.300505773040686</v>
       </c>
     </row>
     <row r="8743" spans="1:2">
@@ -70315,7 +70315,7 @@
         <v>8741</v>
       </c>
       <c r="B8743">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8744" spans="1:2">
@@ -70395,7 +70395,7 @@
         <v>8751</v>
       </c>
       <c r="B8753">
-        <v>-1</v>
+        <v>3.920596354206307</v>
       </c>
     </row>
     <row r="8754" spans="1:2">
@@ -70403,7 +70403,7 @@
         <v>8752</v>
       </c>
       <c r="B8754">
-        <v>-1</v>
+        <v>6.189950980937919</v>
       </c>
     </row>
     <row r="8755" spans="1:2">
@@ -70411,7 +70411,7 @@
         <v>8753</v>
       </c>
       <c r="B8755">
-        <v>-1</v>
+        <v>3.930771949515477</v>
       </c>
     </row>
     <row r="8756" spans="1:2">
@@ -70443,7 +70443,7 @@
         <v>8757</v>
       </c>
       <c r="B8759">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8760" spans="1:2">
@@ -70451,7 +70451,7 @@
         <v>8758</v>
       </c>
       <c r="B8760">
-        <v>-1</v>
+        <v>4.76169549813884</v>
       </c>
     </row>
     <row r="8761" spans="1:2">
@@ -70459,7 +70459,7 @@
         <v>8759</v>
       </c>
       <c r="B8761">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8762" spans="1:2">
@@ -70515,7 +70515,7 @@
         <v>8766</v>
       </c>
       <c r="B8768">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8769" spans="1:2">
@@ -70523,7 +70523,7 @@
         <v>8767</v>
       </c>
       <c r="B8769">
-        <v>-1</v>
+        <v>4.325244762068836</v>
       </c>
     </row>
     <row r="8770" spans="1:2">
@@ -70531,7 +70531,7 @@
         <v>8768</v>
       </c>
       <c r="B8770">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8771" spans="1:2">
@@ -70779,7 +70779,7 @@
         <v>8799</v>
       </c>
       <c r="B8801">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8802" spans="1:2">
@@ -70787,7 +70787,7 @@
         <v>8800</v>
       </c>
       <c r="B8802">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8803" spans="1:2">
@@ -70795,7 +70795,7 @@
         <v>8801</v>
       </c>
       <c r="B8803">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8804" spans="1:2">
@@ -70923,7 +70923,7 @@
         <v>8817</v>
       </c>
       <c r="B8819">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8820" spans="1:2">
@@ -70931,7 +70931,7 @@
         <v>8818</v>
       </c>
       <c r="B8820">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8821" spans="1:2">
@@ -70939,7 +70939,7 @@
         <v>8819</v>
       </c>
       <c r="B8821">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8822" spans="1:2">
@@ -71235,7 +71235,7 @@
         <v>8856</v>
       </c>
       <c r="B8858">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8859" spans="1:2">
@@ -71243,7 +71243,7 @@
         <v>8857</v>
       </c>
       <c r="B8859">
-        <v>-1</v>
+        <v>7.236960940679937</v>
       </c>
     </row>
     <row r="8860" spans="1:2">
@@ -71251,7 +71251,7 @@
         <v>8858</v>
       </c>
       <c r="B8860">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8861" spans="1:2">
@@ -71379,7 +71379,7 @@
         <v>8874</v>
       </c>
       <c r="B8876">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8877" spans="1:2">
@@ -71387,7 +71387,7 @@
         <v>8875</v>
       </c>
       <c r="B8877">
-        <v>-1</v>
+        <v>7.278438209754201</v>
       </c>
     </row>
     <row r="8878" spans="1:2">
@@ -71395,7 +71395,7 @@
         <v>8876</v>
       </c>
       <c r="B8878">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8879" spans="1:2">
@@ -71667,7 +71667,7 @@
         <v>8910</v>
       </c>
       <c r="B8912">
-        <v>-1</v>
+        <v>4.10761868764834</v>
       </c>
     </row>
     <row r="8913" spans="1:2">
@@ -71675,7 +71675,7 @@
         <v>8911</v>
       </c>
       <c r="B8913">
-        <v>-1</v>
+        <v>14.64469190752512</v>
       </c>
     </row>
     <row r="8914" spans="1:2">
@@ -71683,7 +71683,7 @@
         <v>8912</v>
       </c>
       <c r="B8914">
-        <v>-1</v>
+        <v>4.130501618010085</v>
       </c>
     </row>
     <row r="8915" spans="1:2">
@@ -71955,7 +71955,7 @@
         <v>8946</v>
       </c>
       <c r="B8948">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8949" spans="1:2">
@@ -71963,7 +71963,7 @@
         <v>8947</v>
       </c>
       <c r="B8949">
-        <v>-1</v>
+        <v>3.364886791330446</v>
       </c>
     </row>
     <row r="8950" spans="1:2">
@@ -71971,7 +71971,7 @@
         <v>8948</v>
       </c>
       <c r="B8950">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8951" spans="1:2">
@@ -72603,7 +72603,7 @@
         <v>9027</v>
       </c>
       <c r="B9029">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="9030" spans="1:2">
@@ -72611,7 +72611,7 @@
         <v>9028</v>
       </c>
       <c r="B9030">
-        <v>-1</v>
+        <v>5.558815780743043</v>
       </c>
     </row>
     <row r="9031" spans="1:2">
@@ -72619,7 +72619,7 @@
         <v>9029</v>
       </c>
       <c r="B9031">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="9032" spans="1:2">
@@ -72987,7 +72987,7 @@
         <v>9075</v>
       </c>
       <c r="B9077">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="9078" spans="1:2">
@@ -72995,7 +72995,7 @@
         <v>9076</v>
       </c>
       <c r="B9078">
-        <v>-1</v>
+        <v>13.00357867807719</v>
       </c>
     </row>
     <row r="9079" spans="1:2">
@@ -73003,7 +73003,7 @@
         <v>9077</v>
       </c>
       <c r="B9079">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="9080" spans="1:2">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -4251,7 +4251,7 @@
         <v>483</v>
       </c>
       <c r="B485">
-        <v>-1</v>
+        <v>9.456667176965471</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -4259,7 +4259,7 @@
         <v>484</v>
       </c>
       <c r="B486">
-        <v>-1</v>
+        <v>17.74808708936522</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -4267,7 +4267,7 @@
         <v>485</v>
       </c>
       <c r="B487">
-        <v>-1</v>
+        <v>8.691065851788217</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -4683,7 +4683,7 @@
         <v>537</v>
       </c>
       <c r="B539">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -4691,7 +4691,7 @@
         <v>538</v>
       </c>
       <c r="B540">
-        <v>-1</v>
+        <v>7.994692013092375</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -4699,7 +4699,7 @@
         <v>539</v>
       </c>
       <c r="B541">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -5523,7 +5523,7 @@
         <v>642</v>
       </c>
       <c r="B644">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -5531,7 +5531,7 @@
         <v>643</v>
       </c>
       <c r="B645">
-        <v>-1</v>
+        <v>6.054005689111575</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -5539,7 +5539,7 @@
         <v>644</v>
       </c>
       <c r="B646">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -5547,7 +5547,7 @@
         <v>645</v>
       </c>
       <c r="B647">
-        <v>-1</v>
+        <v>7.790841515124248</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -5555,7 +5555,7 @@
         <v>646</v>
       </c>
       <c r="B648">
-        <v>-1</v>
+        <v>19.64678863951209</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -5563,7 +5563,7 @@
         <v>647</v>
       </c>
       <c r="B649">
-        <v>-1</v>
+        <v>6.999282465870527</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -6531,7 +6531,7 @@
         <v>768</v>
       </c>
       <c r="B770">
-        <v>-1</v>
+        <v>3.802960489651808</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -6539,7 +6539,7 @@
         <v>769</v>
       </c>
       <c r="B771">
-        <v>-1</v>
+        <v>126.4132416306447</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -6547,7 +6547,7 @@
         <v>770</v>
       </c>
       <c r="B772">
-        <v>-1</v>
+        <v>3.472265249323381</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -7755,7 +7755,7 @@
         <v>921</v>
       </c>
       <c r="B923">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="924" spans="1:2">
@@ -7763,7 +7763,7 @@
         <v>922</v>
       </c>
       <c r="B924">
-        <v>-1</v>
+        <v>4.925908672145596</v>
       </c>
     </row>
     <row r="925" spans="1:2">
@@ -7771,7 +7771,7 @@
         <v>923</v>
       </c>
       <c r="B925">
-        <v>-1</v>
+        <v>3.345085916977064</v>
       </c>
     </row>
     <row r="926" spans="1:2">
@@ -8067,7 +8067,7 @@
         <v>960</v>
       </c>
       <c r="B962">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="963" spans="1:2">
@@ -8075,7 +8075,7 @@
         <v>961</v>
       </c>
       <c r="B963">
-        <v>-1</v>
+        <v>5.458893552275557</v>
       </c>
     </row>
     <row r="964" spans="1:2">
@@ -8083,7 +8083,7 @@
         <v>962</v>
       </c>
       <c r="B964">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="965" spans="1:2">
@@ -8259,7 +8259,7 @@
         <v>984</v>
       </c>
       <c r="B986">
-        <v>-1</v>
+        <v>3.408739267436267</v>
       </c>
     </row>
     <row r="987" spans="1:2">
@@ -8267,7 +8267,7 @@
         <v>985</v>
       </c>
       <c r="B987">
-        <v>-1</v>
+        <v>6.394729886706241</v>
       </c>
     </row>
     <row r="988" spans="1:2">
@@ -8275,7 +8275,7 @@
         <v>986</v>
       </c>
       <c r="B988">
-        <v>-1</v>
+        <v>3.353360342580647</v>
       </c>
     </row>
     <row r="989" spans="1:2">
@@ -8571,7 +8571,7 @@
         <v>1023</v>
       </c>
       <c r="B1025">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
@@ -8579,7 +8579,7 @@
         <v>1024</v>
       </c>
       <c r="B1026">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
@@ -8587,7 +8587,7 @@
         <v>1025</v>
       </c>
       <c r="B1027">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
@@ -8835,7 +8835,7 @@
         <v>1056</v>
       </c>
       <c r="B1058">
-        <v>-1</v>
+        <v>3.827540960225184</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
@@ -8843,7 +8843,7 @@
         <v>1057</v>
       </c>
       <c r="B1059">
-        <v>-1</v>
+        <v>127.4080988897501</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
@@ -8851,7 +8851,7 @@
         <v>1058</v>
       </c>
       <c r="B1060">
-        <v>-1</v>
+        <v>3.521310903436703</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
@@ -8979,7 +8979,7 @@
         <v>1074</v>
       </c>
       <c r="B1076">
-        <v>-1</v>
+        <v>3.82913329733845</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
@@ -8987,7 +8987,7 @@
         <v>1075</v>
       </c>
       <c r="B1077">
-        <v>-1</v>
+        <v>127.434641822962</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
@@ -8995,7 +8995,7 @@
         <v>1076</v>
       </c>
       <c r="B1078">
-        <v>-1</v>
+        <v>3.52276200204672</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
@@ -9411,7 +9411,7 @@
         <v>1128</v>
       </c>
       <c r="B1130">
-        <v>-1</v>
+        <v>4.278999906546743</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
@@ -9419,7 +9419,7 @@
         <v>1129</v>
       </c>
       <c r="B1131">
-        <v>-1</v>
+        <v>153.5575778573921</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
@@ -9427,7 +9427,7 @@
         <v>1130</v>
       </c>
       <c r="B1132">
-        <v>-1</v>
+        <v>3.84922703678362</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
@@ -13371,7 +13371,7 @@
         <v>1623</v>
       </c>
       <c r="B1625">
-        <v>-1</v>
+        <v>3.759911235051705</v>
       </c>
     </row>
     <row r="1626" spans="1:2">
@@ -13379,7 +13379,7 @@
         <v>1624</v>
       </c>
       <c r="B1626">
-        <v>-1</v>
+        <v>5.962356229732801</v>
       </c>
     </row>
     <row r="1627" spans="1:2">
@@ -13387,7 +13387,7 @@
         <v>1625</v>
       </c>
       <c r="B1627">
-        <v>-1</v>
+        <v>3.66452051922842</v>
       </c>
     </row>
     <row r="1628" spans="1:2">
@@ -13707,7 +13707,7 @@
         <v>1665</v>
       </c>
       <c r="B1667">
-        <v>-1</v>
+        <v>3.442644482465473</v>
       </c>
     </row>
     <row r="1668" spans="1:2">
@@ -13715,7 +13715,7 @@
         <v>1666</v>
       </c>
       <c r="B1668">
-        <v>-1</v>
+        <v>3.656226991141853</v>
       </c>
     </row>
     <row r="1669" spans="1:2">
@@ -13723,7 +13723,7 @@
         <v>1667</v>
       </c>
       <c r="B1669">
-        <v>-1</v>
+        <v>3.56453647421191</v>
       </c>
     </row>
     <row r="1670" spans="1:2">
@@ -13779,7 +13779,7 @@
         <v>1674</v>
       </c>
       <c r="B1676">
-        <v>-1</v>
+        <v>3.382157546376829</v>
       </c>
     </row>
     <row r="1677" spans="1:2">
@@ -13787,7 +13787,7 @@
         <v>1675</v>
       </c>
       <c r="B1677">
-        <v>-1</v>
+        <v>3.756739656750074</v>
       </c>
     </row>
     <row r="1678" spans="1:2">
@@ -13795,7 +13795,7 @@
         <v>1676</v>
       </c>
       <c r="B1678">
-        <v>-1</v>
+        <v>3.551534916554044</v>
       </c>
     </row>
     <row r="1679" spans="1:2">
@@ -13827,7 +13827,7 @@
         <v>1680</v>
       </c>
       <c r="B1682">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1683" spans="1:2">
@@ -13835,7 +13835,7 @@
         <v>1681</v>
       </c>
       <c r="B1683">
-        <v>-1</v>
+        <v>7.010785347349424</v>
       </c>
     </row>
     <row r="1684" spans="1:2">
@@ -13843,7 +13843,7 @@
         <v>1682</v>
       </c>
       <c r="B1684">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1685" spans="1:2">
@@ -13899,7 +13899,7 @@
         <v>1689</v>
       </c>
       <c r="B1691">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1692" spans="1:2">
@@ -13907,7 +13907,7 @@
         <v>1690</v>
       </c>
       <c r="B1692">
-        <v>-1</v>
+        <v>9.101154583838767</v>
       </c>
     </row>
     <row r="1693" spans="1:2">
@@ -13915,7 +13915,7 @@
         <v>1691</v>
       </c>
       <c r="B1693">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1694" spans="1:2">
@@ -14619,7 +14619,7 @@
         <v>1779</v>
       </c>
       <c r="B1781">
-        <v>-1</v>
+        <v>6.653210618715488</v>
       </c>
     </row>
     <row r="1782" spans="1:2">
@@ -14627,7 +14627,7 @@
         <v>1780</v>
       </c>
       <c r="B1782">
-        <v>-1</v>
+        <v>17.31235670517289</v>
       </c>
     </row>
     <row r="1783" spans="1:2">
@@ -14635,7 +14635,7 @@
         <v>1781</v>
       </c>
       <c r="B1783">
-        <v>-1</v>
+        <v>5.849558502807895</v>
       </c>
     </row>
     <row r="1784" spans="1:2">
@@ -15123,7 +15123,7 @@
         <v>1842</v>
       </c>
       <c r="B1844">
-        <v>-1</v>
+        <v>7.869672240810033</v>
       </c>
     </row>
     <row r="1845" spans="1:2">
@@ -15131,7 +15131,7 @@
         <v>1843</v>
       </c>
       <c r="B1845">
-        <v>-1</v>
+        <v>11.99734936666121</v>
       </c>
     </row>
     <row r="1846" spans="1:2">
@@ -15139,7 +15139,7 @@
         <v>1844</v>
       </c>
       <c r="B1846">
-        <v>-1</v>
+        <v>6.81660488098943</v>
       </c>
     </row>
     <row r="1847" spans="1:2">
@@ -15171,7 +15171,7 @@
         <v>1848</v>
       </c>
       <c r="B1850">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1851" spans="1:2">
@@ -15179,7 +15179,7 @@
         <v>1849</v>
       </c>
       <c r="B1851">
-        <v>-1</v>
+        <v>5.08872478239083</v>
       </c>
     </row>
     <row r="1852" spans="1:2">
@@ -15187,7 +15187,7 @@
         <v>1850</v>
       </c>
       <c r="B1852">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1853" spans="1:2">
@@ -15195,7 +15195,7 @@
         <v>1851</v>
       </c>
       <c r="B1853">
-        <v>-1</v>
+        <v>7.931061446909793</v>
       </c>
     </row>
     <row r="1854" spans="1:2">
@@ -15203,7 +15203,7 @@
         <v>1852</v>
       </c>
       <c r="B1854">
-        <v>-1</v>
+        <v>19.45077616961257</v>
       </c>
     </row>
     <row r="1855" spans="1:2">
@@ -15211,7 +15211,7 @@
         <v>1853</v>
       </c>
       <c r="B1855">
-        <v>-1</v>
+        <v>6.81660488098943</v>
       </c>
     </row>
     <row r="1856" spans="1:2">
@@ -15219,7 +15219,7 @@
         <v>1854</v>
       </c>
       <c r="B1856">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1857" spans="1:2">
@@ -15227,7 +15227,7 @@
         <v>1855</v>
       </c>
       <c r="B1857">
-        <v>-1</v>
+        <v>3.835779021621399</v>
       </c>
     </row>
     <row r="1858" spans="1:2">
@@ -15235,7 +15235,7 @@
         <v>1856</v>
       </c>
       <c r="B1858">
-        <v>-1</v>
+        <v>3.413627582489087</v>
       </c>
     </row>
     <row r="1859" spans="1:2">
@@ -15555,7 +15555,7 @@
         <v>1896</v>
       </c>
       <c r="B1898">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1899" spans="1:2">
@@ -15563,7 +15563,7 @@
         <v>1897</v>
       </c>
       <c r="B1899">
-        <v>-1</v>
+        <v>27.87329069586969</v>
       </c>
     </row>
     <row r="1900" spans="1:2">
@@ -15571,7 +15571,7 @@
         <v>1898</v>
       </c>
       <c r="B1900">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1901" spans="1:2">
@@ -15795,7 +15795,7 @@
         <v>1926</v>
       </c>
       <c r="B1928">
-        <v>-1</v>
+        <v>3.480518962029167</v>
       </c>
     </row>
     <row r="1929" spans="1:2">
@@ -15803,7 +15803,7 @@
         <v>1927</v>
       </c>
       <c r="B1929">
-        <v>-1</v>
+        <v>6.21460965094196</v>
       </c>
     </row>
     <row r="1930" spans="1:2">
@@ -15811,7 +15811,7 @@
         <v>1928</v>
       </c>
       <c r="B1930">
-        <v>-1</v>
+        <v>3.522126170779893</v>
       </c>
     </row>
     <row r="1931" spans="1:2">
@@ -16635,7 +16635,7 @@
         <v>2031</v>
       </c>
       <c r="B2033">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2034" spans="1:2">
@@ -16643,7 +16643,7 @@
         <v>2032</v>
       </c>
       <c r="B2034">
-        <v>-1</v>
+        <v>14.5423381814311</v>
       </c>
     </row>
     <row r="2035" spans="1:2">
@@ -16651,7 +16651,7 @@
         <v>2033</v>
       </c>
       <c r="B2035">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2036" spans="1:2">
@@ -16947,7 +16947,7 @@
         <v>2070</v>
       </c>
       <c r="B2072">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2073" spans="1:2">
@@ -16955,7 +16955,7 @@
         <v>2071</v>
       </c>
       <c r="B2073">
-        <v>-1</v>
+        <v>4.2674739754885</v>
       </c>
     </row>
     <row r="2074" spans="1:2">
@@ -16963,7 +16963,7 @@
         <v>2072</v>
       </c>
       <c r="B2074">
-        <v>-1</v>
+        <v>3.6119317456627</v>
       </c>
     </row>
     <row r="2075" spans="1:2">
@@ -16971,7 +16971,7 @@
         <v>2073</v>
       </c>
       <c r="B2075">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2076" spans="1:2">
@@ -16979,7 +16979,7 @@
         <v>2074</v>
       </c>
       <c r="B2076">
-        <v>-1</v>
+        <v>4.458456305863468</v>
       </c>
     </row>
     <row r="2077" spans="1:2">
@@ -16987,7 +16987,7 @@
         <v>2075</v>
       </c>
       <c r="B2077">
-        <v>-1</v>
+        <v>3.417249695102886</v>
       </c>
     </row>
     <row r="2078" spans="1:2">
@@ -17043,7 +17043,7 @@
         <v>2082</v>
       </c>
       <c r="B2084">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2085" spans="1:2">
@@ -17051,7 +17051,7 @@
         <v>2083</v>
       </c>
       <c r="B2085">
-        <v>-1</v>
+        <v>7.852449767067338</v>
       </c>
     </row>
     <row r="2086" spans="1:2">
@@ -17059,7 +17059,7 @@
         <v>2084</v>
       </c>
       <c r="B2086">
-        <v>-1</v>
+        <v>3.417249695102886</v>
       </c>
     </row>
     <row r="2087" spans="1:2">
@@ -17139,7 +17139,7 @@
         <v>2094</v>
       </c>
       <c r="B2096">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2097" spans="1:2">
@@ -17147,7 +17147,7 @@
         <v>2095</v>
       </c>
       <c r="B2097">
-        <v>-1</v>
+        <v>12.14363418956139</v>
       </c>
     </row>
     <row r="2098" spans="1:2">
@@ -17155,7 +17155,7 @@
         <v>2096</v>
       </c>
       <c r="B2098">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2099" spans="1:2">
@@ -17187,7 +17187,7 @@
         <v>2100</v>
       </c>
       <c r="B2102">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2103" spans="1:2">
@@ -17195,7 +17195,7 @@
         <v>2101</v>
       </c>
       <c r="B2103">
-        <v>-1</v>
+        <v>5.345362190878866</v>
       </c>
     </row>
     <row r="2104" spans="1:2">
@@ -17203,7 +17203,7 @@
         <v>2102</v>
       </c>
       <c r="B2104">
-        <v>-1</v>
+        <v>3.437384166697321</v>
       </c>
     </row>
     <row r="2105" spans="1:2">
@@ -17403,7 +17403,7 @@
         <v>2127</v>
       </c>
       <c r="B2129">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2130" spans="1:2">
@@ -17411,7 +17411,7 @@
         <v>2128</v>
       </c>
       <c r="B2130">
-        <v>-1</v>
+        <v>4.634258824472004</v>
       </c>
     </row>
     <row r="2131" spans="1:2">
@@ -17419,7 +17419,7 @@
         <v>2129</v>
       </c>
       <c r="B2131">
-        <v>-1</v>
+        <v>3.42345919083813</v>
       </c>
     </row>
     <row r="2132" spans="1:2">
@@ -17763,7 +17763,7 @@
         <v>2172</v>
       </c>
       <c r="B2174">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2175" spans="1:2">
@@ -17771,7 +17771,7 @@
         <v>2173</v>
       </c>
       <c r="B2175">
-        <v>-1</v>
+        <v>111.7822204538989</v>
       </c>
     </row>
     <row r="2176" spans="1:2">
@@ -17779,7 +17779,7 @@
         <v>2174</v>
       </c>
       <c r="B2176">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2177" spans="1:2">
@@ -19899,7 +19899,7 @@
         <v>2439</v>
       </c>
       <c r="B2441">
-        <v>-1</v>
+        <v>3.337579654729639</v>
       </c>
     </row>
     <row r="2442" spans="1:2">
@@ -19907,7 +19907,7 @@
         <v>2440</v>
       </c>
       <c r="B2442">
-        <v>-1</v>
+        <v>3.437007067520925</v>
       </c>
     </row>
     <row r="2443" spans="1:2">
@@ -19915,7 +19915,7 @@
         <v>2441</v>
       </c>
       <c r="B2443">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2444" spans="1:2">
@@ -20235,7 +20235,7 @@
         <v>2481</v>
       </c>
       <c r="B2483">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2484" spans="1:2">
@@ -20243,7 +20243,7 @@
         <v>2482</v>
       </c>
       <c r="B2484">
-        <v>-1</v>
+        <v>8.379522715268827</v>
       </c>
     </row>
     <row r="2485" spans="1:2">
@@ -20251,7 +20251,7 @@
         <v>2483</v>
       </c>
       <c r="B2485">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2486" spans="1:2">
@@ -20787,7 +20787,7 @@
         <v>2550</v>
       </c>
       <c r="B2552">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2553" spans="1:2">
@@ -20795,7 +20795,7 @@
         <v>2551</v>
       </c>
       <c r="B2553">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2554" spans="1:2">
@@ -20803,7 +20803,7 @@
         <v>2552</v>
       </c>
       <c r="B2554">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2555" spans="1:2">
@@ -22155,7 +22155,7 @@
         <v>2721</v>
       </c>
       <c r="B2723">
-        <v>-1</v>
+        <v>4.587461090516943</v>
       </c>
     </row>
     <row r="2724" spans="1:2">
@@ -22163,7 +22163,7 @@
         <v>2722</v>
       </c>
       <c r="B2724">
-        <v>-1</v>
+        <v>5.179261697583792</v>
       </c>
     </row>
     <row r="2725" spans="1:2">
@@ -22171,7 +22171,7 @@
         <v>2723</v>
       </c>
       <c r="B2725">
-        <v>-1</v>
+        <v>3.857426523397356</v>
       </c>
     </row>
     <row r="2726" spans="1:2">
@@ -22515,7 +22515,7 @@
         <v>2766</v>
       </c>
       <c r="B2768">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="2769" spans="1:2">
@@ -22523,7 +22523,7 @@
         <v>2767</v>
       </c>
       <c r="B2769">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2770" spans="1:2">
@@ -22531,7 +22531,7 @@
         <v>2768</v>
       </c>
       <c r="B2770">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2771" spans="1:2">
@@ -22803,7 +22803,7 @@
         <v>2802</v>
       </c>
       <c r="B2804">
-        <v>-1</v>
+        <v>4.765125485342847</v>
       </c>
     </row>
     <row r="2805" spans="1:2">
@@ -22811,7 +22811,7 @@
         <v>2803</v>
       </c>
       <c r="B2805">
-        <v>-1</v>
+        <v>7.780694652754716</v>
       </c>
     </row>
     <row r="2806" spans="1:2">
@@ -22819,7 +22819,7 @@
         <v>2804</v>
       </c>
       <c r="B2806">
-        <v>-1</v>
+        <v>4.08417625730565</v>
       </c>
     </row>
     <row r="2807" spans="1:2">
@@ -22899,7 +22899,7 @@
         <v>2814</v>
       </c>
       <c r="B2816">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2817" spans="1:2">
@@ -22907,7 +22907,7 @@
         <v>2815</v>
       </c>
       <c r="B2817">
-        <v>-1</v>
+        <v>7.78587384257623</v>
       </c>
     </row>
     <row r="2818" spans="1:2">
@@ -22915,7 +22915,7 @@
         <v>2816</v>
       </c>
       <c r="B2818">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2819" spans="1:2">
@@ -23283,7 +23283,7 @@
         <v>2862</v>
       </c>
       <c r="B2864">
-        <v>-1</v>
+        <v>4.101657075121312</v>
       </c>
     </row>
     <row r="2865" spans="1:2">
@@ -23291,7 +23291,7 @@
         <v>2863</v>
       </c>
       <c r="B2865">
-        <v>-1</v>
+        <v>5.811653271316941</v>
       </c>
     </row>
     <row r="2866" spans="1:2">
@@ -23299,7 +23299,7 @@
         <v>2864</v>
       </c>
       <c r="B2866">
-        <v>-1</v>
+        <v>3.487479186142106</v>
       </c>
     </row>
     <row r="2867" spans="1:2">
@@ -23355,7 +23355,7 @@
         <v>2871</v>
       </c>
       <c r="B2873">
-        <v>-1</v>
+        <v>4.100177921256265</v>
       </c>
     </row>
     <row r="2874" spans="1:2">
@@ -23363,7 +23363,7 @@
         <v>2872</v>
       </c>
       <c r="B2874">
-        <v>-1</v>
+        <v>6.588976574415028</v>
       </c>
     </row>
     <row r="2875" spans="1:2">
@@ -23371,7 +23371,7 @@
         <v>2873</v>
       </c>
       <c r="B2875">
-        <v>-1</v>
+        <v>3.487479186142106</v>
       </c>
     </row>
     <row r="2876" spans="1:2">
@@ -23955,7 +23955,7 @@
         <v>2946</v>
       </c>
       <c r="B2948">
-        <v>-1</v>
+        <v>3.84334572356394</v>
       </c>
     </row>
     <row r="2949" spans="1:2">
@@ -23963,7 +23963,7 @@
         <v>2947</v>
       </c>
       <c r="B2949">
-        <v>-1</v>
+        <v>7.556494288432325</v>
       </c>
     </row>
     <row r="2950" spans="1:2">
@@ -23971,7 +23971,7 @@
         <v>2948</v>
       </c>
       <c r="B2950">
-        <v>-1</v>
+        <v>3.35555189736968</v>
       </c>
     </row>
     <row r="2951" spans="1:2">
@@ -24243,7 +24243,7 @@
         <v>2982</v>
       </c>
       <c r="B2984">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2985" spans="1:2">
@@ -24251,7 +24251,7 @@
         <v>2983</v>
       </c>
       <c r="B2985">
-        <v>-1</v>
+        <v>5.257861556165865</v>
       </c>
     </row>
     <row r="2986" spans="1:2">
@@ -24259,7 +24259,7 @@
         <v>2984</v>
       </c>
       <c r="B2986">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2987" spans="1:2">
@@ -24507,7 +24507,7 @@
         <v>3015</v>
       </c>
       <c r="B3017">
-        <v>-1</v>
+        <v>3.354575031141749</v>
       </c>
     </row>
     <row r="3018" spans="1:2">
@@ -24515,7 +24515,7 @@
         <v>3016</v>
       </c>
       <c r="B3018">
-        <v>-1</v>
+        <v>5.507497205494105</v>
       </c>
     </row>
     <row r="3019" spans="1:2">
@@ -24523,7 +24523,7 @@
         <v>3017</v>
       </c>
       <c r="B3019">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3020" spans="1:2">
@@ -25995,7 +25995,7 @@
         <v>3201</v>
       </c>
       <c r="B3203">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3204" spans="1:2">
@@ -26003,7 +26003,7 @@
         <v>3202</v>
       </c>
       <c r="B3204">
-        <v>-1</v>
+        <v>14.68818384318302</v>
       </c>
     </row>
     <row r="3205" spans="1:2">
@@ -26011,7 +26011,7 @@
         <v>3203</v>
       </c>
       <c r="B3205">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3206" spans="1:2">
@@ -28731,7 +28731,7 @@
         <v>3543</v>
       </c>
       <c r="B3545">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3546" spans="1:2">
@@ -28739,7 +28739,7 @@
         <v>3544</v>
       </c>
       <c r="B3546">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3547" spans="1:2">
@@ -28747,7 +28747,7 @@
         <v>3545</v>
       </c>
       <c r="B3547">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3548" spans="1:2">
@@ -28971,7 +28971,7 @@
         <v>3573</v>
       </c>
       <c r="B3575">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3576" spans="1:2">
@@ -28979,7 +28979,7 @@
         <v>3574</v>
       </c>
       <c r="B3576">
-        <v>-1</v>
+        <v>3.358451817412189</v>
       </c>
     </row>
     <row r="3577" spans="1:2">
@@ -28987,7 +28987,7 @@
         <v>3575</v>
       </c>
       <c r="B3577">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3578" spans="1:2">
@@ -29811,7 +29811,7 @@
         <v>3678</v>
       </c>
       <c r="B3680">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3681" spans="1:2">
@@ -29819,7 +29819,7 @@
         <v>3679</v>
       </c>
       <c r="B3681">
-        <v>-1</v>
+        <v>7.574091964382756</v>
       </c>
     </row>
     <row r="3682" spans="1:2">
@@ -29827,7 +29827,7 @@
         <v>3680</v>
       </c>
       <c r="B3682">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3683" spans="1:2">
@@ -30963,7 +30963,7 @@
         <v>3822</v>
       </c>
       <c r="B3824">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3825" spans="1:2">
@@ -30971,7 +30971,7 @@
         <v>3823</v>
       </c>
       <c r="B3825">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3826" spans="1:2">
@@ -30979,7 +30979,7 @@
         <v>3824</v>
       </c>
       <c r="B3826">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3827" spans="1:2">
@@ -31227,7 +31227,7 @@
         <v>3855</v>
       </c>
       <c r="B3857">
-        <v>-1</v>
+        <v>3.960200584197671</v>
       </c>
     </row>
     <row r="3858" spans="1:2">
@@ -31235,7 +31235,7 @@
         <v>3856</v>
       </c>
       <c r="B3858">
-        <v>-1</v>
+        <v>4.465380408773612</v>
       </c>
     </row>
     <row r="3859" spans="1:2">
@@ -31243,7 +31243,7 @@
         <v>3857</v>
       </c>
       <c r="B3859">
-        <v>-1</v>
+        <v>3.341025168741352</v>
       </c>
     </row>
     <row r="3860" spans="1:2">
@@ -33051,7 +33051,7 @@
         <v>4083</v>
       </c>
       <c r="B4085">
-        <v>-1</v>
+        <v>8.464343570328946</v>
       </c>
     </row>
     <row r="4086" spans="1:2">
@@ -33059,7 +33059,7 @@
         <v>4084</v>
       </c>
       <c r="B4086">
-        <v>-1</v>
+        <v>19.84749172423404</v>
       </c>
     </row>
     <row r="4087" spans="1:2">
@@ -33067,7 +33067,7 @@
         <v>4085</v>
       </c>
       <c r="B4087">
-        <v>-1</v>
+        <v>7.169414052957612</v>
       </c>
     </row>
     <row r="4088" spans="1:2">
@@ -33291,7 +33291,7 @@
         <v>4113</v>
       </c>
       <c r="B4115">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4116" spans="1:2">
@@ -33299,7 +33299,7 @@
         <v>4114</v>
       </c>
       <c r="B4116">
-        <v>-1</v>
+        <v>3.596734932711709</v>
       </c>
     </row>
     <row r="4117" spans="1:2">
@@ -33307,7 +33307,7 @@
         <v>4115</v>
       </c>
       <c r="B4117">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4118" spans="1:2">
@@ -33603,7 +33603,7 @@
         <v>4152</v>
       </c>
       <c r="B4154">
-        <v>-1</v>
+        <v>3.930771949515477</v>
       </c>
     </row>
     <row r="4155" spans="1:2">
@@ -33611,7 +33611,7 @@
         <v>4153</v>
       </c>
       <c r="B4155">
-        <v>-1</v>
+        <v>6.7961414950235</v>
       </c>
     </row>
     <row r="4156" spans="1:2">
@@ -33619,7 +33619,7 @@
         <v>4154</v>
       </c>
       <c r="B4156">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4157" spans="1:2">
@@ -36147,7 +36147,7 @@
         <v>4470</v>
       </c>
       <c r="B4472">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4473" spans="1:2">
@@ -36155,7 +36155,7 @@
         <v>4471</v>
       </c>
       <c r="B4473">
-        <v>-1</v>
+        <v>45.81874329771004</v>
       </c>
     </row>
     <row r="4474" spans="1:2">
@@ -36163,7 +36163,7 @@
         <v>4472</v>
       </c>
       <c r="B4474">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4475" spans="1:2">
@@ -36675,7 +36675,7 @@
         <v>4536</v>
       </c>
       <c r="B4538">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4539" spans="1:2">
@@ -36683,7 +36683,7 @@
         <v>4537</v>
       </c>
       <c r="B4539">
-        <v>-1</v>
+        <v>7.911190713654792</v>
       </c>
     </row>
     <row r="4540" spans="1:2">
@@ -36691,7 +36691,7 @@
         <v>4538</v>
       </c>
       <c r="B4540">
-        <v>-1</v>
+        <v>3.375819088612242</v>
       </c>
     </row>
     <row r="4541" spans="1:2">
@@ -39219,7 +39219,7 @@
         <v>4854</v>
       </c>
       <c r="B4856">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4857" spans="1:2">
@@ -39227,7 +39227,7 @@
         <v>4855</v>
       </c>
       <c r="B4857">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4858" spans="1:2">
@@ -39235,7 +39235,7 @@
         <v>4856</v>
       </c>
       <c r="B4858">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4859" spans="1:2">
@@ -40371,7 +40371,7 @@
         <v>4998</v>
       </c>
       <c r="B5000">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5001" spans="1:2">
@@ -40379,7 +40379,7 @@
         <v>4999</v>
       </c>
       <c r="B5001">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5002" spans="1:2">
@@ -40387,7 +40387,7 @@
         <v>5000</v>
       </c>
       <c r="B5002">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5003" spans="1:2">
@@ -40971,7 +40971,7 @@
         <v>5073</v>
       </c>
       <c r="B5075">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5076" spans="1:2">
@@ -40979,7 +40979,7 @@
         <v>5074</v>
       </c>
       <c r="B5076">
-        <v>-1</v>
+        <v>7.442631392365961</v>
       </c>
     </row>
     <row r="5077" spans="1:2">
@@ -40987,7 +40987,7 @@
         <v>5075</v>
       </c>
       <c r="B5077">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5078" spans="1:2">
@@ -41091,7 +41091,7 @@
         <v>5088</v>
       </c>
       <c r="B5090">
-        <v>-1</v>
+        <v>3.776779034668099</v>
       </c>
     </row>
     <row r="5091" spans="1:2">
@@ -41099,7 +41099,7 @@
         <v>5089</v>
       </c>
       <c r="B5091">
-        <v>-1</v>
+        <v>7.117428227673839</v>
       </c>
     </row>
     <row r="5092" spans="1:2">
@@ -41107,7 +41107,7 @@
         <v>5090</v>
       </c>
       <c r="B5092">
-        <v>-1</v>
+        <v>3.776779034668099</v>
       </c>
     </row>
     <row r="5093" spans="1:2">
@@ -42819,7 +42819,7 @@
         <v>5304</v>
       </c>
       <c r="B5306">
-        <v>-1</v>
+        <v>3.323023976277706</v>
       </c>
     </row>
     <row r="5307" spans="1:2">
@@ -42827,7 +42827,7 @@
         <v>5305</v>
       </c>
       <c r="B5307">
-        <v>-1</v>
+        <v>6.144654114941472</v>
       </c>
     </row>
     <row r="5308" spans="1:2">
@@ -42835,7 +42835,7 @@
         <v>5306</v>
       </c>
       <c r="B5308">
-        <v>-1</v>
+        <v>3.323023976277706</v>
       </c>
     </row>
     <row r="5309" spans="1:2">
@@ -42963,7 +42963,7 @@
         <v>5322</v>
       </c>
       <c r="B5324">
-        <v>-1</v>
+        <v>3.497224389872555</v>
       </c>
     </row>
     <row r="5325" spans="1:2">
@@ -42971,7 +42971,7 @@
         <v>5323</v>
       </c>
       <c r="B5325">
-        <v>-1</v>
+        <v>8.074723607570878</v>
       </c>
     </row>
     <row r="5326" spans="1:2">
@@ -42979,7 +42979,7 @@
         <v>5324</v>
       </c>
       <c r="B5326">
-        <v>-1</v>
+        <v>3.497224389872555</v>
       </c>
     </row>
     <row r="5327" spans="1:2">
@@ -43803,7 +43803,7 @@
         <v>5427</v>
       </c>
       <c r="B5429">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5430" spans="1:2">
@@ -43811,7 +43811,7 @@
         <v>5428</v>
       </c>
       <c r="B5430">
-        <v>-1</v>
+        <v>96.82299042589484</v>
       </c>
     </row>
     <row r="5431" spans="1:2">
@@ -43819,7 +43819,7 @@
         <v>5429</v>
       </c>
       <c r="B5431">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5432" spans="1:2">
@@ -44019,7 +44019,7 @@
         <v>5454</v>
       </c>
       <c r="B5456">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5457" spans="1:2">
@@ -44027,7 +44027,7 @@
         <v>5455</v>
       </c>
       <c r="B5457">
-        <v>-1</v>
+        <v>9.127220636617672</v>
       </c>
     </row>
     <row r="5458" spans="1:2">
@@ -44035,7 +44035,7 @@
         <v>5456</v>
       </c>
       <c r="B5458">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5459" spans="1:2">
@@ -44547,7 +44547,7 @@
         <v>5520</v>
       </c>
       <c r="B5522">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5523" spans="1:2">
@@ -44555,7 +44555,7 @@
         <v>5521</v>
       </c>
       <c r="B5523">
-        <v>-1</v>
+        <v>5.936337601144992</v>
       </c>
     </row>
     <row r="5524" spans="1:2">
@@ -44563,7 +44563,7 @@
         <v>5522</v>
       </c>
       <c r="B5524">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5525" spans="1:2">
@@ -45387,7 +45387,7 @@
         <v>5625</v>
       </c>
       <c r="B5627">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5628" spans="1:2">
@@ -45395,7 +45395,7 @@
         <v>5626</v>
       </c>
       <c r="B5628">
-        <v>-1</v>
+        <v>82.07102587225324</v>
       </c>
     </row>
     <row r="5629" spans="1:2">
@@ -45403,7 +45403,7 @@
         <v>5627</v>
       </c>
       <c r="B5629">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5630" spans="1:2">
@@ -45411,7 +45411,7 @@
         <v>5628</v>
       </c>
       <c r="B5630">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5631" spans="1:2">
@@ -45419,7 +45419,7 @@
         <v>5629</v>
       </c>
       <c r="B5631">
-        <v>-1</v>
+        <v>113.1388884143572</v>
       </c>
     </row>
     <row r="5632" spans="1:2">
@@ -45427,7 +45427,7 @@
         <v>5630</v>
       </c>
       <c r="B5632">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5633" spans="1:2">
@@ -45483,7 +45483,7 @@
         <v>5637</v>
       </c>
       <c r="B5639">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5640" spans="1:2">
@@ -45491,7 +45491,7 @@
         <v>5638</v>
       </c>
       <c r="B5640">
-        <v>-1</v>
+        <v>8.117302056607233</v>
       </c>
     </row>
     <row r="5641" spans="1:2">
@@ -45499,7 +45499,7 @@
         <v>5639</v>
       </c>
       <c r="B5641">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5642" spans="1:2">
@@ -47523,7 +47523,7 @@
         <v>5892</v>
       </c>
       <c r="B5894">
-        <v>-1</v>
+        <v>8.297603870355708</v>
       </c>
     </row>
     <row r="5895" spans="1:2">
@@ -47531,7 +47531,7 @@
         <v>5893</v>
       </c>
       <c r="B5895">
-        <v>-1</v>
+        <v>10.56166157095827</v>
       </c>
     </row>
     <row r="5896" spans="1:2">
@@ -47539,7 +47539,7 @@
         <v>5894</v>
       </c>
       <c r="B5896">
-        <v>-1</v>
+        <v>8.363570120457521</v>
       </c>
     </row>
     <row r="5897" spans="1:2">
@@ -48027,7 +48027,7 @@
         <v>5955</v>
       </c>
       <c r="B5957">
-        <v>-1</v>
+        <v>9.266619382900387</v>
       </c>
     </row>
     <row r="5958" spans="1:2">
@@ -48035,7 +48035,7 @@
         <v>5956</v>
       </c>
       <c r="B5958">
-        <v>-1</v>
+        <v>19.49211734773939</v>
       </c>
     </row>
     <row r="5959" spans="1:2">
@@ -48043,7 +48043,7 @@
         <v>5957</v>
       </c>
       <c r="B5959">
-        <v>-1</v>
+        <v>9.266619382900387</v>
       </c>
     </row>
     <row r="5960" spans="1:2">
@@ -48939,7 +48939,7 @@
         <v>6069</v>
       </c>
       <c r="B6071">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6072" spans="1:2">
@@ -48947,7 +48947,7 @@
         <v>6070</v>
       </c>
       <c r="B6072">
-        <v>-1</v>
+        <v>3.395815585909334</v>
       </c>
     </row>
     <row r="6073" spans="1:2">
@@ -48955,7 +48955,7 @@
         <v>6071</v>
       </c>
       <c r="B6073">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6074" spans="1:2">
@@ -48987,7 +48987,7 @@
         <v>6075</v>
       </c>
       <c r="B6077">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6078" spans="1:2">
@@ -48995,7 +48995,7 @@
         <v>6076</v>
       </c>
       <c r="B6078">
-        <v>-1</v>
+        <v>3.514224280534251</v>
       </c>
     </row>
     <row r="6079" spans="1:2">
@@ -49003,7 +49003,7 @@
         <v>6077</v>
       </c>
       <c r="B6079">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6080" spans="1:2">
@@ -49467,7 +49467,7 @@
         <v>6135</v>
       </c>
       <c r="B6137">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6138" spans="1:2">
@@ -49475,7 +49475,7 @@
         <v>6136</v>
       </c>
       <c r="B6138">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6139" spans="1:2">
@@ -49483,7 +49483,7 @@
         <v>6137</v>
       </c>
       <c r="B6139">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6140" spans="1:2">
@@ -50043,7 +50043,7 @@
         <v>6207</v>
       </c>
       <c r="B6209">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6210" spans="1:2">
@@ -50051,7 +50051,7 @@
         <v>6208</v>
       </c>
       <c r="B6210">
-        <v>-1</v>
+        <v>8.36684205229653</v>
       </c>
     </row>
     <row r="6211" spans="1:2">
@@ -50059,7 +50059,7 @@
         <v>6209</v>
       </c>
       <c r="B6211">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6212" spans="1:2">
@@ -50091,7 +50091,7 @@
         <v>6213</v>
       </c>
       <c r="B6215">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6216" spans="1:2">
@@ -50099,7 +50099,7 @@
         <v>6214</v>
       </c>
       <c r="B6216">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6217" spans="1:2">
@@ -50107,7 +50107,7 @@
         <v>6215</v>
       </c>
       <c r="B6217">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6218" spans="1:2">
@@ -50787,7 +50787,7 @@
         <v>6300</v>
       </c>
       <c r="B6302">
-        <v>-1</v>
+        <v>3.383560397907148</v>
       </c>
     </row>
     <row r="6303" spans="1:2">
@@ -50795,7 +50795,7 @@
         <v>6301</v>
       </c>
       <c r="B6303">
-        <v>-1</v>
+        <v>5.21558533870884</v>
       </c>
     </row>
     <row r="6304" spans="1:2">
@@ -50803,7 +50803,7 @@
         <v>6302</v>
       </c>
       <c r="B6304">
-        <v>-1</v>
+        <v>3.573368374827002</v>
       </c>
     </row>
     <row r="6305" spans="1:2">
@@ -51483,7 +51483,7 @@
         <v>6387</v>
       </c>
       <c r="B6389">
-        <v>-1</v>
+        <v>6.653210618715488</v>
       </c>
     </row>
     <row r="6390" spans="1:2">
@@ -51491,7 +51491,7 @@
         <v>6388</v>
       </c>
       <c r="B6390">
-        <v>-1</v>
+        <v>18.88796568564995</v>
       </c>
     </row>
     <row r="6391" spans="1:2">
@@ -51499,7 +51499,7 @@
         <v>6389</v>
       </c>
       <c r="B6391">
-        <v>-1</v>
+        <v>6.653210618715488</v>
       </c>
     </row>
     <row r="6392" spans="1:2">
@@ -51963,7 +51963,7 @@
         <v>6447</v>
       </c>
       <c r="B6449">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6450" spans="1:2">
@@ -51971,7 +51971,7 @@
         <v>6448</v>
       </c>
       <c r="B6450">
-        <v>-1</v>
+        <v>4.285416859353919</v>
       </c>
     </row>
     <row r="6451" spans="1:2">
@@ -51979,7 +51979,7 @@
         <v>6449</v>
       </c>
       <c r="B6451">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6452" spans="1:2">
@@ -52155,7 +52155,7 @@
         <v>6471</v>
       </c>
       <c r="B6473">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6474" spans="1:2">
@@ -52163,7 +52163,7 @@
         <v>6472</v>
       </c>
       <c r="B6474">
-        <v>-1</v>
+        <v>4.494152819804798</v>
       </c>
     </row>
     <row r="6475" spans="1:2">
@@ -52171,7 +52171,7 @@
         <v>6473</v>
       </c>
       <c r="B6475">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6476" spans="1:2">
@@ -52371,7 +52371,7 @@
         <v>6498</v>
       </c>
       <c r="B6500">
-        <v>-1</v>
+        <v>3.489252262541176</v>
       </c>
     </row>
     <row r="6501" spans="1:2">
@@ -52379,7 +52379,7 @@
         <v>6499</v>
       </c>
       <c r="B6501">
-        <v>-1</v>
+        <v>3.81996823211882</v>
       </c>
     </row>
     <row r="6502" spans="1:2">
@@ -52387,7 +52387,7 @@
         <v>6500</v>
       </c>
       <c r="B6502">
-        <v>-1</v>
+        <v>3.3535987080763</v>
       </c>
     </row>
     <row r="6503" spans="1:2">
@@ -52899,7 +52899,7 @@
         <v>6564</v>
       </c>
       <c r="B6566">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6567" spans="1:2">
@@ -52907,7 +52907,7 @@
         <v>6565</v>
       </c>
       <c r="B6567">
-        <v>-1</v>
+        <v>144.5549091626777</v>
       </c>
     </row>
     <row r="6568" spans="1:2">
@@ -52915,7 +52915,7 @@
         <v>6566</v>
       </c>
       <c r="B6568">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6569" spans="1:2">
@@ -53619,7 +53619,7 @@
         <v>6654</v>
       </c>
       <c r="B6656">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6657" spans="1:2">
@@ -53627,7 +53627,7 @@
         <v>6655</v>
       </c>
       <c r="B6657">
-        <v>-1</v>
+        <v>6.76603957409454</v>
       </c>
     </row>
     <row r="6658" spans="1:2">
@@ -53635,7 +53635,7 @@
         <v>6656</v>
       </c>
       <c r="B6658">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6659" spans="1:2">
@@ -54579,7 +54579,7 @@
         <v>6774</v>
       </c>
       <c r="B6776">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6777" spans="1:2">
@@ -54587,7 +54587,7 @@
         <v>6775</v>
       </c>
       <c r="B6777">
-        <v>-1</v>
+        <v>43.10186617895167</v>
       </c>
     </row>
     <row r="6778" spans="1:2">
@@ -54595,7 +54595,7 @@
         <v>6776</v>
       </c>
       <c r="B6778">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6779" spans="1:2">
@@ -56211,7 +56211,7 @@
         <v>6978</v>
       </c>
       <c r="B6980">
-        <v>-1</v>
+        <v>3.826572354559887</v>
       </c>
     </row>
     <row r="6981" spans="1:2">
@@ -56219,7 +56219,7 @@
         <v>6979</v>
       </c>
       <c r="B6981">
-        <v>-1</v>
+        <v>4.721395631117609</v>
       </c>
     </row>
     <row r="6982" spans="1:2">
@@ -56227,7 +56227,7 @@
         <v>6980</v>
       </c>
       <c r="B6982">
-        <v>-1</v>
+        <v>3.826572354559887</v>
       </c>
     </row>
     <row r="6983" spans="1:2">
@@ -56451,7 +56451,7 @@
         <v>7008</v>
       </c>
       <c r="B7010">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7011" spans="1:2">
@@ -56459,7 +56459,7 @@
         <v>7009</v>
       </c>
       <c r="B7011">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7012" spans="1:2">
@@ -56467,7 +56467,7 @@
         <v>7010</v>
       </c>
       <c r="B7012">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7013" spans="1:2">
@@ -56715,7 +56715,7 @@
         <v>7041</v>
       </c>
       <c r="B7043">
-        <v>-1</v>
+        <v>4.450439722346921</v>
       </c>
     </row>
     <row r="7044" spans="1:2">
@@ -56723,7 +56723,7 @@
         <v>7042</v>
       </c>
       <c r="B7044">
-        <v>-1</v>
+        <v>6.02947733823016</v>
       </c>
     </row>
     <row r="7045" spans="1:2">
@@ -56731,7 +56731,7 @@
         <v>7043</v>
       </c>
       <c r="B7045">
-        <v>-1</v>
+        <v>4.482105239838175</v>
       </c>
     </row>
     <row r="7046" spans="1:2">
@@ -56787,7 +56787,7 @@
         <v>7050</v>
       </c>
       <c r="B7052">
-        <v>-1</v>
+        <v>4.482105239838175</v>
       </c>
     </row>
     <row r="7053" spans="1:2">
@@ -56795,7 +56795,7 @@
         <v>7051</v>
       </c>
       <c r="B7053">
-        <v>-1</v>
+        <v>6.042884052041053</v>
       </c>
     </row>
     <row r="7054" spans="1:2">
@@ -56803,7 +56803,7 @@
         <v>7052</v>
       </c>
       <c r="B7054">
-        <v>-1</v>
+        <v>4.482105239838175</v>
       </c>
     </row>
     <row r="7055" spans="1:2">
@@ -57051,7 +57051,7 @@
         <v>7083</v>
       </c>
       <c r="B7085">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7086" spans="1:2">
@@ -57059,7 +57059,7 @@
         <v>7084</v>
       </c>
       <c r="B7086">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7087" spans="1:2">
@@ -57067,7 +57067,7 @@
         <v>7085</v>
       </c>
       <c r="B7087">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7088" spans="1:2">
@@ -57075,7 +57075,7 @@
         <v>7086</v>
       </c>
       <c r="B7088">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7089" spans="1:2">
@@ -57083,7 +57083,7 @@
         <v>7087</v>
       </c>
       <c r="B7089">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7090" spans="1:2">
@@ -57091,7 +57091,7 @@
         <v>7088</v>
       </c>
       <c r="B7090">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7091" spans="1:2">
@@ -57099,7 +57099,7 @@
         <v>7089</v>
       </c>
       <c r="B7091">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7092" spans="1:2">
@@ -57107,7 +57107,7 @@
         <v>7090</v>
       </c>
       <c r="B7092">
-        <v>-1</v>
+        <v>11.58104122260052</v>
       </c>
     </row>
     <row r="7093" spans="1:2">
@@ -57115,7 +57115,7 @@
         <v>7091</v>
       </c>
       <c r="B7093">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7094" spans="1:2">
@@ -57171,7 +57171,7 @@
         <v>7098</v>
       </c>
       <c r="B7100">
-        <v>-1</v>
+        <v>11.48790365174798</v>
       </c>
     </row>
     <row r="7101" spans="1:2">
@@ -57179,7 +57179,7 @@
         <v>7099</v>
       </c>
       <c r="B7101">
-        <v>-1</v>
+        <v>19.34650720391321</v>
       </c>
     </row>
     <row r="7102" spans="1:2">
@@ -57187,7 +57187,7 @@
         <v>7100</v>
       </c>
       <c r="B7102">
-        <v>-1</v>
+        <v>11.30894735453761</v>
       </c>
     </row>
     <row r="7103" spans="1:2">
@@ -57267,7 +57267,7 @@
         <v>7110</v>
       </c>
       <c r="B7112">
-        <v>-1</v>
+        <v>3.481488627140461</v>
       </c>
     </row>
     <row r="7113" spans="1:2">
@@ -57275,7 +57275,7 @@
         <v>7111</v>
       </c>
       <c r="B7113">
-        <v>-1</v>
+        <v>5.255535177908954</v>
       </c>
     </row>
     <row r="7114" spans="1:2">
@@ -57283,7 +57283,7 @@
         <v>7112</v>
       </c>
       <c r="B7114">
-        <v>-1</v>
+        <v>3.427384848232695</v>
       </c>
     </row>
     <row r="7115" spans="1:2">
@@ -57363,7 +57363,7 @@
         <v>7122</v>
       </c>
       <c r="B7124">
-        <v>-1</v>
+        <v>4.622061561672208</v>
       </c>
     </row>
     <row r="7125" spans="1:2">
@@ -57371,7 +57371,7 @@
         <v>7123</v>
       </c>
       <c r="B7125">
-        <v>-1</v>
+        <v>8.592539373410579</v>
       </c>
     </row>
     <row r="7126" spans="1:2">
@@ -57379,7 +57379,7 @@
         <v>7124</v>
       </c>
       <c r="B7126">
-        <v>-1</v>
+        <v>4.622061561672208</v>
       </c>
     </row>
     <row r="7127" spans="1:2">
@@ -57771,7 +57771,7 @@
         <v>7173</v>
       </c>
       <c r="B7175">
-        <v>-1</v>
+        <v>4.024859270926373</v>
       </c>
     </row>
     <row r="7176" spans="1:2">
@@ -57779,7 +57779,7 @@
         <v>7174</v>
       </c>
       <c r="B7176">
-        <v>-1</v>
+        <v>7.685963255340611</v>
       </c>
     </row>
     <row r="7177" spans="1:2">
@@ -57787,7 +57787,7 @@
         <v>7175</v>
       </c>
       <c r="B7177">
-        <v>-1</v>
+        <v>4.024859270926373</v>
       </c>
     </row>
     <row r="7178" spans="1:2">
@@ -58083,7 +58083,7 @@
         <v>7212</v>
       </c>
       <c r="B7214">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7215" spans="1:2">
@@ -58091,7 +58091,7 @@
         <v>7213</v>
       </c>
       <c r="B7215">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7216" spans="1:2">
@@ -58099,7 +58099,7 @@
         <v>7214</v>
       </c>
       <c r="B7216">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7217" spans="1:2">
@@ -58227,7 +58227,7 @@
         <v>7230</v>
       </c>
       <c r="B7232">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7233" spans="1:2">
@@ -58235,7 +58235,7 @@
         <v>7231</v>
       </c>
       <c r="B7233">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7234" spans="1:2">
@@ -58243,7 +58243,7 @@
         <v>7232</v>
       </c>
       <c r="B7234">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7235" spans="1:2">
@@ -58659,7 +58659,7 @@
         <v>7284</v>
       </c>
       <c r="B7286">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7287" spans="1:2">
@@ -58667,7 +58667,7 @@
         <v>7285</v>
       </c>
       <c r="B7287">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="7288" spans="1:2">
@@ -58675,7 +58675,7 @@
         <v>7286</v>
       </c>
       <c r="B7288">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7289" spans="1:2">
@@ -58947,7 +58947,7 @@
         <v>7320</v>
       </c>
       <c r="B7322">
-        <v>-1</v>
+        <v>4.343408042108987</v>
       </c>
     </row>
     <row r="7323" spans="1:2">
@@ -58955,7 +58955,7 @@
         <v>7321</v>
       </c>
       <c r="B7323">
-        <v>-1</v>
+        <v>5.857562803424665</v>
       </c>
     </row>
     <row r="7324" spans="1:2">
@@ -58963,7 +58963,7 @@
         <v>7322</v>
       </c>
       <c r="B7324">
-        <v>-1</v>
+        <v>4.343408042108987</v>
       </c>
     </row>
     <row r="7325" spans="1:2">
@@ -59427,7 +59427,7 @@
         <v>7380</v>
       </c>
       <c r="B7382">
-        <v>-1</v>
+        <v>3.49627115088379</v>
       </c>
     </row>
     <row r="7383" spans="1:2">
@@ -59435,7 +59435,7 @@
         <v>7381</v>
       </c>
       <c r="B7383">
-        <v>-1</v>
+        <v>5.451998104469046</v>
       </c>
     </row>
     <row r="7384" spans="1:2">
@@ -59443,7 +59443,7 @@
         <v>7382</v>
       </c>
       <c r="B7384">
-        <v>-1</v>
+        <v>3.495757646334019</v>
       </c>
     </row>
     <row r="7385" spans="1:2">
@@ -59859,7 +59859,7 @@
         <v>7434</v>
       </c>
       <c r="B7436">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7437" spans="1:2">
@@ -59867,7 +59867,7 @@
         <v>7435</v>
       </c>
       <c r="B7437">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7438" spans="1:2">
@@ -59875,7 +59875,7 @@
         <v>7436</v>
       </c>
       <c r="B7438">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7439" spans="1:2">
@@ -60531,7 +60531,7 @@
         <v>7518</v>
       </c>
       <c r="B7520">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7521" spans="1:2">
@@ -60539,7 +60539,7 @@
         <v>7519</v>
       </c>
       <c r="B7521">
-        <v>-1</v>
+        <v>5.462288649665348</v>
       </c>
     </row>
     <row r="7522" spans="1:2">
@@ -60547,7 +60547,7 @@
         <v>7520</v>
       </c>
       <c r="B7522">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7523" spans="1:2">
@@ -61323,7 +61323,7 @@
         <v>7617</v>
       </c>
       <c r="B7619">
-        <v>-1</v>
+        <v>4.50819134560968</v>
       </c>
     </row>
     <row r="7620" spans="1:2">
@@ -61331,7 +61331,7 @@
         <v>7618</v>
       </c>
       <c r="B7620">
-        <v>-1</v>
+        <v>7.335665321469076</v>
       </c>
     </row>
     <row r="7621" spans="1:2">
@@ -61339,7 +61339,7 @@
         <v>7619</v>
       </c>
       <c r="B7621">
-        <v>-1</v>
+        <v>4.520151878047773</v>
       </c>
     </row>
     <row r="7622" spans="1:2">
@@ -61515,7 +61515,7 @@
         <v>7641</v>
       </c>
       <c r="B7643">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7644" spans="1:2">
@@ -61523,7 +61523,7 @@
         <v>7642</v>
       </c>
       <c r="B7644">
-        <v>-1</v>
+        <v>89.770679382314</v>
       </c>
     </row>
     <row r="7645" spans="1:2">
@@ -61531,7 +61531,7 @@
         <v>7643</v>
       </c>
       <c r="B7645">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7646" spans="1:2">
@@ -62019,7 +62019,7 @@
         <v>7704</v>
       </c>
       <c r="B7706">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7707" spans="1:2">
@@ -62027,7 +62027,7 @@
         <v>7705</v>
       </c>
       <c r="B7707">
-        <v>-1</v>
+        <v>6.896631888760307</v>
       </c>
     </row>
     <row r="7708" spans="1:2">
@@ -62035,7 +62035,7 @@
         <v>7706</v>
       </c>
       <c r="B7708">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7709" spans="1:2">
@@ -62763,7 +62763,7 @@
         <v>7797</v>
       </c>
       <c r="B7799">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7800" spans="1:2">
@@ -62771,7 +62771,7 @@
         <v>7798</v>
       </c>
       <c r="B7800">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7801" spans="1:2">
@@ -62779,7 +62779,7 @@
         <v>7799</v>
       </c>
       <c r="B7801">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7802" spans="1:2">
@@ -63483,7 +63483,7 @@
         <v>7887</v>
       </c>
       <c r="B7889">
-        <v>-1</v>
+        <v>4.32929948676124</v>
       </c>
     </row>
     <row r="7890" spans="1:2">
@@ -63491,7 +63491,7 @@
         <v>7888</v>
       </c>
       <c r="B7890">
-        <v>-1</v>
+        <v>7.026302204059975</v>
       </c>
     </row>
     <row r="7891" spans="1:2">
@@ -63499,7 +63499,7 @@
         <v>7889</v>
       </c>
       <c r="B7891">
-        <v>-1</v>
+        <v>4.359775623426443</v>
       </c>
     </row>
     <row r="7892" spans="1:2">
@@ -64323,7 +64323,7 @@
         <v>7992</v>
       </c>
       <c r="B7994">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7995" spans="1:2">
@@ -64331,7 +64331,7 @@
         <v>7993</v>
       </c>
       <c r="B7995">
-        <v>-1</v>
+        <v>8.123083208256311</v>
       </c>
     </row>
     <row r="7996" spans="1:2">
@@ -64339,7 +64339,7 @@
         <v>7994</v>
       </c>
       <c r="B7996">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7997" spans="1:2">
@@ -65235,7 +65235,7 @@
         <v>8106</v>
       </c>
       <c r="B8108">
-        <v>-1</v>
+        <v>8.356502746766125</v>
       </c>
     </row>
     <row r="8109" spans="1:2">
@@ -65243,7 +65243,7 @@
         <v>8107</v>
       </c>
       <c r="B8109">
-        <v>-1</v>
+        <v>10.34597498841232</v>
       </c>
     </row>
     <row r="8110" spans="1:2">
@@ -65251,7 +65251,7 @@
         <v>8108</v>
       </c>
       <c r="B8110">
-        <v>-1</v>
+        <v>8.431190069915628</v>
       </c>
     </row>
     <row r="8111" spans="1:2">
@@ -65427,7 +65427,7 @@
         <v>8130</v>
       </c>
       <c r="B8132">
-        <v>-1</v>
+        <v>3.442863462176804</v>
       </c>
     </row>
     <row r="8133" spans="1:2">
@@ -65435,7 +65435,7 @@
         <v>8131</v>
       </c>
       <c r="B8133">
-        <v>-1</v>
+        <v>4.18654290132584</v>
       </c>
     </row>
     <row r="8134" spans="1:2">
@@ -65443,7 +65443,7 @@
         <v>8132</v>
       </c>
       <c r="B8134">
-        <v>-1</v>
+        <v>3.442863462176804</v>
       </c>
     </row>
     <row r="8135" spans="1:2">
@@ -65859,7 +65859,7 @@
         <v>8184</v>
       </c>
       <c r="B8186">
-        <v>-1</v>
+        <v>3.918093480514229</v>
       </c>
     </row>
     <row r="8187" spans="1:2">
@@ -65867,7 +65867,7 @@
         <v>8185</v>
       </c>
       <c r="B8187">
-        <v>-1</v>
+        <v>4.943362144768193</v>
       </c>
     </row>
     <row r="8188" spans="1:2">
@@ -65875,7 +65875,7 @@
         <v>8186</v>
       </c>
       <c r="B8188">
-        <v>-1</v>
+        <v>3.918093480514229</v>
       </c>
     </row>
     <row r="8189" spans="1:2">
@@ -65907,7 +65907,7 @@
         <v>8190</v>
       </c>
       <c r="B8192">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8193" spans="1:2">
@@ -65915,7 +65915,7 @@
         <v>8191</v>
       </c>
       <c r="B8193">
-        <v>-1</v>
+        <v>3.759981894107756</v>
       </c>
     </row>
     <row r="8194" spans="1:2">
@@ -65923,7 +65923,7 @@
         <v>8192</v>
       </c>
       <c r="B8194">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8195" spans="1:2">
@@ -65931,7 +65931,7 @@
         <v>8193</v>
       </c>
       <c r="B8195">
-        <v>-1</v>
+        <v>4.10012772663555</v>
       </c>
     </row>
     <row r="8196" spans="1:2">
@@ -65939,7 +65939,7 @@
         <v>8194</v>
       </c>
       <c r="B8196">
-        <v>-1</v>
+        <v>5.519453762297966</v>
       </c>
     </row>
     <row r="8197" spans="1:2">
@@ -65947,7 +65947,7 @@
         <v>8195</v>
       </c>
       <c r="B8197">
-        <v>-1</v>
+        <v>4.112516762320995</v>
       </c>
     </row>
     <row r="8198" spans="1:2">
@@ -67371,7 +67371,7 @@
         <v>8373</v>
       </c>
       <c r="B8375">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8376" spans="1:2">
@@ -67379,7 +67379,7 @@
         <v>8374</v>
       </c>
       <c r="B8376">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8377" spans="1:2">
@@ -67387,7 +67387,7 @@
         <v>8375</v>
       </c>
       <c r="B8377">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8378" spans="1:2">
@@ -68379,7 +68379,7 @@
         <v>8499</v>
       </c>
       <c r="B8501">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8502" spans="1:2">
@@ -68387,7 +68387,7 @@
         <v>8500</v>
       </c>
       <c r="B8502">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8503" spans="1:2">
@@ -68395,7 +68395,7 @@
         <v>8501</v>
       </c>
       <c r="B8503">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8504" spans="1:2">
@@ -68523,7 +68523,7 @@
         <v>8517</v>
       </c>
       <c r="B8519">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8520" spans="1:2">
@@ -68531,7 +68531,7 @@
         <v>8518</v>
       </c>
       <c r="B8520">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8521" spans="1:2">
@@ -68539,7 +68539,7 @@
         <v>8519</v>
       </c>
       <c r="B8521">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8522" spans="1:2">
@@ -70803,7 +70803,7 @@
         <v>8802</v>
       </c>
       <c r="B8804">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8805" spans="1:2">
@@ -70811,7 +70811,7 @@
         <v>8803</v>
       </c>
       <c r="B8805">
-        <v>-1</v>
+        <v>4.932074177563384</v>
       </c>
     </row>
     <row r="8806" spans="1:2">
@@ -70819,7 +70819,7 @@
         <v>8804</v>
       </c>
       <c r="B8806">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8807" spans="1:2">
@@ -71979,7 +71979,7 @@
         <v>8949</v>
       </c>
       <c r="B8951">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8952" spans="1:2">
@@ -71987,7 +71987,7 @@
         <v>8950</v>
       </c>
       <c r="B8952">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8953" spans="1:2">
@@ -71995,7 +71995,7 @@
         <v>8951</v>
       </c>
       <c r="B8953">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8954" spans="1:2">
@@ -72123,7 +72123,7 @@
         <v>8967</v>
       </c>
       <c r="B8969">
-        <v>-1</v>
+        <v>3.307266127533626</v>
       </c>
     </row>
     <row r="8970" spans="1:2">
@@ -72131,7 +72131,7 @@
         <v>8968</v>
       </c>
       <c r="B8970">
-        <v>-1</v>
+        <v>4.666499243733258</v>
       </c>
     </row>
     <row r="8971" spans="1:2">
@@ -72139,7 +72139,7 @@
         <v>8969</v>
       </c>
       <c r="B8971">
-        <v>-1</v>
+        <v>3.319964812135856</v>
       </c>
     </row>
     <row r="8972" spans="1:2">
@@ -73539,7 +73539,7 @@
         <v>9144</v>
       </c>
       <c r="B9146">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="9147" spans="1:2">
@@ -73547,7 +73547,7 @@
         <v>9145</v>
       </c>
       <c r="B9147">
-        <v>-1</v>
+        <v>9.810967028619967</v>
       </c>
     </row>
     <row r="9148" spans="1:2">
@@ -73555,7 +73555,7 @@
         <v>9146</v>
       </c>
       <c r="B9148">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="9149" spans="1:2">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -1515,7 +1515,7 @@
         <v>141</v>
       </c>
       <c r="B143">
-        <v>-1</v>
+        <v>8.899625586124616</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -1523,7 +1523,7 @@
         <v>142</v>
       </c>
       <c r="B144">
-        <v>-1</v>
+        <v>9.788624555622238</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -1531,7 +1531,7 @@
         <v>143</v>
       </c>
       <c r="B145">
-        <v>-1</v>
+        <v>7.82616223722552</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2667,7 +2667,7 @@
         <v>285</v>
       </c>
       <c r="B287">
-        <v>-1</v>
+        <v>10.80141199556365</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -2675,7 +2675,7 @@
         <v>286</v>
       </c>
       <c r="B288">
-        <v>-1</v>
+        <v>20.73796986439483</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -2683,7 +2683,7 @@
         <v>287</v>
       </c>
       <c r="B289">
-        <v>-1</v>
+        <v>9.652286222700447</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3747,7 +3747,7 @@
         <v>420</v>
       </c>
       <c r="B422">
-        <v>-1</v>
+        <v>9.037522913799734</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -3755,7 +3755,7 @@
         <v>421</v>
       </c>
       <c r="B423">
-        <v>-1</v>
+        <v>10.29609818171057</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -3763,7 +3763,7 @@
         <v>422</v>
       </c>
       <c r="B424">
-        <v>-1</v>
+        <v>8.071244113993359</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6915,7 +6915,7 @@
         <v>816</v>
       </c>
       <c r="B818">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="819" spans="1:2">
@@ -6923,7 +6923,7 @@
         <v>817</v>
       </c>
       <c r="B819">
-        <v>-1</v>
+        <v>29.69710375652512</v>
       </c>
     </row>
     <row r="820" spans="1:2">
@@ -6931,7 +6931,7 @@
         <v>818</v>
       </c>
       <c r="B820">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="821" spans="1:2">
@@ -11595,7 +11595,7 @@
         <v>1401</v>
       </c>
       <c r="B1403">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1404" spans="1:2">
@@ -11603,7 +11603,7 @@
         <v>1402</v>
       </c>
       <c r="B1404">
-        <v>-1</v>
+        <v>7.717557405098541</v>
       </c>
     </row>
     <row r="1405" spans="1:2">
@@ -11611,7 +11611,7 @@
         <v>1403</v>
       </c>
       <c r="B1405">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1406" spans="1:2">
@@ -11691,7 +11691,7 @@
         <v>1413</v>
       </c>
       <c r="B1415">
-        <v>-1</v>
+        <v>3.316900313546611</v>
       </c>
     </row>
     <row r="1416" spans="1:2">
@@ -11699,7 +11699,7 @@
         <v>1414</v>
       </c>
       <c r="B1416">
-        <v>-1</v>
+        <v>5.112261674652496</v>
       </c>
     </row>
     <row r="1417" spans="1:2">
@@ -11707,7 +11707,7 @@
         <v>1415</v>
       </c>
       <c r="B1417">
-        <v>-1</v>
+        <v>3.461952816571601</v>
       </c>
     </row>
     <row r="1418" spans="1:2">
@@ -11763,7 +11763,7 @@
         <v>1422</v>
       </c>
       <c r="B1424">
-        <v>-1</v>
+        <v>3.45330190904154</v>
       </c>
     </row>
     <row r="1425" spans="1:2">
@@ -11771,7 +11771,7 @@
         <v>1423</v>
       </c>
       <c r="B1425">
-        <v>-1</v>
+        <v>4.319605942113302</v>
       </c>
     </row>
     <row r="1426" spans="1:2">
@@ -11779,7 +11779,7 @@
         <v>1424</v>
       </c>
       <c r="B1426">
-        <v>-1</v>
+        <v>3.452422575261216</v>
       </c>
     </row>
     <row r="1427" spans="1:2">
@@ -12939,7 +12939,7 @@
         <v>1569</v>
       </c>
       <c r="B1571">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1572" spans="1:2">
@@ -12947,7 +12947,7 @@
         <v>1570</v>
       </c>
       <c r="B1572">
-        <v>-1</v>
+        <v>4.176061692595012</v>
       </c>
     </row>
     <row r="1573" spans="1:2">
@@ -12955,7 +12955,7 @@
         <v>1571</v>
       </c>
       <c r="B1573">
-        <v>-1</v>
+        <v>3.371271246430951</v>
       </c>
     </row>
     <row r="1574" spans="1:2">
@@ -15747,7 +15747,7 @@
         <v>1920</v>
       </c>
       <c r="B1922">
-        <v>-1</v>
+        <v>3.725655208780987</v>
       </c>
     </row>
     <row r="1923" spans="1:2">
@@ -15755,7 +15755,7 @@
         <v>1921</v>
       </c>
       <c r="B1923">
-        <v>-1</v>
+        <v>129.4786558404018</v>
       </c>
     </row>
     <row r="1924" spans="1:2">
@@ -15763,7 +15763,7 @@
         <v>1922</v>
       </c>
       <c r="B1924">
-        <v>-1</v>
+        <v>3.367458370971954</v>
       </c>
     </row>
     <row r="1925" spans="1:2">
@@ -16131,7 +16131,7 @@
         <v>1968</v>
       </c>
       <c r="B1970">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1971" spans="1:2">
@@ -16139,7 +16139,7 @@
         <v>1969</v>
       </c>
       <c r="B1971">
-        <v>-1</v>
+        <v>34.03668798462583</v>
       </c>
     </row>
     <row r="1972" spans="1:2">
@@ -16147,7 +16147,7 @@
         <v>1970</v>
       </c>
       <c r="B1972">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="1973" spans="1:2">
@@ -16371,7 +16371,7 @@
         <v>1998</v>
       </c>
       <c r="B2000">
-        <v>-1</v>
+        <v>3.436080227449878</v>
       </c>
     </row>
     <row r="2001" spans="1:2">
@@ -16379,7 +16379,7 @@
         <v>1999</v>
       </c>
       <c r="B2001">
-        <v>-1</v>
+        <v>8.014092729300103</v>
       </c>
     </row>
     <row r="2002" spans="1:2">
@@ -16387,7 +16387,7 @@
         <v>2000</v>
       </c>
       <c r="B2002">
-        <v>-1</v>
+        <v>3.453052835398118</v>
       </c>
     </row>
     <row r="2003" spans="1:2">
@@ -16899,7 +16899,7 @@
         <v>2064</v>
       </c>
       <c r="B2066">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2067" spans="1:2">
@@ -16907,7 +16907,7 @@
         <v>2065</v>
       </c>
       <c r="B2067">
-        <v>-1</v>
+        <v>5.783602592319292</v>
       </c>
     </row>
     <row r="2068" spans="1:2">
@@ -16915,7 +16915,7 @@
         <v>2066</v>
       </c>
       <c r="B2068">
-        <v>-1</v>
+        <v>3.463248370060246</v>
       </c>
     </row>
     <row r="2069" spans="1:2">
@@ -17283,7 +17283,7 @@
         <v>2112</v>
       </c>
       <c r="B2114">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2115" spans="1:2">
@@ -17291,7 +17291,7 @@
         <v>2113</v>
       </c>
       <c r="B2115">
-        <v>-1</v>
+        <v>15.06697538037417</v>
       </c>
     </row>
     <row r="2116" spans="1:2">
@@ -17299,7 +17299,7 @@
         <v>2114</v>
       </c>
       <c r="B2116">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2117" spans="1:2">
@@ -17715,7 +17715,7 @@
         <v>2166</v>
       </c>
       <c r="B2168">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2169" spans="1:2">
@@ -17723,7 +17723,7 @@
         <v>2167</v>
       </c>
       <c r="B2169">
-        <v>-1</v>
+        <v>39.40820899159354</v>
       </c>
     </row>
     <row r="2170" spans="1:2">
@@ -17731,7 +17731,7 @@
         <v>2168</v>
       </c>
       <c r="B2170">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2171" spans="1:2">
@@ -18243,7 +18243,7 @@
         <v>2232</v>
       </c>
       <c r="B2234">
-        <v>-1</v>
+        <v>3.371326777769079</v>
       </c>
     </row>
     <row r="2235" spans="1:2">
@@ -18251,7 +18251,7 @@
         <v>2233</v>
       </c>
       <c r="B2235">
-        <v>-1</v>
+        <v>6.195284153702652</v>
       </c>
     </row>
     <row r="2236" spans="1:2">
@@ -18259,7 +18259,7 @@
         <v>2234</v>
       </c>
       <c r="B2236">
-        <v>-1</v>
+        <v>3.563961404696148</v>
       </c>
     </row>
     <row r="2237" spans="1:2">
@@ -20931,7 +20931,7 @@
         <v>2568</v>
       </c>
       <c r="B2570">
-        <v>-1</v>
+        <v>5.992906802483999</v>
       </c>
     </row>
     <row r="2571" spans="1:2">
@@ -20939,7 +20939,7 @@
         <v>2569</v>
       </c>
       <c r="B2571">
-        <v>-1</v>
+        <v>8.885150848354051</v>
       </c>
     </row>
     <row r="2572" spans="1:2">
@@ -20947,7 +20947,7 @@
         <v>2570</v>
       </c>
       <c r="B2572">
-        <v>-1</v>
+        <v>4.597302327870246</v>
       </c>
     </row>
     <row r="2573" spans="1:2">
@@ -20979,7 +20979,7 @@
         <v>2574</v>
       </c>
       <c r="B2576">
-        <v>-1</v>
+        <v>4.082409148789523</v>
       </c>
     </row>
     <row r="2577" spans="1:2">
@@ -20987,7 +20987,7 @@
         <v>2575</v>
       </c>
       <c r="B2577">
-        <v>-1</v>
+        <v>5.409222337200115</v>
       </c>
     </row>
     <row r="2578" spans="1:2">
@@ -20995,7 +20995,7 @@
         <v>2576</v>
       </c>
       <c r="B2578">
-        <v>-1</v>
+        <v>3.387847041439884</v>
       </c>
     </row>
     <row r="2579" spans="1:2">
@@ -22083,7 +22083,7 @@
         <v>2712</v>
       </c>
       <c r="B2714">
-        <v>-1</v>
+        <v>4.343408042108987</v>
       </c>
     </row>
     <row r="2715" spans="1:2">
@@ -22091,7 +22091,7 @@
         <v>2713</v>
       </c>
       <c r="B2715">
-        <v>-1</v>
+        <v>4.628080211140961</v>
       </c>
     </row>
     <row r="2716" spans="1:2">
@@ -22099,7 +22099,7 @@
         <v>2714</v>
       </c>
       <c r="B2716">
-        <v>-1</v>
+        <v>3.692838881007476</v>
       </c>
     </row>
     <row r="2717" spans="1:2">
@@ -24963,7 +24963,7 @@
         <v>3072</v>
       </c>
       <c r="B3074">
-        <v>-1</v>
+        <v>4.718757451168454</v>
       </c>
     </row>
     <row r="3075" spans="1:2">
@@ -24971,7 +24971,7 @@
         <v>3073</v>
       </c>
       <c r="B3075">
-        <v>-1</v>
+        <v>136.0520465552852</v>
       </c>
     </row>
     <row r="3076" spans="1:2">
@@ -24979,7 +24979,7 @@
         <v>3074</v>
       </c>
       <c r="B3076">
-        <v>-1</v>
+        <v>4.033792613074905</v>
       </c>
     </row>
     <row r="3077" spans="1:2">
@@ -25851,7 +25851,7 @@
         <v>3183</v>
       </c>
       <c r="B3185">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3186" spans="1:2">
@@ -25859,7 +25859,7 @@
         <v>3184</v>
       </c>
       <c r="B3186">
-        <v>-1</v>
+        <v>11.0066906743545</v>
       </c>
     </row>
     <row r="3187" spans="1:2">
@@ -25867,7 +25867,7 @@
         <v>3185</v>
       </c>
       <c r="B3187">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3188" spans="1:2">
@@ -26427,7 +26427,7 @@
         <v>3255</v>
       </c>
       <c r="B3257">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3258" spans="1:2">
@@ -26435,7 +26435,7 @@
         <v>3256</v>
       </c>
       <c r="B3258">
-        <v>-1</v>
+        <v>12.82095771501159</v>
       </c>
     </row>
     <row r="3259" spans="1:2">
@@ -26443,7 +26443,7 @@
         <v>3257</v>
       </c>
       <c r="B3259">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3260" spans="1:2">
@@ -26571,7 +26571,7 @@
         <v>3273</v>
       </c>
       <c r="B3275">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3276" spans="1:2">
@@ -26579,7 +26579,7 @@
         <v>3274</v>
       </c>
       <c r="B3276">
-        <v>-1</v>
+        <v>17.92610590566307</v>
       </c>
     </row>
     <row r="3277" spans="1:2">
@@ -26587,7 +26587,7 @@
         <v>3275</v>
       </c>
       <c r="B3277">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3278" spans="1:2">
@@ -28443,7 +28443,7 @@
         <v>3507</v>
       </c>
       <c r="B3509">
-        <v>-1</v>
+        <v>8.431190069915628</v>
       </c>
     </row>
     <row r="3510" spans="1:2">
@@ -28451,7 +28451,7 @@
         <v>3508</v>
       </c>
       <c r="B3510">
-        <v>-1</v>
+        <v>8.946981339772208</v>
       </c>
     </row>
     <row r="3511" spans="1:2">
@@ -28459,7 +28459,7 @@
         <v>3509</v>
       </c>
       <c r="B3511">
-        <v>-1</v>
+        <v>7.136207527132987</v>
       </c>
     </row>
     <row r="3512" spans="1:2">
@@ -28539,7 +28539,7 @@
         <v>3519</v>
       </c>
       <c r="B3521">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3522" spans="1:2">
@@ -28547,7 +28547,7 @@
         <v>3520</v>
       </c>
       <c r="B3522">
-        <v>-1</v>
+        <v>3.400938915916929</v>
       </c>
     </row>
     <row r="3523" spans="1:2">
@@ -28555,7 +28555,7 @@
         <v>3521</v>
       </c>
       <c r="B3523">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3524" spans="1:2">
@@ -29595,7 +29595,7 @@
         <v>3651</v>
       </c>
       <c r="B3653">
-        <v>-1</v>
+        <v>11.23724563798866</v>
       </c>
     </row>
     <row r="3654" spans="1:2">
@@ -29603,7 +29603,7 @@
         <v>3652</v>
       </c>
       <c r="B3654">
-        <v>-1</v>
+        <v>20.60618195910786</v>
       </c>
     </row>
     <row r="3655" spans="1:2">
@@ -29611,7 +29611,7 @@
         <v>3653</v>
       </c>
       <c r="B3655">
-        <v>-1</v>
+        <v>9.789798241364267</v>
       </c>
     </row>
     <row r="3656" spans="1:2">
@@ -30507,7 +30507,7 @@
         <v>3765</v>
       </c>
       <c r="B3767">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3768" spans="1:2">
@@ -30515,7 +30515,7 @@
         <v>3766</v>
       </c>
       <c r="B3768">
-        <v>-1</v>
+        <v>3.532101212740102</v>
       </c>
     </row>
     <row r="3769" spans="1:2">
@@ -30523,7 +30523,7 @@
         <v>3767</v>
       </c>
       <c r="B3769">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3770" spans="1:2">
@@ -30699,7 +30699,7 @@
         <v>3789</v>
       </c>
       <c r="B3791">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3792" spans="1:2">
@@ -30707,7 +30707,7 @@
         <v>3790</v>
       </c>
       <c r="B3792">
-        <v>-1</v>
+        <v>3.673840103212722</v>
       </c>
     </row>
     <row r="3793" spans="1:2">
@@ -30715,7 +30715,7 @@
         <v>3791</v>
       </c>
       <c r="B3793">
-        <v>-1</v>
+        <v>3.433707447865131</v>
       </c>
     </row>
     <row r="3794" spans="1:2">
@@ -31011,7 +31011,7 @@
         <v>3828</v>
       </c>
       <c r="B3830">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3831" spans="1:2">
@@ -31019,7 +31019,7 @@
         <v>3829</v>
       </c>
       <c r="B3831">
-        <v>-1</v>
+        <v>3.424570178584152</v>
       </c>
     </row>
     <row r="3832" spans="1:2">
@@ -31027,7 +31027,7 @@
         <v>3830</v>
       </c>
       <c r="B3832">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3833" spans="1:2">
@@ -31107,7 +31107,7 @@
         <v>3840</v>
       </c>
       <c r="B3842">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3843" spans="1:2">
@@ -31115,7 +31115,7 @@
         <v>3841</v>
       </c>
       <c r="B3843">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3844" spans="1:2">
@@ -31123,7 +31123,7 @@
         <v>3842</v>
       </c>
       <c r="B3844">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3845" spans="1:2">
@@ -31299,7 +31299,7 @@
         <v>3864</v>
       </c>
       <c r="B3866">
-        <v>-1</v>
+        <v>4.00675639528929</v>
       </c>
     </row>
     <row r="3867" spans="1:2">
@@ -31307,7 +31307,7 @@
         <v>3865</v>
       </c>
       <c r="B3867">
-        <v>-1</v>
+        <v>4.310625631444931</v>
       </c>
     </row>
     <row r="3868" spans="1:2">
@@ -31315,7 +31315,7 @@
         <v>3866</v>
       </c>
       <c r="B3868">
-        <v>-1</v>
+        <v>3.341025168741352</v>
       </c>
     </row>
     <row r="3869" spans="1:2">
@@ -31779,7 +31779,7 @@
         <v>3924</v>
       </c>
       <c r="B3926">
-        <v>-1</v>
+        <v>3.460532835983543</v>
       </c>
     </row>
     <row r="3927" spans="1:2">
@@ -31787,7 +31787,7 @@
         <v>3925</v>
       </c>
       <c r="B3927">
-        <v>-1</v>
+        <v>4.839823930694576</v>
       </c>
     </row>
     <row r="3928" spans="1:2">
@@ -31795,7 +31795,7 @@
         <v>3926</v>
       </c>
       <c r="B3928">
-        <v>-1</v>
+        <v>3.420181840905423</v>
       </c>
     </row>
     <row r="3929" spans="1:2">
@@ -33579,7 +33579,7 @@
         <v>4149</v>
       </c>
       <c r="B4151">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4152" spans="1:2">
@@ -33587,7 +33587,7 @@
         <v>4150</v>
       </c>
       <c r="B4152">
-        <v>-1</v>
+        <v>4.074746892289339</v>
       </c>
     </row>
     <row r="4153" spans="1:2">
@@ -33595,7 +33595,7 @@
         <v>4151</v>
       </c>
       <c r="B4153">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4154" spans="1:2">
@@ -34563,7 +34563,7 @@
         <v>4272</v>
       </c>
       <c r="B4274">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4275" spans="1:2">
@@ -34571,7 +34571,7 @@
         <v>4273</v>
       </c>
       <c r="B4275">
-        <v>-1</v>
+        <v>41.83253821659134</v>
       </c>
     </row>
     <row r="4276" spans="1:2">
@@ -34579,7 +34579,7 @@
         <v>4274</v>
       </c>
       <c r="B4276">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4277" spans="1:2">
@@ -35307,7 +35307,7 @@
         <v>4365</v>
       </c>
       <c r="B4367">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4368" spans="1:2">
@@ -35315,7 +35315,7 @@
         <v>4366</v>
       </c>
       <c r="B4368">
-        <v>-1</v>
+        <v>4.037548462693696</v>
       </c>
     </row>
     <row r="4369" spans="1:2">
@@ -35323,7 +35323,7 @@
         <v>4367</v>
       </c>
       <c r="B4369">
-        <v>-1</v>
+        <v>3.435762466746328</v>
       </c>
     </row>
     <row r="4370" spans="1:2">
@@ -35907,7 +35907,7 @@
         <v>4440</v>
       </c>
       <c r="B4442">
-        <v>-1</v>
+        <v>4.015389855574192</v>
       </c>
     </row>
     <row r="4443" spans="1:2">
@@ -35915,7 +35915,7 @@
         <v>4441</v>
       </c>
       <c r="B4443">
-        <v>-1</v>
+        <v>9.203259807745734</v>
       </c>
     </row>
     <row r="4444" spans="1:2">
@@ -35923,7 +35923,7 @@
         <v>4442</v>
       </c>
       <c r="B4444">
-        <v>-1</v>
+        <v>3.349347016625193</v>
       </c>
     </row>
     <row r="4445" spans="1:2">
@@ -38331,7 +38331,7 @@
         <v>4743</v>
       </c>
       <c r="B4745">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4746" spans="1:2">
@@ -38339,7 +38339,7 @@
         <v>4744</v>
       </c>
       <c r="B4746">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4747" spans="1:2">
@@ -38347,7 +38347,7 @@
         <v>4745</v>
       </c>
       <c r="B4747">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4748" spans="1:2">
@@ -39291,7 +39291,7 @@
         <v>4863</v>
       </c>
       <c r="B4865">
-        <v>-1</v>
+        <v>4.271898892558301</v>
       </c>
     </row>
     <row r="4866" spans="1:2">
@@ -39299,7 +39299,7 @@
         <v>4864</v>
       </c>
       <c r="B4866">
-        <v>-1</v>
+        <v>7.207680895482005</v>
       </c>
     </row>
     <row r="4867" spans="1:2">
@@ -39307,7 +39307,7 @@
         <v>4865</v>
       </c>
       <c r="B4867">
-        <v>-1</v>
+        <v>4.196394004690818</v>
       </c>
     </row>
     <row r="4868" spans="1:2">
@@ -39411,7 +39411,7 @@
         <v>4878</v>
       </c>
       <c r="B4880">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4881" spans="1:2">
@@ -39419,7 +39419,7 @@
         <v>4879</v>
       </c>
       <c r="B4881">
-        <v>-1</v>
+        <v>4.802194836701634</v>
       </c>
     </row>
     <row r="4882" spans="1:2">
@@ -39427,7 +39427,7 @@
         <v>4880</v>
       </c>
       <c r="B4882">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4883" spans="1:2">
@@ -42843,7 +42843,7 @@
         <v>5307</v>
       </c>
       <c r="B5309">
-        <v>-1</v>
+        <v>8.503621381034389</v>
       </c>
     </row>
     <row r="5310" spans="1:2">
@@ -42851,7 +42851,7 @@
         <v>5308</v>
       </c>
       <c r="B5310">
-        <v>-1</v>
+        <v>20.19973214397132</v>
       </c>
     </row>
     <row r="5311" spans="1:2">
@@ -42859,7 +42859,7 @@
         <v>5309</v>
       </c>
       <c r="B5311">
-        <v>-1</v>
+        <v>8.503621381034389</v>
       </c>
     </row>
     <row r="5312" spans="1:2">
@@ -42939,7 +42939,7 @@
         <v>5319</v>
       </c>
       <c r="B5321">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5322" spans="1:2">
@@ -42947,7 +42947,7 @@
         <v>5320</v>
       </c>
       <c r="B5322">
-        <v>-1</v>
+        <v>4.608535553945736</v>
       </c>
     </row>
     <row r="5323" spans="1:2">
@@ -42955,7 +42955,7 @@
         <v>5321</v>
       </c>
       <c r="B5323">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5324" spans="1:2">
@@ -43707,7 +43707,7 @@
         <v>5415</v>
       </c>
       <c r="B5417">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5418" spans="1:2">
@@ -43715,7 +43715,7 @@
         <v>5416</v>
       </c>
       <c r="B5418">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5419" spans="1:2">
@@ -43723,7 +43723,7 @@
         <v>5417</v>
       </c>
       <c r="B5419">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5420" spans="1:2">
@@ -43947,7 +43947,7 @@
         <v>5445</v>
       </c>
       <c r="B5447">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5448" spans="1:2">
@@ -43955,7 +43955,7 @@
         <v>5446</v>
       </c>
       <c r="B5448">
-        <v>-1</v>
+        <v>113.4758495479898</v>
       </c>
     </row>
     <row r="5449" spans="1:2">
@@ -43963,7 +43963,7 @@
         <v>5447</v>
       </c>
       <c r="B5449">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5450" spans="1:2">
@@ -45939,7 +45939,7 @@
         <v>5694</v>
       </c>
       <c r="B5696">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5697" spans="1:2">
@@ -45947,7 +45947,7 @@
         <v>5695</v>
       </c>
       <c r="B5697">
-        <v>-1</v>
+        <v>39.14482463542814</v>
       </c>
     </row>
     <row r="5698" spans="1:2">
@@ -45955,7 +45955,7 @@
         <v>5696</v>
       </c>
       <c r="B5698">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5699" spans="1:2">
@@ -46995,7 +46995,7 @@
         <v>5826</v>
       </c>
       <c r="B5828">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5829" spans="1:2">
@@ -47003,7 +47003,7 @@
         <v>5827</v>
       </c>
       <c r="B5829">
-        <v>-1</v>
+        <v>3.444873327902276</v>
       </c>
     </row>
     <row r="5830" spans="1:2">
@@ -47011,7 +47011,7 @@
         <v>5828</v>
       </c>
       <c r="B5830">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5831" spans="1:2">
@@ -49251,7 +49251,7 @@
         <v>6108</v>
       </c>
       <c r="B6110">
-        <v>-1</v>
+        <v>7.196177325585329</v>
       </c>
     </row>
     <row r="6111" spans="1:2">
@@ -49259,7 +49259,7 @@
         <v>6109</v>
       </c>
       <c r="B6111">
-        <v>-1</v>
+        <v>9.857180502833319</v>
       </c>
     </row>
     <row r="6112" spans="1:2">
@@ -49267,7 +49267,7 @@
         <v>6110</v>
       </c>
       <c r="B6112">
-        <v>-1</v>
+        <v>7.35507088525349</v>
       </c>
     </row>
     <row r="6113" spans="1:2">
@@ -50115,7 +50115,7 @@
         <v>6216</v>
       </c>
       <c r="B6218">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6219" spans="1:2">
@@ -50123,7 +50123,7 @@
         <v>6217</v>
       </c>
       <c r="B6219">
-        <v>-1</v>
+        <v>6.345980591249811</v>
       </c>
     </row>
     <row r="6220" spans="1:2">
@@ -50131,7 +50131,7 @@
         <v>6218</v>
       </c>
       <c r="B6220">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6221" spans="1:2">
@@ -50691,7 +50691,7 @@
         <v>6288</v>
       </c>
       <c r="B6290">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6291" spans="1:2">
@@ -50699,7 +50699,7 @@
         <v>6289</v>
       </c>
       <c r="B6291">
-        <v>-1</v>
+        <v>9.091638983669682</v>
       </c>
     </row>
     <row r="6292" spans="1:2">
@@ -50707,7 +50707,7 @@
         <v>6290</v>
       </c>
       <c r="B6292">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6293" spans="1:2">
@@ -52851,7 +52851,7 @@
         <v>6558</v>
       </c>
       <c r="B6560">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6561" spans="1:2">
@@ -52859,7 +52859,7 @@
         <v>6559</v>
       </c>
       <c r="B6561">
-        <v>-1</v>
+        <v>39.08746566236809</v>
       </c>
     </row>
     <row r="6562" spans="1:2">
@@ -52867,7 +52867,7 @@
         <v>6560</v>
       </c>
       <c r="B6562">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6563" spans="1:2">
@@ -54147,7 +54147,7 @@
         <v>6720</v>
       </c>
       <c r="B6722">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6723" spans="1:2">
@@ -54155,7 +54155,7 @@
         <v>6721</v>
       </c>
       <c r="B6723">
-        <v>-1</v>
+        <v>17.68221255802113</v>
       </c>
     </row>
     <row r="6724" spans="1:2">
@@ -54163,7 +54163,7 @@
         <v>6722</v>
       </c>
       <c r="B6724">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6725" spans="1:2">
@@ -54723,7 +54723,7 @@
         <v>6792</v>
       </c>
       <c r="B6794">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6795" spans="1:2">
@@ -54731,7 +54731,7 @@
         <v>6793</v>
       </c>
       <c r="B6795">
-        <v>-1</v>
+        <v>43.38425582971867</v>
       </c>
     </row>
     <row r="6796" spans="1:2">
@@ -54739,7 +54739,7 @@
         <v>6794</v>
       </c>
       <c r="B6796">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6797" spans="1:2">
@@ -55107,7 +55107,7 @@
         <v>6840</v>
       </c>
       <c r="B6842">
-        <v>-1</v>
+        <v>3.371326777769079</v>
       </c>
     </row>
     <row r="6843" spans="1:2">
@@ -55115,7 +55115,7 @@
         <v>6841</v>
       </c>
       <c r="B6843">
-        <v>-1</v>
+        <v>6.83290462656756</v>
       </c>
     </row>
     <row r="6844" spans="1:2">
@@ -55123,7 +55123,7 @@
         <v>6842</v>
       </c>
       <c r="B6844">
-        <v>-1</v>
+        <v>3.442065218778434</v>
       </c>
     </row>
     <row r="6845" spans="1:2">
@@ -56163,7 +56163,7 @@
         <v>6972</v>
       </c>
       <c r="B6974">
-        <v>-1</v>
+        <v>9.532883424102456</v>
       </c>
     </row>
     <row r="6975" spans="1:2">
@@ -56171,7 +56171,7 @@
         <v>6973</v>
       </c>
       <c r="B6975">
-        <v>-1</v>
+        <v>11.44819412933759</v>
       </c>
     </row>
     <row r="6976" spans="1:2">
@@ -56179,7 +56179,7 @@
         <v>6974</v>
       </c>
       <c r="B6976">
-        <v>-1</v>
+        <v>9.56895084627385</v>
       </c>
     </row>
     <row r="6977" spans="1:2">
@@ -56619,7 +56619,7 @@
         <v>7029</v>
       </c>
       <c r="B7031">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7032" spans="1:2">
@@ -56627,7 +56627,7 @@
         <v>7030</v>
       </c>
       <c r="B7032">
-        <v>-1</v>
+        <v>3.815558541732422</v>
       </c>
     </row>
     <row r="7033" spans="1:2">
@@ -56635,7 +56635,7 @@
         <v>7031</v>
       </c>
       <c r="B7033">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7034" spans="1:2">
@@ -61107,7 +61107,7 @@
         <v>7590</v>
       </c>
       <c r="B7592">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7593" spans="1:2">
@@ -61115,7 +61115,7 @@
         <v>7591</v>
       </c>
       <c r="B7593">
-        <v>-1</v>
+        <v>6.356356999332347</v>
       </c>
     </row>
     <row r="7594" spans="1:2">
@@ -61123,7 +61123,7 @@
         <v>7592</v>
       </c>
       <c r="B7594">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7595" spans="1:2">
@@ -61227,7 +61227,7 @@
         <v>7605</v>
       </c>
       <c r="B7607">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7608" spans="1:2">
@@ -61235,7 +61235,7 @@
         <v>7606</v>
       </c>
       <c r="B7608">
-        <v>-1</v>
+        <v>5.322904437540821</v>
       </c>
     </row>
     <row r="7609" spans="1:2">
@@ -61243,7 +61243,7 @@
         <v>7607</v>
       </c>
       <c r="B7609">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7610" spans="1:2">
@@ -63747,7 +63747,7 @@
         <v>7920</v>
       </c>
       <c r="B7922">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7923" spans="1:2">
@@ -63755,7 +63755,7 @@
         <v>7921</v>
       </c>
       <c r="B7923">
-        <v>-1</v>
+        <v>5.720233604497049</v>
       </c>
     </row>
     <row r="7924" spans="1:2">
@@ -63763,7 +63763,7 @@
         <v>7922</v>
       </c>
       <c r="B7924">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7925" spans="1:2">
@@ -66291,7 +66291,7 @@
         <v>8238</v>
       </c>
       <c r="B8240">
-        <v>-1</v>
+        <v>3.299999999999881</v>
       </c>
     </row>
     <row r="8241" spans="1:2">
@@ -66299,7 +66299,7 @@
         <v>8239</v>
       </c>
       <c r="B8241">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8242" spans="1:2">
@@ -66307,7 +66307,7 @@
         <v>8240</v>
       </c>
       <c r="B8242">
-        <v>-1</v>
+        <v>3.299999999999881</v>
       </c>
     </row>
     <row r="8243" spans="1:2">
@@ -67443,7 +67443,7 @@
         <v>8382</v>
       </c>
       <c r="B8384">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8385" spans="1:2">
@@ -67451,7 +67451,7 @@
         <v>8383</v>
       </c>
       <c r="B8385">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8386" spans="1:2">
@@ -67459,7 +67459,7 @@
         <v>8384</v>
       </c>
       <c r="B8386">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8387" spans="1:2">
@@ -67683,7 +67683,7 @@
         <v>8412</v>
       </c>
       <c r="B8414">
-        <v>-1</v>
+        <v>9.017244274309332</v>
       </c>
     </row>
     <row r="8415" spans="1:2">
@@ -67691,7 +67691,7 @@
         <v>8413</v>
       </c>
       <c r="B8415">
-        <v>-1</v>
+        <v>11.79318004047318</v>
       </c>
     </row>
     <row r="8416" spans="1:2">
@@ -67699,7 +67699,7 @@
         <v>8414</v>
       </c>
       <c r="B8416">
-        <v>-1</v>
+        <v>9.212426847152265</v>
       </c>
     </row>
     <row r="8417" spans="1:2">
@@ -67971,7 +67971,7 @@
         <v>8448</v>
       </c>
       <c r="B8450">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8451" spans="1:2">
@@ -67979,7 +67979,7 @@
         <v>8449</v>
       </c>
       <c r="B8451">
-        <v>-1</v>
+        <v>3.479647493370597</v>
       </c>
     </row>
     <row r="8452" spans="1:2">
@@ -67987,7 +67987,7 @@
         <v>8450</v>
       </c>
       <c r="B8452">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8453" spans="1:2">
@@ -69843,7 +69843,7 @@
         <v>8682</v>
       </c>
       <c r="B8684">
-        <v>-1</v>
+        <v>8.411493737298404</v>
       </c>
     </row>
     <row r="8685" spans="1:2">
@@ -69851,7 +69851,7 @@
         <v>8683</v>
       </c>
       <c r="B8685">
-        <v>-1</v>
+        <v>15.68804699916028</v>
       </c>
     </row>
     <row r="8686" spans="1:2">
@@ -69859,7 +69859,7 @@
         <v>8684</v>
       </c>
       <c r="B8686">
-        <v>-1</v>
+        <v>8.464343570328946</v>
       </c>
     </row>
     <row r="8687" spans="1:2">
@@ -70179,7 +70179,7 @@
         <v>8724</v>
       </c>
       <c r="B8726">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8727" spans="1:2">
@@ -70187,7 +70187,7 @@
         <v>8725</v>
       </c>
       <c r="B8727">
-        <v>-1</v>
+        <v>4.762641089707486</v>
       </c>
     </row>
     <row r="8728" spans="1:2">
@@ -70195,7 +70195,7 @@
         <v>8726</v>
       </c>
       <c r="B8728">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8729" spans="1:2">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -891,7 +891,7 @@
         <v>63</v>
       </c>
       <c r="B65">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -899,7 +899,7 @@
         <v>64</v>
       </c>
       <c r="B66">
-        <v>-1</v>
+        <v>3.540879826783305</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -907,7 +907,7 @@
         <v>65</v>
       </c>
       <c r="B67">
-        <v>-1</v>
+        <v>3.338133925871967</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1179,7 +1179,7 @@
         <v>99</v>
       </c>
       <c r="B101">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1187,7 +1187,7 @@
         <v>100</v>
       </c>
       <c r="B102">
-        <v>-1</v>
+        <v>3.519057734195297</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1195,7 +1195,7 @@
         <v>101</v>
       </c>
       <c r="B103">
-        <v>-1</v>
+        <v>3.320845940684669</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1371,7 +1371,7 @@
         <v>123</v>
       </c>
       <c r="B125">
-        <v>-1</v>
+        <v>8.46069337180384</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -1379,7 +1379,7 @@
         <v>124</v>
       </c>
       <c r="B126">
-        <v>-1</v>
+        <v>9.156318652114859</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -1387,7 +1387,7 @@
         <v>125</v>
       </c>
       <c r="B127">
-        <v>-1</v>
+        <v>7.396647086293506</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2427,7 +2427,7 @@
         <v>255</v>
       </c>
       <c r="B257">
-        <v>-1</v>
+        <v>4.271898892558301</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -2435,7 +2435,7 @@
         <v>256</v>
       </c>
       <c r="B258">
-        <v>-1</v>
+        <v>6.274107674042916</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -2443,7 +2443,7 @@
         <v>257</v>
       </c>
       <c r="B259">
-        <v>-1</v>
+        <v>3.742233572588471</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -2571,7 +2571,7 @@
         <v>273</v>
       </c>
       <c r="B275">
-        <v>-1</v>
+        <v>4.27468081562401</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -2579,7 +2579,7 @@
         <v>274</v>
       </c>
       <c r="B276">
-        <v>-1</v>
+        <v>6.281192266309821</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -2587,7 +2587,7 @@
         <v>275</v>
       </c>
       <c r="B277">
-        <v>-1</v>
+        <v>3.7442740263541</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3075,7 +3075,7 @@
         <v>336</v>
       </c>
       <c r="B338">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -3083,7 +3083,7 @@
         <v>337</v>
       </c>
       <c r="B339">
-        <v>-1</v>
+        <v>3.741669776557344</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -3091,7 +3091,7 @@
         <v>338</v>
       </c>
       <c r="B340">
-        <v>-1</v>
+        <v>3.378931768778926</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -3483,7 +3483,7 @@
         <v>387</v>
       </c>
       <c r="B389">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -3491,7 +3491,7 @@
         <v>388</v>
       </c>
       <c r="B390">
-        <v>-1</v>
+        <v>3.771312652913594</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -3499,7 +3499,7 @@
         <v>389</v>
       </c>
       <c r="B391">
-        <v>-1</v>
+        <v>3.504213244842291</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -4107,7 +4107,7 @@
         <v>465</v>
       </c>
       <c r="B467">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -4115,7 +4115,7 @@
         <v>466</v>
       </c>
       <c r="B468">
-        <v>-1</v>
+        <v>5.976836259156526</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -4123,7 +4123,7 @@
         <v>467</v>
       </c>
       <c r="B469">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -4179,7 +4179,7 @@
         <v>474</v>
       </c>
       <c r="B476">
-        <v>-1</v>
+        <v>9.624684690902786</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -4187,7 +4187,7 @@
         <v>475</v>
       </c>
       <c r="B477">
-        <v>-1</v>
+        <v>13.92566539357317</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -4195,7 +4195,7 @@
         <v>476</v>
       </c>
       <c r="B478">
-        <v>-1</v>
+        <v>8.691065851788217</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -4275,7 +4275,7 @@
         <v>486</v>
       </c>
       <c r="B488">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -4283,7 +4283,7 @@
         <v>487</v>
       </c>
       <c r="B489">
-        <v>-1</v>
+        <v>4.250725840747349</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -4291,7 +4291,7 @@
         <v>488</v>
       </c>
       <c r="B490">
-        <v>-1</v>
+        <v>3.363045768029882</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -5475,7 +5475,7 @@
         <v>636</v>
       </c>
       <c r="B638">
-        <v>-1</v>
+        <v>7.790744137459948</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -5483,7 +5483,7 @@
         <v>637</v>
       </c>
       <c r="B639">
-        <v>-1</v>
+        <v>10.56814263188477</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -5491,7 +5491,7 @@
         <v>638</v>
       </c>
       <c r="B640">
-        <v>-1</v>
+        <v>6.999282465870527</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -5811,7 +5811,7 @@
         <v>678</v>
       </c>
       <c r="B680">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -5819,7 +5819,7 @@
         <v>679</v>
       </c>
       <c r="B681">
-        <v>-1</v>
+        <v>4.645989098596736</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -5827,7 +5827,7 @@
         <v>680</v>
       </c>
       <c r="B682">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -6027,7 +6027,7 @@
         <v>705</v>
       </c>
       <c r="B707">
-        <v>-1</v>
+        <v>3.496474973477925</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -6035,7 +6035,7 @@
         <v>706</v>
       </c>
       <c r="B708">
-        <v>-1</v>
+        <v>4.795350367034901</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -6043,7 +6043,7 @@
         <v>707</v>
       </c>
       <c r="B709">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -6219,7 +6219,7 @@
         <v>729</v>
       </c>
       <c r="B731">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -6227,7 +6227,7 @@
         <v>730</v>
       </c>
       <c r="B732">
-        <v>-1</v>
+        <v>77.76866985026645</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -6235,7 +6235,7 @@
         <v>731</v>
       </c>
       <c r="B733">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -7107,7 +7107,7 @@
         <v>840</v>
       </c>
       <c r="B842">
-        <v>-1</v>
+        <v>4.252779359590542</v>
       </c>
     </row>
     <row r="843" spans="1:2">
@@ -7115,7 +7115,7 @@
         <v>841</v>
       </c>
       <c r="B843">
-        <v>-1</v>
+        <v>151.7510254665272</v>
       </c>
     </row>
     <row r="844" spans="1:2">
@@ -7123,7 +7123,7 @@
         <v>842</v>
       </c>
       <c r="B844">
-        <v>-1</v>
+        <v>3.7966585031043</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -7395,7 +7395,7 @@
         <v>876</v>
       </c>
       <c r="B878">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -7403,7 +7403,7 @@
         <v>877</v>
       </c>
       <c r="B879">
-        <v>-1</v>
+        <v>4.369692547567105</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -7411,7 +7411,7 @@
         <v>878</v>
       </c>
       <c r="B880">
-        <v>-1</v>
+        <v>3.398928973589466</v>
       </c>
     </row>
     <row r="881" spans="1:2">
@@ -7419,7 +7419,7 @@
         <v>879</v>
       </c>
       <c r="B881">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="882" spans="1:2">
@@ -7427,7 +7427,7 @@
         <v>880</v>
       </c>
       <c r="B882">
-        <v>-1</v>
+        <v>10.02239114780554</v>
       </c>
     </row>
     <row r="883" spans="1:2">
@@ -7435,7 +7435,7 @@
         <v>881</v>
       </c>
       <c r="B883">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="884" spans="1:2">
@@ -7563,7 +7563,7 @@
         <v>897</v>
       </c>
       <c r="B899">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="900" spans="1:2">
@@ -7571,7 +7571,7 @@
         <v>898</v>
       </c>
       <c r="B900">
-        <v>-1</v>
+        <v>12.45668105817599</v>
       </c>
     </row>
     <row r="901" spans="1:2">
@@ -7579,7 +7579,7 @@
         <v>899</v>
       </c>
       <c r="B901">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="902" spans="1:2">
@@ -7755,7 +7755,7 @@
         <v>921</v>
       </c>
       <c r="B923">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="924" spans="1:2">
@@ -7763,7 +7763,7 @@
         <v>922</v>
       </c>
       <c r="B924">
-        <v>-1</v>
+        <v>4.925908672145596</v>
       </c>
     </row>
     <row r="925" spans="1:2">
@@ -7771,7 +7771,7 @@
         <v>923</v>
       </c>
       <c r="B925">
-        <v>-1</v>
+        <v>3.345085916977064</v>
       </c>
     </row>
     <row r="926" spans="1:2">
@@ -10035,7 +10035,7 @@
         <v>1206</v>
       </c>
       <c r="B1208">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
@@ -10043,7 +10043,7 @@
         <v>1207</v>
       </c>
       <c r="B1209">
-        <v>-1</v>
+        <v>3.661247255661593</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
@@ -10051,7 +10051,7 @@
         <v>1208</v>
       </c>
       <c r="B1210">
-        <v>-1</v>
+        <v>3.443992644639682</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
@@ -10107,7 +10107,7 @@
         <v>1215</v>
       </c>
       <c r="B1217">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1218" spans="1:2">
@@ -10115,7 +10115,7 @@
         <v>1216</v>
       </c>
       <c r="B1218">
-        <v>-1</v>
+        <v>3.625191031079522</v>
       </c>
     </row>
     <row r="1219" spans="1:2">
@@ -10123,7 +10123,7 @@
         <v>1217</v>
       </c>
       <c r="B1219">
-        <v>-1</v>
+        <v>3.443992644639682</v>
       </c>
     </row>
     <row r="1220" spans="1:2">
@@ -10875,7 +10875,7 @@
         <v>1311</v>
       </c>
       <c r="B1313">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="1314" spans="1:2">
@@ -10883,7 +10883,7 @@
         <v>1312</v>
       </c>
       <c r="B1314">
-        <v>-1</v>
+        <v>5.651016688486187</v>
       </c>
     </row>
     <row r="1315" spans="1:2">
@@ -10891,7 +10891,7 @@
         <v>1313</v>
       </c>
       <c r="B1315">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1316" spans="1:2">
@@ -10899,7 +10899,7 @@
         <v>1314</v>
       </c>
       <c r="B1316">
-        <v>-1</v>
+        <v>3.505216381174381</v>
       </c>
     </row>
     <row r="1317" spans="1:2">
@@ -10907,7 +10907,7 @@
         <v>1315</v>
       </c>
       <c r="B1317">
-        <v>-1</v>
+        <v>3.631639798155439</v>
       </c>
     </row>
     <row r="1318" spans="1:2">
@@ -10915,7 +10915,7 @@
         <v>1316</v>
       </c>
       <c r="B1318">
-        <v>-1</v>
+        <v>3.536537858932287</v>
       </c>
     </row>
     <row r="1319" spans="1:2">
@@ -10971,7 +10971,7 @@
         <v>1323</v>
       </c>
       <c r="B1325">
-        <v>-1</v>
+        <v>3.352722223750804</v>
       </c>
     </row>
     <row r="1326" spans="1:2">
@@ -10979,7 +10979,7 @@
         <v>1324</v>
       </c>
       <c r="B1326">
-        <v>-1</v>
+        <v>3.697288744666816</v>
       </c>
     </row>
     <row r="1327" spans="1:2">
@@ -10987,7 +10987,7 @@
         <v>1325</v>
       </c>
       <c r="B1327">
-        <v>-1</v>
+        <v>3.536537858932287</v>
       </c>
     </row>
     <row r="1328" spans="1:2">
@@ -11163,7 +11163,7 @@
         <v>1347</v>
       </c>
       <c r="B1349">
-        <v>-1</v>
+        <v>9.266619382900387</v>
       </c>
     </row>
     <row r="1350" spans="1:2">
@@ -11171,7 +11171,7 @@
         <v>1348</v>
       </c>
       <c r="B1350">
-        <v>-1</v>
+        <v>17.10147417544097</v>
       </c>
     </row>
     <row r="1351" spans="1:2">
@@ -11179,7 +11179,7 @@
         <v>1349</v>
       </c>
       <c r="B1351">
-        <v>-1</v>
+        <v>8.365563056264813</v>
       </c>
     </row>
     <row r="1352" spans="1:2">
@@ -12027,7 +12027,7 @@
         <v>1455</v>
       </c>
       <c r="B1457">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1458" spans="1:2">
@@ -12035,7 +12035,7 @@
         <v>1456</v>
       </c>
       <c r="B1458">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1459" spans="1:2">
@@ -12043,7 +12043,7 @@
         <v>1457</v>
       </c>
       <c r="B1459">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1460" spans="1:2">
@@ -12243,7 +12243,7 @@
         <v>1482</v>
       </c>
       <c r="B1484">
-        <v>-1</v>
+        <v>6.751231680395753</v>
       </c>
     </row>
     <row r="1485" spans="1:2">
@@ -12251,7 +12251,7 @@
         <v>1483</v>
       </c>
       <c r="B1485">
-        <v>-1</v>
+        <v>8.485955225043828</v>
       </c>
     </row>
     <row r="1486" spans="1:2">
@@ -12259,7 +12259,7 @@
         <v>1484</v>
       </c>
       <c r="B1486">
-        <v>-1</v>
+        <v>6.14929915898853</v>
       </c>
     </row>
     <row r="1487" spans="1:2">
@@ -12291,7 +12291,7 @@
         <v>1488</v>
       </c>
       <c r="B1490">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1491" spans="1:2">
@@ -12299,7 +12299,7 @@
         <v>1489</v>
       </c>
       <c r="B1491">
-        <v>-1</v>
+        <v>3.724055191435327</v>
       </c>
     </row>
     <row r="1492" spans="1:2">
@@ -12307,7 +12307,7 @@
         <v>1490</v>
       </c>
       <c r="B1492">
-        <v>-1</v>
+        <v>3.459566036821293</v>
       </c>
     </row>
     <row r="1493" spans="1:2">
@@ -12339,7 +12339,7 @@
         <v>1494</v>
       </c>
       <c r="B1496">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1497" spans="1:2">
@@ -12347,7 +12347,7 @@
         <v>1495</v>
       </c>
       <c r="B1497">
-        <v>-1</v>
+        <v>3.965967495370815</v>
       </c>
     </row>
     <row r="1498" spans="1:2">
@@ -12355,7 +12355,7 @@
         <v>1496</v>
       </c>
       <c r="B1498">
-        <v>-1</v>
+        <v>3.608277376510549</v>
       </c>
     </row>
     <row r="1499" spans="1:2">
@@ -12411,7 +12411,7 @@
         <v>1503</v>
       </c>
       <c r="B1505">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1506" spans="1:2">
@@ -12419,7 +12419,7 @@
         <v>1504</v>
       </c>
       <c r="B1506">
-        <v>-1</v>
+        <v>3.858308633420404</v>
       </c>
     </row>
     <row r="1507" spans="1:2">
@@ -12427,7 +12427,7 @@
         <v>1505</v>
       </c>
       <c r="B1507">
-        <v>-1</v>
+        <v>3.608277376510549</v>
       </c>
     </row>
     <row r="1508" spans="1:2">
@@ -13275,7 +13275,7 @@
         <v>1611</v>
       </c>
       <c r="B1613">
-        <v>-1</v>
+        <v>3.468972402105419</v>
       </c>
     </row>
     <row r="1614" spans="1:2">
@@ -13283,7 +13283,7 @@
         <v>1612</v>
       </c>
       <c r="B1614">
-        <v>-1</v>
+        <v>3.732532894347074</v>
       </c>
     </row>
     <row r="1615" spans="1:2">
@@ -13291,7 +13291,7 @@
         <v>1613</v>
       </c>
       <c r="B1615">
-        <v>-1</v>
+        <v>3.592052332525131</v>
       </c>
     </row>
     <row r="1616" spans="1:2">
@@ -13395,7 +13395,7 @@
         <v>1626</v>
       </c>
       <c r="B1628">
-        <v>-1</v>
+        <v>9.552710867989656</v>
       </c>
     </row>
     <row r="1629" spans="1:2">
@@ -13403,7 +13403,7 @@
         <v>1627</v>
       </c>
       <c r="B1629">
-        <v>-1</v>
+        <v>16.03078745257158</v>
       </c>
     </row>
     <row r="1630" spans="1:2">
@@ -13411,7 +13411,7 @@
         <v>1628</v>
       </c>
       <c r="B1630">
-        <v>-1</v>
+        <v>9.146980656604075</v>
       </c>
     </row>
     <row r="1631" spans="1:2">
@@ -13467,7 +13467,7 @@
         <v>1635</v>
       </c>
       <c r="B1637">
-        <v>-1</v>
+        <v>9.981281947216436</v>
       </c>
     </row>
     <row r="1638" spans="1:2">
@@ -13475,7 +13475,7 @@
         <v>1636</v>
       </c>
       <c r="B1638">
-        <v>-1</v>
+        <v>18.83732181181431</v>
       </c>
     </row>
     <row r="1639" spans="1:2">
@@ -13483,7 +13483,7 @@
         <v>1637</v>
       </c>
       <c r="B1639">
-        <v>-1</v>
+        <v>9.146980656604075</v>
       </c>
     </row>
     <row r="1640" spans="1:2">
@@ -13611,7 +13611,7 @@
         <v>1653</v>
       </c>
       <c r="B1655">
-        <v>-1</v>
+        <v>9.985839266832762</v>
       </c>
     </row>
     <row r="1656" spans="1:2">
@@ -13619,7 +13619,7 @@
         <v>1654</v>
       </c>
       <c r="B1656">
-        <v>-1</v>
+        <v>18.8470941776278</v>
       </c>
     </row>
     <row r="1657" spans="1:2">
@@ -13627,7 +13627,7 @@
         <v>1655</v>
       </c>
       <c r="B1657">
-        <v>-1</v>
+        <v>9.15108222370905</v>
       </c>
     </row>
     <row r="1658" spans="1:2">
@@ -14643,7 +14643,7 @@
         <v>1782</v>
       </c>
       <c r="B1784">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1785" spans="1:2">
@@ -14651,7 +14651,7 @@
         <v>1783</v>
       </c>
       <c r="B1785">
-        <v>-1</v>
+        <v>3.874081709325261</v>
       </c>
     </row>
     <row r="1786" spans="1:2">
@@ -14659,7 +14659,7 @@
         <v>1784</v>
       </c>
       <c r="B1786">
-        <v>-1</v>
+        <v>3.448768126096802</v>
       </c>
     </row>
     <row r="1787" spans="1:2">
@@ -15387,7 +15387,7 @@
         <v>1875</v>
       </c>
       <c r="B1877">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1878" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>1876</v>
       </c>
       <c r="B1878">
-        <v>-1</v>
+        <v>6.666206886897541</v>
       </c>
     </row>
     <row r="1879" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>1877</v>
       </c>
       <c r="B1879">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1880" spans="1:2">
@@ -17091,7 +17091,7 @@
         <v>2088</v>
       </c>
       <c r="B2090">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2091" spans="1:2">
@@ -17099,7 +17099,7 @@
         <v>2089</v>
       </c>
       <c r="B2091">
-        <v>-1</v>
+        <v>4.213658139957932</v>
       </c>
     </row>
     <row r="2092" spans="1:2">
@@ -17107,7 +17107,7 @@
         <v>2090</v>
       </c>
       <c r="B2092">
-        <v>-1</v>
+        <v>3.634020463509535</v>
       </c>
     </row>
     <row r="2093" spans="1:2">
@@ -19227,7 +19227,7 @@
         <v>2355</v>
       </c>
       <c r="B2357">
-        <v>-1</v>
+        <v>9.151457215023907</v>
       </c>
     </row>
     <row r="2358" spans="1:2">
@@ -19235,7 +19235,7 @@
         <v>2356</v>
       </c>
       <c r="B2358">
-        <v>-1</v>
+        <v>9.563928735491022</v>
       </c>
     </row>
     <row r="2359" spans="1:2">
@@ -19243,7 +19243,7 @@
         <v>2357</v>
       </c>
       <c r="B2359">
-        <v>-1</v>
+        <v>7.881453957736706</v>
       </c>
     </row>
     <row r="2360" spans="1:2">
@@ -19467,7 +19467,7 @@
         <v>2385</v>
       </c>
       <c r="B2387">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2388" spans="1:2">
@@ -19475,7 +19475,7 @@
         <v>2386</v>
       </c>
       <c r="B2388">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2389" spans="1:2">
@@ -19483,7 +19483,7 @@
         <v>2387</v>
       </c>
       <c r="B2389">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2390" spans="1:2">
@@ -20091,7 +20091,7 @@
         <v>2463</v>
       </c>
       <c r="B2465">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2466" spans="1:2">
@@ -20099,7 +20099,7 @@
         <v>2464</v>
       </c>
       <c r="B2466">
-        <v>-1</v>
+        <v>8.36682820401613</v>
       </c>
     </row>
     <row r="2467" spans="1:2">
@@ -20107,7 +20107,7 @@
         <v>2465</v>
       </c>
       <c r="B2467">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2468" spans="1:2">
@@ -20139,7 +20139,7 @@
         <v>2469</v>
       </c>
       <c r="B2471">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2472" spans="1:2">
@@ -20147,7 +20147,7 @@
         <v>2470</v>
       </c>
       <c r="B2472">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2473" spans="1:2">
@@ -20155,7 +20155,7 @@
         <v>2471</v>
       </c>
       <c r="B2473">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2474" spans="1:2">
@@ -20619,7 +20619,7 @@
         <v>2529</v>
       </c>
       <c r="B2531">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2532" spans="1:2">
@@ -20627,7 +20627,7 @@
         <v>2530</v>
       </c>
       <c r="B2532">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2533" spans="1:2">
@@ -20635,7 +20635,7 @@
         <v>2531</v>
       </c>
       <c r="B2533">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2534" spans="1:2">
@@ -20715,7 +20715,7 @@
         <v>2541</v>
       </c>
       <c r="B2543">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2544" spans="1:2">
@@ -20723,7 +20723,7 @@
         <v>2542</v>
       </c>
       <c r="B2544">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2545" spans="1:2">
@@ -20731,7 +20731,7 @@
         <v>2543</v>
       </c>
       <c r="B2545">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2546" spans="1:2">
@@ -21243,7 +21243,7 @@
         <v>2607</v>
       </c>
       <c r="B2609">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2610" spans="1:2">
@@ -21251,7 +21251,7 @@
         <v>2608</v>
       </c>
       <c r="B2610">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2611" spans="1:2">
@@ -21259,7 +21259,7 @@
         <v>2609</v>
       </c>
       <c r="B2611">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2612" spans="1:2">
@@ -21459,7 +21459,7 @@
         <v>2634</v>
       </c>
       <c r="B2636">
-        <v>-1</v>
+        <v>9.274845306256186</v>
       </c>
     </row>
     <row r="2637" spans="1:2">
@@ -21467,7 +21467,7 @@
         <v>2635</v>
       </c>
       <c r="B2637">
-        <v>-1</v>
+        <v>10.08699795629198</v>
       </c>
     </row>
     <row r="2638" spans="1:2">
@@ -21475,7 +21475,7 @@
         <v>2636</v>
       </c>
       <c r="B2638">
-        <v>-1</v>
+        <v>8.128434713653633</v>
       </c>
     </row>
     <row r="2639" spans="1:2">
@@ -21747,7 +21747,7 @@
         <v>2670</v>
       </c>
       <c r="B2672">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2673" spans="1:2">
@@ -21755,7 +21755,7 @@
         <v>2671</v>
       </c>
       <c r="B2673">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2674" spans="1:2">
@@ -21763,7 +21763,7 @@
         <v>2672</v>
       </c>
       <c r="B2674">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="2675" spans="1:2">
@@ -21867,7 +21867,7 @@
         <v>2685</v>
       </c>
       <c r="B2687">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2688" spans="1:2">
@@ -21875,7 +21875,7 @@
         <v>2686</v>
       </c>
       <c r="B2688">
-        <v>-1</v>
+        <v>3.39510084917507</v>
       </c>
     </row>
     <row r="2689" spans="1:2">
@@ -21883,7 +21883,7 @@
         <v>2687</v>
       </c>
       <c r="B2689">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2690" spans="1:2">
@@ -22395,7 +22395,7 @@
         <v>2751</v>
       </c>
       <c r="B2753">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2754" spans="1:2">
@@ -22403,7 +22403,7 @@
         <v>2752</v>
       </c>
       <c r="B2754">
-        <v>-1</v>
+        <v>8.625655999762783</v>
       </c>
     </row>
     <row r="2755" spans="1:2">
@@ -22411,7 +22411,7 @@
         <v>2753</v>
       </c>
       <c r="B2755">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2756" spans="1:2">
@@ -22515,7 +22515,7 @@
         <v>2766</v>
       </c>
       <c r="B2768">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="2769" spans="1:2">
@@ -22523,7 +22523,7 @@
         <v>2767</v>
       </c>
       <c r="B2769">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2770" spans="1:2">
@@ -22531,7 +22531,7 @@
         <v>2768</v>
       </c>
       <c r="B2770">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2771" spans="1:2">
@@ -23571,7 +23571,7 @@
         <v>2898</v>
       </c>
       <c r="B2900">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2901" spans="1:2">
@@ -23579,7 +23579,7 @@
         <v>2899</v>
       </c>
       <c r="B2901">
-        <v>-1</v>
+        <v>3.627975878489709</v>
       </c>
     </row>
     <row r="2902" spans="1:2">
@@ -23587,7 +23587,7 @@
         <v>2900</v>
       </c>
       <c r="B2902">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2903" spans="1:2">
@@ -23619,7 +23619,7 @@
         <v>2904</v>
       </c>
       <c r="B2906">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2907" spans="1:2">
@@ -23627,7 +23627,7 @@
         <v>2905</v>
       </c>
       <c r="B2907">
-        <v>-1</v>
+        <v>4.191305909668108</v>
       </c>
     </row>
     <row r="2908" spans="1:2">
@@ -23635,7 +23635,7 @@
         <v>2906</v>
       </c>
       <c r="B2908">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2909" spans="1:2">
@@ -23739,7 +23739,7 @@
         <v>2919</v>
       </c>
       <c r="B2921">
-        <v>-1</v>
+        <v>3.671190888220688</v>
       </c>
     </row>
     <row r="2922" spans="1:2">
@@ -23747,7 +23747,7 @@
         <v>2920</v>
       </c>
       <c r="B2922">
-        <v>-1</v>
+        <v>4.475662657229806</v>
       </c>
     </row>
     <row r="2923" spans="1:2">
@@ -23755,7 +23755,7 @@
         <v>2921</v>
       </c>
       <c r="B2923">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2924" spans="1:2">
@@ -23883,7 +23883,7 @@
         <v>2937</v>
       </c>
       <c r="B2939">
-        <v>-1</v>
+        <v>3.842764496775997</v>
       </c>
     </row>
     <row r="2940" spans="1:2">
@@ -23891,7 +23891,7 @@
         <v>2938</v>
       </c>
       <c r="B2940">
-        <v>-1</v>
+        <v>4.994306743053</v>
       </c>
     </row>
     <row r="2941" spans="1:2">
@@ -23899,7 +23899,7 @@
         <v>2939</v>
       </c>
       <c r="B2941">
-        <v>-1</v>
+        <v>3.35555189736968</v>
       </c>
     </row>
     <row r="2942" spans="1:2">
@@ -23907,7 +23907,7 @@
         <v>2940</v>
       </c>
       <c r="B2942">
-        <v>-1</v>
+        <v>9.602653727317179</v>
       </c>
     </row>
     <row r="2943" spans="1:2">
@@ -23915,7 +23915,7 @@
         <v>2941</v>
       </c>
       <c r="B2943">
-        <v>-1</v>
+        <v>12.97812299176634</v>
       </c>
     </row>
     <row r="2944" spans="1:2">
@@ -23923,7 +23923,7 @@
         <v>2942</v>
       </c>
       <c r="B2944">
-        <v>-1</v>
+        <v>8.334845358289433</v>
       </c>
     </row>
     <row r="2945" spans="1:2">
@@ -24171,7 +24171,7 @@
         <v>2973</v>
       </c>
       <c r="B2975">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2976" spans="1:2">
@@ -24179,7 +24179,7 @@
         <v>2974</v>
       </c>
       <c r="B2976">
-        <v>-1</v>
+        <v>3.377246557066882</v>
       </c>
     </row>
     <row r="2977" spans="1:2">
@@ -24187,7 +24187,7 @@
         <v>2975</v>
       </c>
       <c r="B2977">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2978" spans="1:2">
@@ -24363,7 +24363,7 @@
         <v>2997</v>
       </c>
       <c r="B2999">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3000" spans="1:2">
@@ -24371,7 +24371,7 @@
         <v>2998</v>
       </c>
       <c r="B3000">
-        <v>-1</v>
+        <v>4.39954084972941</v>
       </c>
     </row>
     <row r="3001" spans="1:2">
@@ -24379,7 +24379,7 @@
         <v>2999</v>
       </c>
       <c r="B3001">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="3002" spans="1:2">
@@ -24627,7 +24627,7 @@
         <v>3030</v>
       </c>
       <c r="B3032">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3033" spans="1:2">
@@ -24635,7 +24635,7 @@
         <v>3031</v>
       </c>
       <c r="B3033">
-        <v>-1</v>
+        <v>29.89678065822174</v>
       </c>
     </row>
     <row r="3034" spans="1:2">
@@ -24643,7 +24643,7 @@
         <v>3032</v>
       </c>
       <c r="B3034">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3035" spans="1:2">
@@ -25323,7 +25323,7 @@
         <v>3117</v>
       </c>
       <c r="B3119">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3120" spans="1:2">
@@ -25331,7 +25331,7 @@
         <v>3118</v>
       </c>
       <c r="B3120">
-        <v>-1</v>
+        <v>9.854791945741503</v>
       </c>
     </row>
     <row r="3121" spans="1:2">
@@ -25339,7 +25339,7 @@
         <v>3119</v>
       </c>
       <c r="B3121">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="3122" spans="1:2">
@@ -25923,7 +25923,7 @@
         <v>3192</v>
       </c>
       <c r="B3194">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3195" spans="1:2">
@@ -25931,7 +25931,7 @@
         <v>3193</v>
       </c>
       <c r="B3195">
-        <v>-1</v>
+        <v>6.101603466097528</v>
       </c>
     </row>
     <row r="3196" spans="1:2">
@@ -25939,7 +25939,7 @@
         <v>3194</v>
       </c>
       <c r="B3196">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3197" spans="1:2">
@@ -26019,7 +26019,7 @@
         <v>3204</v>
       </c>
       <c r="B3206">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3207" spans="1:2">
@@ -26027,7 +26027,7 @@
         <v>3205</v>
       </c>
       <c r="B3207">
-        <v>-1</v>
+        <v>3.923499165794808</v>
       </c>
     </row>
     <row r="3208" spans="1:2">
@@ -26035,7 +26035,7 @@
         <v>3206</v>
       </c>
       <c r="B3208">
-        <v>-1</v>
+        <v>3.359645251200427</v>
       </c>
     </row>
     <row r="3209" spans="1:2">
@@ -28323,7 +28323,7 @@
         <v>3492</v>
       </c>
       <c r="B3494">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3495" spans="1:2">
@@ -28331,7 +28331,7 @@
         <v>3493</v>
       </c>
       <c r="B3495">
-        <v>-1</v>
+        <v>3.450239558077106</v>
       </c>
     </row>
     <row r="3496" spans="1:2">
@@ -28339,7 +28339,7 @@
         <v>3494</v>
       </c>
       <c r="B3496">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3497" spans="1:2">
@@ -28467,7 +28467,7 @@
         <v>3510</v>
       </c>
       <c r="B3512">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3513" spans="1:2">
@@ -28475,7 +28475,7 @@
         <v>3511</v>
       </c>
       <c r="B3513">
-        <v>-1</v>
+        <v>3.439342740354578</v>
       </c>
     </row>
     <row r="3514" spans="1:2">
@@ -28483,7 +28483,7 @@
         <v>3512</v>
       </c>
       <c r="B3514">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3515" spans="1:2">
@@ -28539,7 +28539,7 @@
         <v>3519</v>
       </c>
       <c r="B3521">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3522" spans="1:2">
@@ -28547,7 +28547,7 @@
         <v>3520</v>
       </c>
       <c r="B3522">
-        <v>-1</v>
+        <v>3.400938915916929</v>
       </c>
     </row>
     <row r="3523" spans="1:2">
@@ -28555,7 +28555,7 @@
         <v>3521</v>
       </c>
       <c r="B3523">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3524" spans="1:2">
@@ -30939,7 +30939,7 @@
         <v>3819</v>
       </c>
       <c r="B3821">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3822" spans="1:2">
@@ -30947,7 +30947,7 @@
         <v>3820</v>
       </c>
       <c r="B3822">
-        <v>-1</v>
+        <v>3.490455034884432</v>
       </c>
     </row>
     <row r="3823" spans="1:2">
@@ -30955,7 +30955,7 @@
         <v>3821</v>
       </c>
       <c r="B3823">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3824" spans="1:2">
@@ -31083,7 +31083,7 @@
         <v>3837</v>
       </c>
       <c r="B3839">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3840" spans="1:2">
@@ -31091,7 +31091,7 @@
         <v>3838</v>
       </c>
       <c r="B3840">
-        <v>-1</v>
+        <v>3.464932799761899</v>
       </c>
     </row>
     <row r="3841" spans="1:2">
@@ -31099,7 +31099,7 @@
         <v>3839</v>
       </c>
       <c r="B3841">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3842" spans="1:2">
@@ -31491,7 +31491,7 @@
         <v>3888</v>
       </c>
       <c r="B3890">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3891" spans="1:2">
@@ -31499,7 +31499,7 @@
         <v>3889</v>
       </c>
       <c r="B3891">
-        <v>-1</v>
+        <v>3.581842168261984</v>
       </c>
     </row>
     <row r="3892" spans="1:2">
@@ -31507,7 +31507,7 @@
         <v>3890</v>
       </c>
       <c r="B3892">
-        <v>-1</v>
+        <v>3.424039618286256</v>
       </c>
     </row>
     <row r="3893" spans="1:2">
@@ -32235,7 +32235,7 @@
         <v>3981</v>
       </c>
       <c r="B3983">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3984" spans="1:2">
@@ -32243,7 +32243,7 @@
         <v>3982</v>
       </c>
       <c r="B3984">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3985" spans="1:2">
@@ -32251,7 +32251,7 @@
         <v>3983</v>
       </c>
       <c r="B3985">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3986" spans="1:2">
@@ -32739,7 +32739,7 @@
         <v>4044</v>
       </c>
       <c r="B4046">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4047" spans="1:2">
@@ -32747,7 +32747,7 @@
         <v>4045</v>
       </c>
       <c r="B4047">
-        <v>-1</v>
+        <v>4.028343861235473</v>
       </c>
     </row>
     <row r="4048" spans="1:2">
@@ -32755,7 +32755,7 @@
         <v>4046</v>
       </c>
       <c r="B4048">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4049" spans="1:2">
@@ -33219,7 +33219,7 @@
         <v>4104</v>
       </c>
       <c r="B4106">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4107" spans="1:2">
@@ -33227,7 +33227,7 @@
         <v>4105</v>
       </c>
       <c r="B4107">
-        <v>-1</v>
+        <v>3.589929596954411</v>
       </c>
     </row>
     <row r="4108" spans="1:2">
@@ -33235,7 +33235,7 @@
         <v>4106</v>
       </c>
       <c r="B4108">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4109" spans="1:2">
@@ -33867,7 +33867,7 @@
         <v>4185</v>
       </c>
       <c r="B4187">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4188" spans="1:2">
@@ -33875,7 +33875,7 @@
         <v>4186</v>
       </c>
       <c r="B4188">
-        <v>-1</v>
+        <v>86.76670339719692</v>
       </c>
     </row>
     <row r="4189" spans="1:2">
@@ -33883,7 +33883,7 @@
         <v>4187</v>
       </c>
       <c r="B4189">
-        <v>-1</v>
+        <v>3.30429788000568</v>
       </c>
     </row>
     <row r="4190" spans="1:2">
@@ -37755,7 +37755,7 @@
         <v>4671</v>
       </c>
       <c r="B4673">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4674" spans="1:2">
@@ -37763,7 +37763,7 @@
         <v>4672</v>
       </c>
       <c r="B4674">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4675" spans="1:2">
@@ -37771,7 +37771,7 @@
         <v>4673</v>
       </c>
       <c r="B4675">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4676" spans="1:2">
@@ -37779,7 +37779,7 @@
         <v>4674</v>
       </c>
       <c r="B4676">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4677" spans="1:2">
@@ -37787,7 +37787,7 @@
         <v>4675</v>
       </c>
       <c r="B4677">
-        <v>-1</v>
+        <v>3.800487113434181</v>
       </c>
     </row>
     <row r="4678" spans="1:2">
@@ -37795,7 +37795,7 @@
         <v>4676</v>
       </c>
       <c r="B4678">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4679" spans="1:2">
@@ -37947,7 +37947,7 @@
         <v>4695</v>
       </c>
       <c r="B4697">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4698" spans="1:2">
@@ -37955,7 +37955,7 @@
         <v>4696</v>
       </c>
       <c r="B4698">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4699" spans="1:2">
@@ -37963,7 +37963,7 @@
         <v>4697</v>
       </c>
       <c r="B4699">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4700" spans="1:2">
@@ -37971,7 +37971,7 @@
         <v>4698</v>
       </c>
       <c r="B4700">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4701" spans="1:2">
@@ -37979,7 +37979,7 @@
         <v>4699</v>
       </c>
       <c r="B4701">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4702" spans="1:2">
@@ -37987,7 +37987,7 @@
         <v>4700</v>
       </c>
       <c r="B4702">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4703" spans="1:2">
@@ -38067,7 +38067,7 @@
         <v>4710</v>
       </c>
       <c r="B4712">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4713" spans="1:2">
@@ -38075,7 +38075,7 @@
         <v>4711</v>
       </c>
       <c r="B4713">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4714" spans="1:2">
@@ -38083,7 +38083,7 @@
         <v>4712</v>
       </c>
       <c r="B4714">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4715" spans="1:2">
@@ -38115,7 +38115,7 @@
         <v>4716</v>
       </c>
       <c r="B4718">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4719" spans="1:2">
@@ -38123,7 +38123,7 @@
         <v>4717</v>
       </c>
       <c r="B4719">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4720" spans="1:2">
@@ -38131,7 +38131,7 @@
         <v>4718</v>
       </c>
       <c r="B4720">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4721" spans="1:2">
@@ -38187,7 +38187,7 @@
         <v>4725</v>
       </c>
       <c r="B4727">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4728" spans="1:2">
@@ -38195,7 +38195,7 @@
         <v>4726</v>
       </c>
       <c r="B4728">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4729" spans="1:2">
@@ -38203,7 +38203,7 @@
         <v>4727</v>
       </c>
       <c r="B4729">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4730" spans="1:2">
@@ -38355,7 +38355,7 @@
         <v>4746</v>
       </c>
       <c r="B4748">
-        <v>-1</v>
+        <v>3.478564081431912</v>
       </c>
     </row>
     <row r="4749" spans="1:2">
@@ -38363,7 +38363,7 @@
         <v>4747</v>
       </c>
       <c r="B4749">
-        <v>-1</v>
+        <v>4.227003373928895</v>
       </c>
     </row>
     <row r="4750" spans="1:2">
@@ -38371,7 +38371,7 @@
         <v>4748</v>
       </c>
       <c r="B4750">
-        <v>-1</v>
+        <v>3.478564081431912</v>
       </c>
     </row>
     <row r="4751" spans="1:2">
@@ -38763,7 +38763,7 @@
         <v>4797</v>
       </c>
       <c r="B4799">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4800" spans="1:2">
@@ -38771,7 +38771,7 @@
         <v>4798</v>
       </c>
       <c r="B4800">
-        <v>-1</v>
+        <v>4.699788060168508</v>
       </c>
     </row>
     <row r="4801" spans="1:2">
@@ -38779,7 +38779,7 @@
         <v>4799</v>
       </c>
       <c r="B4801">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4802" spans="1:2">
@@ -39675,7 +39675,7 @@
         <v>4911</v>
       </c>
       <c r="B4913">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4914" spans="1:2">
@@ -39683,7 +39683,7 @@
         <v>4912</v>
       </c>
       <c r="B4914">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4915" spans="1:2">
@@ -39691,7 +39691,7 @@
         <v>4913</v>
       </c>
       <c r="B4915">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4916" spans="1:2">
@@ -39747,7 +39747,7 @@
         <v>4920</v>
       </c>
       <c r="B4922">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4923" spans="1:2">
@@ -39755,7 +39755,7 @@
         <v>4921</v>
       </c>
       <c r="B4923">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4924" spans="1:2">
@@ -39763,7 +39763,7 @@
         <v>4922</v>
       </c>
       <c r="B4924">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4925" spans="1:2">
@@ -40203,7 +40203,7 @@
         <v>4977</v>
       </c>
       <c r="B4979">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4980" spans="1:2">
@@ -40211,7 +40211,7 @@
         <v>4978</v>
       </c>
       <c r="B4980">
-        <v>-1</v>
+        <v>3.448040237456151</v>
       </c>
     </row>
     <row r="4981" spans="1:2">
@@ -40219,7 +40219,7 @@
         <v>4979</v>
       </c>
       <c r="B4981">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4982" spans="1:2">
@@ -40779,7 +40779,7 @@
         <v>5049</v>
       </c>
       <c r="B5051">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5052" spans="1:2">
@@ -40787,7 +40787,7 @@
         <v>5050</v>
       </c>
       <c r="B5052">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5053" spans="1:2">
@@ -40795,7 +40795,7 @@
         <v>5051</v>
       </c>
       <c r="B5053">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5054" spans="1:2">
@@ -40899,7 +40899,7 @@
         <v>5064</v>
       </c>
       <c r="B5066">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5067" spans="1:2">
@@ -40907,7 +40907,7 @@
         <v>5065</v>
       </c>
       <c r="B5067">
-        <v>-1</v>
+        <v>4.465201523544171</v>
       </c>
     </row>
     <row r="5068" spans="1:2">
@@ -40915,7 +40915,7 @@
         <v>5066</v>
       </c>
       <c r="B5068">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5069" spans="1:2">
@@ -41283,7 +41283,7 @@
         <v>5112</v>
       </c>
       <c r="B5114">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5115" spans="1:2">
@@ -41291,7 +41291,7 @@
         <v>5113</v>
       </c>
       <c r="B5115">
-        <v>-1</v>
+        <v>3.311822418358257</v>
       </c>
     </row>
     <row r="5116" spans="1:2">
@@ -41299,7 +41299,7 @@
         <v>5114</v>
       </c>
       <c r="B5116">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5117" spans="1:2">
@@ -42627,7 +42627,7 @@
         <v>5280</v>
       </c>
       <c r="B5282">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5283" spans="1:2">
@@ -42635,7 +42635,7 @@
         <v>5281</v>
       </c>
       <c r="B5283">
-        <v>-1</v>
+        <v>4.295293851445658</v>
       </c>
     </row>
     <row r="5284" spans="1:2">
@@ -42643,7 +42643,7 @@
         <v>5282</v>
       </c>
       <c r="B5284">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5285" spans="1:2">
@@ -43059,7 +43059,7 @@
         <v>5334</v>
       </c>
       <c r="B5336">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5337" spans="1:2">
@@ -43067,7 +43067,7 @@
         <v>5335</v>
       </c>
       <c r="B5337">
-        <v>-1</v>
+        <v>27.47161230358396</v>
       </c>
     </row>
     <row r="5338" spans="1:2">
@@ -43075,7 +43075,7 @@
         <v>5336</v>
       </c>
       <c r="B5338">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5339" spans="1:2">
@@ -43083,7 +43083,7 @@
         <v>5337</v>
       </c>
       <c r="B5339">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5340" spans="1:2">
@@ -43091,7 +43091,7 @@
         <v>5338</v>
       </c>
       <c r="B5340">
-        <v>-1</v>
+        <v>81.5012368288095</v>
       </c>
     </row>
     <row r="5341" spans="1:2">
@@ -43099,7 +43099,7 @@
         <v>5339</v>
       </c>
       <c r="B5341">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5342" spans="1:2">
@@ -43299,7 +43299,7 @@
         <v>5364</v>
       </c>
       <c r="B5366">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5367" spans="1:2">
@@ -43307,7 +43307,7 @@
         <v>5365</v>
       </c>
       <c r="B5367">
-        <v>-1</v>
+        <v>6.993678057368246</v>
       </c>
     </row>
     <row r="5368" spans="1:2">
@@ -43315,7 +43315,7 @@
         <v>5366</v>
       </c>
       <c r="B5368">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5369" spans="1:2">
@@ -43323,7 +43323,7 @@
         <v>5367</v>
       </c>
       <c r="B5369">
-        <v>-1</v>
+        <v>3.880956286969606</v>
       </c>
     </row>
     <row r="5370" spans="1:2">
@@ -43331,7 +43331,7 @@
         <v>5368</v>
       </c>
       <c r="B5370">
-        <v>-1</v>
+        <v>13.2440109067566</v>
       </c>
     </row>
     <row r="5371" spans="1:2">
@@ -43339,7 +43339,7 @@
         <v>5369</v>
       </c>
       <c r="B5371">
-        <v>-1</v>
+        <v>3.802960489651808</v>
       </c>
     </row>
     <row r="5372" spans="1:2">
@@ -43443,7 +43443,7 @@
         <v>5382</v>
       </c>
       <c r="B5384">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5385" spans="1:2">
@@ -43451,7 +43451,7 @@
         <v>5383</v>
       </c>
       <c r="B5385">
-        <v>-1</v>
+        <v>7.015279068964853</v>
       </c>
     </row>
     <row r="5386" spans="1:2">
@@ -43459,7 +43459,7 @@
         <v>5384</v>
       </c>
       <c r="B5386">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5387" spans="1:2">
@@ -43731,7 +43731,7 @@
         <v>5418</v>
       </c>
       <c r="B5420">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5421" spans="1:2">
@@ -43739,7 +43739,7 @@
         <v>5419</v>
       </c>
       <c r="B5421">
-        <v>-1</v>
+        <v>4.277482309158753</v>
       </c>
     </row>
     <row r="5422" spans="1:2">
@@ -43747,7 +43747,7 @@
         <v>5420</v>
       </c>
       <c r="B5422">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5423" spans="1:2">
@@ -44283,7 +44283,7 @@
         <v>5487</v>
       </c>
       <c r="B5489">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5490" spans="1:2">
@@ -44291,7 +44291,7 @@
         <v>5488</v>
       </c>
       <c r="B5490">
-        <v>-1</v>
+        <v>10.47376751117983</v>
       </c>
     </row>
     <row r="5491" spans="1:2">
@@ -44299,7 +44299,7 @@
         <v>5489</v>
       </c>
       <c r="B5491">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5492" spans="1:2">
@@ -44739,7 +44739,7 @@
         <v>5544</v>
       </c>
       <c r="B5546">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5547" spans="1:2">
@@ -44747,7 +44747,7 @@
         <v>5545</v>
       </c>
       <c r="B5547">
-        <v>-1</v>
+        <v>3.789277765312526</v>
       </c>
     </row>
     <row r="5548" spans="1:2">
@@ -44755,7 +44755,7 @@
         <v>5546</v>
       </c>
       <c r="B5548">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5549" spans="1:2">
@@ -45315,7 +45315,7 @@
         <v>5616</v>
       </c>
       <c r="B5618">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5619" spans="1:2">
@@ -45323,7 +45323,7 @@
         <v>5617</v>
       </c>
       <c r="B5619">
-        <v>-1</v>
+        <v>4.277358486770133</v>
       </c>
     </row>
     <row r="5620" spans="1:2">
@@ -45331,7 +45331,7 @@
         <v>5618</v>
       </c>
       <c r="B5620">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5621" spans="1:2">
@@ -47163,7 +47163,7 @@
         <v>5847</v>
       </c>
       <c r="B5849">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5850" spans="1:2">
@@ -47171,7 +47171,7 @@
         <v>5848</v>
       </c>
       <c r="B5850">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5851" spans="1:2">
@@ -47179,7 +47179,7 @@
         <v>5849</v>
       </c>
       <c r="B5851">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5852" spans="1:2">
@@ -47331,7 +47331,7 @@
         <v>5868</v>
       </c>
       <c r="B5870">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5871" spans="1:2">
@@ -47339,7 +47339,7 @@
         <v>5869</v>
       </c>
       <c r="B5871">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5872" spans="1:2">
@@ -47347,7 +47347,7 @@
         <v>5870</v>
       </c>
       <c r="B5872">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5873" spans="1:2">
@@ -47475,7 +47475,7 @@
         <v>5886</v>
       </c>
       <c r="B5888">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5889" spans="1:2">
@@ -47483,7 +47483,7 @@
         <v>5887</v>
       </c>
       <c r="B5889">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5890" spans="1:2">
@@ -47491,7 +47491,7 @@
         <v>5888</v>
       </c>
       <c r="B5890">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5891" spans="1:2">
@@ -47883,7 +47883,7 @@
         <v>5937</v>
       </c>
       <c r="B5939">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5940" spans="1:2">
@@ -47891,7 +47891,7 @@
         <v>5938</v>
       </c>
       <c r="B5940">
-        <v>-1</v>
+        <v>7.230126635522193</v>
       </c>
     </row>
     <row r="5941" spans="1:2">
@@ -47899,7 +47899,7 @@
         <v>5939</v>
       </c>
       <c r="B5941">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5942" spans="1:2">
@@ -47955,7 +47955,7 @@
         <v>5946</v>
       </c>
       <c r="B5948">
-        <v>-1</v>
+        <v>9.372829322532027</v>
       </c>
     </row>
     <row r="5949" spans="1:2">
@@ -47963,7 +47963,7 @@
         <v>5947</v>
       </c>
       <c r="B5949">
-        <v>-1</v>
+        <v>15.35456153395605</v>
       </c>
     </row>
     <row r="5950" spans="1:2">
@@ -47971,7 +47971,7 @@
         <v>5948</v>
       </c>
       <c r="B5950">
-        <v>-1</v>
+        <v>9.266619382900387</v>
       </c>
     </row>
     <row r="5951" spans="1:2">
@@ -48771,7 +48771,7 @@
         <v>6048</v>
       </c>
       <c r="B6050">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6051" spans="1:2">
@@ -48779,7 +48779,7 @@
         <v>6049</v>
       </c>
       <c r="B6051">
-        <v>-1</v>
+        <v>3.6157053915576</v>
       </c>
     </row>
     <row r="6052" spans="1:2">
@@ -48787,7 +48787,7 @@
         <v>6050</v>
       </c>
       <c r="B6052">
-        <v>-1</v>
+        <v>3.30798110827395</v>
       </c>
     </row>
     <row r="6053" spans="1:2">
@@ -48819,7 +48819,7 @@
         <v>6054</v>
       </c>
       <c r="B6056">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6057" spans="1:2">
@@ -48827,7 +48827,7 @@
         <v>6055</v>
       </c>
       <c r="B6057">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6058" spans="1:2">
@@ -48835,7 +48835,7 @@
         <v>6056</v>
       </c>
       <c r="B6058">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6059" spans="1:2">
@@ -48891,7 +48891,7 @@
         <v>6063</v>
       </c>
       <c r="B6065">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6066" spans="1:2">
@@ -48899,7 +48899,7 @@
         <v>6064</v>
       </c>
       <c r="B6066">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6067" spans="1:2">
@@ -48907,7 +48907,7 @@
         <v>6065</v>
       </c>
       <c r="B6067">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6068" spans="1:2">
@@ -49347,7 +49347,7 @@
         <v>6120</v>
       </c>
       <c r="B6122">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6123" spans="1:2">
@@ -49355,7 +49355,7 @@
         <v>6121</v>
       </c>
       <c r="B6123">
-        <v>-1</v>
+        <v>3.562075854232916</v>
       </c>
     </row>
     <row r="6124" spans="1:2">
@@ -49363,7 +49363,7 @@
         <v>6122</v>
       </c>
       <c r="B6124">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6125" spans="1:2">
@@ -49371,7 +49371,7 @@
         <v>6123</v>
       </c>
       <c r="B6125">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6126" spans="1:2">
@@ -49379,7 +49379,7 @@
         <v>6124</v>
       </c>
       <c r="B6126">
-        <v>-1</v>
+        <v>3.357250716288873</v>
       </c>
     </row>
     <row r="6127" spans="1:2">
@@ -49387,7 +49387,7 @@
         <v>6125</v>
       </c>
       <c r="B6127">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6128" spans="1:2">
@@ -50187,7 +50187,7 @@
         <v>6225</v>
       </c>
       <c r="B6227">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6228" spans="1:2">
@@ -50195,7 +50195,7 @@
         <v>6226</v>
       </c>
       <c r="B6228">
-        <v>-1</v>
+        <v>8.374979594708176</v>
       </c>
     </row>
     <row r="6229" spans="1:2">
@@ -50203,7 +50203,7 @@
         <v>6227</v>
       </c>
       <c r="B6229">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6230" spans="1:2">
@@ -51267,7 +51267,7 @@
         <v>6360</v>
       </c>
       <c r="B6362">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6363" spans="1:2">
@@ -51275,7 +51275,7 @@
         <v>6361</v>
       </c>
       <c r="B6363">
-        <v>-1</v>
+        <v>5.786313927846553</v>
       </c>
     </row>
     <row r="6364" spans="1:2">
@@ -51283,7 +51283,7 @@
         <v>6362</v>
       </c>
       <c r="B6364">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6365" spans="1:2">
@@ -51387,7 +51387,7 @@
         <v>6375</v>
       </c>
       <c r="B6377">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6378" spans="1:2">
@@ -51395,7 +51395,7 @@
         <v>6376</v>
       </c>
       <c r="B6378">
-        <v>-1</v>
+        <v>3.758598749671072</v>
       </c>
     </row>
     <row r="6379" spans="1:2">
@@ -51403,7 +51403,7 @@
         <v>6377</v>
       </c>
       <c r="B6379">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6380" spans="1:2">
@@ -51531,7 +51531,7 @@
         <v>6393</v>
       </c>
       <c r="B6395">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6396" spans="1:2">
@@ -51539,7 +51539,7 @@
         <v>6394</v>
       </c>
       <c r="B6396">
-        <v>-1</v>
+        <v>4.051346913274035</v>
       </c>
     </row>
     <row r="6397" spans="1:2">
@@ -51547,7 +51547,7 @@
         <v>6395</v>
       </c>
       <c r="B6397">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6398" spans="1:2">
@@ -52275,7 +52275,7 @@
         <v>6486</v>
       </c>
       <c r="B6488">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6489" spans="1:2">
@@ -52283,7 +52283,7 @@
         <v>6487</v>
       </c>
       <c r="B6489">
-        <v>-1</v>
+        <v>31.39043683473417</v>
       </c>
     </row>
     <row r="6490" spans="1:2">
@@ -52291,7 +52291,7 @@
         <v>6488</v>
       </c>
       <c r="B6490">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6491" spans="1:2">
@@ -52539,7 +52539,7 @@
         <v>6519</v>
       </c>
       <c r="B6521">
-        <v>-1</v>
+        <v>3.733261714003466</v>
       </c>
     </row>
     <row r="6522" spans="1:2">
@@ -52547,7 +52547,7 @@
         <v>6520</v>
       </c>
       <c r="B6522">
-        <v>-1</v>
+        <v>13.91508048108147</v>
       </c>
     </row>
     <row r="6523" spans="1:2">
@@ -52555,7 +52555,7 @@
         <v>6521</v>
       </c>
       <c r="B6523">
-        <v>-1</v>
+        <v>3.725655208780987</v>
       </c>
     </row>
     <row r="6524" spans="1:2">
@@ -55875,7 +55875,7 @@
         <v>6936</v>
       </c>
       <c r="B6938">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6939" spans="1:2">
@@ -55883,7 +55883,7 @@
         <v>6937</v>
       </c>
       <c r="B6939">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6940" spans="1:2">
@@ -55891,7 +55891,7 @@
         <v>6938</v>
       </c>
       <c r="B6940">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6941" spans="1:2">
@@ -56643,7 +56643,7 @@
         <v>7032</v>
       </c>
       <c r="B7034">
-        <v>-1</v>
+        <v>4.247968470580322</v>
       </c>
     </row>
     <row r="7035" spans="1:2">
@@ -56651,7 +56651,7 @@
         <v>7033</v>
       </c>
       <c r="B7035">
-        <v>-1</v>
+        <v>5.536855302208465</v>
       </c>
     </row>
     <row r="7036" spans="1:2">
@@ -56659,7 +56659,7 @@
         <v>7034</v>
       </c>
       <c r="B7036">
-        <v>-1</v>
+        <v>4.247968470580322</v>
       </c>
     </row>
     <row r="7037" spans="1:2">
@@ -57027,7 +57027,7 @@
         <v>7080</v>
       </c>
       <c r="B7082">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7083" spans="1:2">
@@ -57035,7 +57035,7 @@
         <v>7081</v>
       </c>
       <c r="B7083">
-        <v>-1</v>
+        <v>6.823967555058541</v>
       </c>
     </row>
     <row r="7084" spans="1:2">
@@ -57043,7 +57043,7 @@
         <v>7082</v>
       </c>
       <c r="B7084">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7085" spans="1:2">
@@ -57555,7 +57555,7 @@
         <v>7146</v>
       </c>
       <c r="B7148">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7149" spans="1:2">
@@ -57563,7 +57563,7 @@
         <v>7147</v>
       </c>
       <c r="B7149">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7150" spans="1:2">
@@ -57571,7 +57571,7 @@
         <v>7148</v>
       </c>
       <c r="B7150">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7151" spans="1:2">
@@ -58323,7 +58323,7 @@
         <v>7242</v>
       </c>
       <c r="B7244">
-        <v>-1</v>
+        <v>9.274845306256186</v>
       </c>
     </row>
     <row r="7245" spans="1:2">
@@ -58331,7 +58331,7 @@
         <v>7243</v>
       </c>
       <c r="B7245">
-        <v>-1</v>
+        <v>11.34817527300102</v>
       </c>
     </row>
     <row r="7246" spans="1:2">
@@ -58339,7 +58339,7 @@
         <v>7244</v>
       </c>
       <c r="B7246">
-        <v>-1</v>
+        <v>9.381906501642279</v>
       </c>
     </row>
     <row r="7247" spans="1:2">
@@ -59139,7 +59139,7 @@
         <v>7344</v>
       </c>
       <c r="B7346">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7347" spans="1:2">
@@ -59147,7 +59147,7 @@
         <v>7345</v>
       </c>
       <c r="B7347">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="7348" spans="1:2">
@@ -59155,7 +59155,7 @@
         <v>7346</v>
       </c>
       <c r="B7348">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7349" spans="1:2">
@@ -59187,7 +59187,7 @@
         <v>7350</v>
       </c>
       <c r="B7352">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7353" spans="1:2">
@@ -59195,7 +59195,7 @@
         <v>7351</v>
       </c>
       <c r="B7353">
-        <v>-1</v>
+        <v>7.544407173693279</v>
       </c>
     </row>
     <row r="7354" spans="1:2">
@@ -59203,7 +59203,7 @@
         <v>7352</v>
       </c>
       <c r="B7354">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7355" spans="1:2">
@@ -65211,7 +65211,7 @@
         <v>8103</v>
       </c>
       <c r="B8105">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8106" spans="1:2">
@@ -65219,7 +65219,7 @@
         <v>8104</v>
       </c>
       <c r="B8106">
-        <v>-1</v>
+        <v>3.964872287250465</v>
       </c>
     </row>
     <row r="8107" spans="1:2">
@@ -65227,7 +65227,7 @@
         <v>8105</v>
       </c>
       <c r="B8107">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8108" spans="1:2">
@@ -66075,7 +66075,7 @@
         <v>8211</v>
       </c>
       <c r="B8213">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8214" spans="1:2">
@@ -66083,7 +66083,7 @@
         <v>8212</v>
       </c>
       <c r="B8214">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8215" spans="1:2">
@@ -66091,7 +66091,7 @@
         <v>8213</v>
       </c>
       <c r="B8215">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8216" spans="1:2">
@@ -66387,7 +66387,7 @@
         <v>8250</v>
       </c>
       <c r="B8252">
-        <v>-1</v>
+        <v>11.2953972128104</v>
       </c>
     </row>
     <row r="8253" spans="1:2">
@@ -66395,7 +66395,7 @@
         <v>8251</v>
       </c>
       <c r="B8253">
-        <v>-1</v>
+        <v>19.97492042199202</v>
       </c>
     </row>
     <row r="8254" spans="1:2">
@@ -66403,7 +66403,7 @@
         <v>8252</v>
       </c>
       <c r="B8254">
-        <v>-1</v>
+        <v>11.23724563798866</v>
       </c>
     </row>
     <row r="8255" spans="1:2">
@@ -66699,7 +66699,7 @@
         <v>8289</v>
       </c>
       <c r="B8291">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8292" spans="1:2">
@@ -66707,7 +66707,7 @@
         <v>8290</v>
       </c>
       <c r="B8292">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8293" spans="1:2">
@@ -66715,7 +66715,7 @@
         <v>8291</v>
       </c>
       <c r="B8293">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8294" spans="1:2">
@@ -66843,7 +66843,7 @@
         <v>8307</v>
       </c>
       <c r="B8309">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8310" spans="1:2">
@@ -66851,7 +66851,7 @@
         <v>8308</v>
       </c>
       <c r="B8310">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8311" spans="1:2">
@@ -66859,7 +66859,7 @@
         <v>8309</v>
       </c>
       <c r="B8311">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8312" spans="1:2">
@@ -68403,7 +68403,7 @@
         <v>8502</v>
       </c>
       <c r="B8504">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8505" spans="1:2">
@@ -68411,7 +68411,7 @@
         <v>8503</v>
       </c>
       <c r="B8505">
-        <v>-1</v>
+        <v>10.10688208065409</v>
       </c>
     </row>
     <row r="8506" spans="1:2">
@@ -68419,7 +68419,7 @@
         <v>8504</v>
       </c>
       <c r="B8506">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8507" spans="1:2">
@@ -68691,7 +68691,7 @@
         <v>8538</v>
       </c>
       <c r="B8540">
-        <v>-1</v>
+        <v>11.53323907906057</v>
       </c>
     </row>
     <row r="8541" spans="1:2">
@@ -68699,7 +68699,7 @@
         <v>8539</v>
       </c>
       <c r="B8541">
-        <v>-1</v>
+        <v>23.49845632171659</v>
       </c>
     </row>
     <row r="8542" spans="1:2">
@@ -68707,7 +68707,7 @@
         <v>8540</v>
       </c>
       <c r="B8542">
-        <v>-1</v>
+        <v>12.13381393323756</v>
       </c>
     </row>
     <row r="8543" spans="1:2">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -639,17 +639,17 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>-1</v>
+        <v>7.334687434564635</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>-1</v>
+        <v>8.178237199860005</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>-1</v>
+        <v>6.549972307376173</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -699,47 +699,47 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>-1</v>
+        <v>3.540879826783305</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>-1</v>
+        <v>3.338133925871967</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>-1</v>
+        <v>3.529010534004595</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>-1</v>
+        <v>7.744707573121512</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>-1</v>
+        <v>8.770310549114534</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>-1</v>
+        <v>6.954087084430538</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -819,17 +819,17 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -849,17 +849,17 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>-1</v>
+        <v>3.34232628959974</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -894,32 +894,32 @@
     </row>
     <row r="104" spans="1:1">
       <c r="A104">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105">
-        <v>-1</v>
+        <v>3.31891731446281</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="110" spans="1:1">
@@ -984,32 +984,32 @@
     </row>
     <row r="122" spans="1:1">
       <c r="A122">
-        <v>-1</v>
+        <v>3.307493888349622</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123">
-        <v>-1</v>
+        <v>3.582897942807683</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125">
-        <v>-1</v>
+        <v>8.46069337180384</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126">
-        <v>-1</v>
+        <v>9.156318652114859</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127">
-        <v>-1</v>
+        <v>7.396647086293506</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -1179,17 +1179,17 @@
     </row>
     <row r="161" spans="1:1">
       <c r="A161">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162">
-        <v>-1</v>
+        <v>6.014892951029427</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="164" spans="1:1">
@@ -1209,17 +1209,17 @@
     </row>
     <row r="167" spans="1:1">
       <c r="A167">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168">
-        <v>-1</v>
+        <v>3.307582527142028</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="170" spans="1:1">
@@ -1269,17 +1269,17 @@
     </row>
     <row r="179" spans="1:1">
       <c r="A179">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180">
-        <v>-1</v>
+        <v>6.0236565375827</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="182" spans="1:1">
@@ -1314,77 +1314,77 @@
     </row>
     <row r="188" spans="1:1">
       <c r="A188">
-        <v>-1</v>
+        <v>9.633206740732991</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189">
-        <v>-1</v>
+        <v>13.32739815389843</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190">
-        <v>-1</v>
+        <v>8.596316671461523</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192">
-        <v>-1</v>
+        <v>4.267349044257152</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194">
-        <v>-1</v>
+        <v>3.752316691253654</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195">
-        <v>-1</v>
+        <v>6.343552104504779</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196">
-        <v>-1</v>
+        <v>3.422734364086577</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197">
-        <v>-1</v>
+        <v>9.422724604801058</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198">
-        <v>-1</v>
+        <v>17.64371398953492</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199">
-        <v>-1</v>
+        <v>8.596316671461523</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201">
-        <v>-1</v>
+        <v>3.952006504699801</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="203" spans="1:1">
@@ -1524,47 +1524,47 @@
     </row>
     <row r="230" spans="1:1">
       <c r="A230">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234">
-        <v>-1</v>
+        <v>7.948044726277415</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237">
-        <v>-1</v>
+        <v>3.465619211713178</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="239" spans="1:1">
@@ -1674,17 +1674,17 @@
     </row>
     <row r="260" spans="1:1">
       <c r="A260">
-        <v>-1</v>
+        <v>11.01031228660917</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261">
-        <v>-1</v>
+        <v>15.7487340299825</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262">
-        <v>-1</v>
+        <v>9.645844289694915</v>
       </c>
     </row>
     <row r="263" spans="1:1">
@@ -1974,17 +1974,17 @@
     </row>
     <row r="320" spans="1:1">
       <c r="A320">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321">
-        <v>-1</v>
+        <v>3.637464046655969</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322">
-        <v>-1</v>
+        <v>3.348986682038624</v>
       </c>
     </row>
     <row r="323" spans="1:1">
@@ -2049,17 +2049,17 @@
     </row>
     <row r="335" spans="1:1">
       <c r="A335">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336">
-        <v>-1</v>
+        <v>3.825150586786741</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337">
-        <v>-1</v>
+        <v>3.559868452588155</v>
       </c>
     </row>
     <row r="338" spans="1:1">
@@ -2094,32 +2094,32 @@
     </row>
     <row r="344" spans="1:1">
       <c r="A344">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="345" spans="1:1">
       <c r="A345">
-        <v>-1</v>
+        <v>3.831701549077371</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346">
-        <v>-1</v>
+        <v>3.520333945297716</v>
       </c>
     </row>
     <row r="347" spans="1:1">
       <c r="A347">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348">
-        <v>-1</v>
+        <v>3.991902205165732</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349">
-        <v>-1</v>
+        <v>3.336222411265832</v>
       </c>
     </row>
     <row r="350" spans="1:1">
@@ -2244,32 +2244,32 @@
     </row>
     <row r="374" spans="1:1">
       <c r="A374">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="375" spans="1:1">
       <c r="A375">
-        <v>-1</v>
+        <v>3.640121624493675</v>
       </c>
     </row>
     <row r="376" spans="1:1">
       <c r="A376">
-        <v>-1</v>
+        <v>3.359042936831158</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="380" spans="1:1">
@@ -2289,17 +2289,17 @@
     </row>
     <row r="383" spans="1:1">
       <c r="A383">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="384" spans="1:1">
       <c r="A384">
-        <v>-1</v>
+        <v>3.64102740113621</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385">
-        <v>-1</v>
+        <v>3.315780413959724</v>
       </c>
     </row>
     <row r="386" spans="1:1">
@@ -2604,17 +2604,17 @@
     </row>
     <row r="446" spans="1:1">
       <c r="A446">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="447" spans="1:1">
       <c r="A447">
-        <v>-1</v>
+        <v>3.351078227195603</v>
       </c>
     </row>
     <row r="448" spans="1:1">
       <c r="A448">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="449" spans="1:1">
@@ -2634,17 +2634,17 @@
     </row>
     <row r="452" spans="1:1">
       <c r="A452">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="453" spans="1:1">
       <c r="A453">
-        <v>-1</v>
+        <v>3.71677213093784</v>
       </c>
     </row>
     <row r="454" spans="1:1">
       <c r="A454">
-        <v>-1</v>
+        <v>3.381028318788926</v>
       </c>
     </row>
     <row r="455" spans="1:1">
@@ -2724,32 +2724,32 @@
     </row>
     <row r="470" spans="1:1">
       <c r="A470">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="471" spans="1:1">
       <c r="A471">
-        <v>-1</v>
+        <v>4.248928277297592</v>
       </c>
     </row>
     <row r="472" spans="1:1">
       <c r="A472">
-        <v>-1</v>
+        <v>3.363503462445805</v>
       </c>
     </row>
     <row r="473" spans="1:1">
       <c r="A473">
-        <v>-1</v>
+        <v>3.825444230335506</v>
       </c>
     </row>
     <row r="474" spans="1:1">
       <c r="A474">
-        <v>-1</v>
+        <v>5.827433505326218</v>
       </c>
     </row>
     <row r="475" spans="1:1">
       <c r="A475">
-        <v>-1</v>
+        <v>3.471889798073025</v>
       </c>
     </row>
     <row r="476" spans="1:1">
@@ -2874,17 +2874,17 @@
     </row>
     <row r="500" spans="1:1">
       <c r="A500">
-        <v>-1</v>
+        <v>3.778365912883286</v>
       </c>
     </row>
     <row r="501" spans="1:1">
       <c r="A501">
-        <v>-1</v>
+        <v>6.517880014462774</v>
       </c>
     </row>
     <row r="502" spans="1:1">
       <c r="A502">
-        <v>-1</v>
+        <v>3.473335840763969</v>
       </c>
     </row>
     <row r="503" spans="1:1">
@@ -2919,32 +2919,32 @@
     </row>
     <row r="509" spans="1:1">
       <c r="A509">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="510" spans="1:1">
       <c r="A510">
-        <v>-1</v>
+        <v>3.496766215949743</v>
       </c>
     </row>
     <row r="511" spans="1:1">
       <c r="A511">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="512" spans="1:1">
       <c r="A512">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="513" spans="1:1">
       <c r="A513">
-        <v>-1</v>
+        <v>4.696437757251126</v>
       </c>
     </row>
     <row r="514" spans="1:1">
       <c r="A514">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="515" spans="1:1">
@@ -2964,17 +2964,17 @@
     </row>
     <row r="518" spans="1:1">
       <c r="A518">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="519" spans="1:1">
       <c r="A519">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="520" spans="1:1">
       <c r="A520">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="521" spans="1:1">
@@ -3009,17 +3009,17 @@
     </row>
     <row r="527" spans="1:1">
       <c r="A527">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="528" spans="1:1">
       <c r="A528">
-        <v>-1</v>
+        <v>3.495441465748073</v>
       </c>
     </row>
     <row r="529" spans="1:1">
       <c r="A529">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="530" spans="1:1">
@@ -3399,32 +3399,32 @@
     </row>
     <row r="605" spans="1:1">
       <c r="A605">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="606" spans="1:1">
       <c r="A606">
-        <v>-1</v>
+        <v>3.860272177404456</v>
       </c>
     </row>
     <row r="607" spans="1:1">
       <c r="A607">
-        <v>-1</v>
+        <v>3.3567363449303</v>
       </c>
     </row>
     <row r="608" spans="1:1">
       <c r="A608">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="609" spans="1:1">
       <c r="A609">
-        <v>-1</v>
+        <v>4.467033351254646</v>
       </c>
     </row>
     <row r="610" spans="1:1">
       <c r="A610">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="611" spans="1:1">
@@ -3534,17 +3534,17 @@
     </row>
     <row r="632" spans="1:1">
       <c r="A632">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="633" spans="1:1">
       <c r="A633">
-        <v>-1</v>
+        <v>3.84751080321617</v>
       </c>
     </row>
     <row r="634" spans="1:1">
       <c r="A634">
-        <v>-1</v>
+        <v>3.344490155225111</v>
       </c>
     </row>
     <row r="635" spans="1:1">
@@ -3564,17 +3564,17 @@
     </row>
     <row r="638" spans="1:1">
       <c r="A638">
-        <v>-1</v>
+        <v>7.790744137459948</v>
       </c>
     </row>
     <row r="639" spans="1:1">
       <c r="A639">
-        <v>-1</v>
+        <v>10.56814263188477</v>
       </c>
     </row>
     <row r="640" spans="1:1">
       <c r="A640">
-        <v>-1</v>
+        <v>6.999282465870527</v>
       </c>
     </row>
     <row r="641" spans="1:1">
@@ -3594,17 +3594,17 @@
     </row>
     <row r="644" spans="1:1">
       <c r="A644">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="645" spans="1:1">
       <c r="A645">
-        <v>-1</v>
+        <v>6.054005689111575</v>
       </c>
     </row>
     <row r="646" spans="1:1">
       <c r="A646">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="647" spans="1:1">
@@ -3714,32 +3714,32 @@
     </row>
     <row r="668" spans="1:1">
       <c r="A668">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="669" spans="1:1">
       <c r="A669">
-        <v>-1</v>
+        <v>3.822575705818587</v>
       </c>
     </row>
     <row r="670" spans="1:1">
       <c r="A670">
-        <v>-1</v>
+        <v>3.32712164619795</v>
       </c>
     </row>
     <row r="671" spans="1:1">
       <c r="A671">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="672" spans="1:1">
       <c r="A672">
-        <v>-1</v>
+        <v>3.649634676888436</v>
       </c>
     </row>
     <row r="673" spans="1:1">
       <c r="A673">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="674" spans="1:1">
@@ -3759,32 +3759,32 @@
     </row>
     <row r="677" spans="1:1">
       <c r="A677">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="678" spans="1:1">
       <c r="A678">
-        <v>-1</v>
+        <v>3.825401112224314</v>
       </c>
     </row>
     <row r="679" spans="1:1">
       <c r="A679">
-        <v>-1</v>
+        <v>3.32712164619795</v>
       </c>
     </row>
     <row r="680" spans="1:1">
       <c r="A680">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="681" spans="1:1">
       <c r="A681">
-        <v>-1</v>
+        <v>4.645989098596736</v>
       </c>
     </row>
     <row r="682" spans="1:1">
       <c r="A682">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="683" spans="1:1">
@@ -3804,17 +3804,17 @@
     </row>
     <row r="686" spans="1:1">
       <c r="A686">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="687" spans="1:1">
       <c r="A687">
-        <v>-1</v>
+        <v>3.81535728240654</v>
       </c>
     </row>
     <row r="688" spans="1:1">
       <c r="A688">
-        <v>-1</v>
+        <v>3.341602002091593</v>
       </c>
     </row>
     <row r="689" spans="1:1">
@@ -3849,17 +3849,17 @@
     </row>
     <row r="695" spans="1:1">
       <c r="A695">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="696" spans="1:1">
       <c r="A696">
-        <v>-1</v>
+        <v>3.933138444134943</v>
       </c>
     </row>
     <row r="697" spans="1:1">
       <c r="A697">
-        <v>-1</v>
+        <v>3.341602002091593</v>
       </c>
     </row>
     <row r="698" spans="1:1">
@@ -3939,17 +3939,17 @@
     </row>
     <row r="713" spans="1:1">
       <c r="A713">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="714" spans="1:1">
       <c r="A714">
-        <v>-1</v>
+        <v>4.305590183067065</v>
       </c>
     </row>
     <row r="715" spans="1:1">
       <c r="A715">
-        <v>-1</v>
+        <v>3.313312588990369</v>
       </c>
     </row>
     <row r="716" spans="1:1">
@@ -3984,17 +3984,17 @@
     </row>
     <row r="722" spans="1:1">
       <c r="A722">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="723" spans="1:1">
       <c r="A723">
-        <v>-1</v>
+        <v>3.882874209921328</v>
       </c>
     </row>
     <row r="724" spans="1:1">
       <c r="A724">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="725" spans="1:1">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="734" spans="1:1">
       <c r="A734">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="735" spans="1:1">
       <c r="A735">
-        <v>-1</v>
+        <v>107.2735874974383</v>
       </c>
     </row>
     <row r="736" spans="1:1">
       <c r="A736">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="737" spans="1:1">
       <c r="A737">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="738" spans="1:1">
       <c r="A738">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="739" spans="1:1">
       <c r="A739">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="740" spans="1:1">
@@ -4089,17 +4089,17 @@
     </row>
     <row r="743" spans="1:1">
       <c r="A743">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="744" spans="1:1">
       <c r="A744">
-        <v>-1</v>
+        <v>5.931746605160937</v>
       </c>
     </row>
     <row r="745" spans="1:1">
       <c r="A745">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="746" spans="1:1">
@@ -4119,17 +4119,17 @@
     </row>
     <row r="749" spans="1:1">
       <c r="A749">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="750" spans="1:1">
       <c r="A750">
-        <v>-1</v>
+        <v>77.78129171906397</v>
       </c>
     </row>
     <row r="751" spans="1:1">
       <c r="A751">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="752" spans="1:1">
@@ -4164,17 +4164,17 @@
     </row>
     <row r="758" spans="1:1">
       <c r="A758">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="759" spans="1:1">
       <c r="A759">
-        <v>-1</v>
+        <v>6.363008695484673</v>
       </c>
     </row>
     <row r="760" spans="1:1">
       <c r="A760">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="761" spans="1:1">
@@ -4344,62 +4344,62 @@
     </row>
     <row r="794" spans="1:1">
       <c r="A794">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="795" spans="1:1">
       <c r="A795">
-        <v>-1</v>
+        <v>3.867416533339496</v>
       </c>
     </row>
     <row r="796" spans="1:1">
       <c r="A796">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="797" spans="1:1">
       <c r="A797">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="798" spans="1:1">
       <c r="A798">
-        <v>-1</v>
+        <v>7.131718659580466</v>
       </c>
     </row>
     <row r="799" spans="1:1">
       <c r="A799">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="800" spans="1:1">
       <c r="A800">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="801" spans="1:1">
       <c r="A801">
-        <v>-1</v>
+        <v>29.59246160775354</v>
       </c>
     </row>
     <row r="802" spans="1:1">
       <c r="A802">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="803" spans="1:1">
       <c r="A803">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="804" spans="1:1">
       <c r="A804">
-        <v>-1</v>
+        <v>90.62696879667058</v>
       </c>
     </row>
     <row r="805" spans="1:1">
       <c r="A805">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="806" spans="1:1">
@@ -4464,17 +4464,17 @@
     </row>
     <row r="818" spans="1:1">
       <c r="A818">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="819" spans="1:1">
       <c r="A819">
-        <v>-1</v>
+        <v>29.69710375652512</v>
       </c>
     </row>
     <row r="820" spans="1:1">
       <c r="A820">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="821" spans="1:1">
@@ -4809,17 +4809,17 @@
     </row>
     <row r="887" spans="1:1">
       <c r="A887">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="888" spans="1:1">
       <c r="A888">
-        <v>-1</v>
+        <v>4.097586606340187</v>
       </c>
     </row>
     <row r="889" spans="1:1">
       <c r="A889">
-        <v>-1</v>
+        <v>3.357626330276697</v>
       </c>
     </row>
     <row r="890" spans="1:1">
@@ -4839,32 +4839,32 @@
     </row>
     <row r="893" spans="1:1">
       <c r="A893">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="894" spans="1:1">
       <c r="A894">
-        <v>-1</v>
+        <v>4.374700202987425</v>
       </c>
     </row>
     <row r="895" spans="1:1">
       <c r="A895">
-        <v>-1</v>
+        <v>3.538844462147384</v>
       </c>
     </row>
     <row r="896" spans="1:1">
       <c r="A896">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="897" spans="1:1">
       <c r="A897">
-        <v>-1</v>
+        <v>5.31461031498166</v>
       </c>
     </row>
     <row r="898" spans="1:1">
       <c r="A898">
-        <v>-1</v>
+        <v>3.357626330276697</v>
       </c>
     </row>
     <row r="899" spans="1:1">
@@ -4884,17 +4884,17 @@
     </row>
     <row r="902" spans="1:1">
       <c r="A902">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="903" spans="1:1">
       <c r="A903">
-        <v>-1</v>
+        <v>4.375428339173726</v>
       </c>
     </row>
     <row r="904" spans="1:1">
       <c r="A904">
-        <v>-1</v>
+        <v>3.566911641349857</v>
       </c>
     </row>
     <row r="905" spans="1:1">
@@ -4929,32 +4929,32 @@
     </row>
     <row r="911" spans="1:1">
       <c r="A911">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="912" spans="1:1">
       <c r="A912">
-        <v>-1</v>
+        <v>4.371893313295105</v>
       </c>
     </row>
     <row r="913" spans="1:1">
       <c r="A913">
-        <v>-1</v>
+        <v>3.566911641349857</v>
       </c>
     </row>
     <row r="914" spans="1:1">
       <c r="A914">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="915" spans="1:1">
       <c r="A915">
-        <v>-1</v>
+        <v>5.452892442228197</v>
       </c>
     </row>
     <row r="916" spans="1:1">
       <c r="A916">
-        <v>-1</v>
+        <v>3.386895574781934</v>
       </c>
     </row>
     <row r="917" spans="1:1">
@@ -4989,17 +4989,17 @@
     </row>
     <row r="923" spans="1:1">
       <c r="A923">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="924" spans="1:1">
       <c r="A924">
-        <v>-1</v>
+        <v>4.925908672145596</v>
       </c>
     </row>
     <row r="925" spans="1:1">
       <c r="A925">
-        <v>-1</v>
+        <v>3.345085916977064</v>
       </c>
     </row>
     <row r="926" spans="1:1">
@@ -5064,17 +5064,17 @@
     </row>
     <row r="938" spans="1:1">
       <c r="A938">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="939" spans="1:1">
       <c r="A939">
-        <v>-1</v>
+        <v>4.334685753757284</v>
       </c>
     </row>
     <row r="940" spans="1:1">
       <c r="A940">
-        <v>-1</v>
+        <v>3.551267871135133</v>
       </c>
     </row>
     <row r="941" spans="1:1">
@@ -5109,17 +5109,17 @@
     </row>
     <row r="947" spans="1:1">
       <c r="A947">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="948" spans="1:1">
       <c r="A948">
-        <v>-1</v>
+        <v>4.328686820767036</v>
       </c>
     </row>
     <row r="949" spans="1:1">
       <c r="A949">
-        <v>-1</v>
+        <v>3.551267871135133</v>
       </c>
     </row>
     <row r="950" spans="1:1">
@@ -5304,17 +5304,17 @@
     </row>
     <row r="986" spans="1:1">
       <c r="A986">
-        <v>-1</v>
+        <v>3.408739267436267</v>
       </c>
     </row>
     <row r="987" spans="1:1">
       <c r="A987">
-        <v>-1</v>
+        <v>6.394729886706241</v>
       </c>
     </row>
     <row r="988" spans="1:1">
       <c r="A988">
-        <v>-1</v>
+        <v>3.353360342580647</v>
       </c>
     </row>
     <row r="989" spans="1:1">
@@ -5439,32 +5439,32 @@
     </row>
     <row r="1013" spans="1:1">
       <c r="A1013">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1014" spans="1:1">
       <c r="A1014">
-        <v>-1</v>
+        <v>7.296213683888131</v>
       </c>
     </row>
     <row r="1015" spans="1:1">
       <c r="A1015">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1016" spans="1:1">
       <c r="A1016">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1017" spans="1:1">
       <c r="A1017">
-        <v>-1</v>
+        <v>28.02733928126144</v>
       </c>
     </row>
     <row r="1018" spans="1:1">
       <c r="A1018">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1019" spans="1:1">
@@ -5634,17 +5634,17 @@
     </row>
     <row r="1052" spans="1:1">
       <c r="A1052">
-        <v>-1</v>
+        <v>9.782990284538695</v>
       </c>
     </row>
     <row r="1053" spans="1:1">
       <c r="A1053">
-        <v>-1</v>
+        <v>43.26328422384282</v>
       </c>
     </row>
     <row r="1054" spans="1:1">
       <c r="A1054">
-        <v>-1</v>
+        <v>8.826462836649029</v>
       </c>
     </row>
     <row r="1055" spans="1:1">
@@ -5799,17 +5799,17 @@
     </row>
     <row r="1085" spans="1:1">
       <c r="A1085">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1086" spans="1:1">
       <c r="A1086">
-        <v>-1</v>
+        <v>8.833809018412154</v>
       </c>
     </row>
     <row r="1087" spans="1:1">
       <c r="A1087">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1088" spans="1:1">
@@ -5844,17 +5844,17 @@
     </row>
     <row r="1094" spans="1:1">
       <c r="A1094">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1095" spans="1:1">
       <c r="A1095">
-        <v>-1</v>
+        <v>129.3396373955661</v>
       </c>
     </row>
     <row r="1096" spans="1:1">
       <c r="A1096">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1097" spans="1:1">
@@ -6294,32 +6294,32 @@
     </row>
     <row r="1184" spans="1:1">
       <c r="A1184">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1185" spans="1:1">
       <c r="A1185">
-        <v>-1</v>
+        <v>3.420865752011126</v>
       </c>
     </row>
     <row r="1186" spans="1:1">
       <c r="A1186">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1187" spans="1:1">
       <c r="A1187">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="1188" spans="1:1">
       <c r="A1188">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1189" spans="1:1">
       <c r="A1189">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1190" spans="1:1">
@@ -6354,17 +6354,17 @@
     </row>
     <row r="1196" spans="1:1">
       <c r="A1196">
-        <v>-1</v>
+        <v>6.555506883719864</v>
       </c>
     </row>
     <row r="1197" spans="1:1">
       <c r="A1197">
-        <v>-1</v>
+        <v>7.67959082869496</v>
       </c>
     </row>
     <row r="1198" spans="1:1">
       <c r="A1198">
-        <v>-1</v>
+        <v>5.815494462537374</v>
       </c>
     </row>
     <row r="1199" spans="1:1">
@@ -6384,17 +6384,17 @@
     </row>
     <row r="1202" spans="1:1">
       <c r="A1202">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1203" spans="1:1">
       <c r="A1203">
-        <v>-1</v>
+        <v>3.427862929406178</v>
       </c>
     </row>
     <row r="1204" spans="1:1">
       <c r="A1204">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1205" spans="1:1">
@@ -6579,17 +6579,17 @@
     </row>
     <row r="1241" spans="1:1">
       <c r="A1241">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1242" spans="1:1">
       <c r="A1242">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1243" spans="1:1">
       <c r="A1243">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1244" spans="1:1">
@@ -6654,32 +6654,32 @@
     </row>
     <row r="1256" spans="1:1">
       <c r="A1256">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1257" spans="1:1">
       <c r="A1257">
-        <v>-1</v>
+        <v>3.376818666558545</v>
       </c>
     </row>
     <row r="1258" spans="1:1">
       <c r="A1258">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1259" spans="1:1">
       <c r="A1259">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1260" spans="1:1">
       <c r="A1260">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1261" spans="1:1">
       <c r="A1261">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1262" spans="1:1">
@@ -6729,17 +6729,17 @@
     </row>
     <row r="1271" spans="1:1">
       <c r="A1271">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1272" spans="1:1">
       <c r="A1272">
-        <v>-1</v>
+        <v>3.607326112370446</v>
       </c>
     </row>
     <row r="1273" spans="1:1">
       <c r="A1273">
-        <v>-1</v>
+        <v>3.434689357296672</v>
       </c>
     </row>
     <row r="1274" spans="1:1">
@@ -6924,32 +6924,32 @@
     </row>
     <row r="1310" spans="1:1">
       <c r="A1310">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1311" spans="1:1">
       <c r="A1311">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1312" spans="1:1">
       <c r="A1312">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1313" spans="1:1">
       <c r="A1313">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="1314" spans="1:1">
       <c r="A1314">
-        <v>-1</v>
+        <v>5.651016688486187</v>
       </c>
     </row>
     <row r="1315" spans="1:1">
       <c r="A1315">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1316" spans="1:1">
@@ -7059,32 +7059,32 @@
     </row>
     <row r="1337" spans="1:1">
       <c r="A1337">
-        <v>-1</v>
+        <v>3.683148610981579</v>
       </c>
     </row>
     <row r="1338" spans="1:1">
       <c r="A1338">
-        <v>-1</v>
+        <v>5.274537390445778</v>
       </c>
     </row>
     <row r="1339" spans="1:1">
       <c r="A1339">
-        <v>-1</v>
+        <v>3.312725165905395</v>
       </c>
     </row>
     <row r="1340" spans="1:1">
       <c r="A1340">
-        <v>-1</v>
+        <v>9.372829322532027</v>
       </c>
     </row>
     <row r="1341" spans="1:1">
       <c r="A1341">
-        <v>-1</v>
+        <v>13.56115130705052</v>
       </c>
     </row>
     <row r="1342" spans="1:1">
       <c r="A1342">
-        <v>-1</v>
+        <v>8.365563056264813</v>
       </c>
     </row>
     <row r="1343" spans="1:1">
@@ -7104,17 +7104,17 @@
     </row>
     <row r="1346" spans="1:1">
       <c r="A1346">
-        <v>-1</v>
+        <v>3.66954480424686</v>
       </c>
     </row>
     <row r="1347" spans="1:1">
       <c r="A1347">
-        <v>-1</v>
+        <v>6.182248450798522</v>
       </c>
     </row>
     <row r="1348" spans="1:1">
       <c r="A1348">
-        <v>-1</v>
+        <v>3.312725165905395</v>
       </c>
     </row>
     <row r="1349" spans="1:1">
@@ -7254,17 +7254,17 @@
     </row>
     <row r="1376" spans="1:1">
       <c r="A1376">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1377" spans="1:1">
       <c r="A1377">
-        <v>-1</v>
+        <v>4.757682371161631</v>
       </c>
     </row>
     <row r="1378" spans="1:1">
       <c r="A1378">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1379" spans="1:1">
@@ -7299,17 +7299,17 @@
     </row>
     <row r="1385" spans="1:1">
       <c r="A1385">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1386" spans="1:1">
       <c r="A1386">
-        <v>-1</v>
+        <v>7.704346759001412</v>
       </c>
     </row>
     <row r="1387" spans="1:1">
       <c r="A1387">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1388" spans="1:1">
@@ -7389,17 +7389,17 @@
     </row>
     <row r="1403" spans="1:1">
       <c r="A1403">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1404" spans="1:1">
       <c r="A1404">
-        <v>-1</v>
+        <v>7.717557405098541</v>
       </c>
     </row>
     <row r="1405" spans="1:1">
       <c r="A1405">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1406" spans="1:1">
@@ -7464,17 +7464,17 @@
     </row>
     <row r="1418" spans="1:1">
       <c r="A1418">
-        <v>-1</v>
+        <v>4.182939871275937</v>
       </c>
     </row>
     <row r="1419" spans="1:1">
       <c r="A1419">
-        <v>-1</v>
+        <v>7.241856997668538</v>
       </c>
     </row>
     <row r="1420" spans="1:1">
       <c r="A1420">
-        <v>-1</v>
+        <v>3.686577460843043</v>
       </c>
     </row>
     <row r="1421" spans="1:1">
@@ -7644,32 +7644,32 @@
     </row>
     <row r="1454" spans="1:1">
       <c r="A1454">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1455" spans="1:1">
       <c r="A1455">
-        <v>-1</v>
+        <v>3.734239954846541</v>
       </c>
     </row>
     <row r="1456" spans="1:1">
       <c r="A1456">
-        <v>-1</v>
+        <v>3.472082122665832</v>
       </c>
     </row>
     <row r="1457" spans="1:1">
       <c r="A1457">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1458" spans="1:1">
       <c r="A1458">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1459" spans="1:1">
       <c r="A1459">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1460" spans="1:1">
@@ -7689,17 +7689,17 @@
     </row>
     <row r="1463" spans="1:1">
       <c r="A1463">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1464" spans="1:1">
       <c r="A1464">
-        <v>-1</v>
+        <v>3.769667067021332</v>
       </c>
     </row>
     <row r="1465" spans="1:1">
       <c r="A1465">
-        <v>-1</v>
+        <v>3.425519959569656</v>
       </c>
     </row>
     <row r="1466" spans="1:1">
@@ -7734,32 +7734,32 @@
     </row>
     <row r="1472" spans="1:1">
       <c r="A1472">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1473" spans="1:1">
       <c r="A1473">
-        <v>-1</v>
+        <v>3.692865324315409</v>
       </c>
     </row>
     <row r="1474" spans="1:1">
       <c r="A1474">
-        <v>-1</v>
+        <v>3.425519959569656</v>
       </c>
     </row>
     <row r="1475" spans="1:1">
       <c r="A1475">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1476" spans="1:1">
       <c r="A1476">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1477" spans="1:1">
       <c r="A1477">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1478" spans="1:1">
@@ -7794,17 +7794,17 @@
     </row>
     <row r="1484" spans="1:1">
       <c r="A1484">
-        <v>-1</v>
+        <v>6.751231680395753</v>
       </c>
     </row>
     <row r="1485" spans="1:1">
       <c r="A1485">
-        <v>-1</v>
+        <v>8.485955225043828</v>
       </c>
     </row>
     <row r="1486" spans="1:1">
       <c r="A1486">
-        <v>-1</v>
+        <v>6.14929915898853</v>
       </c>
     </row>
     <row r="1487" spans="1:1">
@@ -7824,17 +7824,17 @@
     </row>
     <row r="1490" spans="1:1">
       <c r="A1490">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1491" spans="1:1">
       <c r="A1491">
-        <v>-1</v>
+        <v>3.724055191435327</v>
       </c>
     </row>
     <row r="1492" spans="1:1">
       <c r="A1492">
-        <v>-1</v>
+        <v>3.459566036821293</v>
       </c>
     </row>
     <row r="1493" spans="1:1">
@@ -7959,17 +7959,17 @@
     </row>
     <row r="1517" spans="1:1">
       <c r="A1517">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1518" spans="1:1">
       <c r="A1518">
-        <v>-1</v>
+        <v>3.752343687451209</v>
       </c>
     </row>
     <row r="1519" spans="1:1">
       <c r="A1519">
-        <v>-1</v>
+        <v>3.433717586839213</v>
       </c>
     </row>
     <row r="1520" spans="1:1">
@@ -8049,17 +8049,17 @@
     </row>
     <row r="1535" spans="1:1">
       <c r="A1535">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1536" spans="1:1">
       <c r="A1536">
-        <v>-1</v>
+        <v>3.727768066787251</v>
       </c>
     </row>
     <row r="1537" spans="1:1">
       <c r="A1537">
-        <v>-1</v>
+        <v>3.385948509196224</v>
       </c>
     </row>
     <row r="1538" spans="1:1">
@@ -8094,17 +8094,17 @@
     </row>
     <row r="1544" spans="1:1">
       <c r="A1544">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1545" spans="1:1">
       <c r="A1545">
-        <v>-1</v>
+        <v>3.650395499626113</v>
       </c>
     </row>
     <row r="1546" spans="1:1">
       <c r="A1546">
-        <v>-1</v>
+        <v>3.385948509196224</v>
       </c>
     </row>
     <row r="1547" spans="1:1">
@@ -8139,32 +8139,32 @@
     </row>
     <row r="1553" spans="1:1">
       <c r="A1553">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="1554" spans="1:1">
       <c r="A1554">
-        <v>-1</v>
+        <v>3.959903249420449</v>
       </c>
     </row>
     <row r="1555" spans="1:1">
       <c r="A1555">
-        <v>-1</v>
+        <v>3.419569343761797</v>
       </c>
     </row>
     <row r="1556" spans="1:1">
       <c r="A1556">
-        <v>-1</v>
+        <v>8.047881289345904</v>
       </c>
     </row>
     <row r="1557" spans="1:1">
       <c r="A1557">
-        <v>-1</v>
+        <v>9.752879191398877</v>
       </c>
     </row>
     <row r="1558" spans="1:1">
       <c r="A1558">
-        <v>-1</v>
+        <v>7.202172091301828</v>
       </c>
     </row>
     <row r="1559" spans="1:1">
@@ -8184,17 +8184,17 @@
     </row>
     <row r="1562" spans="1:1">
       <c r="A1562">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1563" spans="1:1">
       <c r="A1563">
-        <v>-1</v>
+        <v>3.810533747577327</v>
       </c>
     </row>
     <row r="1564" spans="1:1">
       <c r="A1564">
-        <v>-1</v>
+        <v>3.419569343761797</v>
       </c>
     </row>
     <row r="1565" spans="1:1">
@@ -8229,32 +8229,32 @@
     </row>
     <row r="1571" spans="1:1">
       <c r="A1571">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1572" spans="1:1">
       <c r="A1572">
-        <v>-1</v>
+        <v>4.176061692595012</v>
       </c>
     </row>
     <row r="1573" spans="1:1">
       <c r="A1573">
-        <v>-1</v>
+        <v>3.371271246430951</v>
       </c>
     </row>
     <row r="1574" spans="1:1">
       <c r="A1574">
-        <v>-1</v>
+        <v>8.522323996915727</v>
       </c>
     </row>
     <row r="1575" spans="1:1">
       <c r="A1575">
-        <v>-1</v>
+        <v>10.37205620322087</v>
       </c>
     </row>
     <row r="1576" spans="1:1">
       <c r="A1576">
-        <v>-1</v>
+        <v>7.642274034023099</v>
       </c>
     </row>
     <row r="1577" spans="1:1">
@@ -8319,32 +8319,32 @@
     </row>
     <row r="1589" spans="1:1">
       <c r="A1589">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1590" spans="1:1">
       <c r="A1590">
-        <v>-1</v>
+        <v>3.617236601388907</v>
       </c>
     </row>
     <row r="1591" spans="1:1">
       <c r="A1591">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1592" spans="1:1">
       <c r="A1592">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1593" spans="1:1">
       <c r="A1593">
-        <v>-1</v>
+        <v>5.176802457085228</v>
       </c>
     </row>
     <row r="1594" spans="1:1">
       <c r="A1594">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1595" spans="1:1">
@@ -8364,17 +8364,17 @@
     </row>
     <row r="1598" spans="1:1">
       <c r="A1598">
-        <v>-1</v>
+        <v>3.300000000000103</v>
       </c>
     </row>
     <row r="1599" spans="1:1">
       <c r="A1599">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1600" spans="1:1">
       <c r="A1600">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1601" spans="1:1">
@@ -8514,17 +8514,17 @@
     </row>
     <row r="1628" spans="1:1">
       <c r="A1628">
-        <v>-1</v>
+        <v>9.552710867989656</v>
       </c>
     </row>
     <row r="1629" spans="1:1">
       <c r="A1629">
-        <v>-1</v>
+        <v>16.03078745257158</v>
       </c>
     </row>
     <row r="1630" spans="1:1">
       <c r="A1630">
-        <v>-1</v>
+        <v>9.146980656604075</v>
       </c>
     </row>
     <row r="1631" spans="1:1">
@@ -8679,17 +8679,17 @@
     </row>
     <row r="1661" spans="1:1">
       <c r="A1661">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1662" spans="1:1">
       <c r="A1662">
-        <v>-1</v>
+        <v>3.563669524550939</v>
       </c>
     </row>
     <row r="1663" spans="1:1">
       <c r="A1663">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1664" spans="1:1">
@@ -8724,17 +8724,17 @@
     </row>
     <row r="1670" spans="1:1">
       <c r="A1670">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1671" spans="1:1">
       <c r="A1671">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1672" spans="1:1">
       <c r="A1672">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1673" spans="1:1">
@@ -8859,17 +8859,17 @@
     </row>
     <row r="1697" spans="1:1">
       <c r="A1697">
-        <v>-1</v>
+        <v>4.28015227918046</v>
       </c>
     </row>
     <row r="1698" spans="1:1">
       <c r="A1698">
-        <v>-1</v>
+        <v>6.965695882492973</v>
       </c>
     </row>
     <row r="1699" spans="1:1">
       <c r="A1699">
-        <v>-1</v>
+        <v>4.061644933817165</v>
       </c>
     </row>
     <row r="1700" spans="1:1">
@@ -9069,17 +9069,17 @@
     </row>
     <row r="1739" spans="1:1">
       <c r="A1739">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1740" spans="1:1">
       <c r="A1740">
-        <v>-1</v>
+        <v>3.888359639824746</v>
       </c>
     </row>
     <row r="1741" spans="1:1">
       <c r="A1741">
-        <v>-1</v>
+        <v>3.485139756167643</v>
       </c>
     </row>
     <row r="1742" spans="1:1">
@@ -9114,32 +9114,32 @@
     </row>
     <row r="1748" spans="1:1">
       <c r="A1748">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1749" spans="1:1">
       <c r="A1749">
-        <v>-1</v>
+        <v>3.882556474383581</v>
       </c>
     </row>
     <row r="1750" spans="1:1">
       <c r="A1750">
-        <v>-1</v>
+        <v>3.461390480220095</v>
       </c>
     </row>
     <row r="1751" spans="1:1">
       <c r="A1751">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1752" spans="1:1">
       <c r="A1752">
-        <v>-1</v>
+        <v>3.690160373857476</v>
       </c>
     </row>
     <row r="1753" spans="1:1">
       <c r="A1753">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1754" spans="1:1">
@@ -9159,32 +9159,32 @@
     </row>
     <row r="1757" spans="1:1">
       <c r="A1757">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1758" spans="1:1">
       <c r="A1758">
-        <v>-1</v>
+        <v>3.893457644977194</v>
       </c>
     </row>
     <row r="1759" spans="1:1">
       <c r="A1759">
-        <v>-1</v>
+        <v>3.461390480220095</v>
       </c>
     </row>
     <row r="1760" spans="1:1">
       <c r="A1760">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1761" spans="1:1">
       <c r="A1761">
-        <v>-1</v>
+        <v>4.770353519866665</v>
       </c>
     </row>
     <row r="1762" spans="1:1">
       <c r="A1762">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1763" spans="1:1">
@@ -9384,17 +9384,17 @@
     </row>
     <row r="1802" spans="1:1">
       <c r="A1802">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1803" spans="1:1">
       <c r="A1803">
-        <v>-1</v>
+        <v>3.843706001919922</v>
       </c>
     </row>
     <row r="1804" spans="1:1">
       <c r="A1804">
-        <v>-1</v>
+        <v>3.452605700616473</v>
       </c>
     </row>
     <row r="1805" spans="1:1">
@@ -9429,17 +9429,17 @@
     </row>
     <row r="1811" spans="1:1">
       <c r="A1811">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1812" spans="1:1">
       <c r="A1812">
-        <v>-1</v>
+        <v>3.851183934224656</v>
       </c>
     </row>
     <row r="1813" spans="1:1">
       <c r="A1813">
-        <v>-1</v>
+        <v>3.452605700616473</v>
       </c>
     </row>
     <row r="1814" spans="1:1">
@@ -9474,17 +9474,17 @@
     </row>
     <row r="1820" spans="1:1">
       <c r="A1820">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1821" spans="1:1">
       <c r="A1821">
-        <v>-1</v>
+        <v>3.845641898851659</v>
       </c>
     </row>
     <row r="1822" spans="1:1">
       <c r="A1822">
-        <v>-1</v>
+        <v>3.427757370504225</v>
       </c>
     </row>
     <row r="1823" spans="1:1">
@@ -9564,17 +9564,17 @@
     </row>
     <row r="1838" spans="1:1">
       <c r="A1838">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1839" spans="1:1">
       <c r="A1839">
-        <v>-1</v>
+        <v>3.833914393082827</v>
       </c>
     </row>
     <row r="1840" spans="1:1">
       <c r="A1840">
-        <v>-1</v>
+        <v>3.438787648829567</v>
       </c>
     </row>
     <row r="1841" spans="1:1">
@@ -9744,17 +9744,17 @@
     </row>
     <row r="1874" spans="1:1">
       <c r="A1874">
-        <v>-1</v>
+        <v>3.497600354271158</v>
       </c>
     </row>
     <row r="1875" spans="1:1">
       <c r="A1875">
-        <v>-1</v>
+        <v>3.953391326306543</v>
       </c>
     </row>
     <row r="1876" spans="1:1">
       <c r="A1876">
-        <v>-1</v>
+        <v>3.555705406833187</v>
       </c>
     </row>
     <row r="1877" spans="1:1">
@@ -9879,17 +9879,17 @@
     </row>
     <row r="1901" spans="1:1">
       <c r="A1901">
-        <v>-1</v>
+        <v>3.3535987080763</v>
       </c>
     </row>
     <row r="1902" spans="1:1">
       <c r="A1902">
-        <v>-1</v>
+        <v>80.1845366350841</v>
       </c>
     </row>
     <row r="1903" spans="1:1">
       <c r="A1903">
-        <v>-1</v>
+        <v>3.543817565055485</v>
       </c>
     </row>
     <row r="1904" spans="1:1">
@@ -9924,17 +9924,17 @@
     </row>
     <row r="1910" spans="1:1">
       <c r="A1910">
-        <v>-1</v>
+        <v>3.488871432729734</v>
       </c>
     </row>
     <row r="1911" spans="1:1">
       <c r="A1911">
-        <v>-1</v>
+        <v>6.198006216515339</v>
       </c>
     </row>
     <row r="1912" spans="1:1">
       <c r="A1912">
-        <v>-1</v>
+        <v>3.534018300944997</v>
       </c>
     </row>
     <row r="1913" spans="1:1">
@@ -10494,17 +10494,17 @@
     </row>
     <row r="2024" spans="1:1">
       <c r="A2024">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2025" spans="1:1">
       <c r="A2025">
-        <v>-1</v>
+        <v>10.52024183867557</v>
       </c>
     </row>
     <row r="2026" spans="1:1">
       <c r="A2026">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2027" spans="1:1">
@@ -10569,17 +10569,17 @@
     </row>
     <row r="2039" spans="1:1">
       <c r="A2039">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2040" spans="1:1">
       <c r="A2040">
-        <v>-1</v>
+        <v>3.986064388511679</v>
       </c>
     </row>
     <row r="2041" spans="1:1">
       <c r="A2041">
-        <v>-1</v>
+        <v>3.430033549407963</v>
       </c>
     </row>
     <row r="2042" spans="1:1">
@@ -10674,17 +10674,17 @@
     </row>
     <row r="2060" spans="1:1">
       <c r="A2060">
-        <v>-1</v>
+        <v>6.812139695784558</v>
       </c>
     </row>
     <row r="2061" spans="1:1">
       <c r="A2061">
-        <v>-1</v>
+        <v>18.28098496643054</v>
       </c>
     </row>
     <row r="2062" spans="1:1">
       <c r="A2062">
-        <v>-1</v>
+        <v>6.180155297161082</v>
       </c>
     </row>
     <row r="2063" spans="1:1">
@@ -11064,17 +11064,17 @@
     </row>
     <row r="2138" spans="1:1">
       <c r="A2138">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2139" spans="1:1">
       <c r="A2139">
-        <v>-1</v>
+        <v>6.754262298658597</v>
       </c>
     </row>
     <row r="2140" spans="1:1">
       <c r="A2140">
-        <v>-1</v>
+        <v>3.42345919083813</v>
       </c>
     </row>
     <row r="2141" spans="1:1">
@@ -12039,17 +12039,17 @@
     </row>
     <row r="2333" spans="1:1">
       <c r="A2333">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2334" spans="1:1">
       <c r="A2334">
-        <v>-1</v>
+        <v>3.330160590873077</v>
       </c>
     </row>
     <row r="2335" spans="1:1">
       <c r="A2335">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2336" spans="1:1">
@@ -12129,32 +12129,32 @@
     </row>
     <row r="2351" spans="1:1">
       <c r="A2351">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2352" spans="1:1">
       <c r="A2352">
-        <v>-1</v>
+        <v>3.341084876377209</v>
       </c>
     </row>
     <row r="2353" spans="1:1">
       <c r="A2353">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2354" spans="1:1">
       <c r="A2354">
-        <v>-1</v>
+        <v>3.663628505619365</v>
       </c>
     </row>
     <row r="2355" spans="1:1">
       <c r="A2355">
-        <v>-1</v>
+        <v>3.821476666602497</v>
       </c>
     </row>
     <row r="2356" spans="1:1">
       <c r="A2356">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="2357" spans="1:1">
@@ -12174,32 +12174,32 @@
     </row>
     <row r="2360" spans="1:1">
       <c r="A2360">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2361" spans="1:1">
       <c r="A2361">
-        <v>-1</v>
+        <v>3.342524604254282</v>
       </c>
     </row>
     <row r="2362" spans="1:1">
       <c r="A2362">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2363" spans="1:1">
       <c r="A2363">
-        <v>-1</v>
+        <v>3.817200244717567</v>
       </c>
     </row>
     <row r="2364" spans="1:1">
       <c r="A2364">
-        <v>-1</v>
+        <v>4.047629363128403</v>
       </c>
     </row>
     <row r="2365" spans="1:1">
       <c r="A2365">
-        <v>-1</v>
+        <v>3.339056157918407</v>
       </c>
     </row>
     <row r="2366" spans="1:1">
@@ -12219,17 +12219,17 @@
     </row>
     <row r="2369" spans="1:1">
       <c r="A2369">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2370" spans="1:1">
       <c r="A2370">
-        <v>-1</v>
+        <v>3.318072970073049</v>
       </c>
     </row>
     <row r="2371" spans="1:1">
       <c r="A2371">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2372" spans="1:1">
@@ -12294,17 +12294,17 @@
     </row>
     <row r="2384" spans="1:1">
       <c r="A2384">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2385" spans="1:1">
       <c r="A2385">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2386" spans="1:1">
       <c r="A2386">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2387" spans="1:1">
@@ -12339,62 +12339,62 @@
     </row>
     <row r="2393" spans="1:1">
       <c r="A2393">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2394" spans="1:1">
       <c r="A2394">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2395" spans="1:1">
       <c r="A2395">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2396" spans="1:1">
       <c r="A2396">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2397" spans="1:1">
       <c r="A2397">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2398" spans="1:1">
       <c r="A2398">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2399" spans="1:1">
       <c r="A2399">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2400" spans="1:1">
       <c r="A2400">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2401" spans="1:1">
       <c r="A2401">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2402" spans="1:1">
       <c r="A2402">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2403" spans="1:1">
       <c r="A2403">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2404" spans="1:1">
       <c r="A2404">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2405" spans="1:1">
@@ -12429,17 +12429,17 @@
     </row>
     <row r="2411" spans="1:1">
       <c r="A2411">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2412" spans="1:1">
       <c r="A2412">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2413" spans="1:1">
       <c r="A2413">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2414" spans="1:1">
@@ -12474,32 +12474,32 @@
     </row>
     <row r="2420" spans="1:1">
       <c r="A2420">
-        <v>-1</v>
+        <v>10.78312456699278</v>
       </c>
     </row>
     <row r="2421" spans="1:1">
       <c r="A2421">
-        <v>-1</v>
+        <v>11.00556470294056</v>
       </c>
     </row>
     <row r="2422" spans="1:1">
       <c r="A2422">
-        <v>-1</v>
+        <v>9.12777299497478</v>
       </c>
     </row>
     <row r="2423" spans="1:1">
       <c r="A2423">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2424" spans="1:1">
       <c r="A2424">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2425" spans="1:1">
       <c r="A2425">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2426" spans="1:1">
@@ -12609,17 +12609,17 @@
     </row>
     <row r="2447" spans="1:1">
       <c r="A2447">
-        <v>-1</v>
+        <v>11.31108623166675</v>
       </c>
     </row>
     <row r="2448" spans="1:1">
       <c r="A2448">
-        <v>-1</v>
+        <v>11.61768884926908</v>
       </c>
     </row>
     <row r="2449" spans="1:1">
       <c r="A2449">
-        <v>-1</v>
+        <v>9.565473562881088</v>
       </c>
     </row>
     <row r="2450" spans="1:1">
@@ -12684,17 +12684,17 @@
     </row>
     <row r="2462" spans="1:1">
       <c r="A2462">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2463" spans="1:1">
       <c r="A2463">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2464" spans="1:1">
       <c r="A2464">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2465" spans="1:1">
@@ -12729,17 +12729,17 @@
     </row>
     <row r="2471" spans="1:1">
       <c r="A2471">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2472" spans="1:1">
       <c r="A2472">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2473" spans="1:1">
       <c r="A2473">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2474" spans="1:1">
@@ -12879,17 +12879,17 @@
     </row>
     <row r="2501" spans="1:1">
       <c r="A2501">
-        <v>-1</v>
+        <v>11.30894735453761</v>
       </c>
     </row>
     <row r="2502" spans="1:1">
       <c r="A2502">
-        <v>-1</v>
+        <v>21.05045797930562</v>
       </c>
     </row>
     <row r="2503" spans="1:1">
       <c r="A2503">
-        <v>-1</v>
+        <v>9.968534398574313</v>
       </c>
     </row>
     <row r="2504" spans="1:1">
@@ -12909,17 +12909,17 @@
     </row>
     <row r="2507" spans="1:1">
       <c r="A2507">
-        <v>-1</v>
+        <v>4.745887422752959</v>
       </c>
     </row>
     <row r="2508" spans="1:1">
       <c r="A2508">
-        <v>-1</v>
+        <v>6.587557250464871</v>
       </c>
     </row>
     <row r="2509" spans="1:1">
       <c r="A2509">
-        <v>-1</v>
+        <v>3.986111646927715</v>
       </c>
     </row>
     <row r="2510" spans="1:1">
@@ -12999,17 +12999,17 @@
     </row>
     <row r="2525" spans="1:1">
       <c r="A2525">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2526" spans="1:1">
       <c r="A2526">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2527" spans="1:1">
       <c r="A2527">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2528" spans="1:1">
@@ -13089,17 +13089,17 @@
     </row>
     <row r="2543" spans="1:1">
       <c r="A2543">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2544" spans="1:1">
       <c r="A2544">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2545" spans="1:1">
       <c r="A2545">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2546" spans="1:1">
@@ -13389,32 +13389,32 @@
     </row>
     <row r="2603" spans="1:1">
       <c r="A2603">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2604" spans="1:1">
       <c r="A2604">
-        <v>-1</v>
+        <v>3.625211467937284</v>
       </c>
     </row>
     <row r="2605" spans="1:1">
       <c r="A2605">
-        <v>-1</v>
+        <v>3.364562736062093</v>
       </c>
     </row>
     <row r="2606" spans="1:1">
       <c r="A2606">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2607" spans="1:1">
       <c r="A2607">
-        <v>-1</v>
+        <v>3.446033268218551</v>
       </c>
     </row>
     <row r="2608" spans="1:1">
       <c r="A2608">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2609" spans="1:1">
@@ -13434,32 +13434,32 @@
     </row>
     <row r="2612" spans="1:1">
       <c r="A2612">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2613" spans="1:1">
       <c r="A2613">
-        <v>-1</v>
+        <v>3.636299326868531</v>
       </c>
     </row>
     <row r="2614" spans="1:1">
       <c r="A2614">
-        <v>-1</v>
+        <v>3.32472062448097</v>
       </c>
     </row>
     <row r="2615" spans="1:1">
       <c r="A2615">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2616" spans="1:1">
       <c r="A2616">
-        <v>-1</v>
+        <v>3.453750204475448</v>
       </c>
     </row>
     <row r="2617" spans="1:1">
       <c r="A2617">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2618" spans="1:1">
@@ -13539,17 +13539,17 @@
     </row>
     <row r="2633" spans="1:1">
       <c r="A2633">
-        <v>-1</v>
+        <v>3.709614837232067</v>
       </c>
     </row>
     <row r="2634" spans="1:1">
       <c r="A2634">
-        <v>-1</v>
+        <v>4.164658341535688</v>
       </c>
     </row>
     <row r="2635" spans="1:1">
       <c r="A2635">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2636" spans="1:1">
@@ -13569,17 +13569,17 @@
     </row>
     <row r="2639" spans="1:1">
       <c r="A2639">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2640" spans="1:1">
       <c r="A2640">
-        <v>-1</v>
+        <v>3.615921756582718</v>
       </c>
     </row>
     <row r="2641" spans="1:1">
       <c r="A2641">
-        <v>-1</v>
+        <v>3.353169966429359</v>
       </c>
     </row>
     <row r="2642" spans="1:1">
@@ -13614,17 +13614,17 @@
     </row>
     <row r="2648" spans="1:1">
       <c r="A2648">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2649" spans="1:1">
       <c r="A2649">
-        <v>-1</v>
+        <v>3.627399401554521</v>
       </c>
     </row>
     <row r="2650" spans="1:1">
       <c r="A2650">
-        <v>-1</v>
+        <v>3.312884474377498</v>
       </c>
     </row>
     <row r="2651" spans="1:1">
@@ -13659,17 +13659,17 @@
     </row>
     <row r="2657" spans="1:1">
       <c r="A2657">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2658" spans="1:1">
       <c r="A2658">
-        <v>-1</v>
+        <v>3.581237726538222</v>
       </c>
     </row>
     <row r="2659" spans="1:1">
       <c r="A2659">
-        <v>-1</v>
+        <v>3.312884474377498</v>
       </c>
     </row>
     <row r="2660" spans="1:1">
@@ -13704,17 +13704,17 @@
     </row>
     <row r="2666" spans="1:1">
       <c r="A2666">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2667" spans="1:1">
       <c r="A2667">
-        <v>-1</v>
+        <v>3.608284554022645</v>
       </c>
     </row>
     <row r="2668" spans="1:1">
       <c r="A2668">
-        <v>-1</v>
+        <v>3.31671819521977</v>
       </c>
     </row>
     <row r="2669" spans="1:1">
@@ -13734,17 +13734,17 @@
     </row>
     <row r="2672" spans="1:1">
       <c r="A2672">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2673" spans="1:1">
       <c r="A2673">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2674" spans="1:1">
       <c r="A2674">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="2675" spans="1:1">
@@ -13764,32 +13764,32 @@
     </row>
     <row r="2678" spans="1:1">
       <c r="A2678">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2679" spans="1:1">
       <c r="A2679">
-        <v>-1</v>
+        <v>3.389767103741281</v>
       </c>
     </row>
     <row r="2680" spans="1:1">
       <c r="A2680">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2681" spans="1:1">
       <c r="A2681">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2682" spans="1:1">
       <c r="A2682">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2683" spans="1:1">
       <c r="A2683">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="2684" spans="1:1">
@@ -13809,17 +13809,17 @@
     </row>
     <row r="2687" spans="1:1">
       <c r="A2687">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2688" spans="1:1">
       <c r="A2688">
-        <v>-1</v>
+        <v>3.39510084917507</v>
       </c>
     </row>
     <row r="2689" spans="1:1">
       <c r="A2689">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2690" spans="1:1">
@@ -13959,17 +13959,17 @@
     </row>
     <row r="2717" spans="1:1">
       <c r="A2717">
-        <v>-1</v>
+        <v>11.14678541447194</v>
       </c>
     </row>
     <row r="2718" spans="1:1">
       <c r="A2718">
-        <v>-1</v>
+        <v>11.48223562290258</v>
       </c>
     </row>
     <row r="2719" spans="1:1">
       <c r="A2719">
-        <v>-1</v>
+        <v>9.433151465445588</v>
       </c>
     </row>
     <row r="2720" spans="1:1">
@@ -14049,32 +14049,32 @@
     </row>
     <row r="2735" spans="1:1">
       <c r="A2735">
-        <v>-1</v>
+        <v>11.57884105050656</v>
       </c>
     </row>
     <row r="2736" spans="1:1">
       <c r="A2736">
-        <v>-1</v>
+        <v>12.11420182361971</v>
       </c>
     </row>
     <row r="2737" spans="1:1">
       <c r="A2737">
-        <v>-1</v>
+        <v>9.852369891194922</v>
       </c>
     </row>
     <row r="2738" spans="1:1">
       <c r="A2738">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2739" spans="1:1">
       <c r="A2739">
-        <v>-1</v>
+        <v>3.510459042461767</v>
       </c>
     </row>
     <row r="2740" spans="1:1">
       <c r="A2740">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2741" spans="1:1">
@@ -14454,17 +14454,17 @@
     </row>
     <row r="2816" spans="1:1">
       <c r="A2816">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2817" spans="1:1">
       <c r="A2817">
-        <v>-1</v>
+        <v>7.78587384257623</v>
       </c>
     </row>
     <row r="2818" spans="1:1">
       <c r="A2818">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2819" spans="1:1">
@@ -14844,17 +14844,17 @@
     </row>
     <row r="2894" spans="1:1">
       <c r="A2894">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2895" spans="1:1">
       <c r="A2895">
-        <v>-1</v>
+        <v>3.80280146061639</v>
       </c>
     </row>
     <row r="2896" spans="1:1">
       <c r="A2896">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2897" spans="1:1">
@@ -14874,32 +14874,32 @@
     </row>
     <row r="2900" spans="1:1">
       <c r="A2900">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2901" spans="1:1">
       <c r="A2901">
-        <v>-1</v>
+        <v>3.627975878489709</v>
       </c>
     </row>
     <row r="2902" spans="1:1">
       <c r="A2902">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2903" spans="1:1">
       <c r="A2903">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2904" spans="1:1">
       <c r="A2904">
-        <v>-1</v>
+        <v>3.441099646335233</v>
       </c>
     </row>
     <row r="2905" spans="1:1">
       <c r="A2905">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2906" spans="1:1">
@@ -14964,17 +14964,17 @@
     </row>
     <row r="2918" spans="1:1">
       <c r="A2918">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2919" spans="1:1">
       <c r="A2919">
-        <v>-1</v>
+        <v>3.620199954819703</v>
       </c>
     </row>
     <row r="2920" spans="1:1">
       <c r="A2920">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2921" spans="1:1">
@@ -14994,17 +14994,17 @@
     </row>
     <row r="2924" spans="1:1">
       <c r="A2924">
-        <v>-1</v>
+        <v>9.160535425414107</v>
       </c>
     </row>
     <row r="2925" spans="1:1">
       <c r="A2925">
-        <v>-1</v>
+        <v>11.42681056951815</v>
       </c>
     </row>
     <row r="2926" spans="1:1">
       <c r="A2926">
-        <v>-1</v>
+        <v>7.91889680755784</v>
       </c>
     </row>
     <row r="2927" spans="1:1">
@@ -15174,32 +15174,32 @@
     </row>
     <row r="2960" spans="1:1">
       <c r="A2960">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2961" spans="1:1">
       <c r="A2961">
-        <v>-1</v>
+        <v>3.867876303783802</v>
       </c>
     </row>
     <row r="2962" spans="1:1">
       <c r="A2962">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2963" spans="1:1">
       <c r="A2963">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="2964" spans="1:1">
       <c r="A2964">
-        <v>-1</v>
+        <v>3.577333008411099</v>
       </c>
     </row>
     <row r="2965" spans="1:1">
       <c r="A2965">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2966" spans="1:1">
@@ -15234,32 +15234,32 @@
     </row>
     <row r="2972" spans="1:1">
       <c r="A2972">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2973" spans="1:1">
       <c r="A2973">
-        <v>-1</v>
+        <v>3.572829992737114</v>
       </c>
     </row>
     <row r="2974" spans="1:1">
       <c r="A2974">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2975" spans="1:1">
       <c r="A2975">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2976" spans="1:1">
       <c r="A2976">
-        <v>-1</v>
+        <v>3.377246557066882</v>
       </c>
     </row>
     <row r="2977" spans="1:1">
       <c r="A2977">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2978" spans="1:1">
@@ -15279,17 +15279,17 @@
     </row>
     <row r="2981" spans="1:1">
       <c r="A2981">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2982" spans="1:1">
       <c r="A2982">
-        <v>-1</v>
+        <v>3.963313706466043</v>
       </c>
     </row>
     <row r="2983" spans="1:1">
       <c r="A2983">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2984" spans="1:1">
@@ -15324,17 +15324,17 @@
     </row>
     <row r="2990" spans="1:1">
       <c r="A2990">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2991" spans="1:1">
       <c r="A2991">
-        <v>-1</v>
+        <v>3.995200999233095</v>
       </c>
     </row>
     <row r="2992" spans="1:1">
       <c r="A2992">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="2993" spans="1:1">
@@ -15414,17 +15414,17 @@
     </row>
     <row r="3008" spans="1:1">
       <c r="A3008">
-        <v>-1</v>
+        <v>3.350476707930039</v>
       </c>
     </row>
     <row r="3009" spans="1:1">
       <c r="A3009">
-        <v>-1</v>
+        <v>4.257673589696265</v>
       </c>
     </row>
     <row r="3010" spans="1:1">
       <c r="A3010">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3011" spans="1:1">
@@ -15519,17 +15519,17 @@
     </row>
     <row r="3029" spans="1:1">
       <c r="A3029">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3030" spans="1:1">
       <c r="A3030">
-        <v>-1</v>
+        <v>7.591809610756505</v>
       </c>
     </row>
     <row r="3031" spans="1:1">
       <c r="A3031">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3032" spans="1:1">
@@ -15549,17 +15549,17 @@
     </row>
     <row r="3035" spans="1:1">
       <c r="A3035">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3036" spans="1:1">
       <c r="A3036">
-        <v>-1</v>
+        <v>84.03011136368121</v>
       </c>
     </row>
     <row r="3037" spans="1:1">
       <c r="A3037">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="3038" spans="1:1">
@@ -15879,17 +15879,17 @@
     </row>
     <row r="3101" spans="1:1">
       <c r="A3101">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3102" spans="1:1">
       <c r="A3102">
-        <v>-1</v>
+        <v>9.818275937155196</v>
       </c>
     </row>
     <row r="3103" spans="1:1">
       <c r="A3103">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3104" spans="1:1">
@@ -15984,17 +15984,17 @@
     </row>
     <row r="3122" spans="1:1">
       <c r="A3122">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3123" spans="1:1">
       <c r="A3123">
-        <v>-1</v>
+        <v>37.86003915246437</v>
       </c>
     </row>
     <row r="3124" spans="1:1">
       <c r="A3124">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3125" spans="1:1">
@@ -16269,17 +16269,17 @@
     </row>
     <row r="3179" spans="1:1">
       <c r="A3179">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3180" spans="1:1">
       <c r="A3180">
-        <v>-1</v>
+        <v>3.91547508147474</v>
       </c>
     </row>
     <row r="3181" spans="1:1">
       <c r="A3181">
-        <v>-1</v>
+        <v>3.370848918393388</v>
       </c>
     </row>
     <row r="3182" spans="1:1">
@@ -16359,17 +16359,17 @@
     </row>
     <row r="3197" spans="1:1">
       <c r="A3197">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3198" spans="1:1">
       <c r="A3198">
-        <v>-1</v>
+        <v>4.373406586887219</v>
       </c>
     </row>
     <row r="3199" spans="1:1">
       <c r="A3199">
-        <v>-1</v>
+        <v>3.331861528880276</v>
       </c>
     </row>
     <row r="3200" spans="1:1">
@@ -16404,17 +16404,17 @@
     </row>
     <row r="3206" spans="1:1">
       <c r="A3206">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3207" spans="1:1">
       <c r="A3207">
-        <v>-1</v>
+        <v>3.923499165794808</v>
       </c>
     </row>
     <row r="3208" spans="1:1">
       <c r="A3208">
-        <v>-1</v>
+        <v>3.359645251200427</v>
       </c>
     </row>
     <row r="3209" spans="1:1">
@@ -16584,17 +16584,17 @@
     </row>
     <row r="3242" spans="1:1">
       <c r="A3242">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3243" spans="1:1">
       <c r="A3243">
-        <v>-1</v>
+        <v>3.875081680096781</v>
       </c>
     </row>
     <row r="3244" spans="1:1">
       <c r="A3244">
-        <v>-1</v>
+        <v>3.323327179299218</v>
       </c>
     </row>
     <row r="3245" spans="1:1">
@@ -16614,17 +16614,17 @@
     </row>
     <row r="3248" spans="1:1">
       <c r="A3248">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3249" spans="1:1">
       <c r="A3249">
-        <v>-1</v>
+        <v>5.922659342183801</v>
       </c>
     </row>
     <row r="3250" spans="1:1">
       <c r="A3250">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3251" spans="1:1">
@@ -16659,32 +16659,32 @@
     </row>
     <row r="3257" spans="1:1">
       <c r="A3257">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3258" spans="1:1">
       <c r="A3258">
-        <v>-1</v>
+        <v>12.82095771501159</v>
       </c>
     </row>
     <row r="3259" spans="1:1">
       <c r="A3259">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3260" spans="1:1">
       <c r="A3260">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3261" spans="1:1">
       <c r="A3261">
-        <v>-1</v>
+        <v>3.871926276505477</v>
       </c>
     </row>
     <row r="3262" spans="1:1">
       <c r="A3262">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3263" spans="1:1">
@@ -16764,17 +16764,17 @@
     </row>
     <row r="3278" spans="1:1">
       <c r="A3278">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3279" spans="1:1">
       <c r="A3279">
-        <v>-1</v>
+        <v>4.39535310228385</v>
       </c>
     </row>
     <row r="3280" spans="1:1">
       <c r="A3280">
-        <v>-1</v>
+        <v>3.310482106380763</v>
       </c>
     </row>
     <row r="3281" spans="1:1">
@@ -16809,17 +16809,17 @@
     </row>
     <row r="3287" spans="1:1">
       <c r="A3287">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3288" spans="1:1">
       <c r="A3288">
-        <v>-1</v>
+        <v>4.799371484227222</v>
       </c>
     </row>
     <row r="3289" spans="1:1">
       <c r="A3289">
-        <v>-1</v>
+        <v>3.310482106380763</v>
       </c>
     </row>
     <row r="3290" spans="1:1">
@@ -17724,17 +17724,17 @@
     </row>
     <row r="3470" spans="1:1">
       <c r="A3470">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3471" spans="1:1">
       <c r="A3471">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3472" spans="1:1">
       <c r="A3472">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3473" spans="1:1">
@@ -17769,17 +17769,17 @@
     </row>
     <row r="3479" spans="1:1">
       <c r="A3479">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3480" spans="1:1">
       <c r="A3480">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3481" spans="1:1">
       <c r="A3481">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3482" spans="1:1">
@@ -17904,17 +17904,17 @@
     </row>
     <row r="3506" spans="1:1">
       <c r="A3506">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3507" spans="1:1">
       <c r="A3507">
-        <v>-1</v>
+        <v>3.442221593586658</v>
       </c>
     </row>
     <row r="3508" spans="1:1">
       <c r="A3508">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3509" spans="1:1">
@@ -18054,17 +18054,17 @@
     </row>
     <row r="3536" spans="1:1">
       <c r="A3536">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3537" spans="1:1">
       <c r="A3537">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3538" spans="1:1">
       <c r="A3538">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3539" spans="1:1">
@@ -18189,17 +18189,17 @@
     </row>
     <row r="3563" spans="1:1">
       <c r="A3563">
-        <v>-1</v>
+        <v>3.300000000000081</v>
       </c>
     </row>
     <row r="3564" spans="1:1">
       <c r="A3564">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3565" spans="1:1">
       <c r="A3565">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3566" spans="1:1">
@@ -18234,17 +18234,17 @@
     </row>
     <row r="3572" spans="1:1">
       <c r="A3572">
-        <v>-1</v>
+        <v>10.21385031020523</v>
       </c>
     </row>
     <row r="3573" spans="1:1">
       <c r="A3573">
-        <v>-1</v>
+        <v>10.60047488536164</v>
       </c>
     </row>
     <row r="3574" spans="1:1">
       <c r="A3574">
-        <v>-1</v>
+        <v>8.5177270410707</v>
       </c>
     </row>
     <row r="3575" spans="1:1">
@@ -18399,17 +18399,17 @@
     </row>
     <row r="3605" spans="1:1">
       <c r="A3605">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3606" spans="1:1">
       <c r="A3606">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3607" spans="1:1">
       <c r="A3607">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3608" spans="1:1">
@@ -18489,32 +18489,32 @@
     </row>
     <row r="3623" spans="1:1">
       <c r="A3623">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3624" spans="1:1">
       <c r="A3624">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3625" spans="1:1">
       <c r="A3625">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3626" spans="1:1">
       <c r="A3626">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3627" spans="1:1">
       <c r="A3627">
-        <v>-1</v>
+        <v>4.965489969862746</v>
       </c>
     </row>
     <row r="3628" spans="1:1">
       <c r="A3628">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3629" spans="1:1">
@@ -18759,32 +18759,32 @@
     </row>
     <row r="3677" spans="1:1">
       <c r="A3677">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3678" spans="1:1">
       <c r="A3678">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3679" spans="1:1">
       <c r="A3679">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3680" spans="1:1">
       <c r="A3680">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3681" spans="1:1">
       <c r="A3681">
-        <v>-1</v>
+        <v>7.574091964382756</v>
       </c>
     </row>
     <row r="3682" spans="1:1">
       <c r="A3682">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3683" spans="1:1">
@@ -19104,32 +19104,32 @@
     </row>
     <row r="3746" spans="1:1">
       <c r="A3746">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3747" spans="1:1">
       <c r="A3747">
-        <v>-1</v>
+        <v>3.752629344048519</v>
       </c>
     </row>
     <row r="3748" spans="1:1">
       <c r="A3748">
-        <v>-1</v>
+        <v>3.445270807643297</v>
       </c>
     </row>
     <row r="3749" spans="1:1">
       <c r="A3749">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3750" spans="1:1">
       <c r="A3750">
-        <v>-1</v>
+        <v>3.556018321149446</v>
       </c>
     </row>
     <row r="3751" spans="1:1">
       <c r="A3751">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3752" spans="1:1">
@@ -19209,17 +19209,17 @@
     </row>
     <row r="3767" spans="1:1">
       <c r="A3767">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3768" spans="1:1">
       <c r="A3768">
-        <v>-1</v>
+        <v>3.532101212740102</v>
       </c>
     </row>
     <row r="3769" spans="1:1">
       <c r="A3769">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3770" spans="1:1">
@@ -19464,17 +19464,17 @@
     </row>
     <row r="3818" spans="1:1">
       <c r="A3818">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3819" spans="1:1">
       <c r="A3819">
-        <v>-1</v>
+        <v>3.695829955655028</v>
       </c>
     </row>
     <row r="3820" spans="1:1">
       <c r="A3820">
-        <v>-1</v>
+        <v>3.389967491704016</v>
       </c>
     </row>
     <row r="3821" spans="1:1">
@@ -19569,17 +19569,17 @@
     </row>
     <row r="3839" spans="1:1">
       <c r="A3839">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3840" spans="1:1">
       <c r="A3840">
-        <v>-1</v>
+        <v>3.464932799761899</v>
       </c>
     </row>
     <row r="3841" spans="1:1">
       <c r="A3841">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3842" spans="1:1">
@@ -20199,17 +20199,17 @@
     </row>
     <row r="3965" spans="1:1">
       <c r="A3965">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3966" spans="1:1">
       <c r="A3966">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3967" spans="1:1">
       <c r="A3967">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3968" spans="1:1">
@@ -20604,17 +20604,17 @@
     </row>
     <row r="4046" spans="1:1">
       <c r="A4046">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4047" spans="1:1">
       <c r="A4047">
-        <v>-1</v>
+        <v>4.028343861235473</v>
       </c>
     </row>
     <row r="4048" spans="1:1">
       <c r="A4048">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4049" spans="1:1">
@@ -20634,17 +20634,17 @@
     </row>
     <row r="4052" spans="1:1">
       <c r="A4052">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4053" spans="1:1">
       <c r="A4053">
-        <v>-1</v>
+        <v>3.651583606930187</v>
       </c>
     </row>
     <row r="4054" spans="1:1">
       <c r="A4054">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4055" spans="1:1">
@@ -20724,17 +20724,17 @@
     </row>
     <row r="4070" spans="1:1">
       <c r="A4070">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4071" spans="1:1">
       <c r="A4071">
-        <v>-1</v>
+        <v>3.639313787900078</v>
       </c>
     </row>
     <row r="4072" spans="1:1">
       <c r="A4072">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4073" spans="1:1">
@@ -20949,17 +20949,17 @@
     </row>
     <row r="4115" spans="1:1">
       <c r="A4115">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4116" spans="1:1">
       <c r="A4116">
-        <v>-1</v>
+        <v>3.596734932711709</v>
       </c>
     </row>
     <row r="4117" spans="1:1">
       <c r="A4117">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4118" spans="1:1">
@@ -20994,17 +20994,17 @@
     </row>
     <row r="4124" spans="1:1">
       <c r="A4124">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4125" spans="1:1">
       <c r="A4125">
-        <v>-1</v>
+        <v>3.591219382913513</v>
       </c>
     </row>
     <row r="4126" spans="1:1">
       <c r="A4126">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4127" spans="1:1">
@@ -22014,17 +22014,17 @@
     </row>
     <row r="4328" spans="1:1">
       <c r="A4328">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4329" spans="1:1">
       <c r="A4329">
-        <v>-1</v>
+        <v>12.62978953685517</v>
       </c>
     </row>
     <row r="4330" spans="1:1">
       <c r="A4330">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4331" spans="1:1">
@@ -22194,17 +22194,17 @@
     </row>
     <row r="4364" spans="1:1">
       <c r="A4364">
-        <v>-1</v>
+        <v>8.616936009312472</v>
       </c>
     </row>
     <row r="4365" spans="1:1">
       <c r="A4365">
-        <v>-1</v>
+        <v>22.48658971137066</v>
       </c>
     </row>
     <row r="4366" spans="1:1">
       <c r="A4366">
-        <v>-1</v>
+        <v>7.533585062869553</v>
       </c>
     </row>
     <row r="4367" spans="1:1">
@@ -23499,32 +23499,32 @@
     </row>
     <row r="4625" spans="1:1">
       <c r="A4625">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4626" spans="1:1">
       <c r="A4626">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4627" spans="1:1">
       <c r="A4627">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4628" spans="1:1">
       <c r="A4628">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4629" spans="1:1">
       <c r="A4629">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4630" spans="1:1">
       <c r="A4630">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4631" spans="1:1">
@@ -23559,32 +23559,32 @@
     </row>
     <row r="4637" spans="1:1">
       <c r="A4637">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4638" spans="1:1">
       <c r="A4638">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4639" spans="1:1">
       <c r="A4639">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4640" spans="1:1">
       <c r="A4640">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4641" spans="1:1">
       <c r="A4641">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4642" spans="1:1">
       <c r="A4642">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4643" spans="1:1">
@@ -23649,17 +23649,17 @@
     </row>
     <row r="4655" spans="1:1">
       <c r="A4655">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4656" spans="1:1">
       <c r="A4656">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4657" spans="1:1">
       <c r="A4657">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4658" spans="1:1">
@@ -23694,32 +23694,32 @@
     </row>
     <row r="4664" spans="1:1">
       <c r="A4664">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4665" spans="1:1">
       <c r="A4665">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4666" spans="1:1">
       <c r="A4666">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4667" spans="1:1">
       <c r="A4667">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4668" spans="1:1">
       <c r="A4668">
-        <v>-1</v>
+        <v>3.79010395889009</v>
       </c>
     </row>
     <row r="4669" spans="1:1">
       <c r="A4669">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4670" spans="1:1">
@@ -23859,77 +23859,77 @@
     </row>
     <row r="4697" spans="1:1">
       <c r="A4697">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4698" spans="1:1">
       <c r="A4698">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4699" spans="1:1">
       <c r="A4699">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4700" spans="1:1">
       <c r="A4700">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4701" spans="1:1">
       <c r="A4701">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4702" spans="1:1">
       <c r="A4702">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4703" spans="1:1">
       <c r="A4703">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4704" spans="1:1">
       <c r="A4704">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4705" spans="1:1">
       <c r="A4705">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4706" spans="1:1">
       <c r="A4706">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4707" spans="1:1">
       <c r="A4707">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4708" spans="1:1">
       <c r="A4708">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4709" spans="1:1">
       <c r="A4709">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4710" spans="1:1">
       <c r="A4710">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4711" spans="1:1">
       <c r="A4711">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4712" spans="1:1">
@@ -23949,17 +23949,17 @@
     </row>
     <row r="4715" spans="1:1">
       <c r="A4715">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4716" spans="1:1">
       <c r="A4716">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4717" spans="1:1">
       <c r="A4717">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4718" spans="1:1">
@@ -24009,47 +24009,47 @@
     </row>
     <row r="4727" spans="1:1">
       <c r="A4727">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4728" spans="1:1">
       <c r="A4728">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4729" spans="1:1">
       <c r="A4729">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4730" spans="1:1">
       <c r="A4730">
-        <v>-1</v>
+        <v>3.307493888349622</v>
       </c>
     </row>
     <row r="4731" spans="1:1">
       <c r="A4731">
-        <v>-1</v>
+        <v>3.979214749251325</v>
       </c>
     </row>
     <row r="4732" spans="1:1">
       <c r="A4732">
-        <v>-1</v>
+        <v>3.307493888349622</v>
       </c>
     </row>
     <row r="4733" spans="1:1">
       <c r="A4733">
-        <v>-1</v>
+        <v>8.46069337180384</v>
       </c>
     </row>
     <row r="4734" spans="1:1">
       <c r="A4734">
-        <v>-1</v>
+        <v>10.23296543096215</v>
       </c>
     </row>
     <row r="4735" spans="1:1">
       <c r="A4735">
-        <v>-1</v>
+        <v>8.46069337180384</v>
       </c>
     </row>
     <row r="4736" spans="1:1">
@@ -24084,17 +24084,17 @@
     </row>
     <row r="4742" spans="1:1">
       <c r="A4742">
-        <v>-1</v>
+        <v>8.86212771391326</v>
       </c>
     </row>
     <row r="4743" spans="1:1">
       <c r="A4743">
-        <v>-1</v>
+        <v>10.86267187022203</v>
       </c>
     </row>
     <row r="4744" spans="1:1">
       <c r="A4744">
-        <v>-1</v>
+        <v>8.899625586124616</v>
       </c>
     </row>
     <row r="4745" spans="1:1">
@@ -24114,17 +24114,17 @@
     </row>
     <row r="4748" spans="1:1">
       <c r="A4748">
-        <v>-1</v>
+        <v>3.478564081431912</v>
       </c>
     </row>
     <row r="4749" spans="1:1">
       <c r="A4749">
-        <v>-1</v>
+        <v>4.227003373928895</v>
       </c>
     </row>
     <row r="4750" spans="1:1">
       <c r="A4750">
-        <v>-1</v>
+        <v>3.478564081431912</v>
       </c>
     </row>
     <row r="4751" spans="1:1">
@@ -24204,47 +24204,47 @@
     </row>
     <row r="4766" spans="1:1">
       <c r="A4766">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4767" spans="1:1">
       <c r="A4767">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="4768" spans="1:1">
       <c r="A4768">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4769" spans="1:1">
       <c r="A4769">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4770" spans="1:1">
       <c r="A4770">
-        <v>-1</v>
+        <v>7.5274481291146</v>
       </c>
     </row>
     <row r="4771" spans="1:1">
       <c r="A4771">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4772" spans="1:1">
       <c r="A4772">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4773" spans="1:1">
       <c r="A4773">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4774" spans="1:1">
       <c r="A4774">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4775" spans="1:1">
@@ -24294,17 +24294,17 @@
     </row>
     <row r="4784" spans="1:1">
       <c r="A4784">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4785" spans="1:1">
       <c r="A4785">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4786" spans="1:1">
       <c r="A4786">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4787" spans="1:1">
@@ -24339,17 +24339,17 @@
     </row>
     <row r="4793" spans="1:1">
       <c r="A4793">
-        <v>-1</v>
+        <v>3.826013285086283</v>
       </c>
     </row>
     <row r="4794" spans="1:1">
       <c r="A4794">
-        <v>-1</v>
+        <v>6.071092729480798</v>
       </c>
     </row>
     <row r="4795" spans="1:1">
       <c r="A4795">
-        <v>-1</v>
+        <v>3.752316691253654</v>
       </c>
     </row>
     <row r="4796" spans="1:1">
@@ -24384,17 +24384,17 @@
     </row>
     <row r="4802" spans="1:1">
       <c r="A4802">
-        <v>-1</v>
+        <v>3.752316691253654</v>
       </c>
     </row>
     <row r="4803" spans="1:1">
       <c r="A4803">
-        <v>-1</v>
+        <v>7.028329356705454</v>
       </c>
     </row>
     <row r="4804" spans="1:1">
       <c r="A4804">
-        <v>-1</v>
+        <v>3.752316691253654</v>
       </c>
     </row>
     <row r="4805" spans="1:1">
@@ -24414,32 +24414,32 @@
     </row>
     <row r="4808" spans="1:1">
       <c r="A4808">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="4809" spans="1:1">
       <c r="A4809">
-        <v>-1</v>
+        <v>4.067567943297801</v>
       </c>
     </row>
     <row r="4810" spans="1:1">
       <c r="A4810">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4811" spans="1:1">
       <c r="A4811">
-        <v>-1</v>
+        <v>3.828255046016815</v>
       </c>
     </row>
     <row r="4812" spans="1:1">
       <c r="A4812">
-        <v>-1</v>
+        <v>6.077432086579893</v>
       </c>
     </row>
     <row r="4813" spans="1:1">
       <c r="A4813">
-        <v>-1</v>
+        <v>3.754061680944376</v>
       </c>
     </row>
     <row r="4814" spans="1:1">
@@ -24474,17 +24474,17 @@
     </row>
     <row r="4820" spans="1:1">
       <c r="A4820">
-        <v>-1</v>
+        <v>3.754061680944376</v>
       </c>
     </row>
     <row r="4821" spans="1:1">
       <c r="A4821">
-        <v>-1</v>
+        <v>7.031843155712814</v>
       </c>
     </row>
     <row r="4822" spans="1:1">
       <c r="A4822">
-        <v>-1</v>
+        <v>3.754061680944376</v>
       </c>
     </row>
     <row r="4823" spans="1:1">
@@ -24519,32 +24519,32 @@
     </row>
     <row r="4829" spans="1:1">
       <c r="A4829">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4830" spans="1:1">
       <c r="A4830">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4831" spans="1:1">
       <c r="A4831">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4832" spans="1:1">
       <c r="A4832">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4833" spans="1:1">
       <c r="A4833">
-        <v>-1</v>
+        <v>5.797705601551916</v>
       </c>
     </row>
     <row r="4834" spans="1:1">
       <c r="A4834">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4835" spans="1:1">
@@ -24564,77 +24564,77 @@
     </row>
     <row r="4838" spans="1:1">
       <c r="A4838">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4839" spans="1:1">
       <c r="A4839">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4840" spans="1:1">
       <c r="A4840">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4841" spans="1:1">
       <c r="A4841">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4842" spans="1:1">
       <c r="A4842">
-        <v>-1</v>
+        <v>10.23816900009314</v>
       </c>
     </row>
     <row r="4843" spans="1:1">
       <c r="A4843">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4844" spans="1:1">
       <c r="A4844">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4845" spans="1:1">
       <c r="A4845">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4846" spans="1:1">
       <c r="A4846">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4847" spans="1:1">
       <c r="A4847">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4848" spans="1:1">
       <c r="A4848">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4849" spans="1:1">
       <c r="A4849">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4850" spans="1:1">
       <c r="A4850">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4851" spans="1:1">
       <c r="A4851">
-        <v>-1</v>
+        <v>5.819214680389551</v>
       </c>
     </row>
     <row r="4852" spans="1:1">
       <c r="A4852">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4853" spans="1:1">
@@ -24669,17 +24669,17 @@
     </row>
     <row r="4859" spans="1:1">
       <c r="A4859">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4860" spans="1:1">
       <c r="A4860">
-        <v>-1</v>
+        <v>10.25726449574961</v>
       </c>
     </row>
     <row r="4861" spans="1:1">
       <c r="A4861">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4862" spans="1:1">
@@ -24759,17 +24759,17 @@
     </row>
     <row r="4877" spans="1:1">
       <c r="A4877">
-        <v>-1</v>
+        <v>10.79415387497151</v>
       </c>
     </row>
     <row r="4878" spans="1:1">
       <c r="A4878">
-        <v>-1</v>
+        <v>24.28485896825649</v>
       </c>
     </row>
     <row r="4879" spans="1:1">
       <c r="A4879">
-        <v>-1</v>
+        <v>10.79415387497151</v>
       </c>
     </row>
     <row r="4880" spans="1:1">
@@ -24924,17 +24924,17 @@
     </row>
     <row r="4910" spans="1:1">
       <c r="A4910">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4911" spans="1:1">
       <c r="A4911">
-        <v>-1</v>
+        <v>3.314148535777162</v>
       </c>
     </row>
     <row r="4912" spans="1:1">
       <c r="A4912">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4913" spans="1:1">
@@ -25134,17 +25134,17 @@
     </row>
     <row r="4952" spans="1:1">
       <c r="A4952">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4953" spans="1:1">
       <c r="A4953">
-        <v>-1</v>
+        <v>3.485766935347812</v>
       </c>
     </row>
     <row r="4954" spans="1:1">
       <c r="A4954">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4955" spans="1:1">
@@ -25239,17 +25239,17 @@
     </row>
     <row r="4973" spans="1:1">
       <c r="A4973">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4974" spans="1:1">
       <c r="A4974">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4975" spans="1:1">
       <c r="A4975">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4976" spans="1:1">
@@ -25599,17 +25599,17 @@
     </row>
     <row r="5045" spans="1:1">
       <c r="A5045">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5046" spans="1:1">
       <c r="A5046">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5047" spans="1:1">
       <c r="A5047">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5048" spans="1:1">
@@ -25644,17 +25644,17 @@
     </row>
     <row r="5054" spans="1:1">
       <c r="A5054">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5055" spans="1:1">
       <c r="A5055">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5056" spans="1:1">
       <c r="A5056">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5057" spans="1:1">
@@ -25974,17 +25974,17 @@
     </row>
     <row r="5120" spans="1:1">
       <c r="A5120">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5121" spans="1:1">
       <c r="A5121">
-        <v>-1</v>
+        <v>6.248501491480307</v>
       </c>
     </row>
     <row r="5122" spans="1:1">
       <c r="A5122">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5123" spans="1:1">
@@ -26349,17 +26349,17 @@
     </row>
     <row r="5195" spans="1:1">
       <c r="A5195">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5196" spans="1:1">
       <c r="A5196">
-        <v>-1</v>
+        <v>3.527617936845728</v>
       </c>
     </row>
     <row r="5197" spans="1:1">
       <c r="A5197">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5198" spans="1:1">
@@ -26379,17 +26379,17 @@
     </row>
     <row r="5201" spans="1:1">
       <c r="A5201">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5202" spans="1:1">
       <c r="A5202">
-        <v>-1</v>
+        <v>9.002744330198432</v>
       </c>
     </row>
     <row r="5203" spans="1:1">
       <c r="A5203">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5204" spans="1:1">
@@ -26424,47 +26424,47 @@
     </row>
     <row r="5210" spans="1:1">
       <c r="A5210">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5211" spans="1:1">
       <c r="A5211">
-        <v>-1</v>
+        <v>3.73634860538079</v>
       </c>
     </row>
     <row r="5212" spans="1:1">
       <c r="A5212">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5213" spans="1:1">
       <c r="A5213">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5214" spans="1:1">
       <c r="A5214">
-        <v>-1</v>
+        <v>3.527207522328379</v>
       </c>
     </row>
     <row r="5215" spans="1:1">
       <c r="A5215">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5216" spans="1:1">
       <c r="A5216">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5217" spans="1:1">
       <c r="A5217">
-        <v>-1</v>
+        <v>4.424350085304207</v>
       </c>
     </row>
     <row r="5218" spans="1:1">
       <c r="A5218">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5219" spans="1:1">
@@ -26514,17 +26514,17 @@
     </row>
     <row r="5228" spans="1:1">
       <c r="A5228">
-        <v>-1</v>
+        <v>7.355937796184597</v>
       </c>
     </row>
     <row r="5229" spans="1:1">
       <c r="A5229">
-        <v>-1</v>
+        <v>10.53727756702758</v>
       </c>
     </row>
     <row r="5230" spans="1:1">
       <c r="A5230">
-        <v>-1</v>
+        <v>7.373185587659459</v>
       </c>
     </row>
     <row r="5231" spans="1:1">
@@ -26589,17 +26589,17 @@
     </row>
     <row r="5243" spans="1:1">
       <c r="A5243">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5244" spans="1:1">
       <c r="A5244">
-        <v>-1</v>
+        <v>4.385234611215127</v>
       </c>
     </row>
     <row r="5245" spans="1:1">
       <c r="A5245">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5246" spans="1:1">
@@ -26634,17 +26634,17 @@
     </row>
     <row r="5252" spans="1:1">
       <c r="A5252">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5253" spans="1:1">
       <c r="A5253">
-        <v>-1</v>
+        <v>6.665139416525401</v>
       </c>
     </row>
     <row r="5254" spans="1:1">
       <c r="A5254">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5255" spans="1:1">
@@ -26694,32 +26694,32 @@
     </row>
     <row r="5264" spans="1:1">
       <c r="A5264">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5265" spans="1:1">
       <c r="A5265">
-        <v>-1</v>
+        <v>3.555839467113042</v>
       </c>
     </row>
     <row r="5266" spans="1:1">
       <c r="A5266">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5267" spans="1:1">
       <c r="A5267">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5268" spans="1:1">
       <c r="A5268">
-        <v>-1</v>
+        <v>3.476142080143574</v>
       </c>
     </row>
     <row r="5269" spans="1:1">
       <c r="A5269">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5270" spans="1:1">
@@ -26799,17 +26799,17 @@
     </row>
     <row r="5285" spans="1:1">
       <c r="A5285">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5286" spans="1:1">
       <c r="A5286">
-        <v>-1</v>
+        <v>3.592695968823734</v>
       </c>
     </row>
     <row r="5287" spans="1:1">
       <c r="A5287">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5288" spans="1:1">
@@ -26844,17 +26844,17 @@
     </row>
     <row r="5294" spans="1:1">
       <c r="A5294">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5295" spans="1:1">
       <c r="A5295">
-        <v>-1</v>
+        <v>3.588460358633672</v>
       </c>
     </row>
     <row r="5296" spans="1:1">
       <c r="A5296">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5297" spans="1:1">
@@ -26994,17 +26994,17 @@
     </row>
     <row r="5324" spans="1:1">
       <c r="A5324">
-        <v>-1</v>
+        <v>3.497224389872555</v>
       </c>
     </row>
     <row r="5325" spans="1:1">
       <c r="A5325">
-        <v>-1</v>
+        <v>8.074723607570878</v>
       </c>
     </row>
     <row r="5326" spans="1:1">
       <c r="A5326">
-        <v>-1</v>
+        <v>3.497224389872555</v>
       </c>
     </row>
     <row r="5327" spans="1:1">
@@ -27204,17 +27204,17 @@
     </row>
     <row r="5366" spans="1:1">
       <c r="A5366">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5367" spans="1:1">
       <c r="A5367">
-        <v>-1</v>
+        <v>6.993678057368246</v>
       </c>
     </row>
     <row r="5368" spans="1:1">
       <c r="A5368">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5369" spans="1:1">
@@ -27384,47 +27384,47 @@
     </row>
     <row r="5402" spans="1:1">
       <c r="A5402">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5403" spans="1:1">
       <c r="A5403">
-        <v>-1</v>
+        <v>4.26291822571061</v>
       </c>
     </row>
     <row r="5404" spans="1:1">
       <c r="A5404">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5405" spans="1:1">
       <c r="A5405">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5406" spans="1:1">
       <c r="A5406">
-        <v>-1</v>
+        <v>8.508569414560085</v>
       </c>
     </row>
     <row r="5407" spans="1:1">
       <c r="A5407">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5408" spans="1:1">
       <c r="A5408">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5409" spans="1:1">
       <c r="A5409">
-        <v>-1</v>
+        <v>34.36758550018239</v>
       </c>
     </row>
     <row r="5410" spans="1:1">
       <c r="A5410">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5411" spans="1:1">
@@ -27519,17 +27519,17 @@
     </row>
     <row r="5429" spans="1:1">
       <c r="A5429">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5430" spans="1:1">
       <c r="A5430">
-        <v>-1</v>
+        <v>96.82299042589484</v>
       </c>
     </row>
     <row r="5431" spans="1:1">
       <c r="A5431">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5432" spans="1:1">
@@ -27744,17 +27744,17 @@
     </row>
     <row r="5474" spans="1:1">
       <c r="A5474">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5475" spans="1:1">
       <c r="A5475">
-        <v>-1</v>
+        <v>3.828420223504847</v>
       </c>
     </row>
     <row r="5476" spans="1:1">
       <c r="A5476">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5477" spans="1:1">
@@ -27774,17 +27774,17 @@
     </row>
     <row r="5480" spans="1:1">
       <c r="A5480">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5481" spans="1:1">
       <c r="A5481">
-        <v>-1</v>
+        <v>4.192305470447099</v>
       </c>
     </row>
     <row r="5482" spans="1:1">
       <c r="A5482">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5483" spans="1:1">
@@ -27834,17 +27834,17 @@
     </row>
     <row r="5492" spans="1:1">
       <c r="A5492">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5493" spans="1:1">
       <c r="A5493">
-        <v>-1</v>
+        <v>3.826365145872646</v>
       </c>
     </row>
     <row r="5494" spans="1:1">
       <c r="A5494">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5495" spans="1:1">
@@ -27879,17 +27879,17 @@
     </row>
     <row r="5501" spans="1:1">
       <c r="A5501">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5502" spans="1:1">
       <c r="A5502">
-        <v>-1</v>
+        <v>4.085452167396719</v>
       </c>
     </row>
     <row r="5503" spans="1:1">
       <c r="A5503">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5504" spans="1:1">
@@ -28149,17 +28149,17 @@
     </row>
     <row r="5555" spans="1:1">
       <c r="A5555">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5556" spans="1:1">
       <c r="A5556">
-        <v>-1</v>
+        <v>3.785428186829276</v>
       </c>
     </row>
     <row r="5557" spans="1:1">
       <c r="A5557">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5558" spans="1:1">
@@ -29229,17 +29229,17 @@
     </row>
     <row r="5771" spans="1:1">
       <c r="A5771">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5772" spans="1:1">
       <c r="A5772">
-        <v>-1</v>
+        <v>3.308860224784094</v>
       </c>
     </row>
     <row r="5773" spans="1:1">
       <c r="A5773">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5774" spans="1:1">
@@ -29274,17 +29274,17 @@
     </row>
     <row r="5780" spans="1:1">
       <c r="A5780">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5781" spans="1:1">
       <c r="A5781">
-        <v>-1</v>
+        <v>3.32560657907166</v>
       </c>
     </row>
     <row r="5782" spans="1:1">
       <c r="A5782">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5783" spans="1:1">
@@ -29304,17 +29304,17 @@
     </row>
     <row r="5786" spans="1:1">
       <c r="A5786">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5787" spans="1:1">
       <c r="A5787">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5788" spans="1:1">
       <c r="A5788">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5789" spans="1:1">
@@ -29424,17 +29424,17 @@
     </row>
     <row r="5810" spans="1:1">
       <c r="A5810">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5811" spans="1:1">
       <c r="A5811">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5812" spans="1:1">
       <c r="A5812">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5813" spans="1:1">
@@ -29544,17 +29544,17 @@
     </row>
     <row r="5834" spans="1:1">
       <c r="A5834">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5835" spans="1:1">
       <c r="A5835">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5836" spans="1:1">
       <c r="A5836">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5837" spans="1:1">
@@ -29649,17 +29649,17 @@
     </row>
     <row r="5855" spans="1:1">
       <c r="A5855">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5856" spans="1:1">
       <c r="A5856">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5857" spans="1:1">
       <c r="A5857">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5858" spans="1:1">
@@ -29709,17 +29709,17 @@
     </row>
     <row r="5867" spans="1:1">
       <c r="A5867">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5868" spans="1:1">
       <c r="A5868">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5869" spans="1:1">
       <c r="A5869">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5870" spans="1:1">
@@ -29799,17 +29799,17 @@
     </row>
     <row r="5885" spans="1:1">
       <c r="A5885">
-        <v>-1</v>
+        <v>7.891898670967179</v>
       </c>
     </row>
     <row r="5886" spans="1:1">
       <c r="A5886">
-        <v>-1</v>
+        <v>9.824107726587295</v>
       </c>
     </row>
     <row r="5887" spans="1:1">
       <c r="A5887">
-        <v>-1</v>
+        <v>7.891898670967179</v>
       </c>
     </row>
     <row r="5888" spans="1:1">
@@ -29934,17 +29934,17 @@
     </row>
     <row r="5912" spans="1:1">
       <c r="A5912">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5913" spans="1:1">
       <c r="A5913">
-        <v>-1</v>
+        <v>4.559770557895049</v>
       </c>
     </row>
     <row r="5914" spans="1:1">
       <c r="A5914">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5915" spans="1:1">
@@ -29964,17 +29964,17 @@
     </row>
     <row r="5918" spans="1:1">
       <c r="A5918">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5919" spans="1:1">
       <c r="A5919">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5920" spans="1:1">
       <c r="A5920">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5921" spans="1:1">
@@ -30084,32 +30084,32 @@
     </row>
     <row r="5942" spans="1:1">
       <c r="A5942">
-        <v>-1</v>
+        <v>3.505153868512356</v>
       </c>
     </row>
     <row r="5943" spans="1:1">
       <c r="A5943">
-        <v>-1</v>
+        <v>3.956007544042961</v>
       </c>
     </row>
     <row r="5944" spans="1:1">
       <c r="A5944">
-        <v>-1</v>
+        <v>3.356747578864194</v>
       </c>
     </row>
     <row r="5945" spans="1:1">
       <c r="A5945">
-        <v>-1</v>
+        <v>3.683148610981579</v>
       </c>
     </row>
     <row r="5946" spans="1:1">
       <c r="A5946">
-        <v>-1</v>
+        <v>5.884709592932436</v>
       </c>
     </row>
     <row r="5947" spans="1:1">
       <c r="A5947">
-        <v>-1</v>
+        <v>3.66954480424686</v>
       </c>
     </row>
     <row r="5948" spans="1:1">
@@ -30144,17 +30144,17 @@
     </row>
     <row r="5954" spans="1:1">
       <c r="A5954">
-        <v>-1</v>
+        <v>3.66954480424686</v>
       </c>
     </row>
     <row r="5955" spans="1:1">
       <c r="A5955">
-        <v>-1</v>
+        <v>6.925453291996031</v>
       </c>
     </row>
     <row r="5956" spans="1:1">
       <c r="A5956">
-        <v>-1</v>
+        <v>3.66954480424686</v>
       </c>
     </row>
     <row r="5957" spans="1:1">
@@ -30294,17 +30294,17 @@
     </row>
     <row r="5984" spans="1:1">
       <c r="A5984">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5985" spans="1:1">
       <c r="A5985">
-        <v>-1</v>
+        <v>6.561794027999712</v>
       </c>
     </row>
     <row r="5986" spans="1:1">
       <c r="A5986">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5987" spans="1:1">
@@ -30339,17 +30339,17 @@
     </row>
     <row r="5993" spans="1:1">
       <c r="A5993">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5994" spans="1:1">
       <c r="A5994">
-        <v>-1</v>
+        <v>10.15555140143298</v>
       </c>
     </row>
     <row r="5995" spans="1:1">
       <c r="A5995">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5996" spans="1:1">
@@ -30624,17 +30624,17 @@
     </row>
     <row r="6050" spans="1:1">
       <c r="A6050">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6051" spans="1:1">
       <c r="A6051">
-        <v>-1</v>
+        <v>3.6157053915576</v>
       </c>
     </row>
     <row r="6052" spans="1:1">
       <c r="A6052">
-        <v>-1</v>
+        <v>3.30798110827395</v>
       </c>
     </row>
     <row r="6053" spans="1:1">
@@ -30654,17 +30654,17 @@
     </row>
     <row r="6056" spans="1:1">
       <c r="A6056">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6057" spans="1:1">
       <c r="A6057">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6058" spans="1:1">
       <c r="A6058">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6059" spans="1:1">
@@ -30729,17 +30729,17 @@
     </row>
     <row r="6071" spans="1:1">
       <c r="A6071">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6072" spans="1:1">
       <c r="A6072">
-        <v>-1</v>
+        <v>3.395815585909334</v>
       </c>
     </row>
     <row r="6073" spans="1:1">
       <c r="A6073">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6074" spans="1:1">
@@ -30819,17 +30819,17 @@
     </row>
     <row r="6089" spans="1:1">
       <c r="A6089">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6090" spans="1:1">
       <c r="A6090">
-        <v>-1</v>
+        <v>3.53393937839992</v>
       </c>
     </row>
     <row r="6091" spans="1:1">
       <c r="A6091">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6092" spans="1:1">
@@ -31089,17 +31089,17 @@
     </row>
     <row r="6143" spans="1:1">
       <c r="A6143">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6144" spans="1:1">
       <c r="A6144">
-        <v>-1</v>
+        <v>3.33152484977457</v>
       </c>
     </row>
     <row r="6145" spans="1:1">
       <c r="A6145">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6146" spans="1:1">
@@ -31164,17 +31164,17 @@
     </row>
     <row r="6158" spans="1:1">
       <c r="A6158">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6159" spans="1:1">
       <c r="A6159">
-        <v>-1</v>
+        <v>3.55139837679217</v>
       </c>
     </row>
     <row r="6160" spans="1:1">
       <c r="A6160">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6161" spans="1:1">
@@ -31224,17 +31224,17 @@
     </row>
     <row r="6170" spans="1:1">
       <c r="A6170">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6171" spans="1:1">
       <c r="A6171">
-        <v>-1</v>
+        <v>3.858791972667297</v>
       </c>
     </row>
     <row r="6172" spans="1:1">
       <c r="A6172">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6173" spans="1:1">
@@ -31359,17 +31359,17 @@
     </row>
     <row r="6197" spans="1:1">
       <c r="A6197">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6198" spans="1:1">
       <c r="A6198">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6199" spans="1:1">
       <c r="A6199">
-        <v>-1</v>
+        <v>3.300000000000103</v>
       </c>
     </row>
     <row r="6200" spans="1:1">
@@ -31539,17 +31539,17 @@
     </row>
     <row r="6233" spans="1:1">
       <c r="A6233">
-        <v>-1</v>
+        <v>3.759911235051705</v>
       </c>
     </row>
     <row r="6234" spans="1:1">
       <c r="A6234">
-        <v>-1</v>
+        <v>6.334324361705934</v>
       </c>
     </row>
     <row r="6235" spans="1:1">
       <c r="A6235">
-        <v>-1</v>
+        <v>3.997012670505207</v>
       </c>
     </row>
     <row r="6236" spans="1:1">
@@ -32094,17 +32094,17 @@
     </row>
     <row r="6344" spans="1:1">
       <c r="A6344">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6345" spans="1:1">
       <c r="A6345">
-        <v>-1</v>
+        <v>4.500732361933135</v>
       </c>
     </row>
     <row r="6346" spans="1:1">
       <c r="A6346">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6347" spans="1:1">
@@ -32154,17 +32154,17 @@
     </row>
     <row r="6356" spans="1:1">
       <c r="A6356">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6357" spans="1:1">
       <c r="A6357">
-        <v>-1</v>
+        <v>3.541953242089213</v>
       </c>
     </row>
     <row r="6358" spans="1:1">
       <c r="A6358">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6359" spans="1:1">
@@ -32244,17 +32244,17 @@
     </row>
     <row r="6374" spans="1:1">
       <c r="A6374">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6375" spans="1:1">
       <c r="A6375">
-        <v>-1</v>
+        <v>3.529495849800424</v>
       </c>
     </row>
     <row r="6376" spans="1:1">
       <c r="A6376">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6377" spans="1:1">
@@ -32424,17 +32424,17 @@
     </row>
     <row r="6410" spans="1:1">
       <c r="A6410">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6411" spans="1:1">
       <c r="A6411">
-        <v>-1</v>
+        <v>3.483141012207769</v>
       </c>
     </row>
     <row r="6412" spans="1:1">
       <c r="A6412">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6413" spans="1:1">
@@ -32604,17 +32604,17 @@
     </row>
     <row r="6446" spans="1:1">
       <c r="A6446">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6447" spans="1:1">
       <c r="A6447">
-        <v>-1</v>
+        <v>3.471915804574688</v>
       </c>
     </row>
     <row r="6448" spans="1:1">
       <c r="A6448">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6449" spans="1:1">
@@ -32964,17 +32964,17 @@
     </row>
     <row r="6518" spans="1:1">
       <c r="A6518">
-        <v>-1</v>
+        <v>3.488871432729734</v>
       </c>
     </row>
     <row r="6519" spans="1:1">
       <c r="A6519">
-        <v>-1</v>
+        <v>7.098819110753373</v>
       </c>
     </row>
     <row r="6520" spans="1:1">
       <c r="A6520">
-        <v>-1</v>
+        <v>3.357634879991167</v>
       </c>
     </row>
     <row r="6521" spans="1:1">
@@ -33384,17 +33384,17 @@
     </row>
     <row r="6602" spans="1:1">
       <c r="A6602">
-        <v>-1</v>
+        <v>4.245371273510823</v>
       </c>
     </row>
     <row r="6603" spans="1:1">
       <c r="A6603">
-        <v>-1</v>
+        <v>174.667124280429</v>
       </c>
     </row>
     <row r="6604" spans="1:1">
       <c r="A6604">
-        <v>-1</v>
+        <v>4.245371273510823</v>
       </c>
     </row>
     <row r="6605" spans="1:1">
@@ -33519,17 +33519,17 @@
     </row>
     <row r="6629" spans="1:1">
       <c r="A6629">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6630" spans="1:1">
       <c r="A6630">
-        <v>-1</v>
+        <v>3.616191306631888</v>
       </c>
     </row>
     <row r="6631" spans="1:1">
       <c r="A6631">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6632" spans="1:1">
@@ -33609,17 +33609,17 @@
     </row>
     <row r="6647" spans="1:1">
       <c r="A6647">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6648" spans="1:1">
       <c r="A6648">
-        <v>-1</v>
+        <v>3.613565673699304</v>
       </c>
     </row>
     <row r="6649" spans="1:1">
       <c r="A6649">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6650" spans="1:1">
@@ -34254,17 +34254,17 @@
     </row>
     <row r="6776" spans="1:1">
       <c r="A6776">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6777" spans="1:1">
       <c r="A6777">
-        <v>-1</v>
+        <v>43.10186617895167</v>
       </c>
     </row>
     <row r="6778" spans="1:1">
       <c r="A6778">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6779" spans="1:1">
@@ -34974,17 +34974,17 @@
     </row>
     <row r="6920" spans="1:1">
       <c r="A6920">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6921" spans="1:1">
       <c r="A6921">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6922" spans="1:1">
       <c r="A6922">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6923" spans="1:1">
@@ -35124,17 +35124,17 @@
     </row>
     <row r="6950" spans="1:1">
       <c r="A6950">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6951" spans="1:1">
       <c r="A6951">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6952" spans="1:1">
       <c r="A6952">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6953" spans="1:1">
@@ -35244,17 +35244,17 @@
     </row>
     <row r="6974" spans="1:1">
       <c r="A6974">
-        <v>-1</v>
+        <v>9.532883424102456</v>
       </c>
     </row>
     <row r="6975" spans="1:1">
       <c r="A6975">
-        <v>-1</v>
+        <v>11.44819412933759</v>
       </c>
     </row>
     <row r="6976" spans="1:1">
       <c r="A6976">
-        <v>-1</v>
+        <v>9.56895084627385</v>
       </c>
     </row>
     <row r="6977" spans="1:1">
@@ -35304,47 +35304,47 @@
     </row>
     <row r="6986" spans="1:1">
       <c r="A6986">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6987" spans="1:1">
       <c r="A6987">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6988" spans="1:1">
       <c r="A6988">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6989" spans="1:1">
       <c r="A6989">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6990" spans="1:1">
       <c r="A6990">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6991" spans="1:1">
       <c r="A6991">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="6992" spans="1:1">
       <c r="A6992">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6993" spans="1:1">
       <c r="A6993">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6994" spans="1:1">
       <c r="A6994">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6995" spans="1:1">
@@ -35394,17 +35394,17 @@
     </row>
     <row r="7004" spans="1:1">
       <c r="A7004">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="7005" spans="1:1">
       <c r="A7005">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7006" spans="1:1">
       <c r="A7006">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7007" spans="1:1">
@@ -35424,17 +35424,17 @@
     </row>
     <row r="7010" spans="1:1">
       <c r="A7010">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7011" spans="1:1">
       <c r="A7011">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7012" spans="1:1">
       <c r="A7012">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7013" spans="1:1">
@@ -35814,17 +35814,17 @@
     </row>
     <row r="7088" spans="1:1">
       <c r="A7088">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7089" spans="1:1">
       <c r="A7089">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7090" spans="1:1">
       <c r="A7090">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7091" spans="1:1">
@@ -35904,17 +35904,17 @@
     </row>
     <row r="7106" spans="1:1">
       <c r="A7106">
-        <v>-1</v>
+        <v>4.617870629751364</v>
       </c>
     </row>
     <row r="7107" spans="1:1">
       <c r="A7107">
-        <v>-1</v>
+        <v>8.588261109542294</v>
       </c>
     </row>
     <row r="7108" spans="1:1">
       <c r="A7108">
-        <v>-1</v>
+        <v>4.617870629751364</v>
       </c>
     </row>
     <row r="7109" spans="1:1">
@@ -35964,17 +35964,17 @@
     </row>
     <row r="7118" spans="1:1">
       <c r="A7118">
-        <v>-1</v>
+        <v>11.49626664444358</v>
       </c>
     </row>
     <row r="7119" spans="1:1">
       <c r="A7119">
-        <v>-1</v>
+        <v>19.3845850909819</v>
       </c>
     </row>
     <row r="7120" spans="1:1">
       <c r="A7120">
-        <v>-1</v>
+        <v>11.31578359662323</v>
       </c>
     </row>
     <row r="7121" spans="1:1">
@@ -36489,17 +36489,17 @@
     </row>
     <row r="7223" spans="1:1">
       <c r="A7223">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7224" spans="1:1">
       <c r="A7224">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7225" spans="1:1">
       <c r="A7225">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7226" spans="1:1">
@@ -37209,17 +37209,17 @@
     </row>
     <row r="7367" spans="1:1">
       <c r="A7367">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7368" spans="1:1">
       <c r="A7368">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7369" spans="1:1">
       <c r="A7369">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="7370" spans="1:1">
@@ -37494,17 +37494,17 @@
     </row>
     <row r="7424" spans="1:1">
       <c r="A7424">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7425" spans="1:1">
       <c r="A7425">
-        <v>-1</v>
+        <v>11.65738022105744</v>
       </c>
     </row>
     <row r="7426" spans="1:1">
       <c r="A7426">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7427" spans="1:1">
@@ -37569,17 +37569,17 @@
     </row>
     <row r="7439" spans="1:1">
       <c r="A7439">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7440" spans="1:1">
       <c r="A7440">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7441" spans="1:1">
       <c r="A7441">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7442" spans="1:1">
@@ -37824,32 +37824,32 @@
     </row>
     <row r="7490" spans="1:1">
       <c r="A7490">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7491" spans="1:1">
       <c r="A7491">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7492" spans="1:1">
       <c r="A7492">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7493" spans="1:1">
       <c r="A7493">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7494" spans="1:1">
       <c r="A7494">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7495" spans="1:1">
       <c r="A7495">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7496" spans="1:1">
@@ -37869,17 +37869,17 @@
     </row>
     <row r="7499" spans="1:1">
       <c r="A7499">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7500" spans="1:1">
       <c r="A7500">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7501" spans="1:1">
       <c r="A7501">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7502" spans="1:1">
@@ -37914,17 +37914,17 @@
     </row>
     <row r="7508" spans="1:1">
       <c r="A7508">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7509" spans="1:1">
       <c r="A7509">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7510" spans="1:1">
       <c r="A7510">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7511" spans="1:1">
@@ -38004,17 +38004,17 @@
     </row>
     <row r="7526" spans="1:1">
       <c r="A7526">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="7527" spans="1:1">
       <c r="A7527">
-        <v>-1</v>
+        <v>3.717054467169734</v>
       </c>
     </row>
     <row r="7528" spans="1:1">
       <c r="A7528">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7529" spans="1:1">
@@ -38184,17 +38184,17 @@
     </row>
     <row r="7562" spans="1:1">
       <c r="A7562">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7563" spans="1:1">
       <c r="A7563">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7564" spans="1:1">
       <c r="A7564">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="7565" spans="1:1">
@@ -38649,17 +38649,17 @@
     </row>
     <row r="7655" spans="1:1">
       <c r="A7655">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7656" spans="1:1">
       <c r="A7656">
-        <v>-1</v>
+        <v>9.486791416302086</v>
       </c>
     </row>
     <row r="7657" spans="1:1">
       <c r="A7657">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7658" spans="1:1">
@@ -39264,17 +39264,17 @@
     </row>
     <row r="7778" spans="1:1">
       <c r="A7778">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7779" spans="1:1">
       <c r="A7779">
-        <v>-1</v>
+        <v>3.457737583245701</v>
       </c>
     </row>
     <row r="7780" spans="1:1">
       <c r="A7780">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7781" spans="1:1">
@@ -39804,17 +39804,17 @@
     </row>
     <row r="7886" spans="1:1">
       <c r="A7886">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7887" spans="1:1">
       <c r="A7887">
-        <v>-1</v>
+        <v>4.675489236094521</v>
       </c>
     </row>
     <row r="7888" spans="1:1">
       <c r="A7888">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7889" spans="1:1">
@@ -40734,32 +40734,32 @@
     </row>
     <row r="8072" spans="1:1">
       <c r="A8072">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8073" spans="1:1">
       <c r="A8073">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8074" spans="1:1">
       <c r="A8074">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8075" spans="1:1">
       <c r="A8075">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8076" spans="1:1">
       <c r="A8076">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8077" spans="1:1">
       <c r="A8077">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8078" spans="1:1">
@@ -41079,32 +41079,32 @@
     </row>
     <row r="8141" spans="1:1">
       <c r="A8141">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8142" spans="1:1">
       <c r="A8142">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8143" spans="1:1">
       <c r="A8143">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8144" spans="1:1">
       <c r="A8144">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8145" spans="1:1">
       <c r="A8145">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8146" spans="1:1">
       <c r="A8146">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8147" spans="1:1">
@@ -41229,17 +41229,17 @@
     </row>
     <row r="8171" spans="1:1">
       <c r="A8171">
-        <v>-1</v>
+        <v>3.300000000000081</v>
       </c>
     </row>
     <row r="8172" spans="1:1">
       <c r="A8172">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8173" spans="1:1">
       <c r="A8173">
-        <v>-1</v>
+        <v>3.300000000000081</v>
       </c>
     </row>
     <row r="8174" spans="1:1">
@@ -41814,17 +41814,17 @@
     </row>
     <row r="8288" spans="1:1">
       <c r="A8288">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8289" spans="1:1">
       <c r="A8289">
-        <v>-1</v>
+        <v>11.70630449358104</v>
       </c>
     </row>
     <row r="8290" spans="1:1">
       <c r="A8290">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8291" spans="1:1">
@@ -42159,17 +42159,17 @@
     </row>
     <row r="8357" spans="1:1">
       <c r="A8357">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8358" spans="1:1">
       <c r="A8358">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8359" spans="1:1">
       <c r="A8359">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8360" spans="1:1">
@@ -42249,17 +42249,17 @@
     </row>
     <row r="8375" spans="1:1">
       <c r="A8375">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8376" spans="1:1">
       <c r="A8376">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8377" spans="1:1">
       <c r="A8377">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8378" spans="1:1">
@@ -43584,32 +43584,32 @@
     </row>
     <row r="8642" spans="1:1">
       <c r="A8642">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8643" spans="1:1">
       <c r="A8643">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8644" spans="1:1">
       <c r="A8644">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8645" spans="1:1">
       <c r="A8645">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8646" spans="1:1">
       <c r="A8646">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8647" spans="1:1">
       <c r="A8647">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8648" spans="1:1">
@@ -43824,17 +43824,17 @@
     </row>
     <row r="8690" spans="1:1">
       <c r="A8690">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8691" spans="1:1">
       <c r="A8691">
-        <v>-1</v>
+        <v>6.547087812042129</v>
       </c>
     </row>
     <row r="8692" spans="1:1">
       <c r="A8692">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8693" spans="1:1">
@@ -43944,17 +43944,17 @@
     </row>
     <row r="8714" spans="1:1">
       <c r="A8714">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8715" spans="1:1">
       <c r="A8715">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8716" spans="1:1">
       <c r="A8716">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8717" spans="1:1">
@@ -45759,17 +45759,17 @@
     </row>
     <row r="9077" spans="1:1">
       <c r="A9077">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="9078" spans="1:1">
       <c r="A9078">
-        <v>-1</v>
+        <v>13.00357867807719</v>
       </c>
     </row>
     <row r="9079" spans="1:1">
       <c r="A9079">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="9080" spans="1:1">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -1044,17 +1044,17 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134">
-        <v>-1</v>
+        <v>8.86212771391326</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135">
-        <v>-1</v>
+        <v>9.777586651088953</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136">
-        <v>-1</v>
+        <v>7.82616223722552</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -1074,32 +1074,32 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140">
-        <v>-1</v>
+        <v>3.478564081431912</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141">
-        <v>-1</v>
+        <v>3.800062452863739</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143">
-        <v>-1</v>
+        <v>8.899625586124616</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144">
-        <v>-1</v>
+        <v>9.788624555622238</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145">
-        <v>-1</v>
+        <v>7.82616223722552</v>
       </c>
     </row>
     <row r="146" spans="1:1">
@@ -1254,17 +1254,17 @@
     </row>
     <row r="176" spans="1:1">
       <c r="A176">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -1419,17 +1419,17 @@
     </row>
     <row r="209" spans="1:1">
       <c r="A209">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210">
-        <v>-1</v>
+        <v>4.266676572361872</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="212" spans="1:1">
@@ -1614,17 +1614,17 @@
     </row>
     <row r="248" spans="1:1">
       <c r="A248">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="251" spans="1:1">
@@ -2364,17 +2364,17 @@
     </row>
     <row r="398" spans="1:1">
       <c r="A398">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399">
-        <v>-1</v>
+        <v>3.823283638647079</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400">
-        <v>-1</v>
+        <v>3.532518266682527</v>
       </c>
     </row>
     <row r="401" spans="1:1">
@@ -2589,17 +2589,17 @@
     </row>
     <row r="443" spans="1:1">
       <c r="A443">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="444" spans="1:1">
       <c r="A444">
-        <v>-1</v>
+        <v>3.538287297568776</v>
       </c>
     </row>
     <row r="445" spans="1:1">
       <c r="A445">
-        <v>-1</v>
+        <v>3.381484987036809</v>
       </c>
     </row>
     <row r="446" spans="1:1">
@@ -2769,17 +2769,17 @@
     </row>
     <row r="479" spans="1:1">
       <c r="A479">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="480" spans="1:1">
       <c r="A480">
-        <v>-1</v>
+        <v>4.473993137132459</v>
       </c>
     </row>
     <row r="481" spans="1:1">
       <c r="A481">
-        <v>-1</v>
+        <v>3.363503462445805</v>
       </c>
     </row>
     <row r="482" spans="1:1">
@@ -2904,17 +2904,17 @@
     </row>
     <row r="506" spans="1:1">
       <c r="A506">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="507" spans="1:1">
       <c r="A507">
-        <v>-1</v>
+        <v>3.679325654684895</v>
       </c>
     </row>
     <row r="508" spans="1:1">
       <c r="A508">
-        <v>-1</v>
+        <v>3.3466843324782</v>
       </c>
     </row>
     <row r="509" spans="1:1">
@@ -3699,17 +3699,17 @@
     </row>
     <row r="665" spans="1:1">
       <c r="A665">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="666" spans="1:1">
       <c r="A666">
-        <v>-1</v>
+        <v>8.880035657881535</v>
       </c>
     </row>
     <row r="667" spans="1:1">
       <c r="A667">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="668" spans="1:1">
@@ -4194,32 +4194,32 @@
     </row>
     <row r="764" spans="1:1">
       <c r="A764">
-        <v>-1</v>
+        <v>9.783676150472441</v>
       </c>
     </row>
     <row r="765" spans="1:1">
       <c r="A765">
-        <v>-1</v>
+        <v>39.0984887726474</v>
       </c>
     </row>
     <row r="766" spans="1:1">
       <c r="A766">
-        <v>-1</v>
+        <v>8.731597351776754</v>
       </c>
     </row>
     <row r="767" spans="1:1">
       <c r="A767">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="768" spans="1:1">
       <c r="A768">
-        <v>-1</v>
+        <v>92.46403844001004</v>
       </c>
     </row>
     <row r="769" spans="1:1">
       <c r="A769">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="770" spans="1:1">
@@ -4779,17 +4779,17 @@
     </row>
     <row r="881" spans="1:1">
       <c r="A881">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="882" spans="1:1">
       <c r="A882">
-        <v>-1</v>
+        <v>10.02239114780554</v>
       </c>
     </row>
     <row r="883" spans="1:1">
       <c r="A883">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="884" spans="1:1">
@@ -5499,17 +5499,17 @@
     </row>
     <row r="1025" spans="1:1">
       <c r="A1025">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1026" spans="1:1">
       <c r="A1026">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1027" spans="1:1">
       <c r="A1027">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1028" spans="1:1">
@@ -6429,17 +6429,17 @@
     </row>
     <row r="1211" spans="1:1">
       <c r="A1211">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="1212" spans="1:1">
       <c r="A1212">
-        <v>-1</v>
+        <v>3.443177127131536</v>
       </c>
     </row>
     <row r="1213" spans="1:1">
       <c r="A1213">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1214" spans="1:1">
@@ -6474,17 +6474,17 @@
     </row>
     <row r="1220" spans="1:1">
       <c r="A1220">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1221" spans="1:1">
       <c r="A1221">
-        <v>-1</v>
+        <v>3.407127029177204</v>
       </c>
     </row>
     <row r="1222" spans="1:1">
       <c r="A1222">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1223" spans="1:1">
@@ -6834,17 +6834,17 @@
     </row>
     <row r="1292" spans="1:1">
       <c r="A1292">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1293" spans="1:1">
       <c r="A1293">
-        <v>-1</v>
+        <v>3.549371059670114</v>
       </c>
     </row>
     <row r="1294" spans="1:1">
       <c r="A1294">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1295" spans="1:1">
@@ -7014,17 +7014,17 @@
     </row>
     <row r="1328" spans="1:1">
       <c r="A1328">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1329" spans="1:1">
       <c r="A1329">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1330" spans="1:1">
       <c r="A1330">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1331" spans="1:1">
@@ -7134,47 +7134,47 @@
     </row>
     <row r="1352" spans="1:1">
       <c r="A1352">
-        <v>-1</v>
+        <v>3.496832619967361</v>
       </c>
     </row>
     <row r="1353" spans="1:1">
       <c r="A1353">
-        <v>-1</v>
+        <v>3.948766948941262</v>
       </c>
     </row>
     <row r="1354" spans="1:1">
       <c r="A1354">
-        <v>-1</v>
+        <v>3.514679351257821</v>
       </c>
     </row>
     <row r="1355" spans="1:1">
       <c r="A1355">
-        <v>-1</v>
+        <v>3.685316857867205</v>
       </c>
     </row>
     <row r="1356" spans="1:1">
       <c r="A1356">
-        <v>-1</v>
+        <v>5.27764142030377</v>
       </c>
     </row>
     <row r="1357" spans="1:1">
       <c r="A1357">
-        <v>-1</v>
+        <v>3.314076103430241</v>
       </c>
     </row>
     <row r="1358" spans="1:1">
       <c r="A1358">
-        <v>-1</v>
+        <v>9.379956687282665</v>
       </c>
     </row>
     <row r="1359" spans="1:1">
       <c r="A1359">
-        <v>-1</v>
+        <v>13.58844008610722</v>
       </c>
     </row>
     <row r="1360" spans="1:1">
       <c r="A1360">
-        <v>-1</v>
+        <v>8.370065681542748</v>
       </c>
     </row>
     <row r="1361" spans="1:1">
@@ -7629,17 +7629,17 @@
     </row>
     <row r="1451" spans="1:1">
       <c r="A1451">
-        <v>-1</v>
+        <v>3.30798110827395</v>
       </c>
     </row>
     <row r="1452" spans="1:1">
       <c r="A1452">
-        <v>-1</v>
+        <v>3.905769649497381</v>
       </c>
     </row>
     <row r="1453" spans="1:1">
       <c r="A1453">
-        <v>-1</v>
+        <v>3.663104538670381</v>
       </c>
     </row>
     <row r="1454" spans="1:1">
@@ -7764,17 +7764,17 @@
     </row>
     <row r="1478" spans="1:1">
       <c r="A1478">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1479" spans="1:1">
       <c r="A1479">
-        <v>-1</v>
+        <v>4.009595477813033</v>
       </c>
     </row>
     <row r="1480" spans="1:1">
       <c r="A1480">
-        <v>-1</v>
+        <v>3.652570770403485</v>
       </c>
     </row>
     <row r="1481" spans="1:1">
@@ -7839,32 +7839,32 @@
     </row>
     <row r="1493" spans="1:1">
       <c r="A1493">
-        <v>-1</v>
+        <v>6.930377656953435</v>
       </c>
     </row>
     <row r="1494" spans="1:1">
       <c r="A1494">
-        <v>-1</v>
+        <v>8.296729053279551</v>
       </c>
     </row>
     <row r="1495" spans="1:1">
       <c r="A1495">
-        <v>-1</v>
+        <v>6.14929915898853</v>
       </c>
     </row>
     <row r="1496" spans="1:1">
       <c r="A1496">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1497" spans="1:1">
       <c r="A1497">
-        <v>-1</v>
+        <v>3.965967495370815</v>
       </c>
     </row>
     <row r="1498" spans="1:1">
       <c r="A1498">
-        <v>-1</v>
+        <v>3.608277376510549</v>
       </c>
     </row>
     <row r="1499" spans="1:1">
@@ -7989,17 +7989,17 @@
     </row>
     <row r="1523" spans="1:1">
       <c r="A1523">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1524" spans="1:1">
       <c r="A1524">
-        <v>-1</v>
+        <v>3.871580380674566</v>
       </c>
     </row>
     <row r="1525" spans="1:1">
       <c r="A1525">
-        <v>-1</v>
+        <v>3.631396130295794</v>
       </c>
     </row>
     <row r="1526" spans="1:1">
@@ -8019,17 +8019,17 @@
     </row>
     <row r="1529" spans="1:1">
       <c r="A1529">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1530" spans="1:1">
       <c r="A1530">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1531" spans="1:1">
       <c r="A1531">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1532" spans="1:1">
@@ -8169,17 +8169,17 @@
     </row>
     <row r="1559" spans="1:1">
       <c r="A1559">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1560" spans="1:1">
       <c r="A1560">
-        <v>-1</v>
+        <v>3.86178755555191</v>
       </c>
     </row>
     <row r="1561" spans="1:1">
       <c r="A1561">
-        <v>-1</v>
+        <v>3.619503988675388</v>
       </c>
     </row>
     <row r="1562" spans="1:1">
@@ -8274,17 +8274,17 @@
     </row>
     <row r="1580" spans="1:1">
       <c r="A1580">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1581" spans="1:1">
       <c r="A1581">
-        <v>-1</v>
+        <v>4.023136562150176</v>
       </c>
     </row>
     <row r="1582" spans="1:1">
       <c r="A1582">
-        <v>-1</v>
+        <v>3.371271246430951</v>
       </c>
     </row>
     <row r="1583" spans="1:1">
@@ -8349,17 +8349,17 @@
     </row>
     <row r="1595" spans="1:1">
       <c r="A1595">
-        <v>-1</v>
+        <v>3.482032953670089</v>
       </c>
     </row>
     <row r="1596" spans="1:1">
       <c r="A1596">
-        <v>-1</v>
+        <v>3.745877484734517</v>
       </c>
     </row>
     <row r="1597" spans="1:1">
       <c r="A1597">
-        <v>-1</v>
+        <v>3.605388063942971</v>
       </c>
     </row>
     <row r="1598" spans="1:1">
@@ -8409,17 +8409,17 @@
     </row>
     <row r="1607" spans="1:1">
       <c r="A1607">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1608" spans="1:1">
       <c r="A1608">
-        <v>-1</v>
+        <v>3.615758039579453</v>
       </c>
     </row>
     <row r="1609" spans="1:1">
       <c r="A1609">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1610" spans="1:1">
@@ -8499,17 +8499,17 @@
     </row>
     <row r="1625" spans="1:1">
       <c r="A1625">
-        <v>-1</v>
+        <v>3.759911235051705</v>
       </c>
     </row>
     <row r="1626" spans="1:1">
       <c r="A1626">
-        <v>-1</v>
+        <v>5.962356229732801</v>
       </c>
     </row>
     <row r="1627" spans="1:1">
       <c r="A1627">
-        <v>-1</v>
+        <v>3.66452051922842</v>
       </c>
     </row>
     <row r="1628" spans="1:1">
@@ -8529,17 +8529,17 @@
     </row>
     <row r="1631" spans="1:1">
       <c r="A1631">
-        <v>-1</v>
+        <v>3.478374132046258</v>
       </c>
     </row>
     <row r="1632" spans="1:1">
       <c r="A1632">
-        <v>-1</v>
+        <v>5.026848702348885</v>
       </c>
     </row>
     <row r="1633" spans="1:1">
       <c r="A1633">
-        <v>-1</v>
+        <v>3.588531203760792</v>
       </c>
     </row>
     <row r="1634" spans="1:1">
@@ -8634,17 +8634,17 @@
     </row>
     <row r="1652" spans="1:1">
       <c r="A1652">
-        <v>-1</v>
+        <v>3.998372625366797</v>
       </c>
     </row>
     <row r="1653" spans="1:1">
       <c r="A1653">
-        <v>-1</v>
+        <v>6.90416209068645</v>
       </c>
     </row>
     <row r="1654" spans="1:1">
       <c r="A1654">
-        <v>-1</v>
+        <v>3.665756755702709</v>
       </c>
     </row>
     <row r="1655" spans="1:1">
@@ -8694,17 +8694,17 @@
     </row>
     <row r="1664" spans="1:1">
       <c r="A1664">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1665" spans="1:1">
       <c r="A1665">
-        <v>-1</v>
+        <v>6.965236017131538</v>
       </c>
     </row>
     <row r="1666" spans="1:1">
       <c r="A1666">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1667" spans="1:1">
@@ -9144,17 +9144,17 @@
     </row>
     <row r="1754" spans="1:1">
       <c r="A1754">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="1755" spans="1:1">
       <c r="A1755">
-        <v>-1</v>
+        <v>4.882472647275504</v>
       </c>
     </row>
     <row r="1756" spans="1:1">
       <c r="A1756">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1757" spans="1:1">
@@ -9294,17 +9294,17 @@
     </row>
     <row r="1784" spans="1:1">
       <c r="A1784">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1785" spans="1:1">
       <c r="A1785">
-        <v>-1</v>
+        <v>3.874081709325261</v>
       </c>
     </row>
     <row r="1786" spans="1:1">
       <c r="A1786">
-        <v>-1</v>
+        <v>3.448768126096802</v>
       </c>
     </row>
     <row r="1787" spans="1:1">
@@ -9324,17 +9324,17 @@
     </row>
     <row r="1790" spans="1:1">
       <c r="A1790">
-        <v>-1</v>
+        <v>7.079533974724439</v>
       </c>
     </row>
     <row r="1791" spans="1:1">
       <c r="A1791">
-        <v>-1</v>
+        <v>11.98184593879449</v>
       </c>
     </row>
     <row r="1792" spans="1:1">
       <c r="A1792">
-        <v>-1</v>
+        <v>6.290904915376272</v>
       </c>
     </row>
     <row r="1793" spans="1:1">
@@ -9759,32 +9759,32 @@
     </row>
     <row r="1877" spans="1:1">
       <c r="A1877">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1878" spans="1:1">
       <c r="A1878">
-        <v>-1</v>
+        <v>6.666206886897541</v>
       </c>
     </row>
     <row r="1879" spans="1:1">
       <c r="A1879">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1880" spans="1:1">
       <c r="A1880">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1881" spans="1:1">
       <c r="A1881">
-        <v>-1</v>
+        <v>27.73297758859389</v>
       </c>
     </row>
     <row r="1882" spans="1:1">
       <c r="A1882">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1883" spans="1:1">
@@ -9834,17 +9834,17 @@
     </row>
     <row r="1892" spans="1:1">
       <c r="A1892">
-        <v>-1</v>
+        <v>3.489252262541176</v>
       </c>
     </row>
     <row r="1893" spans="1:1">
       <c r="A1893">
-        <v>-1</v>
+        <v>3.950939610943793</v>
       </c>
     </row>
     <row r="1894" spans="1:1">
       <c r="A1894">
-        <v>-1</v>
+        <v>3.543817565055485</v>
       </c>
     </row>
     <row r="1895" spans="1:1">
@@ -9864,17 +9864,17 @@
     </row>
     <row r="1898" spans="1:1">
       <c r="A1898">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1899" spans="1:1">
       <c r="A1899">
-        <v>-1</v>
+        <v>27.87329069586969</v>
       </c>
     </row>
     <row r="1900" spans="1:1">
       <c r="A1900">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="1901" spans="1:1">
@@ -10134,17 +10134,17 @@
     </row>
     <row r="1952" spans="1:1">
       <c r="A1952">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1953" spans="1:1">
       <c r="A1953">
-        <v>-1</v>
+        <v>33.87892647543717</v>
       </c>
     </row>
     <row r="1954" spans="1:1">
       <c r="A1954">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="1955" spans="1:1">
@@ -10554,17 +10554,17 @@
     </row>
     <row r="2036" spans="1:1">
       <c r="A2036">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2037" spans="1:1">
       <c r="A2037">
-        <v>-1</v>
+        <v>4.274733722805002</v>
       </c>
     </row>
     <row r="2038" spans="1:1">
       <c r="A2038">
-        <v>-1</v>
+        <v>3.622687209623687</v>
       </c>
     </row>
     <row r="2039" spans="1:1">
@@ -11184,32 +11184,32 @@
     </row>
     <row r="2162" spans="1:1">
       <c r="A2162">
-        <v>-1</v>
+        <v>3.415708837859088</v>
       </c>
     </row>
     <row r="2163" spans="1:1">
       <c r="A2163">
-        <v>-1</v>
+        <v>5.084532504589745</v>
       </c>
     </row>
     <row r="2164" spans="1:1">
       <c r="A2164">
-        <v>-1</v>
+        <v>3.611382875049696</v>
       </c>
     </row>
     <row r="2165" spans="1:1">
       <c r="A2165">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2166" spans="1:1">
       <c r="A2166">
-        <v>-1</v>
+        <v>9.532983696482733</v>
       </c>
     </row>
     <row r="2167" spans="1:1">
       <c r="A2167">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2168" spans="1:1">
@@ -11379,17 +11379,17 @@
     </row>
     <row r="2201" spans="1:1">
       <c r="A2201">
-        <v>-1</v>
+        <v>3.805317624376636</v>
       </c>
     </row>
     <row r="2202" spans="1:1">
       <c r="A2202">
-        <v>-1</v>
+        <v>15.72868874573343</v>
       </c>
     </row>
     <row r="2203" spans="1:1">
       <c r="A2203">
-        <v>-1</v>
+        <v>3.714888059582278</v>
       </c>
     </row>
     <row r="2204" spans="1:1">
@@ -12054,17 +12054,17 @@
     </row>
     <row r="2336" spans="1:1">
       <c r="A2336">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2337" spans="1:1">
       <c r="A2337">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2338" spans="1:1">
       <c r="A2338">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2339" spans="1:1">
@@ -12549,17 +12549,17 @@
     </row>
     <row r="2435" spans="1:1">
       <c r="A2435">
-        <v>-1</v>
+        <v>4.450439722346921</v>
       </c>
     </row>
     <row r="2436" spans="1:1">
       <c r="A2436">
-        <v>-1</v>
+        <v>4.701376314373995</v>
       </c>
     </row>
     <row r="2437" spans="1:1">
       <c r="A2437">
-        <v>-1</v>
+        <v>3.761513044845577</v>
       </c>
     </row>
     <row r="2438" spans="1:1">
@@ -12849,17 +12849,17 @@
     </row>
     <row r="2495" spans="1:1">
       <c r="A2495">
-        <v>-1</v>
+        <v>3.425609462173984</v>
       </c>
     </row>
     <row r="2496" spans="1:1">
       <c r="A2496">
-        <v>-1</v>
+        <v>5.176039894955863</v>
       </c>
     </row>
     <row r="2497" spans="1:1">
       <c r="A2497">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2498" spans="1:1">
@@ -13074,17 +13074,17 @@
     </row>
     <row r="2540" spans="1:1">
       <c r="A2540">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2541" spans="1:1">
       <c r="A2541">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2542" spans="1:1">
       <c r="A2542">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2543" spans="1:1">
@@ -13494,17 +13494,17 @@
     </row>
     <row r="2624" spans="1:1">
       <c r="A2624">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="2625" spans="1:1">
       <c r="A2625">
-        <v>-1</v>
+        <v>3.408626347903665</v>
       </c>
     </row>
     <row r="2626" spans="1:1">
       <c r="A2626">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="2627" spans="1:1">
@@ -14424,17 +14424,17 @@
     </row>
     <row r="2810" spans="1:1">
       <c r="A2810">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2811" spans="1:1">
       <c r="A2811">
-        <v>-1</v>
+        <v>3.447794402723869</v>
       </c>
     </row>
     <row r="2812" spans="1:1">
       <c r="A2812">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2813" spans="1:1">
@@ -14514,17 +14514,17 @@
     </row>
     <row r="2828" spans="1:1">
       <c r="A2828">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2829" spans="1:1">
       <c r="A2829">
-        <v>-1</v>
+        <v>3.446526827756125</v>
       </c>
     </row>
     <row r="2830" spans="1:1">
       <c r="A2830">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2831" spans="1:1">
@@ -14919,17 +14919,17 @@
     </row>
     <row r="2909" spans="1:1">
       <c r="A2909">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="2910" spans="1:1">
       <c r="A2910">
-        <v>-1</v>
+        <v>3.735051399957745</v>
       </c>
     </row>
     <row r="2911" spans="1:1">
       <c r="A2911">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2912" spans="1:1">
@@ -15084,17 +15084,17 @@
     </row>
     <row r="2942" spans="1:1">
       <c r="A2942">
-        <v>-1</v>
+        <v>9.602653727317179</v>
       </c>
     </row>
     <row r="2943" spans="1:1">
       <c r="A2943">
-        <v>-1</v>
+        <v>12.97812299176634</v>
       </c>
     </row>
     <row r="2944" spans="1:1">
       <c r="A2944">
-        <v>-1</v>
+        <v>8.334845358289433</v>
       </c>
     </row>
     <row r="2945" spans="1:1">
@@ -15339,17 +15339,17 @@
     </row>
     <row r="2993" spans="1:1">
       <c r="A2993">
-        <v>-1</v>
+        <v>4.251179130864147</v>
       </c>
     </row>
     <row r="2994" spans="1:1">
       <c r="A2994">
-        <v>-1</v>
+        <v>5.46398570368437</v>
       </c>
     </row>
     <row r="2995" spans="1:1">
       <c r="A2995">
-        <v>-1</v>
+        <v>3.606412028949724</v>
       </c>
     </row>
     <row r="2996" spans="1:1">
@@ -15504,17 +15504,17 @@
     </row>
     <row r="3026" spans="1:1">
       <c r="A3026">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3027" spans="1:1">
       <c r="A3027">
-        <v>-1</v>
+        <v>4.019846460513977</v>
       </c>
     </row>
     <row r="3028" spans="1:1">
       <c r="A3028">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="3029" spans="1:1">
@@ -15594,17 +15594,17 @@
     </row>
     <row r="3044" spans="1:1">
       <c r="A3044">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3045" spans="1:1">
       <c r="A3045">
-        <v>-1</v>
+        <v>4.033714397768707</v>
       </c>
     </row>
     <row r="3046" spans="1:1">
       <c r="A3046">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3047" spans="1:1">
@@ -15684,17 +15684,17 @@
     </row>
     <row r="3062" spans="1:1">
       <c r="A3062">
-        <v>-1</v>
+        <v>3.528285914611939</v>
       </c>
     </row>
     <row r="3063" spans="1:1">
       <c r="A3063">
-        <v>-1</v>
+        <v>8.012987040193797</v>
       </c>
     </row>
     <row r="3064" spans="1:1">
       <c r="A3064">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3065" spans="1:1">
@@ -16239,17 +16239,17 @@
     </row>
     <row r="3173" spans="1:1">
       <c r="A3173">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3174" spans="1:1">
       <c r="A3174">
-        <v>-1</v>
+        <v>3.774669146778153</v>
       </c>
     </row>
     <row r="3175" spans="1:1">
       <c r="A3175">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3176" spans="1:1">
@@ -16419,17 +16419,17 @@
     </row>
     <row r="3209" spans="1:1">
       <c r="A3209">
-        <v>-1</v>
+        <v>3.734807955031438</v>
       </c>
     </row>
     <row r="3210" spans="1:1">
       <c r="A3210">
-        <v>-1</v>
+        <v>4.941262858327534</v>
       </c>
     </row>
     <row r="3211" spans="1:1">
       <c r="A3211">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3212" spans="1:1">
@@ -16959,17 +16959,17 @@
     </row>
     <row r="3317" spans="1:1">
       <c r="A3317">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="3318" spans="1:1">
       <c r="A3318">
-        <v>-1</v>
+        <v>9.058518009066596</v>
       </c>
     </row>
     <row r="3319" spans="1:1">
       <c r="A3319">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3320" spans="1:1">
@@ -18039,17 +18039,17 @@
     </row>
     <row r="3533" spans="1:1">
       <c r="A3533">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3534" spans="1:1">
       <c r="A3534">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3535" spans="1:1">
       <c r="A3535">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3536" spans="1:1">
@@ -18069,17 +18069,17 @@
     </row>
     <row r="3539" spans="1:1">
       <c r="A3539">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3540" spans="1:1">
       <c r="A3540">
-        <v>-1</v>
+        <v>3.372583071062563</v>
       </c>
     </row>
     <row r="3541" spans="1:1">
       <c r="A3541">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3542" spans="1:1">
@@ -18444,17 +18444,17 @@
     </row>
     <row r="3614" spans="1:1">
       <c r="A3614">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3615" spans="1:1">
       <c r="A3615">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3616" spans="1:1">
       <c r="A3616">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3617" spans="1:1">
@@ -18564,17 +18564,17 @@
     </row>
     <row r="3638" spans="1:1">
       <c r="A3638">
-        <v>-1</v>
+        <v>3.369733750683435</v>
       </c>
     </row>
     <row r="3639" spans="1:1">
       <c r="A3639">
-        <v>-1</v>
+        <v>4.291037354915339</v>
       </c>
     </row>
     <row r="3640" spans="1:1">
       <c r="A3640">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="3641" spans="1:1">
@@ -19194,17 +19194,17 @@
     </row>
     <row r="3764" spans="1:1">
       <c r="A3764">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3765" spans="1:1">
       <c r="A3765">
-        <v>-1</v>
+        <v>3.730562352399991</v>
       </c>
     </row>
     <row r="3766" spans="1:1">
       <c r="A3766">
-        <v>-1</v>
+        <v>3.400551823797926</v>
       </c>
     </row>
     <row r="3767" spans="1:1">
@@ -19254,17 +19254,17 @@
     </row>
     <row r="3776" spans="1:1">
       <c r="A3776">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3777" spans="1:1">
       <c r="A3777">
-        <v>-1</v>
+        <v>3.448223773989212</v>
       </c>
     </row>
     <row r="3778" spans="1:1">
       <c r="A3778">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3779" spans="1:1">
@@ -19284,17 +19284,17 @@
     </row>
     <row r="3782" spans="1:1">
       <c r="A3782">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3783" spans="1:1">
       <c r="A3783">
-        <v>-1</v>
+        <v>3.743648844350811</v>
       </c>
     </row>
     <row r="3784" spans="1:1">
       <c r="A3784">
-        <v>-1</v>
+        <v>3.433707447865131</v>
       </c>
     </row>
     <row r="3785" spans="1:1">
@@ -20589,17 +20589,17 @@
     </row>
     <row r="4043" spans="1:1">
       <c r="A4043">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4044" spans="1:1">
       <c r="A4044">
-        <v>-1</v>
+        <v>3.657398571207571</v>
       </c>
     </row>
     <row r="4045" spans="1:1">
       <c r="A4045">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4046" spans="1:1">
@@ -20934,17 +20934,17 @@
     </row>
     <row r="4112" spans="1:1">
       <c r="A4112">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4113" spans="1:1">
       <c r="A4113">
-        <v>-1</v>
+        <v>6.00748096617385</v>
       </c>
     </row>
     <row r="4114" spans="1:1">
       <c r="A4114">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4115" spans="1:1">
@@ -21084,17 +21084,17 @@
     </row>
     <row r="4142" spans="1:1">
       <c r="A4142">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4143" spans="1:1">
       <c r="A4143">
-        <v>-1</v>
+        <v>3.674996908357564</v>
       </c>
     </row>
     <row r="4144" spans="1:1">
       <c r="A4144">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4145" spans="1:1">
@@ -21354,17 +21354,17 @@
     </row>
     <row r="4196" spans="1:1">
       <c r="A4196">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4197" spans="1:1">
       <c r="A4197">
-        <v>-1</v>
+        <v>4.255011535548503</v>
       </c>
     </row>
     <row r="4198" spans="1:1">
       <c r="A4198">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4199" spans="1:1">
@@ -21669,17 +21669,17 @@
     </row>
     <row r="4259" spans="1:1">
       <c r="A4259">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4260" spans="1:1">
       <c r="A4260">
-        <v>-1</v>
+        <v>105.6169723701042</v>
       </c>
     </row>
     <row r="4261" spans="1:1">
       <c r="A4261">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4262" spans="1:1">
@@ -22344,17 +22344,17 @@
     </row>
     <row r="4394" spans="1:1">
       <c r="A4394">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4395" spans="1:1">
       <c r="A4395">
-        <v>-1</v>
+        <v>3.79857103348058</v>
       </c>
     </row>
     <row r="4396" spans="1:1">
       <c r="A4396">
-        <v>-1</v>
+        <v>3.392145865394336</v>
       </c>
     </row>
     <row r="4397" spans="1:1">
@@ -22389,17 +22389,17 @@
     </row>
     <row r="4403" spans="1:1">
       <c r="A4403">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4404" spans="1:1">
       <c r="A4404">
-        <v>-1</v>
+        <v>4.237509166454867</v>
       </c>
     </row>
     <row r="4405" spans="1:1">
       <c r="A4405">
-        <v>-1</v>
+        <v>3.392145865394336</v>
       </c>
     </row>
     <row r="4406" spans="1:1">
@@ -23679,17 +23679,17 @@
     </row>
     <row r="4661" spans="1:1">
       <c r="A4661">
-        <v>-1</v>
+        <v>7.334687434564635</v>
       </c>
     </row>
     <row r="4662" spans="1:1">
       <c r="A4662">
-        <v>-1</v>
+        <v>8.966308225772446</v>
       </c>
     </row>
     <row r="4663" spans="1:1">
       <c r="A4663">
-        <v>-1</v>
+        <v>7.334687434564635</v>
       </c>
     </row>
     <row r="4664" spans="1:1">
@@ -24189,17 +24189,17 @@
     </row>
     <row r="4763" spans="1:1">
       <c r="A4763">
-        <v>-1</v>
+        <v>3.299999999999881</v>
       </c>
     </row>
     <row r="4764" spans="1:1">
       <c r="A4764">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4765" spans="1:1">
       <c r="A4765">
-        <v>-1</v>
+        <v>3.299999999999881</v>
       </c>
     </row>
     <row r="4766" spans="1:1">
@@ -24369,17 +24369,17 @@
     </row>
     <row r="4799" spans="1:1">
       <c r="A4799">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4800" spans="1:1">
       <c r="A4800">
-        <v>-1</v>
+        <v>4.699788060168508</v>
       </c>
     </row>
     <row r="4801" spans="1:1">
       <c r="A4801">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4802" spans="1:1">
@@ -24939,17 +24939,17 @@
     </row>
     <row r="4913" spans="1:1">
       <c r="A4913">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4914" spans="1:1">
       <c r="A4914">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="4915" spans="1:1">
       <c r="A4915">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4916" spans="1:1">
@@ -25029,17 +25029,17 @@
     </row>
     <row r="4931" spans="1:1">
       <c r="A4931">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4932" spans="1:1">
       <c r="A4932">
-        <v>-1</v>
+        <v>3.299999999999903</v>
       </c>
     </row>
     <row r="4933" spans="1:1">
       <c r="A4933">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="4934" spans="1:1">
@@ -25404,17 +25404,17 @@
     </row>
     <row r="5006" spans="1:1">
       <c r="A5006">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5007" spans="1:1">
       <c r="A5007">
-        <v>-1</v>
+        <v>3.460312415632494</v>
       </c>
     </row>
     <row r="5008" spans="1:1">
       <c r="A5008">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5009" spans="1:1">
@@ -25584,17 +25584,17 @@
     </row>
     <row r="5042" spans="1:1">
       <c r="A5042">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5043" spans="1:1">
       <c r="A5043">
-        <v>-1</v>
+        <v>3.370566423827648</v>
       </c>
     </row>
     <row r="5044" spans="1:1">
       <c r="A5044">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5045" spans="1:1">
@@ -25674,32 +25674,32 @@
     </row>
     <row r="5060" spans="1:1">
       <c r="A5060">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5061" spans="1:1">
       <c r="A5061">
-        <v>-1</v>
+        <v>3.369363049202456</v>
       </c>
     </row>
     <row r="5062" spans="1:1">
       <c r="A5062">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5063" spans="1:1">
       <c r="A5063">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5064" spans="1:1">
       <c r="A5064">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5065" spans="1:1">
       <c r="A5065">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5066" spans="1:1">
@@ -25764,17 +25764,17 @@
     </row>
     <row r="5078" spans="1:1">
       <c r="A5078">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5079" spans="1:1">
       <c r="A5079">
-        <v>-1</v>
+        <v>4.19722675381673</v>
       </c>
     </row>
     <row r="5080" spans="1:1">
       <c r="A5080">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5081" spans="1:1">
@@ -26034,17 +26034,17 @@
     </row>
     <row r="5132" spans="1:1">
       <c r="A5132">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5133" spans="1:1">
       <c r="A5133">
-        <v>-1</v>
+        <v>3.310543112440523</v>
       </c>
     </row>
     <row r="5134" spans="1:1">
       <c r="A5134">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5135" spans="1:1">
@@ -27054,32 +27054,32 @@
     </row>
     <row r="5336" spans="1:1">
       <c r="A5336">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5337" spans="1:1">
       <c r="A5337">
-        <v>-1</v>
+        <v>27.47161230358396</v>
       </c>
     </row>
     <row r="5338" spans="1:1">
       <c r="A5338">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5339" spans="1:1">
       <c r="A5339">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5340" spans="1:1">
       <c r="A5340">
-        <v>-1</v>
+        <v>81.5012368288095</v>
       </c>
     </row>
     <row r="5341" spans="1:1">
       <c r="A5341">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5342" spans="1:1">
@@ -27249,17 +27249,17 @@
     </row>
     <row r="5375" spans="1:1">
       <c r="A5375">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5376" spans="1:1">
       <c r="A5376">
-        <v>-1</v>
+        <v>96.45264909268418</v>
       </c>
     </row>
     <row r="5377" spans="1:1">
       <c r="A5377">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5378" spans="1:1">
@@ -27789,17 +27789,17 @@
     </row>
     <row r="5483" spans="1:1">
       <c r="A5483">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5484" spans="1:1">
       <c r="A5484">
-        <v>-1</v>
+        <v>3.826246668269428</v>
       </c>
     </row>
     <row r="5485" spans="1:1">
       <c r="A5485">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5486" spans="1:1">
@@ -29259,17 +29259,17 @@
     </row>
     <row r="5777" spans="1:1">
       <c r="A5777">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5778" spans="1:1">
       <c r="A5778">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5779" spans="1:1">
       <c r="A5779">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5780" spans="1:1">
@@ -29394,17 +29394,17 @@
     </row>
     <row r="5804" spans="1:1">
       <c r="A5804">
-        <v>-1</v>
+        <v>6.555506883719864</v>
       </c>
     </row>
     <row r="5805" spans="1:1">
       <c r="A5805">
-        <v>-1</v>
+        <v>8.48533680822009</v>
       </c>
     </row>
     <row r="5806" spans="1:1">
       <c r="A5806">
-        <v>-1</v>
+        <v>6.618774861495691</v>
       </c>
     </row>
     <row r="5807" spans="1:1">
@@ -29454,32 +29454,32 @@
     </row>
     <row r="5816" spans="1:1">
       <c r="A5816">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5817" spans="1:1">
       <c r="A5817">
-        <v>-1</v>
+        <v>3.313503355659453</v>
       </c>
     </row>
     <row r="5818" spans="1:1">
       <c r="A5818">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5819" spans="1:1">
       <c r="A5819">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="5820" spans="1:1">
       <c r="A5820">
-        <v>-1</v>
+        <v>3.46142914037989</v>
       </c>
     </row>
     <row r="5821" spans="1:1">
       <c r="A5821">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5822" spans="1:1">
@@ -29499,17 +29499,17 @@
     </row>
     <row r="5825" spans="1:1">
       <c r="A5825">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5826" spans="1:1">
       <c r="A5826">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5827" spans="1:1">
       <c r="A5827">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="5828" spans="1:1">
@@ -29634,17 +29634,17 @@
     </row>
     <row r="5852" spans="1:1">
       <c r="A5852">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5853" spans="1:1">
       <c r="A5853">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5854" spans="1:1">
       <c r="A5854">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5855" spans="1:1">
@@ -29664,17 +29664,17 @@
     </row>
     <row r="5858" spans="1:1">
       <c r="A5858">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5859" spans="1:1">
       <c r="A5859">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5860" spans="1:1">
       <c r="A5860">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5861" spans="1:1">
@@ -29814,17 +29814,17 @@
     </row>
     <row r="5888" spans="1:1">
       <c r="A5888">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5889" spans="1:1">
       <c r="A5889">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5890" spans="1:1">
       <c r="A5890">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5891" spans="1:1">
@@ -29979,17 +29979,17 @@
     </row>
     <row r="5921" spans="1:1">
       <c r="A5921">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5922" spans="1:1">
       <c r="A5922">
-        <v>-1</v>
+        <v>7.217750460593775</v>
       </c>
     </row>
     <row r="5923" spans="1:1">
       <c r="A5923">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="5924" spans="1:1">
@@ -30009,17 +30009,17 @@
     </row>
     <row r="5927" spans="1:1">
       <c r="A5927">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5928" spans="1:1">
       <c r="A5928">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5929" spans="1:1">
       <c r="A5929">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5930" spans="1:1">
@@ -30699,32 +30699,32 @@
     </row>
     <row r="6065" spans="1:1">
       <c r="A6065">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6066" spans="1:1">
       <c r="A6066">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6067" spans="1:1">
       <c r="A6067">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6068" spans="1:1">
       <c r="A6068">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6069" spans="1:1">
       <c r="A6069">
-        <v>-1</v>
+        <v>3.593462867766495</v>
       </c>
     </row>
     <row r="6070" spans="1:1">
       <c r="A6070">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6071" spans="1:1">
@@ -30774,17 +30774,17 @@
     </row>
     <row r="6080" spans="1:1">
       <c r="A6080">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6081" spans="1:1">
       <c r="A6081">
-        <v>-1</v>
+        <v>3.319942185539859</v>
       </c>
     </row>
     <row r="6082" spans="1:1">
       <c r="A6082">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6083" spans="1:1">
@@ -30804,17 +30804,17 @@
     </row>
     <row r="6086" spans="1:1">
       <c r="A6086">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6087" spans="1:1">
       <c r="A6087">
-        <v>-1</v>
+        <v>3.606670392569566</v>
       </c>
     </row>
     <row r="6088" spans="1:1">
       <c r="A6088">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6089" spans="1:1">
@@ -30834,17 +30834,17 @@
     </row>
     <row r="6092" spans="1:1">
       <c r="A6092">
-        <v>-1</v>
+        <v>6.751231680395753</v>
       </c>
     </row>
     <row r="6093" spans="1:1">
       <c r="A6093">
-        <v>-1</v>
+        <v>9.26755560131658</v>
       </c>
     </row>
     <row r="6094" spans="1:1">
       <c r="A6094">
-        <v>-1</v>
+        <v>6.930377656953435</v>
       </c>
     </row>
     <row r="6095" spans="1:1">
@@ -30894,32 +30894,32 @@
     </row>
     <row r="6104" spans="1:1">
       <c r="A6104">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6105" spans="1:1">
       <c r="A6105">
-        <v>-1</v>
+        <v>3.584180524791436</v>
       </c>
     </row>
     <row r="6106" spans="1:1">
       <c r="A6106">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6107" spans="1:1">
       <c r="A6107">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6108" spans="1:1">
       <c r="A6108">
-        <v>-1</v>
+        <v>3.740357000952621</v>
       </c>
     </row>
     <row r="6109" spans="1:1">
       <c r="A6109">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6110" spans="1:1">
@@ -30954,17 +30954,17 @@
     </row>
     <row r="6116" spans="1:1">
       <c r="A6116">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6117" spans="1:1">
       <c r="A6117">
-        <v>-1</v>
+        <v>3.58964170260363</v>
       </c>
     </row>
     <row r="6118" spans="1:1">
       <c r="A6118">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6119" spans="1:1">
@@ -31404,17 +31404,17 @@
     </row>
     <row r="6206" spans="1:1">
       <c r="A6206">
-        <v>-1</v>
+        <v>3.300000000000103</v>
       </c>
     </row>
     <row r="6207" spans="1:1">
       <c r="A6207">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6208" spans="1:1">
       <c r="A6208">
-        <v>-1</v>
+        <v>3.300000000000103</v>
       </c>
     </row>
     <row r="6209" spans="1:1">
@@ -31434,32 +31434,32 @@
     </row>
     <row r="6212" spans="1:1">
       <c r="A6212">
-        <v>-1</v>
+        <v>3.425333919475748</v>
       </c>
     </row>
     <row r="6213" spans="1:1">
       <c r="A6213">
-        <v>-1</v>
+        <v>3.442949157401554</v>
       </c>
     </row>
     <row r="6214" spans="1:1">
       <c r="A6214">
-        <v>-1</v>
+        <v>3.468972402105419</v>
       </c>
     </row>
     <row r="6215" spans="1:1">
       <c r="A6215">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6216" spans="1:1">
       <c r="A6216">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6217" spans="1:1">
       <c r="A6217">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6218" spans="1:1">
@@ -31734,17 +31734,17 @@
     </row>
     <row r="6272" spans="1:1">
       <c r="A6272">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6273" spans="1:1">
       <c r="A6273">
-        <v>-1</v>
+        <v>9.044203876043621</v>
       </c>
     </row>
     <row r="6274" spans="1:1">
       <c r="A6274">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6275" spans="1:1">
@@ -31779,47 +31779,47 @@
     </row>
     <row r="6281" spans="1:1">
       <c r="A6281">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6282" spans="1:1">
       <c r="A6282">
-        <v>-1</v>
+        <v>11.68227059336342</v>
       </c>
     </row>
     <row r="6283" spans="1:1">
       <c r="A6283">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6284" spans="1:1">
       <c r="A6284">
-        <v>-1</v>
+        <v>3.382157546376829</v>
       </c>
     </row>
     <row r="6285" spans="1:1">
       <c r="A6285">
-        <v>-1</v>
+        <v>3.374447468692798</v>
       </c>
     </row>
     <row r="6286" spans="1:1">
       <c r="A6286">
-        <v>-1</v>
+        <v>3.429520890144899</v>
       </c>
     </row>
     <row r="6287" spans="1:1">
       <c r="A6287">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6288" spans="1:1">
       <c r="A6288">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6289" spans="1:1">
       <c r="A6289">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6290" spans="1:1">
@@ -31914,17 +31914,17 @@
     </row>
     <row r="6308" spans="1:1">
       <c r="A6308">
-        <v>-1</v>
+        <v>11.11036520272629</v>
       </c>
     </row>
     <row r="6309" spans="1:1">
       <c r="A6309">
-        <v>-1</v>
+        <v>22.117362701525</v>
       </c>
     </row>
     <row r="6310" spans="1:1">
       <c r="A6310">
-        <v>-1</v>
+        <v>11.57064568605439</v>
       </c>
     </row>
     <row r="6311" spans="1:1">
@@ -32109,17 +32109,17 @@
     </row>
     <row r="6347" spans="1:1">
       <c r="A6347">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6348" spans="1:1">
       <c r="A6348">
-        <v>-1</v>
+        <v>3.547763503675649</v>
       </c>
     </row>
     <row r="6349" spans="1:1">
       <c r="A6349">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6350" spans="1:1">
@@ -32139,17 +32139,17 @@
     </row>
     <row r="6353" spans="1:1">
       <c r="A6353">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6354" spans="1:1">
       <c r="A6354">
-        <v>-1</v>
+        <v>10.54461237375611</v>
       </c>
     </row>
     <row r="6355" spans="1:1">
       <c r="A6355">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6356" spans="1:1">
@@ -32169,17 +32169,17 @@
     </row>
     <row r="6359" spans="1:1">
       <c r="A6359">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="6360" spans="1:1">
       <c r="A6360">
-        <v>-1</v>
+        <v>3.329872282046908</v>
       </c>
     </row>
     <row r="6361" spans="1:1">
       <c r="A6361">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6362" spans="1:1">
@@ -32259,17 +32259,17 @@
     </row>
     <row r="6377" spans="1:1">
       <c r="A6377">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6378" spans="1:1">
       <c r="A6378">
-        <v>-1</v>
+        <v>3.758598749671072</v>
       </c>
     </row>
     <row r="6379" spans="1:1">
       <c r="A6379">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6380" spans="1:1">
@@ -32334,17 +32334,17 @@
     </row>
     <row r="6392" spans="1:1">
       <c r="A6392">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6393" spans="1:1">
       <c r="A6393">
-        <v>-1</v>
+        <v>3.532385741086896</v>
       </c>
     </row>
     <row r="6394" spans="1:1">
       <c r="A6394">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6395" spans="1:1">
@@ -32529,17 +32529,17 @@
     </row>
     <row r="6431" spans="1:1">
       <c r="A6431">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6432" spans="1:1">
       <c r="A6432">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6433" spans="1:1">
       <c r="A6433">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6434" spans="1:1">
@@ -33174,17 +33174,17 @@
     </row>
     <row r="6560" spans="1:1">
       <c r="A6560">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6561" spans="1:1">
       <c r="A6561">
-        <v>-1</v>
+        <v>39.08746566236809</v>
       </c>
     </row>
     <row r="6562" spans="1:1">
       <c r="A6562">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6563" spans="1:1">
@@ -33534,17 +33534,17 @@
     </row>
     <row r="6632" spans="1:1">
       <c r="A6632">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6633" spans="1:1">
       <c r="A6633">
-        <v>-1</v>
+        <v>11.50623479947172</v>
       </c>
     </row>
     <row r="6634" spans="1:1">
       <c r="A6634">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6635" spans="1:1">
@@ -34329,17 +34329,17 @@
     </row>
     <row r="6791" spans="1:1">
       <c r="A6791">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="6792" spans="1:1">
       <c r="A6792">
-        <v>-1</v>
+        <v>10.49257552617198</v>
       </c>
     </row>
     <row r="6793" spans="1:1">
       <c r="A6793">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6794" spans="1:1">
@@ -34614,17 +34614,17 @@
     </row>
     <row r="6848" spans="1:1">
       <c r="A6848">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6849" spans="1:1">
       <c r="A6849">
-        <v>-1</v>
+        <v>52.92187601530516</v>
       </c>
     </row>
     <row r="6850" spans="1:1">
       <c r="A6850">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6851" spans="1:1">
@@ -35019,17 +35019,17 @@
     </row>
     <row r="6929" spans="1:1">
       <c r="A6929">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6930" spans="1:1">
       <c r="A6930">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6931" spans="1:1">
       <c r="A6931">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6932" spans="1:1">
@@ -35169,17 +35169,17 @@
     </row>
     <row r="6959" spans="1:1">
       <c r="A6959">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6960" spans="1:1">
       <c r="A6960">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6961" spans="1:1">
       <c r="A6961">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6962" spans="1:1">
@@ -35214,17 +35214,17 @@
     </row>
     <row r="6968" spans="1:1">
       <c r="A6968">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6969" spans="1:1">
       <c r="A6969">
-        <v>-1</v>
+        <v>3.462155233226671</v>
       </c>
     </row>
     <row r="6970" spans="1:1">
       <c r="A6970">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6971" spans="1:1">
@@ -35379,17 +35379,17 @@
     </row>
     <row r="7001" spans="1:1">
       <c r="A7001">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7002" spans="1:1">
       <c r="A7002">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7003" spans="1:1">
       <c r="A7003">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="7004" spans="1:1">
@@ -35499,17 +35499,17 @@
     </row>
     <row r="7025" spans="1:1">
       <c r="A7025">
-        <v>-1</v>
+        <v>4.225104690749548</v>
       </c>
     </row>
     <row r="7026" spans="1:1">
       <c r="A7026">
-        <v>-1</v>
+        <v>5.5562097179499</v>
       </c>
     </row>
     <row r="7027" spans="1:1">
       <c r="A7027">
-        <v>-1</v>
+        <v>4.247968470580322</v>
       </c>
     </row>
     <row r="7028" spans="1:1">
@@ -35844,17 +35844,17 @@
     </row>
     <row r="7094" spans="1:1">
       <c r="A7094">
-        <v>-1</v>
+        <v>3.479293724388655</v>
       </c>
     </row>
     <row r="7095" spans="1:1">
       <c r="A7095">
-        <v>-1</v>
+        <v>5.249515602738364</v>
       </c>
     </row>
     <row r="7096" spans="1:1">
       <c r="A7096">
-        <v>-1</v>
+        <v>3.425609462173984</v>
       </c>
     </row>
     <row r="7097" spans="1:1">
@@ -35934,17 +35934,17 @@
     </row>
     <row r="7112" spans="1:1">
       <c r="A7112">
-        <v>-1</v>
+        <v>3.481488627140461</v>
       </c>
     </row>
     <row r="7113" spans="1:1">
       <c r="A7113">
-        <v>-1</v>
+        <v>5.255535177908954</v>
       </c>
     </row>
     <row r="7114" spans="1:1">
       <c r="A7114">
-        <v>-1</v>
+        <v>3.427384848232695</v>
       </c>
     </row>
     <row r="7115" spans="1:1">
@@ -36024,17 +36024,17 @@
     </row>
     <row r="7130" spans="1:1">
       <c r="A7130">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7131" spans="1:1">
       <c r="A7131">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7132" spans="1:1">
       <c r="A7132">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7133" spans="1:1">
@@ -36234,17 +36234,17 @@
     </row>
     <row r="7172" spans="1:1">
       <c r="A7172">
-        <v>-1</v>
+        <v>13.51593400623589</v>
       </c>
     </row>
     <row r="7173" spans="1:1">
       <c r="A7173">
-        <v>-1</v>
+        <v>24.84037676492837</v>
       </c>
     </row>
     <row r="7174" spans="1:1">
       <c r="A7174">
-        <v>-1</v>
+        <v>13.33229285730101</v>
       </c>
     </row>
     <row r="7175" spans="1:1">
@@ -36519,17 +36519,17 @@
     </row>
     <row r="7229" spans="1:1">
       <c r="A7229">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="7230" spans="1:1">
       <c r="A7230">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7231" spans="1:1">
       <c r="A7231">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="7232" spans="1:1">
@@ -36564,17 +36564,17 @@
     </row>
     <row r="7238" spans="1:1">
       <c r="A7238">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7239" spans="1:1">
       <c r="A7239">
-        <v>-1</v>
+        <v>3.400071563604856</v>
       </c>
     </row>
     <row r="7240" spans="1:1">
       <c r="A7240">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7241" spans="1:1">
@@ -37194,17 +37194,17 @@
     </row>
     <row r="7364" spans="1:1">
       <c r="A7364">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="7365" spans="1:1">
       <c r="A7365">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="7366" spans="1:1">
       <c r="A7366">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7367" spans="1:1">
@@ -37644,17 +37644,17 @@
     </row>
     <row r="7454" spans="1:1">
       <c r="A7454">
-        <v>-1</v>
+        <v>4.098877684446977</v>
       </c>
     </row>
     <row r="7455" spans="1:1">
       <c r="A7455">
-        <v>-1</v>
+        <v>6.951535357802574</v>
       </c>
     </row>
     <row r="7456" spans="1:1">
       <c r="A7456">
-        <v>-1</v>
+        <v>4.097883144707792</v>
       </c>
     </row>
     <row r="7457" spans="1:1">
@@ -37929,17 +37929,17 @@
     </row>
     <row r="7511" spans="1:1">
       <c r="A7511">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="7512" spans="1:1">
       <c r="A7512">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="7513" spans="1:1">
       <c r="A7513">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7514" spans="1:1">
@@ -38559,17 +38559,17 @@
     </row>
     <row r="7637" spans="1:1">
       <c r="A7637">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="7638" spans="1:1">
       <c r="A7638">
-        <v>-1</v>
+        <v>9.448746369607786</v>
       </c>
     </row>
     <row r="7639" spans="1:1">
       <c r="A7639">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="7640" spans="1:1">
@@ -38754,17 +38754,17 @@
     </row>
     <row r="7676" spans="1:1">
       <c r="A7676">
-        <v>-1</v>
+        <v>11.63915570597864</v>
       </c>
     </row>
     <row r="7677" spans="1:1">
       <c r="A7677">
-        <v>-1</v>
+        <v>51.5975622441082</v>
       </c>
     </row>
     <row r="7678" spans="1:1">
       <c r="A7678">
-        <v>-1</v>
+        <v>11.44848243878489</v>
       </c>
     </row>
     <row r="7679" spans="1:1">
@@ -40764,17 +40764,17 @@
     </row>
     <row r="8078" spans="1:1">
       <c r="A8078">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8079" spans="1:1">
       <c r="A8079">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8080" spans="1:1">
       <c r="A8080">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8081" spans="1:1">
@@ -40794,47 +40794,47 @@
     </row>
     <row r="8084" spans="1:1">
       <c r="A8084">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8085" spans="1:1">
       <c r="A8085">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8086" spans="1:1">
       <c r="A8086">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8087" spans="1:1">
       <c r="A8087">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8088" spans="1:1">
       <c r="A8088">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8089" spans="1:1">
       <c r="A8089">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8090" spans="1:1">
       <c r="A8090">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8091" spans="1:1">
       <c r="A8091">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8092" spans="1:1">
       <c r="A8092">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8093" spans="1:1">
@@ -40854,17 +40854,17 @@
     </row>
     <row r="8096" spans="1:1">
       <c r="A8096">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8097" spans="1:1">
       <c r="A8097">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8098" spans="1:1">
       <c r="A8098">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8099" spans="1:1">
@@ -40884,17 +40884,17 @@
     </row>
     <row r="8102" spans="1:1">
       <c r="A8102">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8103" spans="1:1">
       <c r="A8103">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8104" spans="1:1">
       <c r="A8104">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8105" spans="1:1">
@@ -41064,17 +41064,17 @@
     </row>
     <row r="8138" spans="1:1">
       <c r="A8138">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8139" spans="1:1">
       <c r="A8139">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8140" spans="1:1">
       <c r="A8140">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8141" spans="1:1">
@@ -41139,17 +41139,17 @@
     </row>
     <row r="8153" spans="1:1">
       <c r="A8153">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8154" spans="1:1">
       <c r="A8154">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8155" spans="1:1">
       <c r="A8155">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8156" spans="1:1">
@@ -41244,17 +41244,17 @@
     </row>
     <row r="8174" spans="1:1">
       <c r="A8174">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8175" spans="1:1">
       <c r="A8175">
-        <v>-1</v>
+        <v>3.526398806682163</v>
       </c>
     </row>
     <row r="8176" spans="1:1">
       <c r="A8176">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8177" spans="1:1">
@@ -41424,17 +41424,17 @@
     </row>
     <row r="8210" spans="1:1">
       <c r="A8210">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8211" spans="1:1">
       <c r="A8211">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8212" spans="1:1">
       <c r="A8212">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8213" spans="1:1">
@@ -41604,17 +41604,17 @@
     </row>
     <row r="8246" spans="1:1">
       <c r="A8246">
-        <v>-1</v>
+        <v>3.369733750683435</v>
       </c>
     </row>
     <row r="8247" spans="1:1">
       <c r="A8247">
-        <v>-1</v>
+        <v>5.07605874706063</v>
       </c>
     </row>
     <row r="8248" spans="1:1">
       <c r="A8248">
-        <v>-1</v>
+        <v>3.382490199911636</v>
       </c>
     </row>
     <row r="8249" spans="1:1">
@@ -41859,17 +41859,17 @@
     </row>
     <row r="8297" spans="1:1">
       <c r="A8297">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8298" spans="1:1">
       <c r="A8298">
-        <v>-1</v>
+        <v>18.02245060227803</v>
       </c>
     </row>
     <row r="8299" spans="1:1">
       <c r="A8299">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8300" spans="1:1">
@@ -41964,17 +41964,17 @@
     </row>
     <row r="8318" spans="1:1">
       <c r="A8318">
-        <v>-1</v>
+        <v>4.055177026614587</v>
       </c>
     </row>
     <row r="8319" spans="1:1">
       <c r="A8319">
-        <v>-1</v>
+        <v>6.721520422373395</v>
       </c>
     </row>
     <row r="8320" spans="1:1">
       <c r="A8320">
-        <v>-1</v>
+        <v>4.070439157498273</v>
       </c>
     </row>
     <row r="8321" spans="1:1">
@@ -42144,17 +42144,17 @@
     </row>
     <row r="8354" spans="1:1">
       <c r="A8354">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8355" spans="1:1">
       <c r="A8355">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8356" spans="1:1">
       <c r="A8356">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8357" spans="1:1">
@@ -42204,17 +42204,17 @@
     </row>
     <row r="8366" spans="1:1">
       <c r="A8366">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8367" spans="1:1">
       <c r="A8367">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8368" spans="1:1">
       <c r="A8368">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8369" spans="1:1">
@@ -42234,17 +42234,17 @@
     </row>
     <row r="8372" spans="1:1">
       <c r="A8372">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8373" spans="1:1">
       <c r="A8373">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8374" spans="1:1">
       <c r="A8374">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8375" spans="1:1">
@@ -42279,32 +42279,32 @@
     </row>
     <row r="8381" spans="1:1">
       <c r="A8381">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8382" spans="1:1">
       <c r="A8382">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8383" spans="1:1">
       <c r="A8383">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8384" spans="1:1">
       <c r="A8384">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8385" spans="1:1">
       <c r="A8385">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8386" spans="1:1">
       <c r="A8386">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8387" spans="1:1">
@@ -42324,17 +42324,17 @@
     </row>
     <row r="8390" spans="1:1">
       <c r="A8390">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8391" spans="1:1">
       <c r="A8391">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="8392" spans="1:1">
       <c r="A8392">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8393" spans="1:1">
@@ -42429,17 +42429,17 @@
     </row>
     <row r="8411" spans="1:1">
       <c r="A8411">
-        <v>-1</v>
+        <v>3.475551139313204</v>
       </c>
     </row>
     <row r="8412" spans="1:1">
       <c r="A8412">
-        <v>-1</v>
+        <v>4.453439243560942</v>
       </c>
     </row>
     <row r="8413" spans="1:1">
       <c r="A8413">
-        <v>-1</v>
+        <v>3.49397121167927</v>
       </c>
     </row>
     <row r="8414" spans="1:1">
@@ -42474,17 +42474,17 @@
     </row>
     <row r="8420" spans="1:1">
       <c r="A8420">
-        <v>-1</v>
+        <v>3.49397121167927</v>
       </c>
     </row>
     <row r="8421" spans="1:1">
       <c r="A8421">
-        <v>-1</v>
+        <v>4.335845910207647</v>
       </c>
     </row>
     <row r="8422" spans="1:1">
       <c r="A8422">
-        <v>-1</v>
+        <v>3.49397121167927</v>
       </c>
     </row>
     <row r="8423" spans="1:1">
@@ -42609,17 +42609,17 @@
     </row>
     <row r="8447" spans="1:1">
       <c r="A8447">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8448" spans="1:1">
       <c r="A8448">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8449" spans="1:1">
       <c r="A8449">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8450" spans="1:1">
@@ -42864,17 +42864,17 @@
     </row>
     <row r="8498" spans="1:1">
       <c r="A8498">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8499" spans="1:1">
       <c r="A8499">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="8500" spans="1:1">
       <c r="A8500">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8501" spans="1:1">
@@ -43044,17 +43044,17 @@
     </row>
     <row r="8534" spans="1:1">
       <c r="A8534">
-        <v>-1</v>
+        <v>3.460532835983543</v>
       </c>
     </row>
     <row r="8535" spans="1:1">
       <c r="A8535">
-        <v>-1</v>
+        <v>5.526335079335098</v>
       </c>
     </row>
     <row r="8536" spans="1:1">
       <c r="A8536">
-        <v>-1</v>
+        <v>3.75949895690384</v>
       </c>
     </row>
     <row r="8537" spans="1:1">
@@ -43224,17 +43224,17 @@
     </row>
     <row r="8570" spans="1:1">
       <c r="A8570">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="8571" spans="1:1">
       <c r="A8571">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8572" spans="1:1">
       <c r="A8572">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8573" spans="1:1">
@@ -43329,17 +43329,17 @@
     </row>
     <row r="8591" spans="1:1">
       <c r="A8591">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8592" spans="1:1">
       <c r="A8592">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="8593" spans="1:1">
       <c r="A8593">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="8594" spans="1:1">
@@ -43764,17 +43764,17 @@
     </row>
     <row r="8678" spans="1:1">
       <c r="A8678">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8679" spans="1:1">
       <c r="A8679">
-        <v>-1</v>
+        <v>3.318467372774114</v>
       </c>
     </row>
     <row r="8680" spans="1:1">
       <c r="A8680">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8681" spans="1:1">
@@ -44019,17 +44019,17 @@
     </row>
     <row r="8729" spans="1:1">
       <c r="A8729">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8730" spans="1:1">
       <c r="A8730">
-        <v>-1</v>
+        <v>15.79486512017394</v>
       </c>
     </row>
     <row r="8731" spans="1:1">
       <c r="A8731">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8732" spans="1:1">
@@ -44484,17 +44484,17 @@
     </row>
     <row r="8822" spans="1:1">
       <c r="A8822">
-        <v>-1</v>
+        <v>3.412759097813933</v>
       </c>
     </row>
     <row r="8823" spans="1:1">
       <c r="A8823">
-        <v>-1</v>
+        <v>9.824665989616488</v>
       </c>
     </row>
     <row r="8824" spans="1:1">
       <c r="A8824">
-        <v>-1</v>
+        <v>3.433147864791808</v>
       </c>
     </row>
     <row r="8825" spans="1:1">
@@ -44694,17 +44694,17 @@
     </row>
     <row r="8864" spans="1:1">
       <c r="A8864">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8865" spans="1:1">
       <c r="A8865">
-        <v>-1</v>
+        <v>50.209546413242</v>
       </c>
     </row>
     <row r="8866" spans="1:1">
       <c r="A8866">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8867" spans="1:1">
@@ -45129,17 +45129,17 @@
     </row>
     <row r="8951" spans="1:1">
       <c r="A8951">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="8952" spans="1:1">
       <c r="A8952">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8953" spans="1:1">
       <c r="A8953">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8954" spans="1:1">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -1449,17 +1449,17 @@
     </row>
     <row r="215" spans="1:1">
       <c r="A215">
-        <v>-1</v>
+        <v>9.42826846833511</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216">
-        <v>-1</v>
+        <v>17.65773279540517</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217">
-        <v>-1</v>
+        <v>8.601287839238768</v>
       </c>
     </row>
     <row r="218" spans="1:1">
@@ -3024,17 +3024,17 @@
     </row>
     <row r="530" spans="1:1">
       <c r="A530">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="531" spans="1:1">
       <c r="A531">
-        <v>-1</v>
+        <v>4.719240281033166</v>
       </c>
     </row>
     <row r="532" spans="1:1">
       <c r="A532">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="533" spans="1:1">
@@ -3879,17 +3879,17 @@
     </row>
     <row r="701" spans="1:1">
       <c r="A701">
-        <v>-1</v>
+        <v>8.503621381034389</v>
       </c>
     </row>
     <row r="702" spans="1:1">
       <c r="A702">
-        <v>-1</v>
+        <v>18.00037489642714</v>
       </c>
     </row>
     <row r="703" spans="1:1">
       <c r="A703">
-        <v>-1</v>
+        <v>7.438232882457029</v>
       </c>
     </row>
     <row r="704" spans="1:1">
@@ -5199,17 +5199,17 @@
     </row>
     <row r="965" spans="1:1">
       <c r="A965">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="966" spans="1:1">
       <c r="A966">
-        <v>-1</v>
+        <v>4.500447414019082</v>
       </c>
     </row>
     <row r="967" spans="1:1">
       <c r="A967">
-        <v>-1</v>
+        <v>3.512059798206946</v>
       </c>
     </row>
     <row r="968" spans="1:1">
@@ -5964,17 +5964,17 @@
     </row>
     <row r="1118" spans="1:1">
       <c r="A1118">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="1119" spans="1:1">
       <c r="A1119">
-        <v>-1</v>
+        <v>9.002605971995814</v>
       </c>
     </row>
     <row r="1120" spans="1:1">
       <c r="A1120">
-        <v>-1</v>
+        <v>3.333178555487915</v>
       </c>
     </row>
     <row r="1121" spans="1:1">
@@ -6054,17 +6054,17 @@
     </row>
     <row r="1136" spans="1:1">
       <c r="A1136">
-        <v>-1</v>
+        <v>3.299999999999925</v>
       </c>
     </row>
     <row r="1137" spans="1:1">
       <c r="A1137">
-        <v>-1</v>
+        <v>9.033245214732254</v>
       </c>
     </row>
     <row r="1138" spans="1:1">
       <c r="A1138">
-        <v>-1</v>
+        <v>3.332662779816475</v>
       </c>
     </row>
     <row r="1139" spans="1:1">
@@ -8439,17 +8439,17 @@
     </row>
     <row r="1613" spans="1:1">
       <c r="A1613">
-        <v>-1</v>
+        <v>3.468972402105419</v>
       </c>
     </row>
     <row r="1614" spans="1:1">
       <c r="A1614">
-        <v>-1</v>
+        <v>3.732532894347074</v>
       </c>
     </row>
     <row r="1615" spans="1:1">
       <c r="A1615">
-        <v>-1</v>
+        <v>3.592052332525131</v>
       </c>
     </row>
     <row r="1616" spans="1:1">
@@ -13509,17 +13509,17 @@
     </row>
     <row r="2627" spans="1:1">
       <c r="A2627">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2628" spans="1:1">
       <c r="A2628">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2629" spans="1:1">
       <c r="A2629">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="2630" spans="1:1">
@@ -15924,17 +15924,17 @@
     </row>
     <row r="3110" spans="1:1">
       <c r="A3110">
-        <v>-1</v>
+        <v>3.300000000000058</v>
       </c>
     </row>
     <row r="3111" spans="1:1">
       <c r="A3111">
-        <v>-1</v>
+        <v>144.8564102892055</v>
       </c>
     </row>
     <row r="3112" spans="1:1">
       <c r="A3112">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3113" spans="1:1">
@@ -16059,17 +16059,17 @@
     </row>
     <row r="3137" spans="1:1">
       <c r="A3137">
-        <v>-1</v>
+        <v>6.243220473859901</v>
       </c>
     </row>
     <row r="3138" spans="1:1">
       <c r="A3138">
-        <v>-1</v>
+        <v>18.828479133971</v>
       </c>
     </row>
     <row r="3139" spans="1:1">
       <c r="A3139">
-        <v>-1</v>
+        <v>4.708390494635617</v>
       </c>
     </row>
     <row r="3140" spans="1:1">
@@ -16389,17 +16389,17 @@
     </row>
     <row r="3203" spans="1:1">
       <c r="A3203">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3204" spans="1:1">
       <c r="A3204">
-        <v>-1</v>
+        <v>14.68818384318302</v>
       </c>
     </row>
     <row r="3205" spans="1:1">
       <c r="A3205">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="3206" spans="1:1">
@@ -18594,17 +18594,17 @@
     </row>
     <row r="3644" spans="1:1">
       <c r="A3644">
-        <v>-1</v>
+        <v>11.2953972128104</v>
       </c>
     </row>
     <row r="3645" spans="1:1">
       <c r="A3645">
-        <v>-1</v>
+        <v>16.45142563038871</v>
       </c>
     </row>
     <row r="3646" spans="1:1">
       <c r="A3646">
-        <v>-1</v>
+        <v>9.789798241364267</v>
       </c>
     </row>
     <row r="3647" spans="1:1">
@@ -21669,17 +21669,17 @@
     </row>
     <row r="4259" spans="1:1">
       <c r="A4259">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4260" spans="1:1">
       <c r="A4260">
-        <v>-1</v>
+        <v>105.6169723701042</v>
       </c>
     </row>
     <row r="4261" spans="1:1">
       <c r="A4261">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="4262" spans="1:1">
@@ -23769,17 +23769,17 @@
     </row>
     <row r="4679" spans="1:1">
       <c r="A4679">
-        <v>-1</v>
+        <v>7.744707573121512</v>
       </c>
     </row>
     <row r="4680" spans="1:1">
       <c r="A4680">
-        <v>-1</v>
+        <v>9.566361408840763</v>
       </c>
     </row>
     <row r="4681" spans="1:1">
       <c r="A4681">
-        <v>-1</v>
+        <v>7.744707573121512</v>
       </c>
     </row>
     <row r="4682" spans="1:1">
@@ -24639,17 +24639,17 @@
     </row>
     <row r="4853" spans="1:1">
       <c r="A4853">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4854" spans="1:1">
       <c r="A4854">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="4855" spans="1:1">
       <c r="A4855">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="4856" spans="1:1">
@@ -26874,17 +26874,17 @@
     </row>
     <row r="5300" spans="1:1">
       <c r="A5300">
-        <v>-1</v>
+        <v>8.472834609203161</v>
       </c>
     </row>
     <row r="5301" spans="1:1">
       <c r="A5301">
-        <v>-1</v>
+        <v>12.29742479111543</v>
       </c>
     </row>
     <row r="5302" spans="1:1">
       <c r="A5302">
-        <v>-1</v>
+        <v>8.503621381034389</v>
       </c>
     </row>
     <row r="5303" spans="1:1">
@@ -26919,17 +26919,17 @@
     </row>
     <row r="5309" spans="1:1">
       <c r="A5309">
-        <v>-1</v>
+        <v>8.503621381034389</v>
       </c>
     </row>
     <row r="5310" spans="1:1">
       <c r="A5310">
-        <v>-1</v>
+        <v>20.19973214397132</v>
       </c>
     </row>
     <row r="5311" spans="1:1">
       <c r="A5311">
-        <v>-1</v>
+        <v>8.503621381034389</v>
       </c>
     </row>
     <row r="5312" spans="1:1">
@@ -27189,17 +27189,17 @@
     </row>
     <row r="5363" spans="1:1">
       <c r="A5363">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5364" spans="1:1">
       <c r="A5364">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5365" spans="1:1">
       <c r="A5365">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5366" spans="1:1">
@@ -27429,17 +27429,17 @@
     </row>
     <row r="5411" spans="1:1">
       <c r="A5411">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5412" spans="1:1">
       <c r="A5412">
-        <v>-1</v>
+        <v>96.79940770359576</v>
       </c>
     </row>
     <row r="5413" spans="1:1">
       <c r="A5413">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="5414" spans="1:1">
@@ -27594,17 +27594,17 @@
     </row>
     <row r="5444" spans="1:1">
       <c r="A5444">
-        <v>-1</v>
+        <v>11.17864700117413</v>
       </c>
     </row>
     <row r="5445" spans="1:1">
       <c r="A5445">
-        <v>-1</v>
+        <v>50.33088260012987</v>
       </c>
     </row>
     <row r="5446" spans="1:1">
       <c r="A5446">
-        <v>-1</v>
+        <v>10.95021356860577</v>
       </c>
     </row>
     <row r="5447" spans="1:1">
@@ -27819,17 +27819,17 @@
     </row>
     <row r="5489" spans="1:1">
       <c r="A5489">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5490" spans="1:1">
       <c r="A5490">
-        <v>-1</v>
+        <v>10.47376751117983</v>
       </c>
     </row>
     <row r="5491" spans="1:1">
       <c r="A5491">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="5492" spans="1:1">
@@ -28239,17 +28239,17 @@
     </row>
     <row r="5573" spans="1:1">
       <c r="A5573">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5574" spans="1:1">
       <c r="A5574">
-        <v>-1</v>
+        <v>4.326642054485386</v>
       </c>
     </row>
     <row r="5575" spans="1:1">
       <c r="A5575">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5576" spans="1:1">
@@ -28779,17 +28779,17 @@
     </row>
     <row r="5681" spans="1:1">
       <c r="A5681">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5682" spans="1:1">
       <c r="A5682">
-        <v>-1</v>
+        <v>97.0687974489244</v>
       </c>
     </row>
     <row r="5683" spans="1:1">
       <c r="A5683">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="5684" spans="1:1">
@@ -29049,17 +29049,17 @@
     </row>
     <row r="5735" spans="1:1">
       <c r="A5735">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5736" spans="1:1">
       <c r="A5736">
-        <v>-1</v>
+        <v>114.3702963112977</v>
       </c>
     </row>
     <row r="5737" spans="1:1">
       <c r="A5737">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5738" spans="1:1">
@@ -29139,17 +29139,17 @@
     </row>
     <row r="5753" spans="1:1">
       <c r="A5753">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5754" spans="1:1">
       <c r="A5754">
-        <v>-1</v>
+        <v>114.4017191724764</v>
       </c>
     </row>
     <row r="5755" spans="1:1">
       <c r="A5755">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5756" spans="1:1">
@@ -30069,17 +30069,17 @@
     </row>
     <row r="5939" spans="1:1">
       <c r="A5939">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5940" spans="1:1">
       <c r="A5940">
-        <v>-1</v>
+        <v>7.230126635522193</v>
       </c>
     </row>
     <row r="5941" spans="1:1">
       <c r="A5941">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="5942" spans="1:1">
@@ -30384,17 +30384,17 @@
     </row>
     <row r="6002" spans="1:1">
       <c r="A6002">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6003" spans="1:1">
       <c r="A6003">
-        <v>-1</v>
+        <v>6.598961985655427</v>
       </c>
     </row>
     <row r="6004" spans="1:1">
       <c r="A6004">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="6005" spans="1:1">
@@ -32709,17 +32709,17 @@
     </row>
     <row r="6467" spans="1:1">
       <c r="A6467">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6468" spans="1:1">
       <c r="A6468">
-        <v>-1</v>
+        <v>4.828372303878236</v>
       </c>
     </row>
     <row r="6469" spans="1:1">
       <c r="A6469">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="6470" spans="1:1">
@@ -33174,17 +33174,17 @@
     </row>
     <row r="6560" spans="1:1">
       <c r="A6560">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="6561" spans="1:1">
       <c r="A6561">
-        <v>-1</v>
+        <v>39.08746566236809</v>
       </c>
     </row>
     <row r="6562" spans="1:1">
       <c r="A6562">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="6563" spans="1:1">
@@ -35289,17 +35289,17 @@
     </row>
     <row r="6983" spans="1:1">
       <c r="A6983">
-        <v>-1</v>
+        <v>9.56895084627385</v>
       </c>
     </row>
     <row r="6984" spans="1:1">
       <c r="A6984">
-        <v>-1</v>
+        <v>11.45962781318041</v>
       </c>
     </row>
     <row r="6985" spans="1:1">
       <c r="A6985">
-        <v>-1</v>
+        <v>9.56895084627385</v>
       </c>
     </row>
     <row r="6986" spans="1:1">
@@ -41889,17 +41889,17 @@
     </row>
     <row r="8303" spans="1:1">
       <c r="A8303">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8304" spans="1:1">
       <c r="A8304">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="8305" spans="1:1">
       <c r="A8305">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="8306" spans="1:1">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -4149,17 +4149,17 @@
     </row>
     <row r="755" spans="1:1">
       <c r="A755">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="756" spans="1:1">
       <c r="A756">
-        <v>-1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="757" spans="1:1">
       <c r="A757">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="758" spans="1:1">
@@ -5574,17 +5574,17 @@
     </row>
     <row r="1040" spans="1:1">
       <c r="A1040">
-        <v>-1</v>
+        <v>3.29999999999997</v>
       </c>
     </row>
     <row r="1041" spans="1:1">
       <c r="A1041">
-        <v>-1</v>
+        <v>108.2146556142594</v>
       </c>
     </row>
     <row r="1042" spans="1:1">
       <c r="A1042">
-        <v>-1</v>
+        <v>3.300000000000014</v>
       </c>
     </row>
     <row r="1043" spans="1:1">
@@ -12969,17 +12969,17 @@
     </row>
     <row r="2519" spans="1:1">
       <c r="A2519">
-        <v>-1</v>
+        <v>11.31578359662323</v>
       </c>
     </row>
     <row r="2520" spans="1:1">
       <c r="A2520">
-        <v>-1</v>
+        <v>21.07024755125138</v>
       </c>
     </row>
     <row r="2521" spans="1:1">
       <c r="A2521">
-        <v>-1</v>
+        <v>9.974343340863335</v>
       </c>
     </row>
     <row r="2522" spans="1:1">
@@ -13659,17 +13659,17 @@
     </row>
     <row r="2657" spans="1:1">
       <c r="A2657">
-        <v>-1</v>
+        <v>3.300000000000036</v>
       </c>
     </row>
     <row r="2658" spans="1:1">
       <c r="A2658">
-        <v>-1</v>
+        <v>3.581237726538222</v>
       </c>
     </row>
     <row r="2659" spans="1:1">
       <c r="A2659">
-        <v>-1</v>
+        <v>3.312884474377498</v>
       </c>
     </row>
     <row r="2660" spans="1:1">
@@ -16719,17 +16719,17 @@
     </row>
     <row r="3269" spans="1:1">
       <c r="A3269">
-        <v>-1</v>
+        <v>3.299999999999947</v>
       </c>
     </row>
     <row r="3270" spans="1:1">
       <c r="A3270">
-        <v>-1</v>
+        <v>4.665592215320935</v>
       </c>
     </row>
     <row r="3271" spans="1:1">
       <c r="A3271">
-        <v>-1</v>
+        <v>3.299999999999992</v>
       </c>
     </row>
     <row r="3272" spans="1:1">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -714,17 +714,17 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -879,32 +879,32 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -1029,17 +1029,17 @@
     </row>
     <row r="131" spans="1:1">
       <c r="A131">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -1059,32 +1059,32 @@
     </row>
     <row r="137" spans="1:1">
       <c r="A137">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -1239,32 +1239,32 @@
     </row>
     <row r="173" spans="1:1">
       <c r="A173">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -1344,32 +1344,32 @@
     </row>
     <row r="194" spans="1:1">
       <c r="A194">
-        <v>1.407745272749661</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197">
-        <v>2.416593574757908</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="200" spans="1:1">
@@ -1389,32 +1389,32 @@
     </row>
     <row r="203" spans="1:1">
       <c r="A203">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207">
-        <v>0.2900204105828141</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="209" spans="1:1">
@@ -1449,17 +1449,17 @@
     </row>
     <row r="215" spans="1:1">
       <c r="A215">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216">
-        <v>0.2946780028999285</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="218" spans="1:1">
@@ -1509,17 +1509,17 @@
     </row>
     <row r="227" spans="1:1">
       <c r="A227">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:1">
@@ -1629,17 +1629,17 @@
     </row>
     <row r="251" spans="1:1">
       <c r="A251">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252">
-        <v>0.2929263340022636</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="254" spans="1:1">
@@ -1689,62 +1689,62 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269">
-        <v>2.416593574757842</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -1764,17 +1764,17 @@
     </row>
     <row r="278" spans="1:1">
       <c r="A278">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279">
-        <v>0.2900255783147121</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="281" spans="1:1">
@@ -1809,17 +1809,17 @@
     </row>
     <row r="287" spans="1:1">
       <c r="A287">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288">
-        <v>0.2946847365034699</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="290" spans="1:1">
@@ -1959,17 +1959,17 @@
     </row>
     <row r="317" spans="1:1">
       <c r="A317">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:1">
@@ -2064,32 +2064,32 @@
     </row>
     <row r="338" spans="1:1">
       <c r="A338">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="340" spans="1:1">
       <c r="A340">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="342" spans="1:1">
       <c r="A342">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="343" spans="1:1">
       <c r="A343">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="344" spans="1:1">
@@ -2109,17 +2109,17 @@
     </row>
     <row r="347" spans="1:1">
       <c r="A347">
-        <v>1.40774527274965</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="350" spans="1:1">
@@ -2139,17 +2139,17 @@
     </row>
     <row r="353" spans="1:1">
       <c r="A353">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="354" spans="1:1">
       <c r="A354">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:1">
@@ -2259,47 +2259,47 @@
     </row>
     <row r="377" spans="1:1">
       <c r="A377">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="381" spans="1:1">
       <c r="A381">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="384" spans="1:1">
       <c r="A384">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="386" spans="1:1">
@@ -2364,32 +2364,32 @@
     </row>
     <row r="398" spans="1:1">
       <c r="A398">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="404" spans="1:1">
@@ -2454,32 +2454,32 @@
     </row>
     <row r="416" spans="1:1">
       <c r="A416">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:1">
       <c r="A419">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="422" spans="1:1">
@@ -2559,17 +2559,17 @@
     </row>
     <row r="437" spans="1:1">
       <c r="A437">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="440" spans="1:1">
@@ -2649,17 +2649,17 @@
     </row>
     <row r="455" spans="1:1">
       <c r="A455">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="456" spans="1:1">
       <c r="A456">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="457" spans="1:1">
       <c r="A457">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="458" spans="1:1">
@@ -2739,47 +2739,47 @@
     </row>
     <row r="473" spans="1:1">
       <c r="A473">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="474" spans="1:1">
       <c r="A474">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="475" spans="1:1">
       <c r="A475">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="476" spans="1:1">
       <c r="A476">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="477" spans="1:1">
       <c r="A477">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="478" spans="1:1">
       <c r="A478">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="479" spans="1:1">
       <c r="A479">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="480" spans="1:1">
       <c r="A480">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="481" spans="1:1">
       <c r="A481">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="482" spans="1:1">
@@ -2799,32 +2799,32 @@
     </row>
     <row r="485" spans="1:1">
       <c r="A485">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="486" spans="1:1">
       <c r="A486">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="487" spans="1:1">
       <c r="A487">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="488" spans="1:1">
       <c r="A488">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="489" spans="1:1">
       <c r="A489">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="490" spans="1:1">
       <c r="A490">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="491" spans="1:1">
@@ -2904,47 +2904,47 @@
     </row>
     <row r="506" spans="1:1">
       <c r="A506">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="507" spans="1:1">
       <c r="A507">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508" spans="1:1">
       <c r="A508">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="509" spans="1:1">
       <c r="A509">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="510" spans="1:1">
       <c r="A510">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="511" spans="1:1">
       <c r="A511">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="512" spans="1:1">
       <c r="A512">
-        <v>-1</v>
+        <v>2.41659357475783</v>
       </c>
     </row>
     <row r="513" spans="1:1">
       <c r="A513">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514" spans="1:1">
       <c r="A514">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515" spans="1:1">
@@ -2979,17 +2979,17 @@
     </row>
     <row r="521" spans="1:1">
       <c r="A521">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="522" spans="1:1">
       <c r="A522">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:1">
       <c r="A523">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524" spans="1:1">
@@ -3009,17 +3009,17 @@
     </row>
     <row r="527" spans="1:1">
       <c r="A527">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="528" spans="1:1">
       <c r="A528">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="529" spans="1:1">
       <c r="A529">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="530" spans="1:1">
@@ -3339,17 +3339,17 @@
     </row>
     <row r="593" spans="1:1">
       <c r="A593">
-        <v>-1</v>
+        <v>2.422712137617489</v>
       </c>
     </row>
     <row r="594" spans="1:1">
       <c r="A594">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="595" spans="1:1">
       <c r="A595">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596" spans="1:1">
@@ -3414,17 +3414,17 @@
     </row>
     <row r="608" spans="1:1">
       <c r="A608">
-        <v>1.407745272749783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="609" spans="1:1">
       <c r="A609">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="610" spans="1:1">
       <c r="A610">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="611" spans="1:1">
@@ -3564,17 +3564,17 @@
     </row>
     <row r="638" spans="1:1">
       <c r="A638">
-        <v>2.422843312391854</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="639" spans="1:1">
       <c r="A639">
-        <v>0.2898689119171904</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="640" spans="1:1">
       <c r="A640">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="641" spans="1:1">
@@ -3594,17 +3594,17 @@
     </row>
     <row r="644" spans="1:1">
       <c r="A644">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="645" spans="1:1">
       <c r="A645">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="646" spans="1:1">
       <c r="A646">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="647" spans="1:1">
@@ -3654,17 +3654,17 @@
     </row>
     <row r="656" spans="1:1">
       <c r="A656">
-        <v>2.42278354617208</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="657" spans="1:1">
       <c r="A657">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="658" spans="1:1">
       <c r="A658">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="659" spans="1:1">
@@ -3699,32 +3699,32 @@
     </row>
     <row r="665" spans="1:1">
       <c r="A665">
-        <v>2.422762793580302</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="666" spans="1:1">
       <c r="A666">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="667" spans="1:1">
       <c r="A667">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="668" spans="1:1">
       <c r="A668">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="669" spans="1:1">
       <c r="A669">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="670" spans="1:1">
       <c r="A670">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="671" spans="1:1">
@@ -3759,62 +3759,62 @@
     </row>
     <row r="677" spans="1:1">
       <c r="A677">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="678" spans="1:1">
       <c r="A678">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679" spans="1:1">
       <c r="A679">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="680" spans="1:1">
       <c r="A680">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="681" spans="1:1">
       <c r="A681">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="682" spans="1:1">
       <c r="A682">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="683" spans="1:1">
       <c r="A683">
-        <v>-1</v>
+        <v>2.422602308867472</v>
       </c>
     </row>
     <row r="684" spans="1:1">
       <c r="A684">
-        <v>-1</v>
+        <v>0.2923023058005292</v>
       </c>
     </row>
     <row r="685" spans="1:1">
       <c r="A685">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686" spans="1:1">
       <c r="A686">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="687" spans="1:1">
       <c r="A687">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="688" spans="1:1">
       <c r="A688">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="689" spans="1:1">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="734" spans="1:1">
       <c r="A734">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="735" spans="1:1">
       <c r="A735">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="736" spans="1:1">
       <c r="A736">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="737" spans="1:1">
       <c r="A737">
-        <v>2.41659357475783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="738" spans="1:1">
       <c r="A738">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="739" spans="1:1">
       <c r="A739">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="740" spans="1:1">
@@ -4089,17 +4089,17 @@
     </row>
     <row r="743" spans="1:1">
       <c r="A743">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="744" spans="1:1">
       <c r="A744">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="745" spans="1:1">
       <c r="A745">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="746" spans="1:1">
@@ -4134,17 +4134,17 @@
     </row>
     <row r="752" spans="1:1">
       <c r="A752">
-        <v>1.407745272749616</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="753" spans="1:1">
       <c r="A753">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="754" spans="1:1">
       <c r="A754">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="755" spans="1:1">
@@ -4179,32 +4179,32 @@
     </row>
     <row r="761" spans="1:1">
       <c r="A761">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="762" spans="1:1">
       <c r="A762">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="763" spans="1:1">
       <c r="A763">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="764" spans="1:1">
       <c r="A764">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="765" spans="1:1">
       <c r="A765">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="766" spans="1:1">
       <c r="A766">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="767" spans="1:1">
@@ -4239,17 +4239,17 @@
     </row>
     <row r="773" spans="1:1">
       <c r="A773">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="774" spans="1:1">
       <c r="A774">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="775" spans="1:1">
       <c r="A775">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="776" spans="1:1">
@@ -4269,32 +4269,32 @@
     </row>
     <row r="779" spans="1:1">
       <c r="A779">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="780" spans="1:1">
       <c r="A780">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="781" spans="1:1">
       <c r="A781">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="782" spans="1:1">
       <c r="A782">
-        <v>2.416593574757897</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="783" spans="1:1">
       <c r="A783">
-        <v>0.2899762701205733</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="784" spans="1:1">
       <c r="A784">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="785" spans="1:1">
@@ -4389,17 +4389,17 @@
     </row>
     <row r="803" spans="1:1">
       <c r="A803">
-        <v>1.127766143616094</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="804" spans="1:1">
       <c r="A804">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="805" spans="1:1">
       <c r="A805">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="806" spans="1:1">
@@ -4419,17 +4419,17 @@
     </row>
     <row r="809" spans="1:1">
       <c r="A809">
-        <v>2.416593574757897</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="810" spans="1:1">
       <c r="A810">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="811" spans="1:1">
       <c r="A811">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="812" spans="1:1">
@@ -4449,17 +4449,17 @@
     </row>
     <row r="815" spans="1:1">
       <c r="A815">
-        <v>1.407745272749772</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="816" spans="1:1">
       <c r="A816">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="817" spans="1:1">
       <c r="A817">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="818" spans="1:1">
@@ -4554,17 +4554,17 @@
     </row>
     <row r="836" spans="1:1">
       <c r="A836">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="837" spans="1:1">
       <c r="A837">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="838" spans="1:1">
       <c r="A838">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="839" spans="1:1">
@@ -4629,17 +4629,17 @@
     </row>
     <row r="851" spans="1:1">
       <c r="A851">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="852" spans="1:1">
       <c r="A852">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="853" spans="1:1">
       <c r="A853">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="854" spans="1:1">
@@ -4749,17 +4749,17 @@
     </row>
     <row r="875" spans="1:1">
       <c r="A875">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="876" spans="1:1">
       <c r="A876">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="877" spans="1:1">
       <c r="A877">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="878" spans="1:1">
@@ -4779,17 +4779,17 @@
     </row>
     <row r="881" spans="1:1">
       <c r="A881">
-        <v>-1</v>
+        <v>2.422960343100944</v>
       </c>
     </row>
     <row r="882" spans="1:1">
       <c r="A882">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883" spans="1:1">
       <c r="A883">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="884" spans="1:1">
@@ -4809,17 +4809,17 @@
     </row>
     <row r="887" spans="1:1">
       <c r="A887">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="888" spans="1:1">
       <c r="A888">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="889" spans="1:1">
       <c r="A889">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="890" spans="1:1">
@@ -4884,32 +4884,32 @@
     </row>
     <row r="902" spans="1:1">
       <c r="A902">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="903" spans="1:1">
       <c r="A903">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="904" spans="1:1">
       <c r="A904">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="905" spans="1:1">
       <c r="A905">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="906" spans="1:1">
       <c r="A906">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="907" spans="1:1">
       <c r="A907">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="908" spans="1:1">
@@ -4929,32 +4929,32 @@
     </row>
     <row r="911" spans="1:1">
       <c r="A911">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="912" spans="1:1">
       <c r="A912">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="913" spans="1:1">
       <c r="A913">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="914" spans="1:1">
       <c r="A914">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="915" spans="1:1">
       <c r="A915">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="916" spans="1:1">
       <c r="A916">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="917" spans="1:1">
@@ -4974,17 +4974,17 @@
     </row>
     <row r="920" spans="1:1">
       <c r="A920">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="921" spans="1:1">
       <c r="A921">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="922" spans="1:1">
       <c r="A922">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="923" spans="1:1">
@@ -5079,17 +5079,17 @@
     </row>
     <row r="941" spans="1:1">
       <c r="A941">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="942" spans="1:1">
       <c r="A942">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="943" spans="1:1">
       <c r="A943">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="944" spans="1:1">
@@ -5109,17 +5109,17 @@
     </row>
     <row r="947" spans="1:1">
       <c r="A947">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="948" spans="1:1">
       <c r="A948">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="949" spans="1:1">
       <c r="A949">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="950" spans="1:1">
@@ -5289,17 +5289,17 @@
     </row>
     <row r="983" spans="1:1">
       <c r="A983">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="984" spans="1:1">
       <c r="A984">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="985" spans="1:1">
       <c r="A985">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="986" spans="1:1">
@@ -5439,17 +5439,17 @@
     </row>
     <row r="1013" spans="1:1">
       <c r="A1013">
-        <v>1.407745272749783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1014" spans="1:1">
       <c r="A1014">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1015" spans="1:1">
       <c r="A1015">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1016" spans="1:1">
@@ -5469,17 +5469,17 @@
     </row>
     <row r="1019" spans="1:1">
       <c r="A1019">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1020" spans="1:1">
       <c r="A1020">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1021" spans="1:1">
       <c r="A1021">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1022" spans="1:1">
@@ -5529,17 +5529,17 @@
     </row>
     <row r="1031" spans="1:1">
       <c r="A1031">
-        <v>1.407745272749661</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1032" spans="1:1">
       <c r="A1032">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1033" spans="1:1">
       <c r="A1033">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1034" spans="1:1">
@@ -5814,17 +5814,17 @@
     </row>
     <row r="1088" spans="1:1">
       <c r="A1088">
-        <v>-1</v>
+        <v>2.416593574757864</v>
       </c>
     </row>
     <row r="1089" spans="1:1">
       <c r="A1089">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1090" spans="1:1">
       <c r="A1090">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1091" spans="1:1">
@@ -6294,17 +6294,17 @@
     </row>
     <row r="1184" spans="1:1">
       <c r="A1184">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1185" spans="1:1">
       <c r="A1185">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1186" spans="1:1">
       <c r="A1186">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1187" spans="1:1">
@@ -6414,17 +6414,17 @@
     </row>
     <row r="1208" spans="1:1">
       <c r="A1208">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="1209" spans="1:1">
       <c r="A1209">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1210" spans="1:1">
       <c r="A1210">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1211" spans="1:1">
@@ -6474,17 +6474,17 @@
     </row>
     <row r="1220" spans="1:1">
       <c r="A1220">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1221" spans="1:1">
       <c r="A1221">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1222" spans="1:1">
       <c r="A1222">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1223" spans="1:1">
@@ -6579,32 +6579,32 @@
     </row>
     <row r="1241" spans="1:1">
       <c r="A1241">
-        <v>2.416593574757786</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1242" spans="1:1">
       <c r="A1242">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1243" spans="1:1">
       <c r="A1243">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1244" spans="1:1">
       <c r="A1244">
-        <v>1.127766143615971</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1245" spans="1:1">
       <c r="A1245">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1246" spans="1:1">
       <c r="A1246">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1247" spans="1:1">
@@ -6624,17 +6624,17 @@
     </row>
     <row r="1250" spans="1:1">
       <c r="A1250">
-        <v>-1</v>
+        <v>2.416593574757897</v>
       </c>
     </row>
     <row r="1251" spans="1:1">
       <c r="A1251">
-        <v>-1</v>
+        <v>0.2874188499407571</v>
       </c>
     </row>
     <row r="1252" spans="1:1">
       <c r="A1252">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1253" spans="1:1">
@@ -6654,17 +6654,17 @@
     </row>
     <row r="1256" spans="1:1">
       <c r="A1256">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1257" spans="1:1">
       <c r="A1257">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1258" spans="1:1">
       <c r="A1258">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1259" spans="1:1">
@@ -6729,32 +6729,32 @@
     </row>
     <row r="1271" spans="1:1">
       <c r="A1271">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1272" spans="1:1">
       <c r="A1272">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1273" spans="1:1">
       <c r="A1273">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1274" spans="1:1">
       <c r="A1274">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="1275" spans="1:1">
       <c r="A1275">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1276" spans="1:1">
       <c r="A1276">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1277" spans="1:1">
@@ -6774,17 +6774,17 @@
     </row>
     <row r="1280" spans="1:1">
       <c r="A1280">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="1281" spans="1:1">
       <c r="A1281">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1282" spans="1:1">
       <c r="A1282">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1283" spans="1:1">
@@ -6939,17 +6939,17 @@
     </row>
     <row r="1313" spans="1:1">
       <c r="A1313">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1314" spans="1:1">
       <c r="A1314">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1315" spans="1:1">
       <c r="A1315">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1316" spans="1:1">
@@ -6984,47 +6984,47 @@
     </row>
     <row r="1322" spans="1:1">
       <c r="A1322">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1323" spans="1:1">
       <c r="A1323">
-        <v>0.288115749517126</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1324" spans="1:1">
       <c r="A1324">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1325" spans="1:1">
       <c r="A1325">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1326" spans="1:1">
       <c r="A1326">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1327" spans="1:1">
       <c r="A1327">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1328" spans="1:1">
       <c r="A1328">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1329" spans="1:1">
       <c r="A1329">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1330" spans="1:1">
       <c r="A1330">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1331" spans="1:1">
@@ -7074,17 +7074,17 @@
     </row>
     <row r="1340" spans="1:1">
       <c r="A1340">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1341" spans="1:1">
       <c r="A1341">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1342" spans="1:1">
       <c r="A1342">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1343" spans="1:1">
@@ -7104,17 +7104,17 @@
     </row>
     <row r="1346" spans="1:1">
       <c r="A1346">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1347" spans="1:1">
       <c r="A1347">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1348" spans="1:1">
       <c r="A1348">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1349" spans="1:1">
@@ -7149,32 +7149,32 @@
     </row>
     <row r="1355" spans="1:1">
       <c r="A1355">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1356" spans="1:1">
       <c r="A1356">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1357" spans="1:1">
       <c r="A1357">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1358" spans="1:1">
       <c r="A1358">
-        <v>2.416593574757808</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1359" spans="1:1">
       <c r="A1359">
-        <v>0.289690194483927</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1360" spans="1:1">
       <c r="A1360">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1361" spans="1:1">
@@ -7194,17 +7194,17 @@
     </row>
     <row r="1364" spans="1:1">
       <c r="A1364">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1365" spans="1:1">
       <c r="A1365">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1366" spans="1:1">
       <c r="A1366">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1367" spans="1:1">
@@ -7239,17 +7239,17 @@
     </row>
     <row r="1373" spans="1:1">
       <c r="A1373">
-        <v>1.407745272749783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1374" spans="1:1">
       <c r="A1374">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1375" spans="1:1">
       <c r="A1375">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1376" spans="1:1">
@@ -7284,32 +7284,32 @@
     </row>
     <row r="1382" spans="1:1">
       <c r="A1382">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1383" spans="1:1">
       <c r="A1383">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1384" spans="1:1">
       <c r="A1384">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1385" spans="1:1">
       <c r="A1385">
-        <v>-1</v>
+        <v>2.416593574757875</v>
       </c>
     </row>
     <row r="1386" spans="1:1">
       <c r="A1386">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1387" spans="1:1">
       <c r="A1387">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1388" spans="1:1">
@@ -7374,17 +7374,17 @@
     </row>
     <row r="1400" spans="1:1">
       <c r="A1400">
-        <v>1.407745272749794</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1401" spans="1:1">
       <c r="A1401">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1402" spans="1:1">
       <c r="A1402">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1403" spans="1:1">
@@ -7404,17 +7404,17 @@
     </row>
     <row r="1406" spans="1:1">
       <c r="A1406">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="1407" spans="1:1">
       <c r="A1407">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1408" spans="1:1">
       <c r="A1408">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1409" spans="1:1">
@@ -7509,17 +7509,17 @@
     </row>
     <row r="1427" spans="1:1">
       <c r="A1427">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1428" spans="1:1">
       <c r="A1428">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1429" spans="1:1">
       <c r="A1429">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1430" spans="1:1">
@@ -7644,17 +7644,17 @@
     </row>
     <row r="1454" spans="1:1">
       <c r="A1454">
-        <v>1.407745272749772</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1455" spans="1:1">
       <c r="A1455">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1456" spans="1:1">
       <c r="A1456">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1457" spans="1:1">
@@ -7689,32 +7689,32 @@
     </row>
     <row r="1463" spans="1:1">
       <c r="A1463">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1464" spans="1:1">
       <c r="A1464">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1465" spans="1:1">
       <c r="A1465">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1466" spans="1:1">
       <c r="A1466">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="1467" spans="1:1">
       <c r="A1467">
-        <v>-1</v>
+        <v>0.2874119961166488</v>
       </c>
     </row>
     <row r="1468" spans="1:1">
       <c r="A1468">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1469" spans="1:1">
@@ -7779,62 +7779,62 @@
     </row>
     <row r="1481" spans="1:1">
       <c r="A1481">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1482" spans="1:1">
       <c r="A1482">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1483" spans="1:1">
       <c r="A1483">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1484" spans="1:1">
       <c r="A1484">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1485" spans="1:1">
       <c r="A1485">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1486" spans="1:1">
       <c r="A1486">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1487" spans="1:1">
       <c r="A1487">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1488" spans="1:1">
       <c r="A1488">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1489" spans="1:1">
       <c r="A1489">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1490" spans="1:1">
       <c r="A1490">
-        <v>1.407745272749661</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1491" spans="1:1">
       <c r="A1491">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1492" spans="1:1">
       <c r="A1492">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1493" spans="1:1">
@@ -7974,17 +7974,17 @@
     </row>
     <row r="1520" spans="1:1">
       <c r="A1520">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="1521" spans="1:1">
       <c r="A1521">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1522" spans="1:1">
       <c r="A1522">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1523" spans="1:1">
@@ -8004,17 +8004,17 @@
     </row>
     <row r="1526" spans="1:1">
       <c r="A1526">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1527" spans="1:1">
       <c r="A1527">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1528" spans="1:1">
       <c r="A1528">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1529" spans="1:1">
@@ -8034,17 +8034,17 @@
     </row>
     <row r="1532" spans="1:1">
       <c r="A1532">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1533" spans="1:1">
       <c r="A1533">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1534" spans="1:1">
       <c r="A1534">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1535" spans="1:1">
@@ -8154,17 +8154,17 @@
     </row>
     <row r="1556" spans="1:1">
       <c r="A1556">
-        <v>-1</v>
+        <v>2.416593574757897</v>
       </c>
     </row>
     <row r="1557" spans="1:1">
       <c r="A1557">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1558" spans="1:1">
       <c r="A1558">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1559" spans="1:1">
@@ -8304,32 +8304,32 @@
     </row>
     <row r="1586" spans="1:1">
       <c r="A1586">
-        <v>-1</v>
+        <v>1.127766143616005</v>
       </c>
     </row>
     <row r="1587" spans="1:1">
       <c r="A1587">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1588" spans="1:1">
       <c r="A1588">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1589" spans="1:1">
       <c r="A1589">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1590" spans="1:1">
       <c r="A1590">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1591" spans="1:1">
       <c r="A1591">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1592" spans="1:1">
@@ -8394,17 +8394,17 @@
     </row>
     <row r="1604" spans="1:1">
       <c r="A1604">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="1605" spans="1:1">
       <c r="A1605">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1606" spans="1:1">
       <c r="A1606">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1607" spans="1:1">
@@ -8424,17 +8424,17 @@
     </row>
     <row r="1610" spans="1:1">
       <c r="A1610">
-        <v>2.416593574757808</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1611" spans="1:1">
       <c r="A1611">
-        <v>0.2881089063963893</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1612" spans="1:1">
       <c r="A1612">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1613" spans="1:1">
@@ -8484,17 +8484,17 @@
     </row>
     <row r="1622" spans="1:1">
       <c r="A1622">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1623" spans="1:1">
       <c r="A1623">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1624" spans="1:1">
       <c r="A1624">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1625" spans="1:1">
@@ -8514,17 +8514,17 @@
     </row>
     <row r="1628" spans="1:1">
       <c r="A1628">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1629" spans="1:1">
       <c r="A1629">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1630" spans="1:1">
       <c r="A1630">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1631" spans="1:1">
@@ -8664,32 +8664,32 @@
     </row>
     <row r="1658" spans="1:1">
       <c r="A1658">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="1659" spans="1:1">
       <c r="A1659">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1660" spans="1:1">
       <c r="A1660">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1661" spans="1:1">
       <c r="A1661">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1662" spans="1:1">
       <c r="A1662">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1663" spans="1:1">
       <c r="A1663">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1664" spans="1:1">
@@ -8844,17 +8844,17 @@
     </row>
     <row r="1694" spans="1:1">
       <c r="A1694">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="1695" spans="1:1">
       <c r="A1695">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1696" spans="1:1">
       <c r="A1696">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1697" spans="1:1">
@@ -9099,17 +9099,17 @@
     </row>
     <row r="1745" spans="1:1">
       <c r="A1745">
-        <v>-1</v>
+        <v>2.422731497529562</v>
       </c>
     </row>
     <row r="1746" spans="1:1">
       <c r="A1746">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1747" spans="1:1">
       <c r="A1747">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1748" spans="1:1">
@@ -9129,17 +9129,17 @@
     </row>
     <row r="1751" spans="1:1">
       <c r="A1751">
-        <v>-1</v>
+        <v>1.407745272749783</v>
       </c>
     </row>
     <row r="1752" spans="1:1">
       <c r="A1752">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1753" spans="1:1">
       <c r="A1753">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1754" spans="1:1">
@@ -9234,17 +9234,17 @@
     </row>
     <row r="1772" spans="1:1">
       <c r="A1772">
-        <v>2.422990095899435</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1773" spans="1:1">
       <c r="A1773">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1774" spans="1:1">
       <c r="A1774">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1775" spans="1:1">
@@ -9309,17 +9309,17 @@
     </row>
     <row r="1787" spans="1:1">
       <c r="A1787">
-        <v>-1</v>
+        <v>1.407745272749694</v>
       </c>
     </row>
     <row r="1788" spans="1:1">
       <c r="A1788">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1789" spans="1:1">
       <c r="A1789">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1790" spans="1:1">
@@ -9399,32 +9399,32 @@
     </row>
     <row r="1805" spans="1:1">
       <c r="A1805">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1806" spans="1:1">
       <c r="A1806">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1807" spans="1:1">
       <c r="A1807">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1808" spans="1:1">
       <c r="A1808">
-        <v>2.422811114299162</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1809" spans="1:1">
       <c r="A1809">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1810" spans="1:1">
       <c r="A1810">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1811" spans="1:1">
@@ -9444,17 +9444,17 @@
     </row>
     <row r="1814" spans="1:1">
       <c r="A1814">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1815" spans="1:1">
       <c r="A1815">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1816" spans="1:1">
       <c r="A1816">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1817" spans="1:1">
@@ -9474,32 +9474,32 @@
     </row>
     <row r="1820" spans="1:1">
       <c r="A1820">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1821" spans="1:1">
       <c r="A1821">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1822" spans="1:1">
       <c r="A1822">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1823" spans="1:1">
       <c r="A1823">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1824" spans="1:1">
       <c r="A1824">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1825" spans="1:1">
       <c r="A1825">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1826" spans="1:1">
@@ -9759,17 +9759,17 @@
     </row>
     <row r="1877" spans="1:1">
       <c r="A1877">
-        <v>-1</v>
+        <v>1.407745272749628</v>
       </c>
     </row>
     <row r="1878" spans="1:1">
       <c r="A1878">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1879" spans="1:1">
       <c r="A1879">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1880" spans="1:1">
@@ -9804,17 +9804,17 @@
     </row>
     <row r="1886" spans="1:1">
       <c r="A1886">
-        <v>-1</v>
+        <v>1.407745272749783</v>
       </c>
     </row>
     <row r="1887" spans="1:1">
       <c r="A1887">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1888" spans="1:1">
       <c r="A1888">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1889" spans="1:1">
@@ -9834,17 +9834,17 @@
     </row>
     <row r="1892" spans="1:1">
       <c r="A1892">
-        <v>1.127766143615994</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1893" spans="1:1">
       <c r="A1893">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1894" spans="1:1">
       <c r="A1894">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1895" spans="1:1">
@@ -9939,17 +9939,17 @@
     </row>
     <row r="1913" spans="1:1">
       <c r="A1913">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1914" spans="1:1">
       <c r="A1914">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1915" spans="1:1">
       <c r="A1915">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1916" spans="1:1">
@@ -10029,17 +10029,17 @@
     </row>
     <row r="1931" spans="1:1">
       <c r="A1931">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1932" spans="1:1">
       <c r="A1932">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1933" spans="1:1">
       <c r="A1933">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1934" spans="1:1">
@@ -10119,17 +10119,17 @@
     </row>
     <row r="1949" spans="1:1">
       <c r="A1949">
-        <v>1.407745272749827</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1950" spans="1:1">
       <c r="A1950">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1951" spans="1:1">
       <c r="A1951">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1952" spans="1:1">
@@ -10209,17 +10209,17 @@
     </row>
     <row r="1967" spans="1:1">
       <c r="A1967">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1968" spans="1:1">
       <c r="A1968">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1969" spans="1:1">
       <c r="A1969">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1970" spans="1:1">
@@ -10479,17 +10479,17 @@
     </row>
     <row r="2021" spans="1:1">
       <c r="A2021">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2022" spans="1:1">
       <c r="A2022">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2023" spans="1:1">
       <c r="A2023">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2024" spans="1:1">
@@ -10509,32 +10509,32 @@
     </row>
     <row r="2027" spans="1:1">
       <c r="A2027">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2028" spans="1:1">
       <c r="A2028">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2029" spans="1:1">
       <c r="A2029">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2030" spans="1:1">
       <c r="A2030">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2031" spans="1:1">
       <c r="A2031">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2032" spans="1:1">
       <c r="A2032">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2033" spans="1:1">
@@ -10644,17 +10644,17 @@
     </row>
     <row r="2054" spans="1:1">
       <c r="A2054">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2055" spans="1:1">
       <c r="A2055">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2056" spans="1:1">
       <c r="A2056">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2057" spans="1:1">
@@ -10689,17 +10689,17 @@
     </row>
     <row r="2063" spans="1:1">
       <c r="A2063">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2064" spans="1:1">
       <c r="A2064">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2065" spans="1:1">
       <c r="A2065">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2066" spans="1:1">
@@ -11199,17 +11199,17 @@
     </row>
     <row r="2165" spans="1:1">
       <c r="A2165">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2166" spans="1:1">
       <c r="A2166">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2167" spans="1:1">
       <c r="A2167">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2168" spans="1:1">
@@ -11454,17 +11454,17 @@
     </row>
     <row r="2216" spans="1:1">
       <c r="A2216">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2217" spans="1:1">
       <c r="A2217">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2218" spans="1:1">
       <c r="A2218">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2219" spans="1:1">
@@ -12054,32 +12054,32 @@
     </row>
     <row r="2336" spans="1:1">
       <c r="A2336">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2337" spans="1:1">
       <c r="A2337">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2338" spans="1:1">
       <c r="A2338">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2339" spans="1:1">
       <c r="A2339">
-        <v>-1</v>
+        <v>2.416593574757919</v>
       </c>
     </row>
     <row r="2340" spans="1:1">
       <c r="A2340">
-        <v>-1</v>
+        <v>0.2934493943477556</v>
       </c>
     </row>
     <row r="2341" spans="1:1">
       <c r="A2341">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2342" spans="1:1">
@@ -12204,32 +12204,32 @@
     </row>
     <row r="2366" spans="1:1">
       <c r="A2366">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2367" spans="1:1">
       <c r="A2367">
-        <v>0.2904631421048354</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2368" spans="1:1">
       <c r="A2368">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2369" spans="1:1">
       <c r="A2369">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="2370" spans="1:1">
       <c r="A2370">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2371" spans="1:1">
       <c r="A2371">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2372" spans="1:1">
@@ -12249,17 +12249,17 @@
     </row>
     <row r="2375" spans="1:1">
       <c r="A2375">
-        <v>2.416593574757842</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2376" spans="1:1">
       <c r="A2376">
-        <v>0.2951982105431905</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2377" spans="1:1">
       <c r="A2377">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2378" spans="1:1">
@@ -12309,32 +12309,32 @@
     </row>
     <row r="2387" spans="1:1">
       <c r="A2387">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2388" spans="1:1">
       <c r="A2388">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2389" spans="1:1">
       <c r="A2389">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2390" spans="1:1">
       <c r="A2390">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2391" spans="1:1">
       <c r="A2391">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2392" spans="1:1">
       <c r="A2392">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2393" spans="1:1">
@@ -12369,62 +12369,62 @@
     </row>
     <row r="2399" spans="1:1">
       <c r="A2399">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2400" spans="1:1">
       <c r="A2400">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2401" spans="1:1">
       <c r="A2401">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2402" spans="1:1">
       <c r="A2402">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2403" spans="1:1">
       <c r="A2403">
-        <v>0.2888782042739346</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2404" spans="1:1">
       <c r="A2404">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2405" spans="1:1">
       <c r="A2405">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="2406" spans="1:1">
       <c r="A2406">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2407" spans="1:1">
       <c r="A2407">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2408" spans="1:1">
       <c r="A2408">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2409" spans="1:1">
       <c r="A2409">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2410" spans="1:1">
       <c r="A2410">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2411" spans="1:1">
@@ -12474,62 +12474,62 @@
     </row>
     <row r="2420" spans="1:1">
       <c r="A2420">
-        <v>2.416593574757797</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2421" spans="1:1">
       <c r="A2421">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2422" spans="1:1">
       <c r="A2422">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2423" spans="1:1">
       <c r="A2423">
-        <v>1.127766143616094</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2424" spans="1:1">
       <c r="A2424">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2425" spans="1:1">
       <c r="A2425">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2426" spans="1:1">
       <c r="A2426">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2427" spans="1:1">
       <c r="A2427">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2428" spans="1:1">
       <c r="A2428">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2429" spans="1:1">
       <c r="A2429">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2430" spans="1:1">
       <c r="A2430">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2431" spans="1:1">
       <c r="A2431">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2432" spans="1:1">
@@ -12549,32 +12549,32 @@
     </row>
     <row r="2435" spans="1:1">
       <c r="A2435">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2436" spans="1:1">
       <c r="A2436">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2437" spans="1:1">
       <c r="A2437">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2438" spans="1:1">
       <c r="A2438">
-        <v>2.416593574757808</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2439" spans="1:1">
       <c r="A2439">
-        <v>0.2904682879694143</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2440" spans="1:1">
       <c r="A2440">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2441" spans="1:1">
@@ -12594,32 +12594,32 @@
     </row>
     <row r="2444" spans="1:1">
       <c r="A2444">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2445" spans="1:1">
       <c r="A2445">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2446" spans="1:1">
       <c r="A2446">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2447" spans="1:1">
       <c r="A2447">
-        <v>2.416593574757919</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2448" spans="1:1">
       <c r="A2448">
-        <v>0.2952050018440677</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2449" spans="1:1">
       <c r="A2449">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2450" spans="1:1">
@@ -12654,17 +12654,17 @@
     </row>
     <row r="2456" spans="1:1">
       <c r="A2456">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2457" spans="1:1">
       <c r="A2457">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2458" spans="1:1">
       <c r="A2458">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2459" spans="1:1">
@@ -12729,47 +12729,47 @@
     </row>
     <row r="2471" spans="1:1">
       <c r="A2471">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2472" spans="1:1">
       <c r="A2472">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2473" spans="1:1">
       <c r="A2473">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2474" spans="1:1">
       <c r="A2474">
-        <v>-1</v>
+        <v>2.41659357475793</v>
       </c>
     </row>
     <row r="2475" spans="1:1">
       <c r="A2475">
-        <v>-1</v>
+        <v>0.2895708176056333</v>
       </c>
     </row>
     <row r="2476" spans="1:1">
       <c r="A2476">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2477" spans="1:1">
       <c r="A2477">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2478" spans="1:1">
       <c r="A2478">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2479" spans="1:1">
       <c r="A2479">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2480" spans="1:1">
@@ -12804,17 +12804,17 @@
     </row>
     <row r="2486" spans="1:1">
       <c r="A2486">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="2487" spans="1:1">
       <c r="A2487">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2488" spans="1:1">
       <c r="A2488">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2489" spans="1:1">
@@ -12834,17 +12834,17 @@
     </row>
     <row r="2492" spans="1:1">
       <c r="A2492">
-        <v>2.416593574757953</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2493" spans="1:1">
       <c r="A2493">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2494" spans="1:1">
       <c r="A2494">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2495" spans="1:1">
@@ -12879,17 +12879,17 @@
     </row>
     <row r="2501" spans="1:1">
       <c r="A2501">
-        <v>2.41659357475793</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2502" spans="1:1">
       <c r="A2502">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2503" spans="1:1">
       <c r="A2503">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2504" spans="1:1">
@@ -12939,32 +12939,32 @@
     </row>
     <row r="2513" spans="1:1">
       <c r="A2513">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2514" spans="1:1">
       <c r="A2514">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2515" spans="1:1">
       <c r="A2515">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2516" spans="1:1">
       <c r="A2516">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2517" spans="1:1">
       <c r="A2517">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2518" spans="1:1">
       <c r="A2518">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2519" spans="1:1">
@@ -13029,77 +13029,77 @@
     </row>
     <row r="2531" spans="1:1">
       <c r="A2531">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="2532" spans="1:1">
       <c r="A2532">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2533" spans="1:1">
       <c r="A2533">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2534" spans="1:1">
       <c r="A2534">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2535" spans="1:1">
       <c r="A2535">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2536" spans="1:1">
       <c r="A2536">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2537" spans="1:1">
       <c r="A2537">
-        <v>-1</v>
+        <v>2.416593574757775</v>
       </c>
     </row>
     <row r="2538" spans="1:1">
       <c r="A2538">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2539" spans="1:1">
       <c r="A2539">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2540" spans="1:1">
       <c r="A2540">
-        <v>1.127766143616005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2541" spans="1:1">
       <c r="A2541">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2542" spans="1:1">
       <c r="A2542">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2543" spans="1:1">
       <c r="A2543">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2544" spans="1:1">
       <c r="A2544">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2545" spans="1:1">
       <c r="A2545">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2546" spans="1:1">
@@ -13194,47 +13194,47 @@
     </row>
     <row r="2564" spans="1:1">
       <c r="A2564">
-        <v>2.416593574757842</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2565" spans="1:1">
       <c r="A2565">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2566" spans="1:1">
       <c r="A2566">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2567" spans="1:1">
       <c r="A2567">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2568" spans="1:1">
       <c r="A2568">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2569" spans="1:1">
       <c r="A2569">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2570" spans="1:1">
       <c r="A2570">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2571" spans="1:1">
       <c r="A2571">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2572" spans="1:1">
       <c r="A2572">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2573" spans="1:1">
@@ -13419,17 +13419,17 @@
     </row>
     <row r="2609" spans="1:1">
       <c r="A2609">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="2610" spans="1:1">
       <c r="A2610">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2611" spans="1:1">
       <c r="A2611">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2612" spans="1:1">
@@ -13449,17 +13449,17 @@
     </row>
     <row r="2615" spans="1:1">
       <c r="A2615">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2616" spans="1:1">
       <c r="A2616">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2617" spans="1:1">
       <c r="A2617">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2618" spans="1:1">
@@ -13479,17 +13479,17 @@
     </row>
     <row r="2621" spans="1:1">
       <c r="A2621">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="2622" spans="1:1">
       <c r="A2622">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2623" spans="1:1">
       <c r="A2623">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2624" spans="1:1">
@@ -13509,47 +13509,47 @@
     </row>
     <row r="2627" spans="1:1">
       <c r="A2627">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="2628" spans="1:1">
       <c r="A2628">
-        <v>-1</v>
+        <v>0.2934219627658607</v>
       </c>
     </row>
     <row r="2629" spans="1:1">
       <c r="A2629">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2630" spans="1:1">
       <c r="A2630">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="2631" spans="1:1">
       <c r="A2631">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2632" spans="1:1">
       <c r="A2632">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2633" spans="1:1">
       <c r="A2633">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2634" spans="1:1">
       <c r="A2634">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2635" spans="1:1">
       <c r="A2635">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2636" spans="1:1">
@@ -13569,17 +13569,17 @@
     </row>
     <row r="2639" spans="1:1">
       <c r="A2639">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="2640" spans="1:1">
       <c r="A2640">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2641" spans="1:1">
       <c r="A2641">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2642" spans="1:1">
@@ -13599,32 +13599,32 @@
     </row>
     <row r="2645" spans="1:1">
       <c r="A2645">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2646" spans="1:1">
       <c r="A2646">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2647" spans="1:1">
       <c r="A2647">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2648" spans="1:1">
       <c r="A2648">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="2649" spans="1:1">
       <c r="A2649">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2650" spans="1:1">
       <c r="A2650">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2651" spans="1:1">
@@ -13659,17 +13659,17 @@
     </row>
     <row r="2657" spans="1:1">
       <c r="A2657">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="2658" spans="1:1">
       <c r="A2658">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2659" spans="1:1">
       <c r="A2659">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2660" spans="1:1">
@@ -13704,17 +13704,17 @@
     </row>
     <row r="2666" spans="1:1">
       <c r="A2666">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="2667" spans="1:1">
       <c r="A2667">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2668" spans="1:1">
       <c r="A2668">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2669" spans="1:1">
@@ -13779,17 +13779,17 @@
     </row>
     <row r="2681" spans="1:1">
       <c r="A2681">
-        <v>2.416593574757842</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2682" spans="1:1">
       <c r="A2682">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2683" spans="1:1">
       <c r="A2683">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2684" spans="1:1">
@@ -13809,32 +13809,32 @@
     </row>
     <row r="2687" spans="1:1">
       <c r="A2687">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2688" spans="1:1">
       <c r="A2688">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2689" spans="1:1">
       <c r="A2689">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2690" spans="1:1">
       <c r="A2690">
-        <v>2.416593574757897</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2691" spans="1:1">
       <c r="A2691">
-        <v>0.288860256055723</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2692" spans="1:1">
       <c r="A2692">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2693" spans="1:1">
@@ -14079,17 +14079,17 @@
     </row>
     <row r="2741" spans="1:1">
       <c r="A2741">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2742" spans="1:1">
       <c r="A2742">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2743" spans="1:1">
       <c r="A2743">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2744" spans="1:1">
@@ -14169,17 +14169,17 @@
     </row>
     <row r="2759" spans="1:1">
       <c r="A2759">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2760" spans="1:1">
       <c r="A2760">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2761" spans="1:1">
       <c r="A2761">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2762" spans="1:1">
@@ -14259,17 +14259,17 @@
     </row>
     <row r="2777" spans="1:1">
       <c r="A2777">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2778" spans="1:1">
       <c r="A2778">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2779" spans="1:1">
       <c r="A2779">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2780" spans="1:1">
@@ -14439,17 +14439,17 @@
     </row>
     <row r="2813" spans="1:1">
       <c r="A2813">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2814" spans="1:1">
       <c r="A2814">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2815" spans="1:1">
       <c r="A2815">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2816" spans="1:1">
@@ -14859,47 +14859,47 @@
     </row>
     <row r="2897" spans="1:1">
       <c r="A2897">
-        <v>-1</v>
+        <v>2.430120121121193</v>
       </c>
     </row>
     <row r="2898" spans="1:1">
       <c r="A2898">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2899" spans="1:1">
       <c r="A2899">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2900" spans="1:1">
       <c r="A2900">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2901" spans="1:1">
       <c r="A2901">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2902" spans="1:1">
       <c r="A2902">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2903" spans="1:1">
       <c r="A2903">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2904" spans="1:1">
       <c r="A2904">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2905" spans="1:1">
       <c r="A2905">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2906" spans="1:1">
@@ -14934,17 +14934,17 @@
     </row>
     <row r="2912" spans="1:1">
       <c r="A2912">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2913" spans="1:1">
       <c r="A2913">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2914" spans="1:1">
       <c r="A2914">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2915" spans="1:1">
@@ -14994,47 +14994,47 @@
     </row>
     <row r="2924" spans="1:1">
       <c r="A2924">
-        <v>2.430301121387968</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2925" spans="1:1">
       <c r="A2925">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2926" spans="1:1">
       <c r="A2926">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2927" spans="1:1">
       <c r="A2927">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2928" spans="1:1">
       <c r="A2928">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2929" spans="1:1">
       <c r="A2929">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2930" spans="1:1">
       <c r="A2930">
-        <v>1.407745272749661</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2931" spans="1:1">
       <c r="A2931">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2932" spans="1:1">
       <c r="A2932">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2933" spans="1:1">
@@ -15114,32 +15114,32 @@
     </row>
     <row r="2948" spans="1:1">
       <c r="A2948">
-        <v>1.407745272749783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2949" spans="1:1">
       <c r="A2949">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2950" spans="1:1">
       <c r="A2950">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2951" spans="1:1">
       <c r="A2951">
-        <v>2.430174428906262</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2952" spans="1:1">
       <c r="A2952">
-        <v>0.2951528811379833</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2953" spans="1:1">
       <c r="A2953">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2954" spans="1:1">
@@ -15159,17 +15159,17 @@
     </row>
     <row r="2957" spans="1:1">
       <c r="A2957">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2958" spans="1:1">
       <c r="A2958">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2959" spans="1:1">
       <c r="A2959">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2960" spans="1:1">
@@ -15189,17 +15189,17 @@
     </row>
     <row r="2963" spans="1:1">
       <c r="A2963">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2964" spans="1:1">
       <c r="A2964">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2965" spans="1:1">
       <c r="A2965">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2966" spans="1:1">
@@ -15234,32 +15234,32 @@
     </row>
     <row r="2972" spans="1:1">
       <c r="A2972">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2973" spans="1:1">
       <c r="A2973">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2974" spans="1:1">
       <c r="A2974">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2975" spans="1:1">
       <c r="A2975">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2976" spans="1:1">
       <c r="A2976">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2977" spans="1:1">
       <c r="A2977">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2978" spans="1:1">
@@ -15294,17 +15294,17 @@
     </row>
     <row r="2984" spans="1:1">
       <c r="A2984">
-        <v>1.40774527274965</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2985" spans="1:1">
       <c r="A2985">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2986" spans="1:1">
       <c r="A2986">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2987" spans="1:1">
@@ -15339,17 +15339,17 @@
     </row>
     <row r="2993" spans="1:1">
       <c r="A2993">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2994" spans="1:1">
       <c r="A2994">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2995" spans="1:1">
       <c r="A2995">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2996" spans="1:1">
@@ -15384,17 +15384,17 @@
     </row>
     <row r="3002" spans="1:1">
       <c r="A3002">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3003" spans="1:1">
       <c r="A3003">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3004" spans="1:1">
       <c r="A3004">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3005" spans="1:1">
@@ -15444,17 +15444,17 @@
     </row>
     <row r="3014" spans="1:1">
       <c r="A3014">
-        <v>2.430236566625876</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3015" spans="1:1">
       <c r="A3015">
-        <v>0.2904247650099778</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3016" spans="1:1">
       <c r="A3016">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3017" spans="1:1">
@@ -15474,17 +15474,17 @@
     </row>
     <row r="3020" spans="1:1">
       <c r="A3020">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3021" spans="1:1">
       <c r="A3021">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3022" spans="1:1">
       <c r="A3022">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3023" spans="1:1">
@@ -15549,17 +15549,17 @@
     </row>
     <row r="3035" spans="1:1">
       <c r="A3035">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="3036" spans="1:1">
       <c r="A3036">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3037" spans="1:1">
       <c r="A3037">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3038" spans="1:1">
@@ -15609,32 +15609,32 @@
     </row>
     <row r="3047" spans="1:1">
       <c r="A3047">
-        <v>1.407745272749816</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3048" spans="1:1">
       <c r="A3048">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3049" spans="1:1">
       <c r="A3049">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3050" spans="1:1">
       <c r="A3050">
-        <v>-1</v>
+        <v>2.416593574757797</v>
       </c>
     </row>
     <row r="3051" spans="1:1">
       <c r="A3051">
-        <v>-1</v>
+        <v>0.289505689814884</v>
       </c>
     </row>
     <row r="3052" spans="1:1">
       <c r="A3052">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3053" spans="1:1">
@@ -15684,17 +15684,17 @@
     </row>
     <row r="3062" spans="1:1">
       <c r="A3062">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="3063" spans="1:1">
       <c r="A3063">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3064" spans="1:1">
       <c r="A3064">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3065" spans="1:1">
@@ -15714,17 +15714,17 @@
     </row>
     <row r="3068" spans="1:1">
       <c r="A3068">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3069" spans="1:1">
       <c r="A3069">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3070" spans="1:1">
       <c r="A3070">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3071" spans="1:1">
@@ -15834,17 +15834,17 @@
     </row>
     <row r="3092" spans="1:1">
       <c r="A3092">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3093" spans="1:1">
       <c r="A3093">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3094" spans="1:1">
       <c r="A3094">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3095" spans="1:1">
@@ -15864,32 +15864,32 @@
     </row>
     <row r="3098" spans="1:1">
       <c r="A3098">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="3099" spans="1:1">
       <c r="A3099">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3100" spans="1:1">
       <c r="A3100">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3101" spans="1:1">
       <c r="A3101">
-        <v>-1</v>
+        <v>1.407745272749739</v>
       </c>
     </row>
     <row r="3102" spans="1:1">
       <c r="A3102">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3103" spans="1:1">
       <c r="A3103">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3104" spans="1:1">
@@ -15939,17 +15939,17 @@
     </row>
     <row r="3113" spans="1:1">
       <c r="A3113">
-        <v>-1</v>
+        <v>2.416593574757875</v>
       </c>
     </row>
     <row r="3114" spans="1:1">
       <c r="A3114">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3115" spans="1:1">
       <c r="A3115">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3116" spans="1:1">
@@ -16224,17 +16224,17 @@
     </row>
     <row r="3170" spans="1:1">
       <c r="A3170">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3171" spans="1:1">
       <c r="A3171">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3172" spans="1:1">
       <c r="A3172">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3173" spans="1:1">
@@ -16254,32 +16254,32 @@
     </row>
     <row r="3176" spans="1:1">
       <c r="A3176">
-        <v>-1</v>
+        <v>2.430382272768339</v>
       </c>
     </row>
     <row r="3177" spans="1:1">
       <c r="A3177">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3178" spans="1:1">
       <c r="A3178">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3179" spans="1:1">
       <c r="A3179">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3180" spans="1:1">
       <c r="A3180">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3181" spans="1:1">
       <c r="A3181">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3182" spans="1:1">
@@ -16299,17 +16299,17 @@
     </row>
     <row r="3185" spans="1:1">
       <c r="A3185">
-        <v>-1</v>
+        <v>2.430361133995773</v>
       </c>
     </row>
     <row r="3186" spans="1:1">
       <c r="A3186">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3187" spans="1:1">
       <c r="A3187">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3188" spans="1:1">
@@ -16344,17 +16344,17 @@
     </row>
     <row r="3194" spans="1:1">
       <c r="A3194">
-        <v>-1</v>
+        <v>2.430224988026908</v>
       </c>
     </row>
     <row r="3195" spans="1:1">
       <c r="A3195">
-        <v>-1</v>
+        <v>0.2887993359889207</v>
       </c>
     </row>
     <row r="3196" spans="1:1">
       <c r="A3196">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3197" spans="1:1">
@@ -16404,17 +16404,17 @@
     </row>
     <row r="3206" spans="1:1">
       <c r="A3206">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3207" spans="1:1">
       <c r="A3207">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3208" spans="1:1">
       <c r="A3208">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3209" spans="1:1">
@@ -16584,17 +16584,17 @@
     </row>
     <row r="3242" spans="1:1">
       <c r="A3242">
-        <v>1.127766143616005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3243" spans="1:1">
       <c r="A3243">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3244" spans="1:1">
       <c r="A3244">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3245" spans="1:1">
@@ -16764,17 +16764,17 @@
     </row>
     <row r="3278" spans="1:1">
       <c r="A3278">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3279" spans="1:1">
       <c r="A3279">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3280" spans="1:1">
       <c r="A3280">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3281" spans="1:1">
@@ -16989,17 +16989,17 @@
     </row>
     <row r="3323" spans="1:1">
       <c r="A3323">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3324" spans="1:1">
       <c r="A3324">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3325" spans="1:1">
       <c r="A3325">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3326" spans="1:1">
@@ -17769,32 +17769,32 @@
     </row>
     <row r="3479" spans="1:1">
       <c r="A3479">
-        <v>1.407745272749805</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3480" spans="1:1">
       <c r="A3480">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3481" spans="1:1">
       <c r="A3481">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3482" spans="1:1">
       <c r="A3482">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="3483" spans="1:1">
       <c r="A3483">
-        <v>-1</v>
+        <v>0.2885197042353682</v>
       </c>
     </row>
     <row r="3484" spans="1:1">
       <c r="A3484">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3485" spans="1:1">
@@ -17814,17 +17814,17 @@
     </row>
     <row r="3488" spans="1:1">
       <c r="A3488">
-        <v>1.407745272749816</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3489" spans="1:1">
       <c r="A3489">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3490" spans="1:1">
       <c r="A3490">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3491" spans="1:1">
@@ -17844,32 +17844,32 @@
     </row>
     <row r="3494" spans="1:1">
       <c r="A3494">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="3495" spans="1:1">
       <c r="A3495">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3496" spans="1:1">
       <c r="A3496">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3497" spans="1:1">
       <c r="A3497">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="3498" spans="1:1">
       <c r="A3498">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3499" spans="1:1">
       <c r="A3499">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3500" spans="1:1">
@@ -17919,32 +17919,32 @@
     </row>
     <row r="3509" spans="1:1">
       <c r="A3509">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="3510" spans="1:1">
       <c r="A3510">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3511" spans="1:1">
       <c r="A3511">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3512" spans="1:1">
       <c r="A3512">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="3513" spans="1:1">
       <c r="A3513">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3514" spans="1:1">
       <c r="A3514">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3515" spans="1:1">
@@ -18024,17 +18024,17 @@
     </row>
     <row r="3530" spans="1:1">
       <c r="A3530">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="3531" spans="1:1">
       <c r="A3531">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3532" spans="1:1">
       <c r="A3532">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3533" spans="1:1">
@@ -18084,17 +18084,17 @@
     </row>
     <row r="3542" spans="1:1">
       <c r="A3542">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3543" spans="1:1">
       <c r="A3543">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3544" spans="1:1">
       <c r="A3544">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3545" spans="1:1">
@@ -18129,32 +18129,32 @@
     </row>
     <row r="3551" spans="1:1">
       <c r="A3551">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3552" spans="1:1">
       <c r="A3552">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3553" spans="1:1">
       <c r="A3553">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3554" spans="1:1">
       <c r="A3554">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="3555" spans="1:1">
       <c r="A3555">
-        <v>-1</v>
+        <v>0.2885190324639852</v>
       </c>
     </row>
     <row r="3556" spans="1:1">
       <c r="A3556">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3557" spans="1:1">
@@ -18174,17 +18174,17 @@
     </row>
     <row r="3560" spans="1:1">
       <c r="A3560">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3561" spans="1:1">
       <c r="A3561">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3562" spans="1:1">
       <c r="A3562">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3563" spans="1:1">
@@ -18414,17 +18414,17 @@
     </row>
     <row r="3608" spans="1:1">
       <c r="A3608">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="3609" spans="1:1">
       <c r="A3609">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3610" spans="1:1">
       <c r="A3610">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3611" spans="1:1">
@@ -18504,17 +18504,17 @@
     </row>
     <row r="3626" spans="1:1">
       <c r="A3626">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="3627" spans="1:1">
       <c r="A3627">
-        <v>-1</v>
+        <v>0.2893072406665143</v>
       </c>
     </row>
     <row r="3628" spans="1:1">
       <c r="A3628">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3629" spans="1:1">
@@ -18534,17 +18534,17 @@
     </row>
     <row r="3632" spans="1:1">
       <c r="A3632">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3633" spans="1:1">
       <c r="A3633">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3634" spans="1:1">
       <c r="A3634">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3635" spans="1:1">
@@ -18579,32 +18579,32 @@
     </row>
     <row r="3641" spans="1:1">
       <c r="A3641">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3642" spans="1:1">
       <c r="A3642">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3643" spans="1:1">
       <c r="A3643">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3644" spans="1:1">
       <c r="A3644">
-        <v>2.416593574757908</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3645" spans="1:1">
       <c r="A3645">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3646" spans="1:1">
       <c r="A3646">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3647" spans="1:1">
@@ -18744,47 +18744,47 @@
     </row>
     <row r="3674" spans="1:1">
       <c r="A3674">
-        <v>-1</v>
+        <v>1.127766143615994</v>
       </c>
     </row>
     <row r="3675" spans="1:1">
       <c r="A3675">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3676" spans="1:1">
       <c r="A3676">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3677" spans="1:1">
       <c r="A3677">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3678" spans="1:1">
       <c r="A3678">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3679" spans="1:1">
       <c r="A3679">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3680" spans="1:1">
       <c r="A3680">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="3681" spans="1:1">
       <c r="A3681">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3682" spans="1:1">
       <c r="A3682">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3683" spans="1:1">
@@ -18804,17 +18804,17 @@
     </row>
     <row r="3686" spans="1:1">
       <c r="A3686">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3687" spans="1:1">
       <c r="A3687">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3688" spans="1:1">
       <c r="A3688">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3689" spans="1:1">
@@ -18849,17 +18849,17 @@
     </row>
     <row r="3695" spans="1:1">
       <c r="A3695">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3696" spans="1:1">
       <c r="A3696">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3697" spans="1:1">
       <c r="A3697">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3698" spans="1:1">
@@ -19134,32 +19134,32 @@
     </row>
     <row r="3752" spans="1:1">
       <c r="A3752">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="3753" spans="1:1">
       <c r="A3753">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3754" spans="1:1">
       <c r="A3754">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3755" spans="1:1">
       <c r="A3755">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3756" spans="1:1">
       <c r="A3756">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3757" spans="1:1">
       <c r="A3757">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3758" spans="1:1">
@@ -19209,32 +19209,32 @@
     </row>
     <row r="3767" spans="1:1">
       <c r="A3767">
-        <v>1.407745272749794</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3768" spans="1:1">
       <c r="A3768">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3769" spans="1:1">
       <c r="A3769">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3770" spans="1:1">
       <c r="A3770">
-        <v>-1</v>
+        <v>2.416593574757864</v>
       </c>
     </row>
     <row r="3771" spans="1:1">
       <c r="A3771">
-        <v>-1</v>
+        <v>0.2885118328044389</v>
       </c>
     </row>
     <row r="3772" spans="1:1">
       <c r="A3772">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3773" spans="1:1">
@@ -19284,17 +19284,17 @@
     </row>
     <row r="3782" spans="1:1">
       <c r="A3782">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="3783" spans="1:1">
       <c r="A3783">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3784" spans="1:1">
       <c r="A3784">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3785" spans="1:1">
@@ -19464,17 +19464,17 @@
     </row>
     <row r="3818" spans="1:1">
       <c r="A3818">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="3819" spans="1:1">
       <c r="A3819">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3820" spans="1:1">
       <c r="A3820">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3821" spans="1:1">
@@ -19584,17 +19584,17 @@
     </row>
     <row r="3842" spans="1:1">
       <c r="A3842">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="3843" spans="1:1">
       <c r="A3843">
-        <v>-1</v>
+        <v>0.2885106452022557</v>
       </c>
     </row>
     <row r="3844" spans="1:1">
       <c r="A3844">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3845" spans="1:1">
@@ -19839,32 +19839,32 @@
     </row>
     <row r="3893" spans="1:1">
       <c r="A3893">
-        <v>1.40774527274965</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3894" spans="1:1">
       <c r="A3894">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3895" spans="1:1">
       <c r="A3895">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3896" spans="1:1">
       <c r="A3896">
-        <v>-1</v>
+        <v>2.416593574757864</v>
       </c>
     </row>
     <row r="3897" spans="1:1">
       <c r="A3897">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3898" spans="1:1">
       <c r="A3898">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3899" spans="1:1">
@@ -19884,17 +19884,17 @@
     </row>
     <row r="3902" spans="1:1">
       <c r="A3902">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3903" spans="1:1">
       <c r="A3903">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3904" spans="1:1">
       <c r="A3904">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3905" spans="1:1">
@@ -19944,17 +19944,17 @@
     </row>
     <row r="3914" spans="1:1">
       <c r="A3914">
-        <v>-1</v>
+        <v>2.416593574757908</v>
       </c>
     </row>
     <row r="3915" spans="1:1">
       <c r="A3915">
-        <v>-1</v>
+        <v>0.2893000674230262</v>
       </c>
     </row>
     <row r="3916" spans="1:1">
       <c r="A3916">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3917" spans="1:1">
@@ -20544,107 +20544,107 @@
     </row>
     <row r="4034" spans="1:1">
       <c r="A4034">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4035" spans="1:1">
       <c r="A4035">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4036" spans="1:1">
       <c r="A4036">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4037" spans="1:1">
       <c r="A4037">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4038" spans="1:1">
       <c r="A4038">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4039" spans="1:1">
       <c r="A4039">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4040" spans="1:1">
       <c r="A4040">
-        <v>-1</v>
+        <v>2.430163424702014</v>
       </c>
     </row>
     <row r="4041" spans="1:1">
       <c r="A4041">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4042" spans="1:1">
       <c r="A4042">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4043" spans="1:1">
       <c r="A4043">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4044" spans="1:1">
       <c r="A4044">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4045" spans="1:1">
       <c r="A4045">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4046" spans="1:1">
       <c r="A4046">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4047" spans="1:1">
       <c r="A4047">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4048" spans="1:1">
       <c r="A4048">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4049" spans="1:1">
       <c r="A4049">
-        <v>-1</v>
+        <v>2.43013465181281</v>
       </c>
     </row>
     <row r="4050" spans="1:1">
       <c r="A4050">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4051" spans="1:1">
       <c r="A4051">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4052" spans="1:1">
       <c r="A4052">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4053" spans="1:1">
       <c r="A4053">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4054" spans="1:1">
       <c r="A4054">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4055" spans="1:1">
@@ -20664,17 +20664,17 @@
     </row>
     <row r="4058" spans="1:1">
       <c r="A4058">
-        <v>-1</v>
+        <v>2.430004126271246</v>
       </c>
     </row>
     <row r="4059" spans="1:1">
       <c r="A4059">
-        <v>-1</v>
+        <v>0.2884574189798816</v>
       </c>
     </row>
     <row r="4060" spans="1:1">
       <c r="A4060">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4061" spans="1:1">
@@ -20769,17 +20769,17 @@
     </row>
     <row r="4079" spans="1:1">
       <c r="A4079">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4080" spans="1:1">
       <c r="A4080">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4081" spans="1:1">
       <c r="A4081">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4082" spans="1:1">
@@ -20964,17 +20964,17 @@
     </row>
     <row r="4118" spans="1:1">
       <c r="A4118">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4119" spans="1:1">
       <c r="A4119">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4120" spans="1:1">
       <c r="A4120">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4121" spans="1:1">
@@ -21309,17 +21309,17 @@
     </row>
     <row r="4187" spans="1:1">
       <c r="A4187">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4188" spans="1:1">
       <c r="A4188">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4189" spans="1:1">
       <c r="A4189">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4190" spans="1:1">
@@ -21639,17 +21639,17 @@
     </row>
     <row r="4253" spans="1:1">
       <c r="A4253">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4254" spans="1:1">
       <c r="A4254">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4255" spans="1:1">
       <c r="A4255">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4256" spans="1:1">
@@ -21984,77 +21984,77 @@
     </row>
     <row r="4322" spans="1:1">
       <c r="A4322">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4323" spans="1:1">
       <c r="A4323">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4324" spans="1:1">
       <c r="A4324">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4325" spans="1:1">
       <c r="A4325">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4326" spans="1:1">
       <c r="A4326">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4327" spans="1:1">
       <c r="A4327">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4328" spans="1:1">
       <c r="A4328">
-        <v>-1</v>
+        <v>2.430403305596174</v>
       </c>
     </row>
     <row r="4329" spans="1:1">
       <c r="A4329">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4330" spans="1:1">
       <c r="A4330">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4331" spans="1:1">
       <c r="A4331">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4332" spans="1:1">
       <c r="A4332">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4333" spans="1:1">
       <c r="A4333">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4334" spans="1:1">
       <c r="A4334">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4335" spans="1:1">
       <c r="A4335">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4336" spans="1:1">
       <c r="A4336">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4337" spans="1:1">
@@ -22104,17 +22104,17 @@
     </row>
     <row r="4346" spans="1:1">
       <c r="A4346">
-        <v>-1</v>
+        <v>2.430243470086535</v>
       </c>
     </row>
     <row r="4347" spans="1:1">
       <c r="A4347">
-        <v>-1</v>
+        <v>0.2884494810240779</v>
       </c>
     </row>
     <row r="4348" spans="1:1">
       <c r="A4348">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4349" spans="1:1">
@@ -22209,17 +22209,17 @@
     </row>
     <row r="4367" spans="1:1">
       <c r="A4367">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4368" spans="1:1">
       <c r="A4368">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4369" spans="1:1">
       <c r="A4369">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4370" spans="1:1">
@@ -22749,17 +22749,17 @@
     </row>
     <row r="4475" spans="1:1">
       <c r="A4475">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4476" spans="1:1">
       <c r="A4476">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4477" spans="1:1">
       <c r="A4477">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4478" spans="1:1">
@@ -23679,17 +23679,17 @@
     </row>
     <row r="4661" spans="1:1">
       <c r="A4661">
-        <v>-1</v>
+        <v>2.416593574757897</v>
       </c>
     </row>
     <row r="4662" spans="1:1">
       <c r="A4662">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4663" spans="1:1">
       <c r="A4663">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4664" spans="1:1">
@@ -23709,17 +23709,17 @@
     </row>
     <row r="4667" spans="1:1">
       <c r="A4667">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="4668" spans="1:1">
       <c r="A4668">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4669" spans="1:1">
       <c r="A4669">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4670" spans="1:1">
@@ -23739,17 +23739,17 @@
     </row>
     <row r="4673" spans="1:1">
       <c r="A4673">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="4674" spans="1:1">
       <c r="A4674">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4675" spans="1:1">
       <c r="A4675">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4676" spans="1:1">
@@ -23829,17 +23829,17 @@
     </row>
     <row r="4691" spans="1:1">
       <c r="A4691">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4692" spans="1:1">
       <c r="A4692">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4693" spans="1:1">
       <c r="A4693">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4694" spans="1:1">
@@ -23874,62 +23874,62 @@
     </row>
     <row r="4700" spans="1:1">
       <c r="A4700">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4701" spans="1:1">
       <c r="A4701">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4702" spans="1:1">
       <c r="A4702">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4703" spans="1:1">
       <c r="A4703">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4704" spans="1:1">
       <c r="A4704">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4705" spans="1:1">
       <c r="A4705">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4706" spans="1:1">
       <c r="A4706">
-        <v>2.416593574757919</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4707" spans="1:1">
       <c r="A4707">
-        <v>0.7498017852981209</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4708" spans="1:1">
       <c r="A4708">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4709" spans="1:1">
       <c r="A4709">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4710" spans="1:1">
       <c r="A4710">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4711" spans="1:1">
       <c r="A4711">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4712" spans="1:1">
@@ -23994,32 +23994,32 @@
     </row>
     <row r="4724" spans="1:1">
       <c r="A4724">
-        <v>2.41659357475783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4725" spans="1:1">
       <c r="A4725">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4726" spans="1:1">
       <c r="A4726">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4727" spans="1:1">
       <c r="A4727">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4728" spans="1:1">
       <c r="A4728">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4729" spans="1:1">
       <c r="A4729">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4730" spans="1:1">
@@ -24054,47 +24054,47 @@
     </row>
     <row r="4736" spans="1:1">
       <c r="A4736">
-        <v>1.127766143616005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4737" spans="1:1">
       <c r="A4737">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4738" spans="1:1">
       <c r="A4738">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4739" spans="1:1">
       <c r="A4739">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4740" spans="1:1">
       <c r="A4740">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4741" spans="1:1">
       <c r="A4741">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4742" spans="1:1">
       <c r="A4742">
-        <v>2.416593574757797</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4743" spans="1:1">
       <c r="A4743">
-        <v>0.7497793766966576</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4744" spans="1:1">
       <c r="A4744">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4745" spans="1:1">
@@ -24174,17 +24174,17 @@
     </row>
     <row r="4760" spans="1:1">
       <c r="A4760">
-        <v>2.416593574757786</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4761" spans="1:1">
       <c r="A4761">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4762" spans="1:1">
       <c r="A4762">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4763" spans="1:1">
@@ -24204,17 +24204,17 @@
     </row>
     <row r="4766" spans="1:1">
       <c r="A4766">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4767" spans="1:1">
       <c r="A4767">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4768" spans="1:1">
       <c r="A4768">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4769" spans="1:1">
@@ -24234,17 +24234,17 @@
     </row>
     <row r="4772" spans="1:1">
       <c r="A4772">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4773" spans="1:1">
       <c r="A4773">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4774" spans="1:1">
       <c r="A4774">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4775" spans="1:1">
@@ -24264,32 +24264,32 @@
     </row>
     <row r="4778" spans="1:1">
       <c r="A4778">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4779" spans="1:1">
       <c r="A4779">
-        <v>0.7507670869743244</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4780" spans="1:1">
       <c r="A4780">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4781" spans="1:1">
       <c r="A4781">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4782" spans="1:1">
       <c r="A4782">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4783" spans="1:1">
       <c r="A4783">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4784" spans="1:1">
@@ -24339,47 +24339,47 @@
     </row>
     <row r="4793" spans="1:1">
       <c r="A4793">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4794" spans="1:1">
       <c r="A4794">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4795" spans="1:1">
       <c r="A4795">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4796" spans="1:1">
       <c r="A4796">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4797" spans="1:1">
       <c r="A4797">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4798" spans="1:1">
       <c r="A4798">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4799" spans="1:1">
       <c r="A4799">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4800" spans="1:1">
       <c r="A4800">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4801" spans="1:1">
       <c r="A4801">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4802" spans="1:1">
@@ -24399,32 +24399,32 @@
     </row>
     <row r="4805" spans="1:1">
       <c r="A4805">
-        <v>2.416593574757797</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4806" spans="1:1">
       <c r="A4806">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4807" spans="1:1">
       <c r="A4807">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4808" spans="1:1">
       <c r="A4808">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4809" spans="1:1">
       <c r="A4809">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4810" spans="1:1">
       <c r="A4810">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4811" spans="1:1">
@@ -24444,32 +24444,32 @@
     </row>
     <row r="4814" spans="1:1">
       <c r="A4814">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4815" spans="1:1">
       <c r="A4815">
-        <v>0.7504453884574769</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4816" spans="1:1">
       <c r="A4816">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4817" spans="1:1">
       <c r="A4817">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4818" spans="1:1">
       <c r="A4818">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4819" spans="1:1">
       <c r="A4819">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4820" spans="1:1">
@@ -24504,17 +24504,17 @@
     </row>
     <row r="4826" spans="1:1">
       <c r="A4826">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="4827" spans="1:1">
       <c r="A4827">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4828" spans="1:1">
       <c r="A4828">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4829" spans="1:1">
@@ -24594,47 +24594,47 @@
     </row>
     <row r="4844" spans="1:1">
       <c r="A4844">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4845" spans="1:1">
       <c r="A4845">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4846" spans="1:1">
       <c r="A4846">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4847" spans="1:1">
       <c r="A4847">
-        <v>-1</v>
+        <v>1.407745272749694</v>
       </c>
     </row>
     <row r="4848" spans="1:1">
       <c r="A4848">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4849" spans="1:1">
       <c r="A4849">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4850" spans="1:1">
       <c r="A4850">
-        <v>2.416593574757842</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4851" spans="1:1">
       <c r="A4851">
-        <v>0.7507605572799503</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4852" spans="1:1">
       <c r="A4852">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4853" spans="1:1">
@@ -24684,32 +24684,32 @@
     </row>
     <row r="4862" spans="1:1">
       <c r="A4862">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="4863" spans="1:1">
       <c r="A4863">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4864" spans="1:1">
       <c r="A4864">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4865" spans="1:1">
       <c r="A4865">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4866" spans="1:1">
       <c r="A4866">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4867" spans="1:1">
       <c r="A4867">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4868" spans="1:1">
@@ -24924,62 +24924,62 @@
     </row>
     <row r="4910" spans="1:1">
       <c r="A4910">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="4911" spans="1:1">
       <c r="A4911">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4912" spans="1:1">
       <c r="A4912">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4913" spans="1:1">
       <c r="A4913">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="4914" spans="1:1">
       <c r="A4914">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4915" spans="1:1">
       <c r="A4915">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4916" spans="1:1">
       <c r="A4916">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="4917" spans="1:1">
       <c r="A4917">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4918" spans="1:1">
       <c r="A4918">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4919" spans="1:1">
       <c r="A4919">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4920" spans="1:1">
       <c r="A4920">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4921" spans="1:1">
       <c r="A4921">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4922" spans="1:1">
@@ -25044,47 +25044,47 @@
     </row>
     <row r="4934" spans="1:1">
       <c r="A4934">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4935" spans="1:1">
       <c r="A4935">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4936" spans="1:1">
       <c r="A4936">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4937" spans="1:1">
       <c r="A4937">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4938" spans="1:1">
       <c r="A4938">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4939" spans="1:1">
       <c r="A4939">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4940" spans="1:1">
       <c r="A4940">
-        <v>-1</v>
+        <v>2.41659357475793</v>
       </c>
     </row>
     <row r="4941" spans="1:1">
       <c r="A4941">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4942" spans="1:1">
       <c r="A4942">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4943" spans="1:1">
@@ -25179,17 +25179,17 @@
     </row>
     <row r="4961" spans="1:1">
       <c r="A4961">
-        <v>-1</v>
+        <v>1.127766143616005</v>
       </c>
     </row>
     <row r="4962" spans="1:1">
       <c r="A4962">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4963" spans="1:1">
       <c r="A4963">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4964" spans="1:1">
@@ -25269,17 +25269,17 @@
     </row>
     <row r="4979" spans="1:1">
       <c r="A4979">
-        <v>1.127766143616005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4980" spans="1:1">
       <c r="A4980">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4981" spans="1:1">
       <c r="A4981">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4982" spans="1:1">
@@ -25404,17 +25404,17 @@
     </row>
     <row r="5006" spans="1:1">
       <c r="A5006">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5007" spans="1:1">
       <c r="A5007">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5008" spans="1:1">
       <c r="A5008">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5009" spans="1:1">
@@ -25599,32 +25599,32 @@
     </row>
     <row r="5045" spans="1:1">
       <c r="A5045">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5046" spans="1:1">
       <c r="A5046">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5047" spans="1:1">
       <c r="A5047">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5048" spans="1:1">
       <c r="A5048">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5049" spans="1:1">
       <c r="A5049">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5050" spans="1:1">
       <c r="A5050">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5051" spans="1:1">
@@ -25689,17 +25689,17 @@
     </row>
     <row r="5063" spans="1:1">
       <c r="A5063">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5064" spans="1:1">
       <c r="A5064">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5065" spans="1:1">
       <c r="A5065">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5066" spans="1:1">
@@ -25779,17 +25779,17 @@
     </row>
     <row r="5081" spans="1:1">
       <c r="A5081">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5082" spans="1:1">
       <c r="A5082">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5083" spans="1:1">
       <c r="A5083">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5084" spans="1:1">
@@ -25839,17 +25839,17 @@
     </row>
     <row r="5093" spans="1:1">
       <c r="A5093">
-        <v>2.416593574757897</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5094" spans="1:1">
       <c r="A5094">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5095" spans="1:1">
       <c r="A5095">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5096" spans="1:1">
@@ -26124,32 +26124,32 @@
     </row>
     <row r="5150" spans="1:1">
       <c r="A5150">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="5151" spans="1:1">
       <c r="A5151">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5152" spans="1:1">
       <c r="A5152">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5153" spans="1:1">
       <c r="A5153">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5154" spans="1:1">
       <c r="A5154">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5155" spans="1:1">
       <c r="A5155">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5156" spans="1:1">
@@ -26409,17 +26409,17 @@
     </row>
     <row r="5207" spans="1:1">
       <c r="A5207">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="5208" spans="1:1">
       <c r="A5208">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5209" spans="1:1">
       <c r="A5209">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5210" spans="1:1">
@@ -26439,32 +26439,32 @@
     </row>
     <row r="5213" spans="1:1">
       <c r="A5213">
-        <v>-1</v>
+        <v>1.127766143615994</v>
       </c>
     </row>
     <row r="5214" spans="1:1">
       <c r="A5214">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5215" spans="1:1">
       <c r="A5215">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5216" spans="1:1">
       <c r="A5216">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5217" spans="1:1">
       <c r="A5217">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5218" spans="1:1">
       <c r="A5218">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5219" spans="1:1">
@@ -26514,17 +26514,17 @@
     </row>
     <row r="5228" spans="1:1">
       <c r="A5228">
-        <v>2.422899110022692</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5229" spans="1:1">
       <c r="A5229">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5230" spans="1:1">
       <c r="A5230">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5231" spans="1:1">
@@ -26574,32 +26574,32 @@
     </row>
     <row r="5240" spans="1:1">
       <c r="A5240">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="5241" spans="1:1">
       <c r="A5241">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5242" spans="1:1">
       <c r="A5242">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5243" spans="1:1">
       <c r="A5243">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5244" spans="1:1">
       <c r="A5244">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5245" spans="1:1">
       <c r="A5245">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5246" spans="1:1">
@@ -26694,47 +26694,47 @@
     </row>
     <row r="5264" spans="1:1">
       <c r="A5264">
-        <v>2.42295836016565</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5265" spans="1:1">
       <c r="A5265">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5266" spans="1:1">
       <c r="A5266">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5267" spans="1:1">
       <c r="A5267">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5268" spans="1:1">
       <c r="A5268">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5269" spans="1:1">
       <c r="A5269">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5270" spans="1:1">
       <c r="A5270">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="5271" spans="1:1">
       <c r="A5271">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5272" spans="1:1">
       <c r="A5272">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5273" spans="1:1">
@@ -26769,17 +26769,17 @@
     </row>
     <row r="5279" spans="1:1">
       <c r="A5279">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="5280" spans="1:1">
       <c r="A5280">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5281" spans="1:1">
       <c r="A5281">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5282" spans="1:1">
@@ -26814,17 +26814,17 @@
     </row>
     <row r="5288" spans="1:1">
       <c r="A5288">
-        <v>-1</v>
+        <v>1.407745272749694</v>
       </c>
     </row>
     <row r="5289" spans="1:1">
       <c r="A5289">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5290" spans="1:1">
       <c r="A5290">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5291" spans="1:1">
@@ -27039,47 +27039,47 @@
     </row>
     <row r="5333" spans="1:1">
       <c r="A5333">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5334" spans="1:1">
       <c r="A5334">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5335" spans="1:1">
       <c r="A5335">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5336" spans="1:1">
       <c r="A5336">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5337" spans="1:1">
       <c r="A5337">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5338" spans="1:1">
       <c r="A5338">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5339" spans="1:1">
       <c r="A5339">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5340" spans="1:1">
       <c r="A5340">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5341" spans="1:1">
       <c r="A5341">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5342" spans="1:1">
@@ -27114,32 +27114,32 @@
     </row>
     <row r="5348" spans="1:1">
       <c r="A5348">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5349" spans="1:1">
       <c r="A5349">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5350" spans="1:1">
       <c r="A5350">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5351" spans="1:1">
       <c r="A5351">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5352" spans="1:1">
       <c r="A5352">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5353" spans="1:1">
       <c r="A5353">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5354" spans="1:1">
@@ -27204,17 +27204,17 @@
     </row>
     <row r="5366" spans="1:1">
       <c r="A5366">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="5367" spans="1:1">
       <c r="A5367">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5368" spans="1:1">
       <c r="A5368">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5369" spans="1:1">
@@ -27234,17 +27234,17 @@
     </row>
     <row r="5372" spans="1:1">
       <c r="A5372">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5373" spans="1:1">
       <c r="A5373">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5374" spans="1:1">
       <c r="A5374">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5375" spans="1:1">
@@ -27939,17 +27939,17 @@
     </row>
     <row r="5513" spans="1:1">
       <c r="A5513">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5514" spans="1:1">
       <c r="A5514">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5515" spans="1:1">
       <c r="A5515">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5516" spans="1:1">
@@ -28104,17 +28104,17 @@
     </row>
     <row r="5546" spans="1:1">
       <c r="A5546">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5547" spans="1:1">
       <c r="A5547">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5548" spans="1:1">
       <c r="A5548">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5549" spans="1:1">
@@ -29259,32 +29259,32 @@
     </row>
     <row r="5777" spans="1:1">
       <c r="A5777">
-        <v>-1</v>
+        <v>2.416593574757908</v>
       </c>
     </row>
     <row r="5778" spans="1:1">
       <c r="A5778">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5779" spans="1:1">
       <c r="A5779">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5780" spans="1:1">
       <c r="A5780">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5781" spans="1:1">
       <c r="A5781">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5782" spans="1:1">
       <c r="A5782">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5783" spans="1:1">
@@ -29304,17 +29304,17 @@
     </row>
     <row r="5786" spans="1:1">
       <c r="A5786">
-        <v>2.41659357475783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5787" spans="1:1">
       <c r="A5787">
-        <v>0.7503924159934505</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5788" spans="1:1">
       <c r="A5788">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5789" spans="1:1">
@@ -29364,17 +29364,17 @@
     </row>
     <row r="5798" spans="1:1">
       <c r="A5798">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5799" spans="1:1">
       <c r="A5799">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5800" spans="1:1">
       <c r="A5800">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5801" spans="1:1">
@@ -29394,32 +29394,32 @@
     </row>
     <row r="5804" spans="1:1">
       <c r="A5804">
-        <v>2.416593574757908</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5805" spans="1:1">
       <c r="A5805">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5806" spans="1:1">
       <c r="A5806">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5807" spans="1:1">
       <c r="A5807">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5808" spans="1:1">
       <c r="A5808">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5809" spans="1:1">
       <c r="A5809">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5810" spans="1:1">
@@ -29454,17 +29454,17 @@
     </row>
     <row r="5816" spans="1:1">
       <c r="A5816">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5817" spans="1:1">
       <c r="A5817">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5818" spans="1:1">
       <c r="A5818">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5819" spans="1:1">
@@ -29604,17 +29604,17 @@
     </row>
     <row r="5846" spans="1:1">
       <c r="A5846">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="5847" spans="1:1">
       <c r="A5847">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5848" spans="1:1">
       <c r="A5848">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5849" spans="1:1">
@@ -29634,32 +29634,32 @@
     </row>
     <row r="5852" spans="1:1">
       <c r="A5852">
-        <v>1.127766143616005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5853" spans="1:1">
       <c r="A5853">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5854" spans="1:1">
       <c r="A5854">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5855" spans="1:1">
       <c r="A5855">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5856" spans="1:1">
       <c r="A5856">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5857" spans="1:1">
       <c r="A5857">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5858" spans="1:1">
@@ -29739,17 +29739,17 @@
     </row>
     <row r="5873" spans="1:1">
       <c r="A5873">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5874" spans="1:1">
       <c r="A5874">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5875" spans="1:1">
       <c r="A5875">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5876" spans="1:1">
@@ -29769,17 +29769,17 @@
     </row>
     <row r="5879" spans="1:1">
       <c r="A5879">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5880" spans="1:1">
       <c r="A5880">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5881" spans="1:1">
       <c r="A5881">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5882" spans="1:1">
@@ -29829,17 +29829,17 @@
     </row>
     <row r="5891" spans="1:1">
       <c r="A5891">
-        <v>1.407745272749805</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5892" spans="1:1">
       <c r="A5892">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5893" spans="1:1">
       <c r="A5893">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5894" spans="1:1">
@@ -29949,17 +29949,17 @@
     </row>
     <row r="5915" spans="1:1">
       <c r="A5915">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="5916" spans="1:1">
       <c r="A5916">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5917" spans="1:1">
       <c r="A5917">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5918" spans="1:1">
@@ -30009,17 +30009,17 @@
     </row>
     <row r="5927" spans="1:1">
       <c r="A5927">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="5928" spans="1:1">
       <c r="A5928">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5929" spans="1:1">
       <c r="A5929">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5930" spans="1:1">
@@ -30279,17 +30279,17 @@
     </row>
     <row r="5981" spans="1:1">
       <c r="A5981">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5982" spans="1:1">
       <c r="A5982">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5983" spans="1:1">
       <c r="A5983">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5984" spans="1:1">
@@ -30729,17 +30729,17 @@
     </row>
     <row r="6071" spans="1:1">
       <c r="A6071">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6072" spans="1:1">
       <c r="A6072">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6073" spans="1:1">
       <c r="A6073">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6074" spans="1:1">
@@ -30804,17 +30804,17 @@
     </row>
     <row r="6086" spans="1:1">
       <c r="A6086">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="6087" spans="1:1">
       <c r="A6087">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6088" spans="1:1">
       <c r="A6088">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6089" spans="1:1">
@@ -30864,17 +30864,17 @@
     </row>
     <row r="6098" spans="1:1">
       <c r="A6098">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6099" spans="1:1">
       <c r="A6099">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6100" spans="1:1">
       <c r="A6100">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6101" spans="1:1">
@@ -30984,17 +30984,17 @@
     </row>
     <row r="6122" spans="1:1">
       <c r="A6122">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="6123" spans="1:1">
       <c r="A6123">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6124" spans="1:1">
       <c r="A6124">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6125" spans="1:1">
@@ -31194,32 +31194,32 @@
     </row>
     <row r="6164" spans="1:1">
       <c r="A6164">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="6165" spans="1:1">
       <c r="A6165">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6166" spans="1:1">
       <c r="A6166">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6167" spans="1:1">
       <c r="A6167">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6168" spans="1:1">
       <c r="A6168">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6169" spans="1:1">
       <c r="A6169">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6170" spans="1:1">
@@ -31344,17 +31344,17 @@
     </row>
     <row r="6194" spans="1:1">
       <c r="A6194">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="6195" spans="1:1">
       <c r="A6195">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6196" spans="1:1">
       <c r="A6196">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6197" spans="1:1">
@@ -31734,17 +31734,17 @@
     </row>
     <row r="6272" spans="1:1">
       <c r="A6272">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="6273" spans="1:1">
       <c r="A6273">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6274" spans="1:1">
       <c r="A6274">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6275" spans="1:1">
@@ -32079,62 +32079,62 @@
     </row>
     <row r="6341" spans="1:1">
       <c r="A6341">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="6342" spans="1:1">
       <c r="A6342">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6343" spans="1:1">
       <c r="A6343">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6344" spans="1:1">
       <c r="A6344">
-        <v>2.422918736200785</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6345" spans="1:1">
       <c r="A6345">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6346" spans="1:1">
       <c r="A6346">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6347" spans="1:1">
       <c r="A6347">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6348" spans="1:1">
       <c r="A6348">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6349" spans="1:1">
       <c r="A6349">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6350" spans="1:1">
       <c r="A6350">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="6351" spans="1:1">
       <c r="A6351">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6352" spans="1:1">
       <c r="A6352">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6353" spans="1:1">
@@ -32244,32 +32244,32 @@
     </row>
     <row r="6374" spans="1:1">
       <c r="A6374">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6375" spans="1:1">
       <c r="A6375">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6376" spans="1:1">
       <c r="A6376">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6377" spans="1:1">
       <c r="A6377">
-        <v>1.407745272749639</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6378" spans="1:1">
       <c r="A6378">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6379" spans="1:1">
       <c r="A6379">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6380" spans="1:1">
@@ -32289,17 +32289,17 @@
     </row>
     <row r="6383" spans="1:1">
       <c r="A6383">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6384" spans="1:1">
       <c r="A6384">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6385" spans="1:1">
       <c r="A6385">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6386" spans="1:1">
@@ -32424,47 +32424,47 @@
     </row>
     <row r="6410" spans="1:1">
       <c r="A6410">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="6411" spans="1:1">
       <c r="A6411">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6412" spans="1:1">
       <c r="A6412">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6413" spans="1:1">
       <c r="A6413">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6414" spans="1:1">
       <c r="A6414">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6415" spans="1:1">
       <c r="A6415">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6416" spans="1:1">
       <c r="A6416">
-        <v>2.422969469207092</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6417" spans="1:1">
       <c r="A6417">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6418" spans="1:1">
       <c r="A6418">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6419" spans="1:1">
@@ -32799,17 +32799,17 @@
     </row>
     <row r="6485" spans="1:1">
       <c r="A6485">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="6486" spans="1:1">
       <c r="A6486">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6487" spans="1:1">
       <c r="A6487">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6488" spans="1:1">
@@ -32829,17 +32829,17 @@
     </row>
     <row r="6491" spans="1:1">
       <c r="A6491">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6492" spans="1:1">
       <c r="A6492">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6493" spans="1:1">
       <c r="A6493">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6494" spans="1:1">
@@ -32874,17 +32874,17 @@
     </row>
     <row r="6500" spans="1:1">
       <c r="A6500">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6501" spans="1:1">
       <c r="A6501">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6502" spans="1:1">
       <c r="A6502">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6503" spans="1:1">
@@ -33009,17 +33009,17 @@
     </row>
     <row r="6527" spans="1:1">
       <c r="A6527">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6528" spans="1:1">
       <c r="A6528">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6529" spans="1:1">
       <c r="A6529">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6530" spans="1:1">
@@ -33504,32 +33504,32 @@
     </row>
     <row r="6626" spans="1:1">
       <c r="A6626">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6627" spans="1:1">
       <c r="A6627">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6628" spans="1:1">
       <c r="A6628">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6629" spans="1:1">
       <c r="A6629">
-        <v>1.407745272749783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6630" spans="1:1">
       <c r="A6630">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6631" spans="1:1">
       <c r="A6631">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6632" spans="1:1">
@@ -33549,17 +33549,17 @@
     </row>
     <row r="6635" spans="1:1">
       <c r="A6635">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6636" spans="1:1">
       <c r="A6636">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6637" spans="1:1">
       <c r="A6637">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6638" spans="1:1">
@@ -33684,17 +33684,17 @@
     </row>
     <row r="6662" spans="1:1">
       <c r="A6662">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6663" spans="1:1">
       <c r="A6663">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6664" spans="1:1">
       <c r="A6664">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6665" spans="1:1">
@@ -35034,32 +35034,32 @@
     </row>
     <row r="6932" spans="1:1">
       <c r="A6932">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6933" spans="1:1">
       <c r="A6933">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6934" spans="1:1">
       <c r="A6934">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6935" spans="1:1">
       <c r="A6935">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6936" spans="1:1">
       <c r="A6936">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6937" spans="1:1">
       <c r="A6937">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6938" spans="1:1">
@@ -35094,47 +35094,47 @@
     </row>
     <row r="6944" spans="1:1">
       <c r="A6944">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6945" spans="1:1">
       <c r="A6945">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6946" spans="1:1">
       <c r="A6946">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6947" spans="1:1">
       <c r="A6947">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6948" spans="1:1">
       <c r="A6948">
-        <v>1.11477891823184</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6949" spans="1:1">
       <c r="A6949">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6950" spans="1:1">
       <c r="A6950">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6951" spans="1:1">
       <c r="A6951">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6952" spans="1:1">
       <c r="A6952">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6953" spans="1:1">
@@ -35199,32 +35199,32 @@
     </row>
     <row r="6965" spans="1:1">
       <c r="A6965">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6966" spans="1:1">
       <c r="A6966">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6967" spans="1:1">
       <c r="A6967">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6968" spans="1:1">
       <c r="A6968">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6969" spans="1:1">
       <c r="A6969">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6970" spans="1:1">
       <c r="A6970">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6971" spans="1:1">
@@ -35364,17 +35364,17 @@
     </row>
     <row r="6998" spans="1:1">
       <c r="A6998">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="6999" spans="1:1">
       <c r="A6999">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7000" spans="1:1">
       <c r="A7000">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7001" spans="1:1">
@@ -35409,17 +35409,17 @@
     </row>
     <row r="7007" spans="1:1">
       <c r="A7007">
-        <v>1.407745272749772</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7008" spans="1:1">
       <c r="A7008">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7009" spans="1:1">
       <c r="A7009">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7010" spans="1:1">
@@ -35469,17 +35469,17 @@
     </row>
     <row r="7019" spans="1:1">
       <c r="A7019">
-        <v>2.416593574757908</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7020" spans="1:1">
       <c r="A7020">
-        <v>1.11477891823184</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7021" spans="1:1">
       <c r="A7021">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7022" spans="1:1">
@@ -35574,32 +35574,32 @@
     </row>
     <row r="7040" spans="1:1">
       <c r="A7040">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7041" spans="1:1">
       <c r="A7041">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7042" spans="1:1">
       <c r="A7042">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7043" spans="1:1">
       <c r="A7043">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7044" spans="1:1">
       <c r="A7044">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7045" spans="1:1">
       <c r="A7045">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7046" spans="1:1">
@@ -35619,17 +35619,17 @@
     </row>
     <row r="7049" spans="1:1">
       <c r="A7049">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7050" spans="1:1">
       <c r="A7050">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7051" spans="1:1">
       <c r="A7051">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7052" spans="1:1">
@@ -35694,32 +35694,32 @@
     </row>
     <row r="7064" spans="1:1">
       <c r="A7064">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7065" spans="1:1">
       <c r="A7065">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7066" spans="1:1">
       <c r="A7066">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7067" spans="1:1">
       <c r="A7067">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7068" spans="1:1">
       <c r="A7068">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7069" spans="1:1">
       <c r="A7069">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7070" spans="1:1">
@@ -35739,32 +35739,32 @@
     </row>
     <row r="7073" spans="1:1">
       <c r="A7073">
-        <v>2.416593574757919</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7074" spans="1:1">
       <c r="A7074">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7075" spans="1:1">
       <c r="A7075">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7076" spans="1:1">
       <c r="A7076">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7077" spans="1:1">
       <c r="A7077">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7078" spans="1:1">
       <c r="A7078">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7079" spans="1:1">
@@ -35784,17 +35784,17 @@
     </row>
     <row r="7082" spans="1:1">
       <c r="A7082">
-        <v>-1</v>
+        <v>2.41659357475783</v>
       </c>
     </row>
     <row r="7083" spans="1:1">
       <c r="A7083">
-        <v>-1</v>
+        <v>0.7518067699785358</v>
       </c>
     </row>
     <row r="7084" spans="1:1">
       <c r="A7084">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7085" spans="1:1">
@@ -36039,17 +36039,17 @@
     </row>
     <row r="7133" spans="1:1">
       <c r="A7133">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7134" spans="1:1">
       <c r="A7134">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7135" spans="1:1">
       <c r="A7135">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7136" spans="1:1">
@@ -36234,17 +36234,17 @@
     </row>
     <row r="7172" spans="1:1">
       <c r="A7172">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7173" spans="1:1">
       <c r="A7173">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7174" spans="1:1">
       <c r="A7174">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7175" spans="1:1">
@@ -36399,17 +36399,17 @@
     </row>
     <row r="7205" spans="1:1">
       <c r="A7205">
-        <v>1.407745272749661</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7206" spans="1:1">
       <c r="A7206">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7207" spans="1:1">
       <c r="A7207">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7208" spans="1:1">
@@ -36429,62 +36429,62 @@
     </row>
     <row r="7211" spans="1:1">
       <c r="A7211">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7212" spans="1:1">
       <c r="A7212">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7213" spans="1:1">
       <c r="A7213">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7214" spans="1:1">
       <c r="A7214">
-        <v>-1</v>
+        <v>1.407745272749683</v>
       </c>
     </row>
     <row r="7215" spans="1:1">
       <c r="A7215">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7216" spans="1:1">
       <c r="A7216">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7217" spans="1:1">
       <c r="A7217">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="7218" spans="1:1">
       <c r="A7218">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7219" spans="1:1">
       <c r="A7219">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7220" spans="1:1">
       <c r="A7220">
-        <v>1.127766143616094</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7221" spans="1:1">
       <c r="A7221">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7222" spans="1:1">
       <c r="A7222">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7223" spans="1:1">
@@ -36504,17 +36504,17 @@
     </row>
     <row r="7226" spans="1:1">
       <c r="A7226">
-        <v>-1</v>
+        <v>2.416593574757808</v>
       </c>
     </row>
     <row r="7227" spans="1:1">
       <c r="A7227">
-        <v>-1</v>
+        <v>0.7508071031930963</v>
       </c>
     </row>
     <row r="7228" spans="1:1">
       <c r="A7228">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7229" spans="1:1">
@@ -36594,17 +36594,17 @@
     </row>
     <row r="7244" spans="1:1">
       <c r="A7244">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7245" spans="1:1">
       <c r="A7245">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7246" spans="1:1">
       <c r="A7246">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7247" spans="1:1">
@@ -36744,32 +36744,32 @@
     </row>
     <row r="7274" spans="1:1">
       <c r="A7274">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="7275" spans="1:1">
       <c r="A7275">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7276" spans="1:1">
       <c r="A7276">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7277" spans="1:1">
       <c r="A7277">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="7278" spans="1:1">
       <c r="A7278">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7279" spans="1:1">
       <c r="A7279">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7280" spans="1:1">
@@ -36849,17 +36849,17 @@
     </row>
     <row r="7295" spans="1:1">
       <c r="A7295">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7296" spans="1:1">
       <c r="A7296">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7297" spans="1:1">
       <c r="A7297">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7298" spans="1:1">
@@ -36909,17 +36909,17 @@
     </row>
     <row r="7307" spans="1:1">
       <c r="A7307">
-        <v>2.416593574757842</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7308" spans="1:1">
       <c r="A7308">
-        <v>1.114778918231829</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7309" spans="1:1">
       <c r="A7309">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7310" spans="1:1">
@@ -37104,32 +37104,32 @@
     </row>
     <row r="7346" spans="1:1">
       <c r="A7346">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7347" spans="1:1">
       <c r="A7347">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7348" spans="1:1">
       <c r="A7348">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7349" spans="1:1">
       <c r="A7349">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7350" spans="1:1">
       <c r="A7350">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7351" spans="1:1">
       <c r="A7351">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7352" spans="1:1">
@@ -37194,17 +37194,17 @@
     </row>
     <row r="7364" spans="1:1">
       <c r="A7364">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7365" spans="1:1">
       <c r="A7365">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7366" spans="1:1">
       <c r="A7366">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7367" spans="1:1">
@@ -37494,17 +37494,17 @@
     </row>
     <row r="7424" spans="1:1">
       <c r="A7424">
-        <v>2.416593574757897</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7425" spans="1:1">
       <c r="A7425">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7426" spans="1:1">
       <c r="A7426">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7427" spans="1:1">
@@ -37659,17 +37659,17 @@
     </row>
     <row r="7457" spans="1:1">
       <c r="A7457">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7458" spans="1:1">
       <c r="A7458">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7459" spans="1:1">
       <c r="A7459">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7460" spans="1:1">
@@ -37824,17 +37824,17 @@
     </row>
     <row r="7490" spans="1:1">
       <c r="A7490">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="7491" spans="1:1">
       <c r="A7491">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7492" spans="1:1">
       <c r="A7492">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7493" spans="1:1">
@@ -37854,17 +37854,17 @@
     </row>
     <row r="7496" spans="1:1">
       <c r="A7496">
-        <v>2.430304088515589</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7497" spans="1:1">
       <c r="A7497">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7498" spans="1:1">
       <c r="A7498">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7499" spans="1:1">
@@ -37884,32 +37884,32 @@
     </row>
     <row r="7502" spans="1:1">
       <c r="A7502">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="7503" spans="1:1">
       <c r="A7503">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7504" spans="1:1">
       <c r="A7504">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7505" spans="1:1">
       <c r="A7505">
-        <v>-1</v>
+        <v>2.43037434826523</v>
       </c>
     </row>
     <row r="7506" spans="1:1">
       <c r="A7506">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7507" spans="1:1">
       <c r="A7507">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7508" spans="1:1">
@@ -37944,17 +37944,17 @@
     </row>
     <row r="7514" spans="1:1">
       <c r="A7514">
-        <v>-1</v>
+        <v>2.430164030191129</v>
       </c>
     </row>
     <row r="7515" spans="1:1">
       <c r="A7515">
-        <v>-1</v>
+        <v>0.7507150865456946</v>
       </c>
     </row>
     <row r="7516" spans="1:1">
       <c r="A7516">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7517" spans="1:1">
@@ -37989,17 +37989,17 @@
     </row>
     <row r="7523" spans="1:1">
       <c r="A7523">
-        <v>2.430234019846977</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7524" spans="1:1">
       <c r="A7524">
-        <v>1.114778918231829</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7525" spans="1:1">
       <c r="A7525">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7526" spans="1:1">
@@ -38184,62 +38184,62 @@
     </row>
     <row r="7562" spans="1:1">
       <c r="A7562">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7563" spans="1:1">
       <c r="A7563">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7564" spans="1:1">
       <c r="A7564">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7565" spans="1:1">
       <c r="A7565">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="7566" spans="1:1">
       <c r="A7566">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7567" spans="1:1">
       <c r="A7567">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7568" spans="1:1">
       <c r="A7568">
-        <v>2.430355853184651</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7569" spans="1:1">
       <c r="A7569">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7570" spans="1:1">
       <c r="A7570">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7571" spans="1:1">
       <c r="A7571">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7572" spans="1:1">
       <c r="A7572">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7573" spans="1:1">
       <c r="A7573">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7574" spans="1:1">
@@ -38544,32 +38544,32 @@
     </row>
     <row r="7634" spans="1:1">
       <c r="A7634">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="7635" spans="1:1">
       <c r="A7635">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7636" spans="1:1">
       <c r="A7636">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7637" spans="1:1">
       <c r="A7637">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7638" spans="1:1">
       <c r="A7638">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7639" spans="1:1">
       <c r="A7639">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7640" spans="1:1">
@@ -38589,17 +38589,17 @@
     </row>
     <row r="7643" spans="1:1">
       <c r="A7643">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="7644" spans="1:1">
       <c r="A7644">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7645" spans="1:1">
       <c r="A7645">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7646" spans="1:1">
@@ -39264,17 +39264,17 @@
     </row>
     <row r="7778" spans="1:1">
       <c r="A7778">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7779" spans="1:1">
       <c r="A7779">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7780" spans="1:1">
       <c r="A7780">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7781" spans="1:1">
@@ -39324,17 +39324,17 @@
     </row>
     <row r="7790" spans="1:1">
       <c r="A7790">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7791" spans="1:1">
       <c r="A7791">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7792" spans="1:1">
       <c r="A7792">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7793" spans="1:1">
@@ -39384,17 +39384,17 @@
     </row>
     <row r="7802" spans="1:1">
       <c r="A7802">
-        <v>-1</v>
+        <v>2.430408040736665</v>
       </c>
     </row>
     <row r="7803" spans="1:1">
       <c r="A7803">
-        <v>-1</v>
+        <v>0.7507622714039708</v>
       </c>
     </row>
     <row r="7804" spans="1:1">
       <c r="A7804">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7805" spans="1:1">
@@ -39444,17 +39444,17 @@
     </row>
     <row r="7814" spans="1:1">
       <c r="A7814">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7815" spans="1:1">
       <c r="A7815">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7816" spans="1:1">
       <c r="A7816">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7817" spans="1:1">
@@ -39474,17 +39474,17 @@
     </row>
     <row r="7820" spans="1:1">
       <c r="A7820">
-        <v>2.430475087778139</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7821" spans="1:1">
       <c r="A7821">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7822" spans="1:1">
       <c r="A7822">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7823" spans="1:1">
@@ -39654,32 +39654,32 @@
     </row>
     <row r="7856" spans="1:1">
       <c r="A7856">
-        <v>2.430615960172522</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7857" spans="1:1">
       <c r="A7857">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7858" spans="1:1">
       <c r="A7858">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7859" spans="1:1">
       <c r="A7859">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7860" spans="1:1">
       <c r="A7860">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7861" spans="1:1">
       <c r="A7861">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7862" spans="1:1">
@@ -39849,17 +39849,17 @@
     </row>
     <row r="7895" spans="1:1">
       <c r="A7895">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7896" spans="1:1">
       <c r="A7896">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7897" spans="1:1">
       <c r="A7897">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7898" spans="1:1">
@@ -39984,17 +39984,17 @@
     </row>
     <row r="7922" spans="1:1">
       <c r="A7922">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7923" spans="1:1">
       <c r="A7923">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7924" spans="1:1">
       <c r="A7924">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7925" spans="1:1">
@@ -40749,17 +40749,17 @@
     </row>
     <row r="8075" spans="1:1">
       <c r="A8075">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="8076" spans="1:1">
       <c r="A8076">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8077" spans="1:1">
       <c r="A8077">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8078" spans="1:1">
@@ -40839,32 +40839,32 @@
     </row>
     <row r="8093" spans="1:1">
       <c r="A8093">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="8094" spans="1:1">
       <c r="A8094">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8095" spans="1:1">
       <c r="A8095">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8096" spans="1:1">
       <c r="A8096">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8097" spans="1:1">
       <c r="A8097">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8098" spans="1:1">
       <c r="A8098">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8099" spans="1:1">
@@ -40884,32 +40884,32 @@
     </row>
     <row r="8102" spans="1:1">
       <c r="A8102">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8103" spans="1:1">
       <c r="A8103">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8104" spans="1:1">
       <c r="A8104">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8105" spans="1:1">
       <c r="A8105">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="8106" spans="1:1">
       <c r="A8106">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8107" spans="1:1">
       <c r="A8107">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8108" spans="1:1">
@@ -40929,17 +40929,17 @@
     </row>
     <row r="8111" spans="1:1">
       <c r="A8111">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8112" spans="1:1">
       <c r="A8112">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8113" spans="1:1">
       <c r="A8113">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8114" spans="1:1">
@@ -41124,17 +41124,17 @@
     </row>
     <row r="8150" spans="1:1">
       <c r="A8150">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8151" spans="1:1">
       <c r="A8151">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8152" spans="1:1">
       <c r="A8152">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8153" spans="1:1">
@@ -41244,32 +41244,32 @@
     </row>
     <row r="8174" spans="1:1">
       <c r="A8174">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8175" spans="1:1">
       <c r="A8175">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8176" spans="1:1">
       <c r="A8176">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8177" spans="1:1">
       <c r="A8177">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8178" spans="1:1">
       <c r="A8178">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8179" spans="1:1">
       <c r="A8179">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8180" spans="1:1">
@@ -41424,47 +41424,47 @@
     </row>
     <row r="8210" spans="1:1">
       <c r="A8210">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="8211" spans="1:1">
       <c r="A8211">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8212" spans="1:1">
       <c r="A8212">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8213" spans="1:1">
       <c r="A8213">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8214" spans="1:1">
       <c r="A8214">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8215" spans="1:1">
       <c r="A8215">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8216" spans="1:1">
       <c r="A8216">
-        <v>-1</v>
+        <v>2.416593574757875</v>
       </c>
     </row>
     <row r="8217" spans="1:1">
       <c r="A8217">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8218" spans="1:1">
       <c r="A8218">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8219" spans="1:1">
@@ -41499,17 +41499,17 @@
     </row>
     <row r="8225" spans="1:1">
       <c r="A8225">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8226" spans="1:1">
       <c r="A8226">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8227" spans="1:1">
       <c r="A8227">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8228" spans="1:1">
@@ -41559,17 +41559,17 @@
     </row>
     <row r="8237" spans="1:1">
       <c r="A8237">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="8238" spans="1:1">
       <c r="A8238">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8239" spans="1:1">
       <c r="A8239">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8240" spans="1:1">
@@ -41799,32 +41799,32 @@
     </row>
     <row r="8285" spans="1:1">
       <c r="A8285">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8286" spans="1:1">
       <c r="A8286">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8287" spans="1:1">
       <c r="A8287">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8288" spans="1:1">
       <c r="A8288">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="8289" spans="1:1">
       <c r="A8289">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8290" spans="1:1">
       <c r="A8290">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8291" spans="1:1">
@@ -42234,32 +42234,32 @@
     </row>
     <row r="8372" spans="1:1">
       <c r="A8372">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8373" spans="1:1">
       <c r="A8373">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8374" spans="1:1">
       <c r="A8374">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8375" spans="1:1">
       <c r="A8375">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8376" spans="1:1">
       <c r="A8376">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8377" spans="1:1">
       <c r="A8377">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8378" spans="1:1">
@@ -42384,17 +42384,17 @@
     </row>
     <row r="8402" spans="1:1">
       <c r="A8402">
-        <v>1.407745272749772</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8403" spans="1:1">
       <c r="A8403">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8404" spans="1:1">
       <c r="A8404">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8405" spans="1:1">
@@ -42504,17 +42504,17 @@
     </row>
     <row r="8426" spans="1:1">
       <c r="A8426">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="8427" spans="1:1">
       <c r="A8427">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8428" spans="1:1">
       <c r="A8428">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8429" spans="1:1">
@@ -42534,17 +42534,17 @@
     </row>
     <row r="8432" spans="1:1">
       <c r="A8432">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8433" spans="1:1">
       <c r="A8433">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8434" spans="1:1">
       <c r="A8434">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8435" spans="1:1">
@@ -42879,17 +42879,17 @@
     </row>
     <row r="8501" spans="1:1">
       <c r="A8501">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8502" spans="1:1">
       <c r="A8502">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8503" spans="1:1">
       <c r="A8503">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8504" spans="1:1">
@@ -43599,17 +43599,17 @@
     </row>
     <row r="8645" spans="1:1">
       <c r="A8645">
-        <v>-1</v>
+        <v>1.407745272749694</v>
       </c>
     </row>
     <row r="8646" spans="1:1">
       <c r="A8646">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8647" spans="1:1">
       <c r="A8647">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8648" spans="1:1">
@@ -43644,17 +43644,17 @@
     </row>
     <row r="8654" spans="1:1">
       <c r="A8654">
-        <v>-1</v>
+        <v>1.407745272749694</v>
       </c>
     </row>
     <row r="8655" spans="1:1">
       <c r="A8655">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8656" spans="1:1">
       <c r="A8656">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8657" spans="1:1">
@@ -44304,17 +44304,17 @@
     </row>
     <row r="8786" spans="1:1">
       <c r="A8786">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="8787" spans="1:1">
       <c r="A8787">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8788" spans="1:1">
       <c r="A8788">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8789" spans="1:1">
@@ -44349,17 +44349,17 @@
     </row>
     <row r="8795" spans="1:1">
       <c r="A8795">
-        <v>-1</v>
+        <v>1.127766143616005</v>
       </c>
     </row>
     <row r="8796" spans="1:1">
       <c r="A8796">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8797" spans="1:1">
       <c r="A8797">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8798" spans="1:1">

--- a/src/output/hash_table.xlsx
+++ b/src/output/hash_table.xlsx
@@ -1089,17 +1089,17 @@
     </row>
     <row r="143" spans="1:1">
       <c r="A143">
-        <v>4.233442504238205</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144">
-        <v>26.05845476919577</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145">
-        <v>4.233442504238161</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="146" spans="1:1">
@@ -1614,17 +1614,17 @@
     </row>
     <row r="248" spans="1:1">
       <c r="A248">
-        <v>4.349633931007002</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249">
-        <v>10.65512917904154</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250">
-        <v>4.349633931007024</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="251" spans="1:1">
@@ -1689,17 +1689,17 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263">
-        <v>4.388291517533105</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264">
-        <v>4.388291517533127</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265">
-        <v>4.388291517533238</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="266" spans="1:1">
@@ -1719,17 +1719,17 @@
     </row>
     <row r="269" spans="1:1">
       <c r="A269">
-        <v>6.338943322872459</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270">
-        <v>4.233442504238205</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271">
-        <v>4.233442504238205</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="272" spans="1:1">
@@ -1764,17 +1764,17 @@
     </row>
     <row r="278" spans="1:1">
       <c r="A278">
-        <v>4.952326044589961</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279">
-        <v>18.83187548348985</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280">
-        <v>4.000000000000026</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="281" spans="1:1">
@@ -1794,32 +1794,32 @@
     </row>
     <row r="284" spans="1:1">
       <c r="A284">
-        <v>-1</v>
+        <v>4.349633931007069</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285">
-        <v>-1</v>
+        <v>13.35221755990226</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286">
-        <v>-1</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287">
-        <v>6.404746485939516</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288">
-        <v>29.42424823651596</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289">
-        <v>4.233442504238272</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="290" spans="1:1">
